--- a/horas.xlsx
+++ b/horas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UPC\Curso QP2526\EA\TeamManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F5C8A5-9352-4702-9F80-5664F45A7C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED9087-4351-44B4-A672-5839C872CF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>BACKEND</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Connexions WebApp</t>
+  </si>
+  <si>
+    <t>Agregar libro por isbn</t>
   </si>
 </sst>
 </file>
@@ -1710,6 +1713,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="52" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1740,15 +1746,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1758,9 +1755,15 @@
     <xf numFmtId="0" fontId="54" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="50">
@@ -2156,7 +2159,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2472,7 +2475,7 @@
                   <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.5</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9</c:v>
@@ -2571,7 +2574,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2981,7 +2984,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3390,7 +3393,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3800,7 +3803,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4215,7 +4218,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4526,7 +4529,7 @@
                   <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3</c:v>
@@ -8700,7 +8703,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -9017,19 +9020,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469259-10C4-451F-B658-7DCDC5640A2A}">
   <dimension ref="A2:P22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="26" customWidth="1"/>
-    <col min="4" max="8" width="10.90625" style="26"/>
-    <col min="9" max="9" width="2.6328125" style="31" customWidth="1"/>
-    <col min="10" max="15" width="10.90625" style="26"/>
-    <col min="16" max="16" width="7.81640625" style="26" customWidth="1"/>
-    <col min="17" max="16384" width="10.90625" style="26"/>
+    <col min="1" max="1" width="2.5703125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="26" customWidth="1"/>
+    <col min="4" max="8" width="10.85546875" style="26"/>
+    <col min="9" max="9" width="2.5703125" style="31" customWidth="1"/>
+    <col min="10" max="15" width="10.85546875" style="26"/>
+    <col min="16" max="16" width="7.85546875" style="26" customWidth="1"/>
+    <col min="17" max="16384" width="10.85546875" style="26"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="117" t="s">
         <v>35</v>
       </c>
@@ -9048,7 +9051,7 @@
       <c r="O2" s="118"/>
       <c r="P2" s="119"/>
     </row>
-    <row r="4" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
         <v>21</v>
       </c>
@@ -9073,7 +9076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="35"/>
       <c r="C5" s="27"/>
       <c r="D5" s="36"/>
@@ -9084,7 +9087,7 @@
       <c r="I5" s="37"/>
       <c r="J5" s="36"/>
     </row>
-    <row r="6" spans="1:16" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29"/>
       <c r="B6" s="38" t="s">
         <v>15</v>
@@ -9117,7 +9120,7 @@
       </c>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" spans="1:16" s="31" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" s="31" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -9128,7 +9131,7 @@
       <c r="I7" s="44"/>
       <c r="J7" s="45"/>
     </row>
-    <row r="8" spans="1:16" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29"/>
       <c r="B8" s="46" t="s">
         <v>16</v>
@@ -9161,7 +9164,7 @@
       </c>
       <c r="K8" s="30"/>
     </row>
-    <row r="9" spans="1:16" s="31" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" s="31" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="49"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -9172,7 +9175,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="45"/>
     </row>
-    <row r="10" spans="1:16" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29"/>
       <c r="B10" s="50" t="s">
         <v>17</v>
@@ -9196,16 +9199,16 @@
       </c>
       <c r="H10" s="84">
         <f>SUM(WENJIE!L5:L138)</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I10" s="51"/>
       <c r="J10" s="52">
         <f>SUM(D10:H10)</f>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" spans="1:16" s="31" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" s="31" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="53"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -9216,7 +9219,7 @@
       <c r="I11" s="44"/>
       <c r="J11" s="45"/>
     </row>
-    <row r="12" spans="1:16" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="29"/>
       <c r="B12" s="54" t="s">
         <v>18</v>
@@ -9249,7 +9252,7 @@
       </c>
       <c r="K12" s="30"/>
     </row>
-    <row r="13" spans="1:16" s="31" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" s="31" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="57"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -9260,7 +9263,7 @@
       <c r="I13" s="44"/>
       <c r="J13" s="45"/>
     </row>
-    <row r="14" spans="1:16" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="29"/>
       <c r="B14" s="58" t="s">
         <v>36</v>
@@ -9293,7 +9296,7 @@
       </c>
       <c r="K14" s="30"/>
     </row>
-    <row r="15" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="61"/>
       <c r="C15" s="62"/>
       <c r="D15" s="61"/>
@@ -9304,7 +9307,7 @@
       <c r="I15" s="63"/>
       <c r="J15" s="64"/>
     </row>
-    <row r="16" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="65" t="s">
         <v>19</v>
       </c>
@@ -9327,15 +9330,15 @@
       </c>
       <c r="H16" s="28">
         <f>SUM(H6:H14)</f>
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="I16" s="33"/>
       <c r="J16" s="28">
         <f>SUM(D16:H16)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
@@ -9356,80 +9359,80 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2CD9D50-0C20-46D0-8F5B-32DDB5716BB2}">
   <dimension ref="A1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="11" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.1796875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="F2" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="130"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="131"/>
-      <c r="L2" s="132" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="O2" s="133" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="R2" s="134" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="134"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
@@ -9457,7 +9460,7 @@
       </c>
       <c r="S5" s="74"/>
     </row>
-    <row r="6" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
@@ -9483,7 +9486,7 @@
       </c>
       <c r="S6" s="74"/>
     </row>
-    <row r="7" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
@@ -9509,7 +9512,7 @@
       </c>
       <c r="S7" s="74"/>
     </row>
-    <row r="8" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
@@ -9535,7 +9538,7 @@
       </c>
       <c r="S8" s="74"/>
     </row>
-    <row r="9" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
@@ -9563,7 +9566,7 @@
       </c>
       <c r="S9" s="74"/>
     </row>
-    <row r="10" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
@@ -9589,7 +9592,7 @@
       </c>
       <c r="S10" s="74"/>
     </row>
-    <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
@@ -9615,7 +9618,7 @@
       </c>
       <c r="S11" s="74"/>
     </row>
-    <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
@@ -9643,7 +9646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
@@ -9669,7 +9672,7 @@
       </c>
       <c r="S13" s="74"/>
     </row>
-    <row r="14" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
@@ -9695,7 +9698,7 @@
       </c>
       <c r="S14" s="74"/>
     </row>
-    <row r="15" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
@@ -9721,7 +9724,7 @@
       </c>
       <c r="S15" s="74"/>
     </row>
-    <row r="16" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
@@ -9749,7 +9752,7 @@
       </c>
       <c r="S16" s="74"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
@@ -9775,7 +9778,7 @@
       </c>
       <c r="S17" s="74"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
@@ -9801,7 +9804,7 @@
       </c>
       <c r="S18" s="74"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
@@ -9827,7 +9830,7 @@
       </c>
       <c r="S19" s="74"/>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
@@ -9853,7 +9856,7 @@
       </c>
       <c r="S20" s="74"/>
     </row>
-    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="8"/>
@@ -9866,7 +9869,7 @@
       <c r="R21" s="20"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
@@ -9894,7 +9897,7 @@
       </c>
       <c r="S22" s="74"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
@@ -9920,7 +9923,7 @@
       </c>
       <c r="S23" s="74"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
@@ -9946,7 +9949,7 @@
       </c>
       <c r="S24" s="74"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
@@ -9972,7 +9975,7 @@
       </c>
       <c r="S25" s="74"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
@@ -9998,7 +10001,7 @@
       </c>
       <c r="S26" s="74"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
@@ -10026,7 +10029,7 @@
       </c>
       <c r="S27" s="74"/>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
@@ -10052,7 +10055,7 @@
       </c>
       <c r="S28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
@@ -10078,7 +10081,7 @@
       </c>
       <c r="S29" s="74"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
@@ -10104,7 +10107,7 @@
       </c>
       <c r="S30" s="74"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
@@ -10132,7 +10135,7 @@
       </c>
       <c r="S31" s="74"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
@@ -10158,7 +10161,7 @@
       </c>
       <c r="S32" s="74"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
@@ -10184,7 +10187,7 @@
       </c>
       <c r="S33" s="74"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
@@ -10212,7 +10215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
@@ -10238,7 +10241,7 @@
       </c>
       <c r="S35" s="74"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
@@ -10264,7 +10267,7 @@
       </c>
       <c r="S36" s="74"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
@@ -10290,7 +10293,7 @@
       </c>
       <c r="S37" s="74"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
@@ -10318,7 +10321,7 @@
       </c>
       <c r="S38" s="74"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
@@ -10346,7 +10349,7 @@
       </c>
       <c r="S39" s="74"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
@@ -10372,7 +10375,7 @@
       </c>
       <c r="S40" s="74"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
@@ -10400,7 +10403,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
@@ -10426,7 +10429,7 @@
       </c>
       <c r="S42" s="74"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
@@ -10452,7 +10455,7 @@
       </c>
       <c r="S43" s="74"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
@@ -10478,7 +10481,7 @@
       </c>
       <c r="S44" s="74"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
@@ -10508,7 +10511,7 @@
       </c>
       <c r="S45" s="74"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
@@ -10534,7 +10537,7 @@
       </c>
       <c r="S46" s="74"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
@@ -10560,7 +10563,7 @@
       </c>
       <c r="S47" s="74"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
@@ -10586,7 +10589,7 @@
       </c>
       <c r="S48" s="74"/>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
@@ -10612,7 +10615,7 @@
       </c>
       <c r="S49" s="74"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
@@ -10638,7 +10641,7 @@
       </c>
       <c r="S50" s="74"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
@@ -10664,7 +10667,7 @@
       </c>
       <c r="S51" s="74"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
@@ -10690,7 +10693,7 @@
       </c>
       <c r="S52" s="74"/>
     </row>
-    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="F53" s="13"/>
       <c r="G53" s="8"/>
@@ -10703,7 +10706,7 @@
       <c r="R53" s="20"/>
       <c r="S53" s="23"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
@@ -10731,7 +10734,7 @@
       </c>
       <c r="S54" s="75"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
@@ -10757,7 +10760,7 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
@@ -10783,7 +10786,7 @@
       </c>
       <c r="S56" s="75"/>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
@@ -10809,7 +10812,7 @@
       </c>
       <c r="S57" s="75"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
@@ -10835,7 +10838,7 @@
       </c>
       <c r="S58" s="75"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
@@ -10861,7 +10864,7 @@
       </c>
       <c r="S59" s="75"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
@@ -10887,7 +10890,7 @@
       </c>
       <c r="S60" s="75"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
@@ -10913,7 +10916,7 @@
       </c>
       <c r="S61" s="75"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
@@ -10939,7 +10942,7 @@
       </c>
       <c r="S62" s="75"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
@@ -10965,7 +10968,7 @@
       </c>
       <c r="S63" s="75"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
@@ -10991,7 +10994,7 @@
       </c>
       <c r="S64" s="75"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
@@ -11017,7 +11020,7 @@
       </c>
       <c r="S65" s="75"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
@@ -11043,7 +11046,7 @@
       </c>
       <c r="S66" s="75"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
@@ -11069,7 +11072,7 @@
       </c>
       <c r="S67" s="75"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
@@ -11095,7 +11098,7 @@
       </c>
       <c r="S68" s="75"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
@@ -11125,7 +11128,7 @@
       </c>
       <c r="S69" s="75"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
@@ -11151,7 +11154,7 @@
       </c>
       <c r="S70" s="75"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
@@ -11177,7 +11180,7 @@
       </c>
       <c r="S71" s="75"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
@@ -11203,7 +11206,7 @@
       </c>
       <c r="S72" s="75"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
@@ -11229,7 +11232,7 @@
       </c>
       <c r="S73" s="75"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
@@ -11255,7 +11258,7 @@
       </c>
       <c r="S74" s="75"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
@@ -11281,7 +11284,7 @@
       </c>
       <c r="S75" s="75"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
@@ -11307,7 +11310,7 @@
       </c>
       <c r="S76" s="75"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
@@ -11333,7 +11336,7 @@
       </c>
       <c r="S77" s="75"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
@@ -11359,7 +11362,7 @@
       </c>
       <c r="S78" s="75"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
@@ -11385,7 +11388,7 @@
       </c>
       <c r="S79" s="75"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
@@ -11411,7 +11414,7 @@
       </c>
       <c r="S80" s="75"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
@@ -11437,7 +11440,7 @@
       </c>
       <c r="S81" s="75"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
@@ -11463,7 +11466,7 @@
       </c>
       <c r="S82" s="75"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
@@ -11489,7 +11492,7 @@
       </c>
       <c r="S83" s="75"/>
     </row>
-    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="21"/>
       <c r="D84" s="13"/>
       <c r="F84" s="13"/>
@@ -11503,7 +11506,7 @@
       <c r="R84" s="20"/>
       <c r="S84" s="23"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
@@ -11531,7 +11534,7 @@
       </c>
       <c r="S85" s="75"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
@@ -11557,7 +11560,7 @@
       </c>
       <c r="S86" s="75"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
@@ -11583,7 +11586,7 @@
       </c>
       <c r="S87" s="75"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
@@ -11609,7 +11612,7 @@
       </c>
       <c r="S88" s="75"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
@@ -11635,7 +11638,7 @@
       </c>
       <c r="S89" s="75"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
@@ -11661,7 +11664,7 @@
       </c>
       <c r="S90" s="75"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
@@ -11687,7 +11690,7 @@
       </c>
       <c r="S91" s="75"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
@@ -11713,7 +11716,7 @@
       </c>
       <c r="S92" s="75"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
@@ -11739,7 +11742,7 @@
       </c>
       <c r="S93" s="75"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
@@ -11765,7 +11768,7 @@
       </c>
       <c r="S94" s="75"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
@@ -11791,7 +11794,7 @@
       </c>
       <c r="S95" s="75"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
@@ -11817,7 +11820,7 @@
       </c>
       <c r="S96" s="75"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
@@ -11843,7 +11846,7 @@
       </c>
       <c r="S97" s="75"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
@@ -11869,7 +11872,7 @@
       </c>
       <c r="S98" s="75"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
@@ -11895,7 +11898,7 @@
       </c>
       <c r="S99" s="75"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
@@ -11921,7 +11924,7 @@
       </c>
       <c r="S100" s="75"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
@@ -11947,7 +11950,7 @@
       </c>
       <c r="S101" s="75"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
@@ -11973,7 +11976,7 @@
       </c>
       <c r="S102" s="75"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
@@ -11999,7 +12002,7 @@
       </c>
       <c r="S103" s="75"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
@@ -12025,7 +12028,7 @@
       </c>
       <c r="S104" s="75"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
@@ -12051,7 +12054,7 @@
       </c>
       <c r="S105" s="75"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
@@ -12077,7 +12080,7 @@
       </c>
       <c r="S106" s="75"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
@@ -12103,7 +12106,7 @@
       </c>
       <c r="S107" s="75"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
@@ -12129,7 +12132,7 @@
       </c>
       <c r="S108" s="75"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
@@ -12155,7 +12158,7 @@
       </c>
       <c r="S109" s="75"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
@@ -12181,7 +12184,7 @@
       </c>
       <c r="S110" s="75"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
@@ -12207,7 +12210,7 @@
       </c>
       <c r="S111" s="75"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
@@ -12233,7 +12236,7 @@
       </c>
       <c r="S112" s="75"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
@@ -12259,7 +12262,7 @@
       </c>
       <c r="S113" s="75"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
@@ -12285,7 +12288,7 @@
       </c>
       <c r="S114" s="75"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
@@ -12311,7 +12314,7 @@
       </c>
       <c r="S115" s="75"/>
     </row>
-    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="21"/>
       <c r="D116" s="13"/>
       <c r="F116" s="13"/>
@@ -12325,7 +12328,7 @@
       <c r="R116" s="20"/>
       <c r="S116" s="23"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
@@ -12353,7 +12356,7 @@
       </c>
       <c r="S117" s="75"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
@@ -12379,7 +12382,7 @@
       </c>
       <c r="S118" s="75"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
@@ -12405,7 +12408,7 @@
       </c>
       <c r="S119" s="75"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
@@ -12431,7 +12434,7 @@
       </c>
       <c r="S120" s="75"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
@@ -12457,7 +12460,7 @@
       </c>
       <c r="S121" s="75"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
@@ -12483,7 +12486,7 @@
       </c>
       <c r="S122" s="75"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
@@ -12509,7 +12512,7 @@
       </c>
       <c r="S123" s="75"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
@@ -12535,7 +12538,7 @@
       </c>
       <c r="S124" s="75"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
@@ -12561,7 +12564,7 @@
       </c>
       <c r="S125" s="75"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
@@ -12587,7 +12590,7 @@
       </c>
       <c r="S126" s="75"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
@@ -12613,7 +12616,7 @@
       </c>
       <c r="S127" s="75"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
@@ -12639,7 +12642,7 @@
       </c>
       <c r="S128" s="75"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
@@ -12665,7 +12668,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
@@ -12691,7 +12694,7 @@
       </c>
       <c r="S130" s="75"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
@@ -12717,7 +12720,7 @@
       </c>
       <c r="S131" s="75"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
@@ -12743,7 +12746,7 @@
       </c>
       <c r="S132" s="75"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
@@ -12769,7 +12772,7 @@
       </c>
       <c r="S133" s="75"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
@@ -12795,7 +12798,7 @@
       </c>
       <c r="S134" s="75"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
@@ -12821,7 +12824,7 @@
       </c>
       <c r="S135" s="75"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
@@ -12847,7 +12850,7 @@
       </c>
       <c r="S136" s="75"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
@@ -12873,7 +12876,7 @@
       </c>
       <c r="S137" s="75"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
@@ -12971,80 +12974,80 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88D3A4C-A797-4BB6-9317-62E07FE783D5}">
   <dimension ref="A1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="11" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.1796875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="F2" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="130"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="131"/>
-      <c r="L2" s="132" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="O2" s="133" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="R2" s="134" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="134"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
@@ -13076,7 +13079,7 @@
       </c>
       <c r="S5" s="74"/>
     </row>
-    <row r="6" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
@@ -13106,7 +13109,7 @@
       </c>
       <c r="S6" s="74"/>
     </row>
-    <row r="7" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
@@ -13136,7 +13139,7 @@
       </c>
       <c r="S7" s="74"/>
     </row>
-    <row r="8" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
@@ -13166,7 +13169,7 @@
       </c>
       <c r="S8" s="74"/>
     </row>
-    <row r="9" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
@@ -13198,7 +13201,7 @@
       </c>
       <c r="S9" s="74"/>
     </row>
-    <row r="10" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
@@ -13228,7 +13231,7 @@
       </c>
       <c r="S10" s="74"/>
     </row>
-    <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
@@ -13258,7 +13261,7 @@
       </c>
       <c r="S11" s="74"/>
     </row>
-    <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
@@ -13290,7 +13293,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
@@ -13320,7 +13323,7 @@
       </c>
       <c r="S13" s="74"/>
     </row>
-    <row r="14" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
@@ -13350,7 +13353,7 @@
       </c>
       <c r="S14" s="74"/>
     </row>
-    <row r="15" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
@@ -13380,7 +13383,7 @@
       </c>
       <c r="S15" s="74"/>
     </row>
-    <row r="16" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
@@ -13412,7 +13415,7 @@
       </c>
       <c r="S16" s="74"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
@@ -13442,7 +13445,7 @@
       </c>
       <c r="S17" s="74"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
@@ -13472,7 +13475,7 @@
       </c>
       <c r="S18" s="74"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
@@ -13502,7 +13505,7 @@
       </c>
       <c r="S19" s="74"/>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
@@ -13532,7 +13535,7 @@
       </c>
       <c r="S20" s="74"/>
     </row>
-    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="106"/>
       <c r="G21" s="107"/>
@@ -13549,7 +13552,7 @@
       <c r="R21" s="115"/>
       <c r="S21" s="116"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
@@ -13581,7 +13584,7 @@
       </c>
       <c r="S22" s="74"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
@@ -13611,7 +13614,7 @@
       </c>
       <c r="S23" s="74"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
@@ -13641,7 +13644,7 @@
       </c>
       <c r="S24" s="74"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
@@ -13671,7 +13674,7 @@
       </c>
       <c r="S25" s="74"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
@@ -13701,7 +13704,7 @@
       </c>
       <c r="S26" s="74"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
@@ -13733,7 +13736,7 @@
       </c>
       <c r="S27" s="74"/>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
@@ -13763,7 +13766,7 @@
       </c>
       <c r="S28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
@@ -13793,7 +13796,7 @@
       </c>
       <c r="S29" s="74"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
@@ -13823,7 +13826,7 @@
       </c>
       <c r="S30" s="74"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
@@ -13855,7 +13858,7 @@
       </c>
       <c r="S31" s="74"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
@@ -13885,7 +13888,7 @@
       </c>
       <c r="S32" s="74"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
@@ -13915,7 +13918,7 @@
       </c>
       <c r="S33" s="74"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
@@ -13947,7 +13950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
@@ -13977,7 +13980,7 @@
       </c>
       <c r="S35" s="74"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
@@ -14007,7 +14010,7 @@
       </c>
       <c r="S36" s="74"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
@@ -14037,7 +14040,7 @@
       </c>
       <c r="S37" s="74"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
@@ -14069,7 +14072,7 @@
       </c>
       <c r="S38" s="74"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
@@ -14101,7 +14104,7 @@
       </c>
       <c r="S39" s="74"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
@@ -14131,7 +14134,7 @@
       </c>
       <c r="S40" s="74"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
@@ -14163,7 +14166,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
@@ -14193,7 +14196,7 @@
       </c>
       <c r="S42" s="74"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
@@ -14223,7 +14226,7 @@
       </c>
       <c r="S43" s="74"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
@@ -14253,7 +14256,7 @@
       </c>
       <c r="S44" s="74"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
@@ -14287,7 +14290,7 @@
       </c>
       <c r="S45" s="74"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
@@ -14317,7 +14320,7 @@
       </c>
       <c r="S46" s="74"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
@@ -14347,7 +14350,7 @@
       </c>
       <c r="S47" s="74"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
@@ -14377,7 +14380,7 @@
       </c>
       <c r="S48" s="74"/>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
@@ -14407,7 +14410,7 @@
       </c>
       <c r="S49" s="74"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
@@ -14437,7 +14440,7 @@
       </c>
       <c r="S50" s="74"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
@@ -14467,7 +14470,7 @@
       </c>
       <c r="S51" s="74"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
@@ -14497,7 +14500,7 @@
       </c>
       <c r="S52" s="74"/>
     </row>
-    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="F53" s="106"/>
       <c r="G53" s="107"/>
@@ -14514,7 +14517,7 @@
       <c r="R53" s="115"/>
       <c r="S53" s="116"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
@@ -14546,7 +14549,7 @@
       </c>
       <c r="S54" s="74"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
@@ -14576,7 +14579,7 @@
       </c>
       <c r="S55" s="74"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
@@ -14606,7 +14609,7 @@
       </c>
       <c r="S56" s="74"/>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
@@ -14636,7 +14639,7 @@
       </c>
       <c r="S57" s="74"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
@@ -14666,7 +14669,7 @@
       </c>
       <c r="S58" s="74"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
@@ -14696,7 +14699,7 @@
       </c>
       <c r="S59" s="74"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
@@ -14726,7 +14729,7 @@
       </c>
       <c r="S60" s="74"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
@@ -14756,7 +14759,7 @@
       </c>
       <c r="S61" s="74"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
@@ -14786,7 +14789,7 @@
       </c>
       <c r="S62" s="74"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
@@ -14816,7 +14819,7 @@
       </c>
       <c r="S63" s="74"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
@@ -14846,7 +14849,7 @@
       </c>
       <c r="S64" s="74"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
@@ -14876,7 +14879,7 @@
       </c>
       <c r="S65" s="74"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
@@ -14906,7 +14909,7 @@
       </c>
       <c r="S66" s="74"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
@@ -14936,7 +14939,7 @@
       </c>
       <c r="S67" s="74"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
@@ -14966,7 +14969,7 @@
       </c>
       <c r="S68" s="74"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
@@ -15000,7 +15003,7 @@
       </c>
       <c r="S69" s="74"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
@@ -15030,7 +15033,7 @@
       </c>
       <c r="S70" s="74"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
@@ -15060,7 +15063,7 @@
       </c>
       <c r="S71" s="74"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
@@ -15090,7 +15093,7 @@
       </c>
       <c r="S72" s="74"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
@@ -15120,7 +15123,7 @@
       </c>
       <c r="S73" s="74"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
@@ -15150,7 +15153,7 @@
       </c>
       <c r="S74" s="74"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
@@ -15180,7 +15183,7 @@
       </c>
       <c r="S75" s="74"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
@@ -15210,7 +15213,7 @@
       </c>
       <c r="S76" s="74"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
@@ -15240,7 +15243,7 @@
       </c>
       <c r="S77" s="74"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
@@ -15270,7 +15273,7 @@
       </c>
       <c r="S78" s="74"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
@@ -15300,7 +15303,7 @@
       </c>
       <c r="S79" s="74"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
@@ -15330,7 +15333,7 @@
       </c>
       <c r="S80" s="74"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
@@ -15360,7 +15363,7 @@
       </c>
       <c r="S81" s="74"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
@@ -15390,7 +15393,7 @@
       </c>
       <c r="S82" s="74"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
@@ -15420,7 +15423,7 @@
       </c>
       <c r="S83" s="74"/>
     </row>
-    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="21"/>
       <c r="D84" s="13"/>
       <c r="F84" s="106"/>
@@ -15438,7 +15441,7 @@
       <c r="R84" s="115"/>
       <c r="S84" s="116"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
@@ -15470,7 +15473,7 @@
       </c>
       <c r="S85" s="74"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
@@ -15500,7 +15503,7 @@
       </c>
       <c r="S86" s="74"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
@@ -15530,7 +15533,7 @@
       </c>
       <c r="S87" s="74"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
@@ -15560,7 +15563,7 @@
       </c>
       <c r="S88" s="74"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
@@ -15590,7 +15593,7 @@
       </c>
       <c r="S89" s="74"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
@@ -15620,7 +15623,7 @@
       </c>
       <c r="S90" s="74"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
@@ -15650,7 +15653,7 @@
       </c>
       <c r="S91" s="74"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
@@ -15680,7 +15683,7 @@
       </c>
       <c r="S92" s="74"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
@@ -15710,7 +15713,7 @@
       </c>
       <c r="S93" s="74"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
@@ -15740,7 +15743,7 @@
       </c>
       <c r="S94" s="74"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
@@ -15770,7 +15773,7 @@
       </c>
       <c r="S95" s="74"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
@@ -15800,7 +15803,7 @@
       </c>
       <c r="S96" s="74"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
@@ -15830,7 +15833,7 @@
       </c>
       <c r="S97" s="74"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
@@ -15860,7 +15863,7 @@
       </c>
       <c r="S98" s="74"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
@@ -15890,7 +15893,7 @@
       </c>
       <c r="S99" s="74"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
@@ -15920,7 +15923,7 @@
       </c>
       <c r="S100" s="74"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
@@ -15950,7 +15953,7 @@
       </c>
       <c r="S101" s="74"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
@@ -15980,7 +15983,7 @@
       </c>
       <c r="S102" s="74"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
@@ -16010,7 +16013,7 @@
       </c>
       <c r="S103" s="74"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
@@ -16040,7 +16043,7 @@
       </c>
       <c r="S104" s="74"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
@@ -16070,7 +16073,7 @@
       </c>
       <c r="S105" s="74"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
@@ -16100,7 +16103,7 @@
       </c>
       <c r="S106" s="74"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
@@ -16130,7 +16133,7 @@
       </c>
       <c r="S107" s="74"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
@@ -16160,7 +16163,7 @@
       </c>
       <c r="S108" s="74"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
@@ -16190,7 +16193,7 @@
       </c>
       <c r="S109" s="74"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
@@ -16220,7 +16223,7 @@
       </c>
       <c r="S110" s="74"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
@@ -16250,7 +16253,7 @@
       </c>
       <c r="S111" s="74"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
@@ -16280,7 +16283,7 @@
       </c>
       <c r="S112" s="74"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
@@ -16310,7 +16313,7 @@
       </c>
       <c r="S113" s="74"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
@@ -16340,7 +16343,7 @@
       </c>
       <c r="S114" s="74"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
@@ -16370,7 +16373,7 @@
       </c>
       <c r="S115" s="74"/>
     </row>
-    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="21"/>
       <c r="D116" s="13"/>
       <c r="F116" s="106"/>
@@ -16388,7 +16391,7 @@
       <c r="R116" s="115"/>
       <c r="S116" s="116"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
@@ -16420,7 +16423,7 @@
       </c>
       <c r="S117" s="74"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
@@ -16450,7 +16453,7 @@
       </c>
       <c r="S118" s="74"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
@@ -16480,7 +16483,7 @@
       </c>
       <c r="S119" s="74"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
@@ -16510,7 +16513,7 @@
       </c>
       <c r="S120" s="74"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
@@ -16540,7 +16543,7 @@
       </c>
       <c r="S121" s="74"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
@@ -16570,7 +16573,7 @@
       </c>
       <c r="S122" s="74"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
@@ -16600,7 +16603,7 @@
       </c>
       <c r="S123" s="74"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
@@ -16630,7 +16633,7 @@
       </c>
       <c r="S124" s="74"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
@@ -16660,7 +16663,7 @@
       </c>
       <c r="S125" s="74"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
@@ -16690,7 +16693,7 @@
       </c>
       <c r="S126" s="74"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
@@ -16720,7 +16723,7 @@
       </c>
       <c r="S127" s="74"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
@@ -16750,7 +16753,7 @@
       </c>
       <c r="S128" s="74"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
@@ -16780,7 +16783,7 @@
       </c>
       <c r="S129" s="74"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
@@ -16810,7 +16813,7 @@
       </c>
       <c r="S130" s="74"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
@@ -16840,7 +16843,7 @@
       </c>
       <c r="S131" s="74"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
@@ -16870,7 +16873,7 @@
       </c>
       <c r="S132" s="74"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
@@ -16900,7 +16903,7 @@
       </c>
       <c r="S133" s="74"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
@@ -16930,7 +16933,7 @@
       </c>
       <c r="S134" s="74"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
@@ -16960,7 +16963,7 @@
       </c>
       <c r="S135" s="74"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
@@ -16990,7 +16993,7 @@
       </c>
       <c r="S136" s="74"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
@@ -17020,7 +17023,7 @@
       </c>
       <c r="S137" s="74"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
@@ -17122,80 +17125,80 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19BC2A3-3CFD-4E99-B7D2-ED7A63008A84}">
   <dimension ref="A1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="11" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.1796875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="F2" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="130"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="131"/>
-      <c r="L2" s="132" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="O2" s="133" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="R2" s="134" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="134"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
@@ -17223,7 +17226,7 @@
       </c>
       <c r="S5" s="74"/>
     </row>
-    <row r="6" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
@@ -17249,7 +17252,7 @@
       </c>
       <c r="S6" s="74"/>
     </row>
-    <row r="7" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
@@ -17275,7 +17278,7 @@
       </c>
       <c r="S7" s="74"/>
     </row>
-    <row r="8" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
@@ -17301,7 +17304,7 @@
       </c>
       <c r="S8" s="74"/>
     </row>
-    <row r="9" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
@@ -17329,7 +17332,7 @@
       </c>
       <c r="S9" s="74"/>
     </row>
-    <row r="10" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
@@ -17355,7 +17358,7 @@
       </c>
       <c r="S10" s="74"/>
     </row>
-    <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
@@ -17381,7 +17384,7 @@
       </c>
       <c r="S11" s="74"/>
     </row>
-    <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
@@ -17409,7 +17412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
@@ -17435,7 +17438,7 @@
       </c>
       <c r="S13" s="74"/>
     </row>
-    <row r="14" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
@@ -17461,7 +17464,7 @@
       </c>
       <c r="S14" s="74"/>
     </row>
-    <row r="15" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
@@ -17487,7 +17490,7 @@
       </c>
       <c r="S15" s="74"/>
     </row>
-    <row r="16" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
@@ -17515,7 +17518,7 @@
       </c>
       <c r="S16" s="74"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
@@ -17541,7 +17544,7 @@
       </c>
       <c r="S17" s="74"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
@@ -17567,7 +17570,7 @@
       </c>
       <c r="S18" s="74"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
@@ -17593,7 +17596,7 @@
       </c>
       <c r="S19" s="74"/>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
@@ -17619,7 +17622,7 @@
       </c>
       <c r="S20" s="74"/>
     </row>
-    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="8"/>
@@ -17632,7 +17635,7 @@
       <c r="R21" s="20"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
@@ -17660,7 +17663,7 @@
       </c>
       <c r="S22" s="74"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
@@ -17686,7 +17689,7 @@
       </c>
       <c r="S23" s="74"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
@@ -17712,7 +17715,7 @@
       </c>
       <c r="S24" s="74"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
@@ -17738,7 +17741,7 @@
       </c>
       <c r="S25" s="74"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
@@ -17764,7 +17767,7 @@
       </c>
       <c r="S26" s="74"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
@@ -17792,7 +17795,7 @@
       </c>
       <c r="S27" s="74"/>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
@@ -17818,7 +17821,7 @@
       </c>
       <c r="S28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
@@ -17844,7 +17847,7 @@
       </c>
       <c r="S29" s="74"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
@@ -17870,7 +17873,7 @@
       </c>
       <c r="S30" s="74"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
@@ -17898,7 +17901,7 @@
       </c>
       <c r="S31" s="74"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
@@ -17924,7 +17927,7 @@
       </c>
       <c r="S32" s="74"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
@@ -17950,7 +17953,7 @@
       </c>
       <c r="S33" s="74"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
@@ -17978,7 +17981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
@@ -18004,7 +18007,7 @@
       </c>
       <c r="S35" s="74"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
@@ -18030,7 +18033,7 @@
       </c>
       <c r="S36" s="74"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
@@ -18056,7 +18059,7 @@
       </c>
       <c r="S37" s="74"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
@@ -18086,7 +18089,7 @@
       </c>
       <c r="S38" s="74"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
@@ -18112,7 +18115,7 @@
       </c>
       <c r="S39" s="74"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
@@ -18138,7 +18141,7 @@
       </c>
       <c r="S40" s="74"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
@@ -18166,7 +18169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
@@ -18192,7 +18195,7 @@
       </c>
       <c r="S42" s="74"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
@@ -18218,7 +18221,7 @@
       </c>
       <c r="S43" s="74"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
@@ -18244,7 +18247,7 @@
       </c>
       <c r="S44" s="74"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
@@ -18274,7 +18277,7 @@
       </c>
       <c r="S45" s="74"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
@@ -18300,7 +18303,7 @@
       </c>
       <c r="S46" s="74"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
@@ -18326,7 +18329,7 @@
       </c>
       <c r="S47" s="74"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
@@ -18352,7 +18355,7 @@
       </c>
       <c r="S48" s="74"/>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
@@ -18378,7 +18381,7 @@
       </c>
       <c r="S49" s="74"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
@@ -18404,7 +18407,7 @@
       </c>
       <c r="S50" s="74"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
@@ -18430,7 +18433,7 @@
       </c>
       <c r="S51" s="74"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
@@ -18456,7 +18459,7 @@
       </c>
       <c r="S52" s="74"/>
     </row>
-    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="F53" s="13"/>
       <c r="G53" s="8"/>
@@ -18469,7 +18472,7 @@
       <c r="R53" s="20"/>
       <c r="S53" s="23"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
@@ -18497,7 +18500,7 @@
       </c>
       <c r="S54" s="75"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
@@ -18523,7 +18526,7 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
@@ -18549,7 +18552,7 @@
       </c>
       <c r="S56" s="75"/>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
@@ -18575,7 +18578,7 @@
       </c>
       <c r="S57" s="75"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
@@ -18601,7 +18604,7 @@
       </c>
       <c r="S58" s="75"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
@@ -18627,7 +18630,7 @@
       </c>
       <c r="S59" s="75"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
@@ -18653,7 +18656,7 @@
       </c>
       <c r="S60" s="75"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
@@ -18679,7 +18682,7 @@
       </c>
       <c r="S61" s="75"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
@@ -18705,7 +18708,7 @@
       </c>
       <c r="S62" s="75"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
@@ -18731,7 +18734,7 @@
       </c>
       <c r="S63" s="75"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
@@ -18757,7 +18760,7 @@
       </c>
       <c r="S64" s="75"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
@@ -18783,7 +18786,7 @@
       </c>
       <c r="S65" s="75"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
@@ -18809,7 +18812,7 @@
       </c>
       <c r="S66" s="75"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
@@ -18835,7 +18838,7 @@
       </c>
       <c r="S67" s="75"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
@@ -18865,7 +18868,7 @@
       </c>
       <c r="S68" s="75"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
@@ -18891,7 +18894,7 @@
       </c>
       <c r="S69" s="75"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
@@ -18917,7 +18920,7 @@
       </c>
       <c r="S70" s="75"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
@@ -18943,7 +18946,7 @@
       </c>
       <c r="S71" s="75"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
@@ -18969,7 +18972,7 @@
       </c>
       <c r="S72" s="75"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
@@ -18995,7 +18998,7 @@
       </c>
       <c r="S73" s="75"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
@@ -19021,7 +19024,7 @@
       </c>
       <c r="S74" s="75"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
@@ -19047,7 +19050,7 @@
       </c>
       <c r="S75" s="75"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
@@ -19073,7 +19076,7 @@
       </c>
       <c r="S76" s="75"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
@@ -19099,7 +19102,7 @@
       </c>
       <c r="S77" s="75"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
@@ -19125,7 +19128,7 @@
       </c>
       <c r="S78" s="75"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
@@ -19151,7 +19154,7 @@
       </c>
       <c r="S79" s="75"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
@@ -19177,7 +19180,7 @@
       </c>
       <c r="S80" s="75"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
@@ -19203,7 +19206,7 @@
       </c>
       <c r="S81" s="75"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
@@ -19229,7 +19232,7 @@
       </c>
       <c r="S82" s="75"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
@@ -19255,7 +19258,7 @@
       </c>
       <c r="S83" s="75"/>
     </row>
-    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="21"/>
       <c r="D84" s="13"/>
       <c r="F84" s="13"/>
@@ -19269,7 +19272,7 @@
       <c r="R84" s="20"/>
       <c r="S84" s="23"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
@@ -19297,7 +19300,7 @@
       </c>
       <c r="S85" s="75"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
@@ -19323,7 +19326,7 @@
       </c>
       <c r="S86" s="75"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
@@ -19349,7 +19352,7 @@
       </c>
       <c r="S87" s="75"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
@@ -19375,7 +19378,7 @@
       </c>
       <c r="S88" s="75"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
@@ -19401,7 +19404,7 @@
       </c>
       <c r="S89" s="75"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
@@ -19427,7 +19430,7 @@
       </c>
       <c r="S90" s="75"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
@@ -19453,7 +19456,7 @@
       </c>
       <c r="S91" s="75"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
@@ -19479,7 +19482,7 @@
       </c>
       <c r="S92" s="75"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
@@ -19505,7 +19508,7 @@
       </c>
       <c r="S93" s="75"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
@@ -19531,7 +19534,7 @@
       </c>
       <c r="S94" s="75"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
@@ -19557,7 +19560,7 @@
       </c>
       <c r="S95" s="75"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
@@ -19583,7 +19586,7 @@
       </c>
       <c r="S96" s="75"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
@@ -19609,7 +19612,7 @@
       </c>
       <c r="S97" s="75"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
@@ -19635,7 +19638,7 @@
       </c>
       <c r="S98" s="75"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
@@ -19661,7 +19664,7 @@
       </c>
       <c r="S99" s="75"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
@@ -19687,7 +19690,7 @@
       </c>
       <c r="S100" s="75"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
@@ -19713,7 +19716,7 @@
       </c>
       <c r="S101" s="75"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
@@ -19739,7 +19742,7 @@
       </c>
       <c r="S102" s="75"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
@@ -19765,7 +19768,7 @@
       </c>
       <c r="S103" s="75"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
@@ -19791,7 +19794,7 @@
       </c>
       <c r="S104" s="75"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
@@ -19817,7 +19820,7 @@
       </c>
       <c r="S105" s="75"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
@@ -19843,7 +19846,7 @@
       </c>
       <c r="S106" s="75"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
@@ -19869,7 +19872,7 @@
       </c>
       <c r="S107" s="75"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
@@ -19895,7 +19898,7 @@
       </c>
       <c r="S108" s="75"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
@@ -19921,7 +19924,7 @@
       </c>
       <c r="S109" s="75"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
@@ -19947,7 +19950,7 @@
       </c>
       <c r="S110" s="75"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
@@ -19973,7 +19976,7 @@
       </c>
       <c r="S111" s="75"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
@@ -19999,7 +20002,7 @@
       </c>
       <c r="S112" s="75"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
@@ -20025,7 +20028,7 @@
       </c>
       <c r="S113" s="75"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
@@ -20051,7 +20054,7 @@
       </c>
       <c r="S114" s="75"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
@@ -20077,7 +20080,7 @@
       </c>
       <c r="S115" s="75"/>
     </row>
-    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="21"/>
       <c r="D116" s="13"/>
       <c r="F116" s="13"/>
@@ -20091,7 +20094,7 @@
       <c r="R116" s="20"/>
       <c r="S116" s="23"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
@@ -20119,7 +20122,7 @@
       </c>
       <c r="S117" s="75"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
@@ -20145,7 +20148,7 @@
       </c>
       <c r="S118" s="75"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
@@ -20171,7 +20174,7 @@
       </c>
       <c r="S119" s="75"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
@@ -20197,7 +20200,7 @@
       </c>
       <c r="S120" s="75"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
@@ -20223,7 +20226,7 @@
       </c>
       <c r="S121" s="75"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
@@ -20249,7 +20252,7 @@
       </c>
       <c r="S122" s="75"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
@@ -20275,7 +20278,7 @@
       </c>
       <c r="S123" s="75"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
@@ -20301,7 +20304,7 @@
       </c>
       <c r="S124" s="75"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
@@ -20327,7 +20330,7 @@
       </c>
       <c r="S125" s="75"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
@@ -20353,7 +20356,7 @@
       </c>
       <c r="S126" s="75"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
@@ -20379,7 +20382,7 @@
       </c>
       <c r="S127" s="75"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
@@ -20405,7 +20408,7 @@
       </c>
       <c r="S128" s="75"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
@@ -20431,7 +20434,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
@@ -20457,7 +20460,7 @@
       </c>
       <c r="S130" s="75"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
@@ -20483,7 +20486,7 @@
       </c>
       <c r="S131" s="75"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
@@ -20509,7 +20512,7 @@
       </c>
       <c r="S132" s="75"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
@@ -20535,7 +20538,7 @@
       </c>
       <c r="S133" s="75"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
@@ -20561,7 +20564,7 @@
       </c>
       <c r="S134" s="75"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
@@ -20587,7 +20590,7 @@
       </c>
       <c r="S135" s="75"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
@@ -20613,7 +20616,7 @@
       </c>
       <c r="S136" s="75"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
@@ -20639,7 +20642,7 @@
       </c>
       <c r="S137" s="75"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
@@ -20737,80 +20740,80 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1808E512-9086-4256-BF9F-9A0636DA67FB}">
   <dimension ref="A1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="11" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.1796875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="F2" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="130"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="131"/>
-      <c r="L2" s="132" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="O2" s="133" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="R2" s="134" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="134"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
@@ -20838,7 +20841,7 @@
       </c>
       <c r="S5" s="74"/>
     </row>
-    <row r="6" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
@@ -20864,7 +20867,7 @@
       </c>
       <c r="S6" s="74"/>
     </row>
-    <row r="7" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
@@ -20890,7 +20893,7 @@
       </c>
       <c r="S7" s="74"/>
     </row>
-    <row r="8" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
@@ -20916,7 +20919,7 @@
       </c>
       <c r="S8" s="74"/>
     </row>
-    <row r="9" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
@@ -20944,7 +20947,7 @@
       </c>
       <c r="S9" s="74"/>
     </row>
-    <row r="10" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
@@ -20970,7 +20973,7 @@
       </c>
       <c r="S10" s="74"/>
     </row>
-    <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
@@ -20996,7 +20999,7 @@
       </c>
       <c r="S11" s="74"/>
     </row>
-    <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
@@ -21024,7 +21027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
@@ -21050,7 +21053,7 @@
       </c>
       <c r="S13" s="74"/>
     </row>
-    <row r="14" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
@@ -21076,7 +21079,7 @@
       </c>
       <c r="S14" s="74"/>
     </row>
-    <row r="15" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
@@ -21102,7 +21105,7 @@
       </c>
       <c r="S15" s="74"/>
     </row>
-    <row r="16" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
@@ -21130,7 +21133,7 @@
       </c>
       <c r="S16" s="74"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
@@ -21156,7 +21159,7 @@
       </c>
       <c r="S17" s="74"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
@@ -21182,7 +21185,7 @@
       </c>
       <c r="S18" s="74"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
@@ -21208,7 +21211,7 @@
       </c>
       <c r="S19" s="74"/>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
@@ -21234,7 +21237,7 @@
       </c>
       <c r="S20" s="74"/>
     </row>
-    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="8"/>
@@ -21247,7 +21250,7 @@
       <c r="R21" s="20"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
@@ -21275,7 +21278,7 @@
       </c>
       <c r="S22" s="74"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
@@ -21301,7 +21304,7 @@
       </c>
       <c r="S23" s="74"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
@@ -21327,7 +21330,7 @@
       </c>
       <c r="S24" s="74"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
@@ -21353,7 +21356,7 @@
       </c>
       <c r="S25" s="74"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
@@ -21379,7 +21382,7 @@
       </c>
       <c r="S26" s="74"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
@@ -21407,7 +21410,7 @@
       </c>
       <c r="S27" s="74"/>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
@@ -21433,7 +21436,7 @@
       </c>
       <c r="S28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
@@ -21459,7 +21462,7 @@
       </c>
       <c r="S29" s="74"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
@@ -21485,7 +21488,7 @@
       </c>
       <c r="S30" s="74"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
@@ -21513,7 +21516,7 @@
       </c>
       <c r="S31" s="74"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
@@ -21539,7 +21542,7 @@
       </c>
       <c r="S32" s="74"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
@@ -21565,7 +21568,7 @@
       </c>
       <c r="S33" s="74"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
@@ -21593,7 +21596,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
@@ -21619,7 +21622,7 @@
       </c>
       <c r="S35" s="74"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
@@ -21645,7 +21648,7 @@
       </c>
       <c r="S36" s="74"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
@@ -21675,7 +21678,7 @@
       </c>
       <c r="S37" s="74"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
@@ -21703,7 +21706,7 @@
       </c>
       <c r="S38" s="74"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
@@ -21729,7 +21732,7 @@
       </c>
       <c r="S39" s="74"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
@@ -21757,7 +21760,7 @@
       </c>
       <c r="S40" s="74"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
@@ -21785,7 +21788,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
@@ -21811,7 +21814,7 @@
       </c>
       <c r="S42" s="74"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
@@ -21837,7 +21840,7 @@
       </c>
       <c r="S43" s="74"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
@@ -21863,7 +21866,7 @@
       </c>
       <c r="S44" s="74"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
@@ -21893,7 +21896,7 @@
       </c>
       <c r="S45" s="74"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
@@ -21919,7 +21922,7 @@
       </c>
       <c r="S46" s="74"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
@@ -21945,7 +21948,7 @@
       </c>
       <c r="S47" s="74"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
@@ -21971,7 +21974,7 @@
       </c>
       <c r="S48" s="74"/>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
@@ -21997,7 +22000,7 @@
       </c>
       <c r="S49" s="74"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
@@ -22023,7 +22026,7 @@
       </c>
       <c r="S50" s="74"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
@@ -22049,7 +22052,7 @@
       </c>
       <c r="S51" s="74"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
@@ -22075,7 +22078,7 @@
       </c>
       <c r="S52" s="74"/>
     </row>
-    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="F53" s="13"/>
       <c r="G53" s="8"/>
@@ -22088,7 +22091,7 @@
       <c r="R53" s="20"/>
       <c r="S53" s="23"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
@@ -22116,7 +22119,7 @@
       </c>
       <c r="S54" s="75"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
@@ -22142,7 +22145,7 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
@@ -22168,7 +22171,7 @@
       </c>
       <c r="S56" s="75"/>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
@@ -22194,7 +22197,7 @@
       </c>
       <c r="S57" s="75"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
@@ -22220,7 +22223,7 @@
       </c>
       <c r="S58" s="75"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
@@ -22246,7 +22249,7 @@
       </c>
       <c r="S59" s="75"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
@@ -22272,7 +22275,7 @@
       </c>
       <c r="S60" s="75"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
@@ -22298,7 +22301,7 @@
       </c>
       <c r="S61" s="75"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
@@ -22324,7 +22327,7 @@
       </c>
       <c r="S62" s="75"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
@@ -22350,7 +22353,7 @@
       </c>
       <c r="S63" s="75"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
@@ -22376,7 +22379,7 @@
       </c>
       <c r="S64" s="75"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
@@ -22402,7 +22405,7 @@
       </c>
       <c r="S65" s="75"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
@@ -22428,7 +22431,7 @@
       </c>
       <c r="S66" s="75"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
@@ -22454,7 +22457,7 @@
       </c>
       <c r="S67" s="75"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
@@ -22480,7 +22483,7 @@
       </c>
       <c r="S68" s="75"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
@@ -22506,7 +22509,7 @@
       </c>
       <c r="S69" s="75"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
@@ -22532,7 +22535,7 @@
       </c>
       <c r="S70" s="75"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
@@ -22558,7 +22561,7 @@
       </c>
       <c r="S71" s="75"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
@@ -22584,7 +22587,7 @@
       </c>
       <c r="S72" s="75"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
@@ -22610,7 +22613,7 @@
       </c>
       <c r="S73" s="75"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
@@ -22636,7 +22639,7 @@
       </c>
       <c r="S74" s="75"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
@@ -22662,7 +22665,7 @@
       </c>
       <c r="S75" s="75"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
@@ -22688,7 +22691,7 @@
       </c>
       <c r="S76" s="75"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
@@ -22714,7 +22717,7 @@
       </c>
       <c r="S77" s="75"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
@@ -22740,7 +22743,7 @@
       </c>
       <c r="S78" s="75"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
@@ -22766,7 +22769,7 @@
       </c>
       <c r="S79" s="75"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
@@ -22792,7 +22795,7 @@
       </c>
       <c r="S80" s="75"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
@@ -22818,7 +22821,7 @@
       </c>
       <c r="S81" s="75"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
@@ -22844,7 +22847,7 @@
       </c>
       <c r="S82" s="75"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
@@ -22870,7 +22873,7 @@
       </c>
       <c r="S83" s="75"/>
     </row>
-    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="21"/>
       <c r="D84" s="13"/>
       <c r="F84" s="13"/>
@@ -22884,7 +22887,7 @@
       <c r="R84" s="20"/>
       <c r="S84" s="23"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
@@ -22912,7 +22915,7 @@
       </c>
       <c r="S85" s="75"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
@@ -22938,7 +22941,7 @@
       </c>
       <c r="S86" s="75"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
@@ -22964,7 +22967,7 @@
       </c>
       <c r="S87" s="75"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
@@ -22990,7 +22993,7 @@
       </c>
       <c r="S88" s="75"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
@@ -23016,7 +23019,7 @@
       </c>
       <c r="S89" s="75"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
@@ -23042,7 +23045,7 @@
       </c>
       <c r="S90" s="75"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
@@ -23068,7 +23071,7 @@
       </c>
       <c r="S91" s="75"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
@@ -23094,7 +23097,7 @@
       </c>
       <c r="S92" s="75"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
@@ -23120,7 +23123,7 @@
       </c>
       <c r="S93" s="75"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
@@ -23146,7 +23149,7 @@
       </c>
       <c r="S94" s="75"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
@@ -23172,7 +23175,7 @@
       </c>
       <c r="S95" s="75"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
@@ -23198,7 +23201,7 @@
       </c>
       <c r="S96" s="75"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
@@ -23224,7 +23227,7 @@
       </c>
       <c r="S97" s="75"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
@@ -23250,7 +23253,7 @@
       </c>
       <c r="S98" s="75"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
@@ -23276,7 +23279,7 @@
       </c>
       <c r="S99" s="75"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
@@ -23302,7 +23305,7 @@
       </c>
       <c r="S100" s="75"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
@@ -23328,7 +23331,7 @@
       </c>
       <c r="S101" s="75"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
@@ -23354,7 +23357,7 @@
       </c>
       <c r="S102" s="75"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
@@ -23380,7 +23383,7 @@
       </c>
       <c r="S103" s="75"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
@@ -23406,7 +23409,7 @@
       </c>
       <c r="S104" s="75"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
@@ -23432,7 +23435,7 @@
       </c>
       <c r="S105" s="75"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
@@ -23458,7 +23461,7 @@
       </c>
       <c r="S106" s="75"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
@@ -23484,7 +23487,7 @@
       </c>
       <c r="S107" s="75"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
@@ -23510,7 +23513,7 @@
       </c>
       <c r="S108" s="75"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
@@ -23536,7 +23539,7 @@
       </c>
       <c r="S109" s="75"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
@@ -23562,7 +23565,7 @@
       </c>
       <c r="S110" s="75"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
@@ -23588,7 +23591,7 @@
       </c>
       <c r="S111" s="75"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
@@ -23614,7 +23617,7 @@
       </c>
       <c r="S112" s="75"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
@@ -23640,7 +23643,7 @@
       </c>
       <c r="S113" s="75"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
@@ -23666,7 +23669,7 @@
       </c>
       <c r="S114" s="75"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
@@ -23692,7 +23695,7 @@
       </c>
       <c r="S115" s="75"/>
     </row>
-    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="21"/>
       <c r="D116" s="13"/>
       <c r="F116" s="13"/>
@@ -23706,7 +23709,7 @@
       <c r="R116" s="20"/>
       <c r="S116" s="23"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
@@ -23734,7 +23737,7 @@
       </c>
       <c r="S117" s="75"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
@@ -23760,7 +23763,7 @@
       </c>
       <c r="S118" s="75"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
@@ -23786,7 +23789,7 @@
       </c>
       <c r="S119" s="75"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
@@ -23812,7 +23815,7 @@
       </c>
       <c r="S120" s="75"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
@@ -23838,7 +23841,7 @@
       </c>
       <c r="S121" s="75"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
@@ -23864,7 +23867,7 @@
       </c>
       <c r="S122" s="75"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
@@ -23890,7 +23893,7 @@
       </c>
       <c r="S123" s="75"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
@@ -23916,7 +23919,7 @@
       </c>
       <c r="S124" s="75"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
@@ -23942,7 +23945,7 @@
       </c>
       <c r="S125" s="75"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
@@ -23968,7 +23971,7 @@
       </c>
       <c r="S126" s="75"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
@@ -23994,7 +23997,7 @@
       </c>
       <c r="S127" s="75"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
@@ -24020,7 +24023,7 @@
       </c>
       <c r="S128" s="75"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
@@ -24046,7 +24049,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
@@ -24072,7 +24075,7 @@
       </c>
       <c r="S130" s="75"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
@@ -24098,7 +24101,7 @@
       </c>
       <c r="S131" s="75"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
@@ -24124,7 +24127,7 @@
       </c>
       <c r="S132" s="75"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
@@ -24150,7 +24153,7 @@
       </c>
       <c r="S133" s="75"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
@@ -24176,7 +24179,7 @@
       </c>
       <c r="S134" s="75"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
@@ -24202,7 +24205,7 @@
       </c>
       <c r="S135" s="75"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
@@ -24228,7 +24231,7 @@
       </c>
       <c r="S136" s="75"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
@@ -24254,7 +24257,7 @@
       </c>
       <c r="S137" s="75"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
@@ -24353,80 +24356,80 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9F5440-2F33-4399-87DF-E31A71076149}">
   <dimension ref="A1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="11" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.1796875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="F2" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="130"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="131"/>
-      <c r="L2" s="132" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="O2" s="133" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="R2" s="134" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="134"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
@@ -24454,7 +24457,7 @@
       </c>
       <c r="S5" s="74"/>
     </row>
-    <row r="6" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
@@ -24480,7 +24483,7 @@
       </c>
       <c r="S6" s="74"/>
     </row>
-    <row r="7" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
@@ -24506,7 +24509,7 @@
       </c>
       <c r="S7" s="74"/>
     </row>
-    <row r="8" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
@@ -24532,7 +24535,7 @@
       </c>
       <c r="S8" s="74"/>
     </row>
-    <row r="9" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
@@ -24560,7 +24563,7 @@
       </c>
       <c r="S9" s="74"/>
     </row>
-    <row r="10" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
@@ -24586,7 +24589,7 @@
       </c>
       <c r="S10" s="74"/>
     </row>
-    <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
@@ -24612,7 +24615,7 @@
       </c>
       <c r="S11" s="74"/>
     </row>
-    <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
@@ -24640,7 +24643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
@@ -24666,7 +24669,7 @@
       </c>
       <c r="S13" s="74"/>
     </row>
-    <row r="14" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
@@ -24692,7 +24695,7 @@
       </c>
       <c r="S14" s="74"/>
     </row>
-    <row r="15" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
@@ -24718,7 +24721,7 @@
       </c>
       <c r="S15" s="74"/>
     </row>
-    <row r="16" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
@@ -24746,7 +24749,7 @@
       </c>
       <c r="S16" s="74"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
@@ -24772,7 +24775,7 @@
       </c>
       <c r="S17" s="74"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
@@ -24798,7 +24801,7 @@
       </c>
       <c r="S18" s="74"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
@@ -24824,7 +24827,7 @@
       </c>
       <c r="S19" s="74"/>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
@@ -24850,7 +24853,7 @@
       </c>
       <c r="S20" s="74"/>
     </row>
-    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="8"/>
@@ -24863,7 +24866,7 @@
       <c r="R21" s="20"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
@@ -24891,7 +24894,7 @@
       </c>
       <c r="S22" s="74"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
@@ -24917,7 +24920,7 @@
       </c>
       <c r="S23" s="74"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
@@ -24943,7 +24946,7 @@
       </c>
       <c r="S24" s="74"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
@@ -24969,7 +24972,7 @@
       </c>
       <c r="S25" s="74"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
@@ -24995,7 +24998,7 @@
       </c>
       <c r="S26" s="74"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
@@ -25023,7 +25026,7 @@
       </c>
       <c r="S27" s="74"/>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
@@ -25049,7 +25052,7 @@
       </c>
       <c r="S28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
@@ -25075,7 +25078,7 @@
       </c>
       <c r="S29" s="74"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
@@ -25101,7 +25104,7 @@
       </c>
       <c r="S30" s="74"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
@@ -25129,7 +25132,7 @@
       </c>
       <c r="S31" s="74"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
@@ -25155,7 +25158,7 @@
       </c>
       <c r="S32" s="74"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
@@ -25181,7 +25184,7 @@
       </c>
       <c r="S33" s="74"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
@@ -25209,7 +25212,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
@@ -25235,7 +25238,7 @@
       </c>
       <c r="S35" s="74"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
@@ -25261,7 +25264,7 @@
       </c>
       <c r="S36" s="74"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
@@ -25287,7 +25290,7 @@
       </c>
       <c r="S37" s="74"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
@@ -25315,7 +25318,7 @@
       </c>
       <c r="S38" s="74"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
@@ -25343,7 +25346,7 @@
       </c>
       <c r="S39" s="74"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
@@ -25373,7 +25376,7 @@
       </c>
       <c r="S40" s="74"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
@@ -25401,7 +25404,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
@@ -25427,7 +25430,7 @@
       </c>
       <c r="S42" s="74"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
@@ -25453,7 +25456,7 @@
       </c>
       <c r="S43" s="74"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
@@ -25479,7 +25482,7 @@
       </c>
       <c r="S44" s="74"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
@@ -25509,7 +25512,7 @@
       </c>
       <c r="S45" s="74"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
@@ -25535,7 +25538,7 @@
       </c>
       <c r="S46" s="74"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
@@ -25561,7 +25564,7 @@
       </c>
       <c r="S47" s="74"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
@@ -25587,7 +25590,7 @@
       </c>
       <c r="S48" s="74"/>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
@@ -25613,7 +25616,7 @@
       </c>
       <c r="S49" s="74"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
@@ -25639,7 +25642,7 @@
       </c>
       <c r="S50" s="74"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
@@ -25665,7 +25668,7 @@
       </c>
       <c r="S51" s="74"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
@@ -25691,7 +25694,7 @@
       </c>
       <c r="S52" s="74"/>
     </row>
-    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="12" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="F53" s="13"/>
       <c r="G53" s="8"/>
@@ -25704,7 +25707,7 @@
       <c r="R53" s="20"/>
       <c r="S53" s="23"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
@@ -25732,7 +25735,7 @@
       </c>
       <c r="S54" s="75"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
@@ -25758,7 +25761,7 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
@@ -25784,7 +25787,7 @@
       </c>
       <c r="S56" s="75"/>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
@@ -25812,7 +25815,7 @@
       </c>
       <c r="S57" s="75"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
@@ -25840,7 +25843,7 @@
       </c>
       <c r="S58" s="75"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
@@ -25866,7 +25869,7 @@
       </c>
       <c r="S59" s="75"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
@@ -25892,7 +25895,7 @@
       </c>
       <c r="S60" s="75"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
@@ -25918,7 +25921,7 @@
       </c>
       <c r="S61" s="75"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
@@ -25944,7 +25947,7 @@
       </c>
       <c r="S62" s="75"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
@@ -25970,7 +25973,7 @@
       </c>
       <c r="S63" s="75"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
@@ -25996,7 +25999,7 @@
       </c>
       <c r="S64" s="75"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
@@ -26022,7 +26025,7 @@
       </c>
       <c r="S65" s="75"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
@@ -26048,7 +26051,7 @@
       </c>
       <c r="S66" s="75"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
@@ -26074,7 +26077,7 @@
       </c>
       <c r="S67" s="75"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
@@ -26100,7 +26103,7 @@
       </c>
       <c r="S68" s="75"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
@@ -26114,9 +26117,11 @@
       </c>
       <c r="J69" s="69"/>
       <c r="L69" s="93">
-        <v>0</v>
-      </c>
-      <c r="M69" s="71"/>
+        <v>1</v>
+      </c>
+      <c r="M69" s="71" t="s">
+        <v>88</v>
+      </c>
       <c r="O69" s="94">
         <v>1.5</v>
       </c>
@@ -26128,7 +26133,7 @@
       </c>
       <c r="S69" s="75"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
@@ -26154,7 +26159,7 @@
       </c>
       <c r="S70" s="75"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
@@ -26180,7 +26185,7 @@
       </c>
       <c r="S71" s="75"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
@@ -26206,7 +26211,7 @@
       </c>
       <c r="S72" s="75"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
@@ -26232,7 +26237,7 @@
       </c>
       <c r="S73" s="75"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
@@ -26258,7 +26263,7 @@
       </c>
       <c r="S74" s="75"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
@@ -26284,7 +26289,7 @@
       </c>
       <c r="S75" s="75"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
@@ -26310,7 +26315,7 @@
       </c>
       <c r="S76" s="75"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
@@ -26336,7 +26341,7 @@
       </c>
       <c r="S77" s="75"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
@@ -26362,7 +26367,7 @@
       </c>
       <c r="S78" s="75"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
@@ -26388,7 +26393,7 @@
       </c>
       <c r="S79" s="75"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
@@ -26414,7 +26419,7 @@
       </c>
       <c r="S80" s="75"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
@@ -26440,7 +26445,7 @@
       </c>
       <c r="S81" s="75"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
@@ -26466,7 +26471,7 @@
       </c>
       <c r="S82" s="75"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
@@ -26492,7 +26497,7 @@
       </c>
       <c r="S83" s="75"/>
     </row>
-    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="21"/>
       <c r="D84" s="13"/>
       <c r="F84" s="13"/>
@@ -26506,7 +26511,7 @@
       <c r="R84" s="20"/>
       <c r="S84" s="23"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
@@ -26534,7 +26539,7 @@
       </c>
       <c r="S85" s="75"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
@@ -26560,7 +26565,7 @@
       </c>
       <c r="S86" s="75"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
@@ -26586,7 +26591,7 @@
       </c>
       <c r="S87" s="75"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
@@ -26612,7 +26617,7 @@
       </c>
       <c r="S88" s="75"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
@@ -26638,7 +26643,7 @@
       </c>
       <c r="S89" s="75"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
@@ -26664,7 +26669,7 @@
       </c>
       <c r="S90" s="75"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
@@ -26690,7 +26695,7 @@
       </c>
       <c r="S91" s="75"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
@@ -26716,7 +26721,7 @@
       </c>
       <c r="S92" s="75"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
@@ -26742,7 +26747,7 @@
       </c>
       <c r="S93" s="75"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
@@ -26768,7 +26773,7 @@
       </c>
       <c r="S94" s="75"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
@@ -26794,7 +26799,7 @@
       </c>
       <c r="S95" s="75"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
@@ -26820,7 +26825,7 @@
       </c>
       <c r="S96" s="75"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
@@ -26846,7 +26851,7 @@
       </c>
       <c r="S97" s="75"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
@@ -26872,7 +26877,7 @@
       </c>
       <c r="S98" s="75"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
@@ -26898,7 +26903,7 @@
       </c>
       <c r="S99" s="75"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
@@ -26924,7 +26929,7 @@
       </c>
       <c r="S100" s="75"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
@@ -26950,7 +26955,7 @@
       </c>
       <c r="S101" s="75"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
@@ -26976,7 +26981,7 @@
       </c>
       <c r="S102" s="75"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
@@ -27002,7 +27007,7 @@
       </c>
       <c r="S103" s="75"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
@@ -27028,7 +27033,7 @@
       </c>
       <c r="S104" s="75"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
@@ -27054,7 +27059,7 @@
       </c>
       <c r="S105" s="75"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
@@ -27080,7 +27085,7 @@
       </c>
       <c r="S106" s="75"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
@@ -27106,7 +27111,7 @@
       </c>
       <c r="S107" s="75"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
@@ -27132,7 +27137,7 @@
       </c>
       <c r="S108" s="75"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
@@ -27158,7 +27163,7 @@
       </c>
       <c r="S109" s="75"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
@@ -27184,7 +27189,7 @@
       </c>
       <c r="S110" s="75"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
@@ -27210,7 +27215,7 @@
       </c>
       <c r="S111" s="75"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
@@ -27236,7 +27241,7 @@
       </c>
       <c r="S112" s="75"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
@@ -27262,7 +27267,7 @@
       </c>
       <c r="S113" s="75"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
@@ -27288,7 +27293,7 @@
       </c>
       <c r="S114" s="75"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
@@ -27314,7 +27319,7 @@
       </c>
       <c r="S115" s="75"/>
     </row>
-    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="21"/>
       <c r="D116" s="13"/>
       <c r="F116" s="13"/>
@@ -27328,7 +27333,7 @@
       <c r="R116" s="20"/>
       <c r="S116" s="23"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
@@ -27356,7 +27361,7 @@
       </c>
       <c r="S117" s="75"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
@@ -27382,7 +27387,7 @@
       </c>
       <c r="S118" s="75"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
@@ -27408,7 +27413,7 @@
       </c>
       <c r="S119" s="75"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
@@ -27434,7 +27439,7 @@
       </c>
       <c r="S120" s="75"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
@@ -27460,7 +27465,7 @@
       </c>
       <c r="S121" s="75"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
@@ -27486,7 +27491,7 @@
       </c>
       <c r="S122" s="75"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
@@ -27512,7 +27517,7 @@
       </c>
       <c r="S123" s="75"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
@@ -27538,7 +27543,7 @@
       </c>
       <c r="S124" s="75"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
@@ -27564,7 +27569,7 @@
       </c>
       <c r="S125" s="75"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
@@ -27590,7 +27595,7 @@
       </c>
       <c r="S126" s="75"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
@@ -27616,7 +27621,7 @@
       </c>
       <c r="S127" s="75"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
@@ -27642,7 +27647,7 @@
       </c>
       <c r="S128" s="75"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
@@ -27668,7 +27673,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
@@ -27694,7 +27699,7 @@
       </c>
       <c r="S130" s="75"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
@@ -27720,7 +27725,7 @@
       </c>
       <c r="S131" s="75"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
@@ -27746,7 +27751,7 @@
       </c>
       <c r="S132" s="75"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
@@ -27772,7 +27777,7 @@
       </c>
       <c r="S133" s="75"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
@@ -27798,7 +27803,7 @@
       </c>
       <c r="S134" s="75"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
@@ -27824,7 +27829,7 @@
       </c>
       <c r="S135" s="75"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
@@ -27850,7 +27855,7 @@
       </c>
       <c r="S136" s="75"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
@@ -27876,7 +27881,7 @@
       </c>
       <c r="S137" s="75"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
@@ -27974,42 +27979,42 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653D0077-DF0B-4D1F-9CC1-B4A9B63AFE0C}">
   <dimension ref="B1:H119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="24" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" style="24" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="24" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="24" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="24" customWidth="1"/>
     <col min="4" max="4" width="13" style="24" customWidth="1"/>
-    <col min="5" max="5" width="150.6328125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="2.6328125" style="24" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" style="24" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="24" customWidth="1"/>
-    <col min="9" max="16384" width="10.90625" style="24"/>
+    <col min="5" max="5" width="150.5703125" style="24" customWidth="1"/>
+    <col min="6" max="6" width="2.5703125" style="24" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="24" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="10.85546875" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="135" t="s">
+    <row r="1" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="135" t="s">
+      <c r="C2" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="135" t="s">
+      <c r="D2" s="138" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="138" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-    </row>
-    <row r="4" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="136">
+    <row r="3" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+    </row>
+    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="139">
         <v>1</v>
       </c>
       <c r="C4" s="6"/>
@@ -28026,8 +28031,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="136"/>
+    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="139"/>
       <c r="C5" s="6"/>
       <c r="D5" s="96" t="s">
         <v>47</v>
@@ -28042,8 +28047,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="136"/>
+    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="139"/>
       <c r="C6" s="6"/>
       <c r="D6" s="96" t="s">
         <v>41</v>
@@ -28058,8 +28063,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="136"/>
+    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="139"/>
       <c r="C7" s="6"/>
       <c r="D7" s="96" t="s">
         <v>42</v>
@@ -28068,8 +28073,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="136"/>
+    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="139"/>
       <c r="C8" s="6"/>
       <c r="D8" s="96" t="s">
         <v>43</v>
@@ -28078,8 +28083,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="136"/>
+    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="139"/>
       <c r="C9" s="6"/>
       <c r="D9" s="96" t="s">
         <v>44</v>
@@ -28088,8 +28093,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="136"/>
+    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="139"/>
       <c r="C10" s="6"/>
       <c r="D10" s="96" t="s">
         <v>45</v>
@@ -28098,8 +28103,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="136"/>
+    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="139"/>
       <c r="C11" s="6"/>
       <c r="D11" s="96" t="s">
         <v>46</v>
@@ -28108,8 +28113,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="137">
+    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="135">
         <v>2</v>
       </c>
       <c r="C12" s="103">
@@ -28128,8 +28133,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="138"/>
+    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="136"/>
       <c r="C13" s="103">
         <v>3</v>
       </c>
@@ -28146,8 +28151,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="138"/>
+    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="136"/>
       <c r="C14" s="103">
         <v>3</v>
       </c>
@@ -28164,8 +28169,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="139"/>
+    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="137"/>
       <c r="C15" s="103">
         <v>5</v>
       </c>
@@ -28176,110 +28181,110 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B12:B15"/>

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED9087-4351-44B4-A672-5839C872CF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CAA4EC-FA86-4F18-8D43-183EBEE80B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="90">
   <si>
     <t>BACKEND</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Agregar libro por isbn</t>
+  </si>
+  <si>
+    <t>Libro service updated, post routes, controller and service implemented</t>
   </si>
 </sst>
 </file>
@@ -1701,18 +1704,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1745,6 +1736,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2469,7 +2472,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>79</c:v>
+                  <c:v>80.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>25.5</c:v>
@@ -4523,7 +4526,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>19.5</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.5</c:v>
@@ -9111,12 +9114,12 @@
       </c>
       <c r="H6" s="78">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="I6" s="40"/>
       <c r="J6" s="41">
         <f>SUM(D6:H6)</f>
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="K6" s="30"/>
     </row>
@@ -9330,12 +9333,12 @@
       </c>
       <c r="H16" s="28">
         <f>SUM(H6:H14)</f>
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="I16" s="33"/>
       <c r="J16" s="28">
         <f>SUM(D16:H16)</f>
-        <v>162</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9388,52 +9391,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -9461,7 +9464,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -9487,7 +9490,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -9513,7 +9516,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -9539,7 +9542,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -9567,7 +9570,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -9593,7 +9596,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -9619,7 +9622,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -9647,7 +9650,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -9673,7 +9676,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -9699,7 +9702,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -9725,7 +9728,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -9753,7 +9756,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -9779,7 +9782,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -9805,7 +9808,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -9831,7 +9834,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -9870,7 +9873,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -9898,7 +9901,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -9924,7 +9927,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -9950,7 +9953,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -9976,7 +9979,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -10002,7 +10005,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -10030,7 +10033,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -10056,7 +10059,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -10082,7 +10085,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -10108,7 +10111,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -10136,7 +10139,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -10162,7 +10165,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -10188,7 +10191,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -10216,7 +10219,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -10242,7 +10245,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -10268,7 +10271,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -10294,7 +10297,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -10322,7 +10325,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -10350,7 +10353,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -10376,7 +10379,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -10404,7 +10407,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -10430,7 +10433,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -10456,7 +10459,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -10482,7 +10485,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -10512,7 +10515,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -10538,7 +10541,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -10564,7 +10567,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -10590,7 +10593,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -10616,7 +10619,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -10642,7 +10645,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -10668,7 +10671,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -10707,7 +10710,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -10735,7 +10738,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -10761,7 +10764,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -10787,7 +10790,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -10813,7 +10816,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -10839,7 +10842,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -10865,7 +10868,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -10891,7 +10894,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -10917,7 +10920,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -10943,7 +10946,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -10969,7 +10972,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -10995,7 +10998,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -11021,7 +11024,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -11047,7 +11050,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -11073,7 +11076,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -11099,7 +11102,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -11129,7 +11132,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -11155,7 +11158,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -11181,7 +11184,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -11207,7 +11210,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -11233,7 +11236,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -11259,7 +11262,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -11285,7 +11288,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -11311,7 +11314,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -11337,7 +11340,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -11363,7 +11366,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -11389,7 +11392,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -11415,7 +11418,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -11441,7 +11444,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -11467,7 +11470,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -11507,7 +11510,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -11535,7 +11538,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -11561,7 +11564,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -11587,7 +11590,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -11613,7 +11616,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -11639,7 +11642,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -11665,7 +11668,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -11691,7 +11694,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -11717,7 +11720,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -11743,7 +11746,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -11769,7 +11772,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -11795,7 +11798,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -11821,7 +11824,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -11847,7 +11850,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -11873,7 +11876,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -11899,7 +11902,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -11925,7 +11928,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -11951,7 +11954,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -11977,7 +11980,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -12003,7 +12006,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -12029,7 +12032,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -12055,7 +12058,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -12081,7 +12084,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -12107,7 +12110,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -12133,7 +12136,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -12159,7 +12162,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -12185,7 +12188,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -12211,7 +12214,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -12237,7 +12240,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -12263,7 +12266,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -12289,7 +12292,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -12329,7 +12332,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -12357,7 +12360,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -12383,7 +12386,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -12409,7 +12412,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -12435,7 +12438,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -12461,7 +12464,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -12487,7 +12490,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -12513,7 +12516,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -12539,7 +12542,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -12565,7 +12568,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -12591,7 +12594,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -12617,7 +12620,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -12643,7 +12646,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -12669,7 +12672,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -12695,7 +12698,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -12721,7 +12724,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -12747,7 +12750,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -12773,7 +12776,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -12799,7 +12802,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -12825,7 +12828,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -12851,7 +12854,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -12877,7 +12880,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -12904,17 +12907,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
@@ -13003,52 +13006,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -13080,7 +13083,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -13110,7 +13113,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -13140,7 +13143,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -13170,7 +13173,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -13202,7 +13205,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -13232,7 +13235,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -13262,7 +13265,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -13294,7 +13297,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -13324,7 +13327,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -13354,7 +13357,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -13384,7 +13387,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -13416,7 +13419,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -13446,7 +13449,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -13476,7 +13479,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -13506,7 +13509,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -13553,7 +13556,7 @@
       <c r="S21" s="116"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -13585,7 +13588,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -13615,7 +13618,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -13645,7 +13648,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -13675,7 +13678,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -13705,7 +13708,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -13737,7 +13740,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -13767,7 +13770,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -13797,7 +13800,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -13827,7 +13830,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -13859,7 +13862,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -13889,7 +13892,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -13919,7 +13922,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -13951,7 +13954,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -13981,7 +13984,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -14011,7 +14014,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -14041,7 +14044,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -14073,7 +14076,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -14105,7 +14108,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -14135,7 +14138,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -14167,7 +14170,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -14197,7 +14200,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -14227,7 +14230,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -14257,7 +14260,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -14291,7 +14294,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -14321,7 +14324,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -14351,7 +14354,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -14381,7 +14384,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -14411,7 +14414,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -14441,7 +14444,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -14471,7 +14474,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -14518,7 +14521,7 @@
       <c r="S53" s="116"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -14550,7 +14553,7 @@
       <c r="S54" s="74"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -14580,7 +14583,7 @@
       <c r="S55" s="74"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -14610,7 +14613,7 @@
       <c r="S56" s="74"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -14640,7 +14643,7 @@
       <c r="S57" s="74"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -14670,7 +14673,7 @@
       <c r="S58" s="74"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -14700,7 +14703,7 @@
       <c r="S59" s="74"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -14730,7 +14733,7 @@
       <c r="S60" s="74"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -14760,7 +14763,7 @@
       <c r="S61" s="74"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -14790,7 +14793,7 @@
       <c r="S62" s="74"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -14820,7 +14823,7 @@
       <c r="S63" s="74"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -14850,7 +14853,7 @@
       <c r="S64" s="74"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -14880,7 +14883,7 @@
       <c r="S65" s="74"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -14910,7 +14913,7 @@
       <c r="S66" s="74"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -14940,7 +14943,7 @@
       <c r="S67" s="74"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -14970,7 +14973,7 @@
       <c r="S68" s="74"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -15004,7 +15007,7 @@
       <c r="S69" s="74"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -15034,7 +15037,7 @@
       <c r="S70" s="74"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -15064,7 +15067,7 @@
       <c r="S71" s="74"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -15094,7 +15097,7 @@
       <c r="S72" s="74"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -15124,7 +15127,7 @@
       <c r="S73" s="74"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -15154,7 +15157,7 @@
       <c r="S74" s="74"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -15184,7 +15187,7 @@
       <c r="S75" s="74"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -15214,7 +15217,7 @@
       <c r="S76" s="74"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -15244,7 +15247,7 @@
       <c r="S77" s="74"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -15274,7 +15277,7 @@
       <c r="S78" s="74"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -15304,7 +15307,7 @@
       <c r="S79" s="74"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -15334,7 +15337,7 @@
       <c r="S80" s="74"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -15364,7 +15367,7 @@
       <c r="S81" s="74"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -15394,7 +15397,7 @@
       <c r="S82" s="74"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -15442,7 +15445,7 @@
       <c r="S84" s="116"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -15474,7 +15477,7 @@
       <c r="S85" s="74"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -15504,7 +15507,7 @@
       <c r="S86" s="74"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -15534,7 +15537,7 @@
       <c r="S87" s="74"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -15564,7 +15567,7 @@
       <c r="S88" s="74"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -15594,7 +15597,7 @@
       <c r="S89" s="74"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -15624,7 +15627,7 @@
       <c r="S90" s="74"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -15654,7 +15657,7 @@
       <c r="S91" s="74"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -15684,7 +15687,7 @@
       <c r="S92" s="74"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -15714,7 +15717,7 @@
       <c r="S93" s="74"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -15744,7 +15747,7 @@
       <c r="S94" s="74"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -15774,7 +15777,7 @@
       <c r="S95" s="74"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -15804,7 +15807,7 @@
       <c r="S96" s="74"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -15834,7 +15837,7 @@
       <c r="S97" s="74"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -15864,7 +15867,7 @@
       <c r="S98" s="74"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -15894,7 +15897,7 @@
       <c r="S99" s="74"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -15924,7 +15927,7 @@
       <c r="S100" s="74"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -15954,7 +15957,7 @@
       <c r="S101" s="74"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -15984,7 +15987,7 @@
       <c r="S102" s="74"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -16014,7 +16017,7 @@
       <c r="S103" s="74"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -16044,7 +16047,7 @@
       <c r="S104" s="74"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -16074,7 +16077,7 @@
       <c r="S105" s="74"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -16104,7 +16107,7 @@
       <c r="S106" s="74"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -16134,7 +16137,7 @@
       <c r="S107" s="74"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -16164,7 +16167,7 @@
       <c r="S108" s="74"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -16194,7 +16197,7 @@
       <c r="S109" s="74"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -16224,7 +16227,7 @@
       <c r="S110" s="74"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -16254,7 +16257,7 @@
       <c r="S111" s="74"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -16284,7 +16287,7 @@
       <c r="S112" s="74"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -16314,7 +16317,7 @@
       <c r="S113" s="74"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -16344,7 +16347,7 @@
       <c r="S114" s="74"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -16392,7 +16395,7 @@
       <c r="S116" s="116"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -16424,7 +16427,7 @@
       <c r="S117" s="74"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -16454,7 +16457,7 @@
       <c r="S118" s="74"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -16484,7 +16487,7 @@
       <c r="S119" s="74"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -16514,7 +16517,7 @@
       <c r="S120" s="74"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -16544,7 +16547,7 @@
       <c r="S121" s="74"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -16574,7 +16577,7 @@
       <c r="S122" s="74"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -16604,7 +16607,7 @@
       <c r="S123" s="74"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -16634,7 +16637,7 @@
       <c r="S124" s="74"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -16664,7 +16667,7 @@
       <c r="S125" s="74"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -16694,7 +16697,7 @@
       <c r="S126" s="74"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -16724,7 +16727,7 @@
       <c r="S127" s="74"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -16754,7 +16757,7 @@
       <c r="S128" s="74"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -16784,7 +16787,7 @@
       <c r="S129" s="74"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -16814,7 +16817,7 @@
       <c r="S130" s="74"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -16844,7 +16847,7 @@
       <c r="S131" s="74"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -16874,7 +16877,7 @@
       <c r="S132" s="74"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -16904,7 +16907,7 @@
       <c r="S133" s="74"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -16934,7 +16937,7 @@
       <c r="S134" s="74"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -16964,7 +16967,7 @@
       <c r="S135" s="74"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -16994,7 +16997,7 @@
       <c r="S136" s="74"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -17024,7 +17027,7 @@
       <c r="S137" s="74"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -17055,17 +17058,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
@@ -17154,52 +17157,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -17227,7 +17230,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -17253,7 +17256,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -17279,7 +17282,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -17305,7 +17308,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -17333,7 +17336,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -17359,7 +17362,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -17385,7 +17388,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -17413,7 +17416,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -17439,7 +17442,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -17465,7 +17468,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -17491,7 +17494,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -17519,7 +17522,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -17545,7 +17548,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -17571,7 +17574,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -17597,7 +17600,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -17636,7 +17639,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -17664,7 +17667,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -17690,7 +17693,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -17716,7 +17719,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -17742,7 +17745,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -17768,7 +17771,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -17796,7 +17799,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -17822,7 +17825,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -17848,7 +17851,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -17874,7 +17877,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -17902,7 +17905,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -17928,7 +17931,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -17954,7 +17957,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -17982,7 +17985,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -18008,7 +18011,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -18034,7 +18037,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -18060,7 +18063,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -18090,7 +18093,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -18116,7 +18119,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -18142,7 +18145,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -18170,7 +18173,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -18196,7 +18199,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -18222,7 +18225,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -18248,7 +18251,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -18278,7 +18281,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -18304,7 +18307,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -18330,7 +18333,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -18356,7 +18359,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -18382,7 +18385,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -18408,7 +18411,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -18434,7 +18437,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -18473,7 +18476,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -18501,7 +18504,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -18527,7 +18530,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -18553,7 +18556,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -18579,7 +18582,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -18605,7 +18608,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -18631,7 +18634,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -18657,7 +18660,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -18683,7 +18686,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -18709,7 +18712,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -18735,7 +18738,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -18761,7 +18764,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -18787,7 +18790,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -18813,7 +18816,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -18839,7 +18842,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -18869,7 +18872,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -18895,7 +18898,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -18921,7 +18924,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -18947,7 +18950,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -18973,7 +18976,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -18999,7 +19002,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -19025,7 +19028,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -19051,7 +19054,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -19077,7 +19080,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -19103,7 +19106,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -19129,7 +19132,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -19155,7 +19158,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -19181,7 +19184,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -19207,7 +19210,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -19233,7 +19236,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -19273,7 +19276,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -19301,7 +19304,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -19327,7 +19330,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -19353,7 +19356,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -19379,7 +19382,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -19405,7 +19408,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -19431,7 +19434,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -19457,7 +19460,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -19483,7 +19486,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -19509,7 +19512,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -19535,7 +19538,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -19561,7 +19564,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -19587,7 +19590,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -19613,7 +19616,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -19639,7 +19642,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -19665,7 +19668,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -19691,7 +19694,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -19717,7 +19720,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -19743,7 +19746,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -19769,7 +19772,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -19795,7 +19798,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -19821,7 +19824,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -19847,7 +19850,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -19873,7 +19876,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -19899,7 +19902,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -19925,7 +19928,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -19951,7 +19954,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -19977,7 +19980,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -20003,7 +20006,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -20029,7 +20032,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -20055,7 +20058,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -20095,7 +20098,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -20123,7 +20126,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -20149,7 +20152,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -20175,7 +20178,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -20201,7 +20204,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -20227,7 +20230,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -20253,7 +20256,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -20279,7 +20282,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -20305,7 +20308,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -20331,7 +20334,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -20357,7 +20360,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -20383,7 +20386,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -20409,7 +20412,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -20435,7 +20438,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -20461,7 +20464,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -20487,7 +20490,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -20513,7 +20516,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -20539,7 +20542,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -20565,7 +20568,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -20591,7 +20594,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -20617,7 +20620,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -20643,7 +20646,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -20670,17 +20673,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
@@ -20769,52 +20772,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -20842,7 +20845,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -20868,7 +20871,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -20894,7 +20897,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -20920,7 +20923,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -20948,7 +20951,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -20974,7 +20977,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -21000,7 +21003,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -21028,7 +21031,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -21054,7 +21057,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -21080,7 +21083,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -21106,7 +21109,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -21134,7 +21137,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -21160,7 +21163,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -21186,7 +21189,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -21212,7 +21215,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -21251,7 +21254,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -21279,7 +21282,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -21305,7 +21308,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -21331,7 +21334,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -21357,7 +21360,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -21383,7 +21386,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -21411,7 +21414,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -21437,7 +21440,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -21463,7 +21466,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -21489,7 +21492,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -21517,7 +21520,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -21543,7 +21546,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -21569,7 +21572,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -21597,7 +21600,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -21623,7 +21626,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -21649,7 +21652,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -21679,7 +21682,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -21707,7 +21710,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -21733,7 +21736,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -21761,7 +21764,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -21789,7 +21792,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -21815,7 +21818,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -21841,7 +21844,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -21867,7 +21870,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -21897,7 +21900,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -21923,7 +21926,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -21949,7 +21952,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -21975,7 +21978,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -22001,7 +22004,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -22027,7 +22030,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -22053,7 +22056,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -22092,7 +22095,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -22120,7 +22123,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -22146,7 +22149,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -22172,7 +22175,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -22198,7 +22201,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -22224,7 +22227,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -22250,7 +22253,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -22276,7 +22279,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -22302,7 +22305,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -22328,7 +22331,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -22354,7 +22357,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -22380,7 +22383,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -22406,7 +22409,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -22432,7 +22435,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -22458,7 +22461,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -22484,7 +22487,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -22510,7 +22513,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -22536,7 +22539,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -22562,7 +22565,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -22588,7 +22591,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -22614,7 +22617,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -22640,7 +22643,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -22666,7 +22669,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -22692,7 +22695,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -22718,7 +22721,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -22744,7 +22747,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -22770,7 +22773,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -22796,7 +22799,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -22822,7 +22825,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -22848,7 +22851,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -22888,7 +22891,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -22916,7 +22919,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -22942,7 +22945,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -22968,7 +22971,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -22994,7 +22997,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -23020,7 +23023,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -23046,7 +23049,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -23072,7 +23075,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -23098,7 +23101,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -23124,7 +23127,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -23150,7 +23153,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -23176,7 +23179,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -23202,7 +23205,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -23228,7 +23231,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -23254,7 +23257,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -23280,7 +23283,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -23306,7 +23309,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -23332,7 +23335,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -23358,7 +23361,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -23384,7 +23387,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -23410,7 +23413,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -23436,7 +23439,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -23462,7 +23465,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -23488,7 +23491,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -23514,7 +23517,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -23540,7 +23543,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -23566,7 +23569,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -23592,7 +23595,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -23618,7 +23621,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -23644,7 +23647,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -23670,7 +23673,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -23710,7 +23713,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -23738,7 +23741,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -23764,7 +23767,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -23790,7 +23793,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -23816,7 +23819,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -23842,7 +23845,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -23868,7 +23871,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -23894,7 +23897,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -23920,7 +23923,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -23946,7 +23949,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -23972,7 +23975,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -23998,7 +24001,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -24024,7 +24027,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -24050,7 +24053,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -24076,7 +24079,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -24102,7 +24105,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -24128,7 +24131,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -24154,7 +24157,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -24180,7 +24183,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -24206,7 +24209,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -24232,7 +24235,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -24258,7 +24261,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -24385,52 +24388,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -24458,7 +24461,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -24484,7 +24487,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -24510,7 +24513,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -24536,7 +24539,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -24564,7 +24567,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -24590,7 +24593,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -24616,7 +24619,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -24644,7 +24647,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -24670,7 +24673,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -24696,7 +24699,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -24722,7 +24725,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -24750,7 +24753,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -24776,7 +24779,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -24802,7 +24805,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -24828,7 +24831,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -24867,7 +24870,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -24895,7 +24898,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -24921,7 +24924,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -24947,7 +24950,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -24973,7 +24976,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -24999,7 +25002,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -25027,7 +25030,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -25053,7 +25056,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -25079,7 +25082,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -25105,7 +25108,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -25133,7 +25136,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -25159,7 +25162,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -25185,7 +25188,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -25213,7 +25216,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -25239,7 +25242,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -25265,7 +25268,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -25291,7 +25294,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -25319,7 +25322,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -25347,7 +25350,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -25377,7 +25380,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -25405,7 +25408,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -25431,7 +25434,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -25457,7 +25460,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -25483,7 +25486,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -25513,7 +25516,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -25539,7 +25542,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -25565,7 +25568,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -25591,7 +25594,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -25617,7 +25620,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -25643,7 +25646,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -25669,7 +25672,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -25708,7 +25711,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -25736,7 +25739,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -25762,7 +25765,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -25788,7 +25791,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -25816,7 +25819,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -25844,7 +25847,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -25870,7 +25873,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -25896,7 +25899,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -25922,7 +25925,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -25948,7 +25951,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -25974,7 +25977,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -26000,7 +26003,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -26026,7 +26029,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -26052,7 +26055,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -26078,7 +26081,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -26104,7 +26107,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -26134,7 +26137,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -26160,7 +26163,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -26186,14 +26189,16 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
       <c r="F72" s="91">
-        <v>0</v>
-      </c>
-      <c r="G72" s="67"/>
+        <v>1.5</v>
+      </c>
+      <c r="G72" s="67" t="s">
+        <v>89</v>
+      </c>
       <c r="I72" s="92">
         <v>0</v>
       </c>
@@ -26212,7 +26217,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -26238,7 +26243,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -26264,7 +26269,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -26290,7 +26295,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -26316,7 +26321,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -26342,7 +26347,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -26368,7 +26373,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -26394,7 +26399,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -26420,7 +26425,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -26446,7 +26451,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -26472,7 +26477,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -26512,7 +26517,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -26540,7 +26545,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -26566,7 +26571,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -26592,7 +26597,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -26618,7 +26623,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -26644,7 +26649,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -26670,7 +26675,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -26696,7 +26701,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -26722,7 +26727,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -26748,7 +26753,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -26774,7 +26779,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -26800,7 +26805,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -26826,7 +26831,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -26852,7 +26857,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -26878,7 +26883,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -26904,7 +26909,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -26930,7 +26935,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -26956,7 +26961,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -26982,7 +26987,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -27008,7 +27013,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -27034,7 +27039,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -27060,7 +27065,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -27086,7 +27091,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -27112,7 +27117,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -27138,7 +27143,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -27164,7 +27169,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -27190,7 +27195,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -27216,7 +27221,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -27242,7 +27247,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -27268,7 +27273,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -27294,7 +27299,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -27334,7 +27339,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -27362,7 +27367,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -27388,7 +27393,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -27414,7 +27419,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -27440,7 +27445,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -27466,7 +27471,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -27492,7 +27497,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -27518,7 +27523,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -27544,7 +27549,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -27570,7 +27575,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -27596,7 +27601,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -27622,7 +27627,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -27648,7 +27653,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -27674,7 +27679,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -27700,7 +27705,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -27726,7 +27731,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -27752,7 +27757,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -27778,7 +27783,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -27804,7 +27809,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -27830,7 +27835,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -27856,7 +27861,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -27882,7 +27887,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -27909,17 +27914,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CAA4EC-FA86-4F18-8D43-183EBEE80B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C95C014-ED4F-472B-9B57-5F33BD01DA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>BACKEND</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>Libro service updated, post routes, controller and service implemented</t>
+  </si>
+  <si>
+    <t>devops</t>
   </si>
 </sst>
 </file>
@@ -1704,6 +1707,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1736,18 +1751,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2484,7 +2487,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4538,7 +4541,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9290,12 +9293,12 @@
       </c>
       <c r="H14" s="90">
         <f>SUM(WENJIE!R5:R138)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I14" s="59"/>
       <c r="J14" s="60">
         <f>SUM(D14:H14)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K14" s="30"/>
     </row>
@@ -9333,12 +9336,12 @@
       </c>
       <c r="H16" s="28">
         <f>SUM(H6:H14)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I16" s="33"/>
       <c r="J16" s="28">
         <f>SUM(D16:H16)</f>
-        <v>163.5</v>
+        <v>167.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9391,52 +9394,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="F2" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="127"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="L2" s="129" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="130"/>
-      <c r="R2" s="120" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -9464,7 +9467,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
+      <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -9490,7 +9493,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="132"/>
+      <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -9516,7 +9519,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
+      <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -9542,7 +9545,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
+      <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -9570,7 +9573,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="132"/>
+      <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -9596,7 +9599,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="132"/>
+      <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -9622,7 +9625,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="132"/>
+      <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -9650,7 +9653,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="132"/>
+      <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -9676,7 +9679,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
+      <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -9702,7 +9705,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="132"/>
+      <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -9728,7 +9731,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="132"/>
+      <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -9756,7 +9759,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="132"/>
+      <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -9782,7 +9785,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="132"/>
+      <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -9808,7 +9811,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="132"/>
+      <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -9834,7 +9837,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="133"/>
+      <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -9873,7 +9876,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -9901,7 +9904,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="134"/>
+      <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -9927,7 +9930,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="134"/>
+      <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -9953,7 +9956,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="134"/>
+      <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -9979,7 +9982,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="134"/>
+      <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -10005,7 +10008,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="134"/>
+      <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -10033,7 +10036,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="134"/>
+      <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -10059,7 +10062,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="134"/>
+      <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -10085,7 +10088,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134"/>
+      <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -10111,7 +10114,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="134"/>
+      <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -10139,7 +10142,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="134"/>
+      <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -10165,7 +10168,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="134"/>
+      <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -10191,7 +10194,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134"/>
+      <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -10219,7 +10222,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134"/>
+      <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -10245,7 +10248,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="134"/>
+      <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -10271,7 +10274,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="134"/>
+      <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -10297,7 +10300,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="134"/>
+      <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -10325,7 +10328,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="134"/>
+      <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -10353,7 +10356,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="134"/>
+      <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -10379,7 +10382,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="134"/>
+      <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -10407,7 +10410,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="134"/>
+      <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -10433,7 +10436,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="134"/>
+      <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -10459,7 +10462,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="134"/>
+      <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -10485,7 +10488,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="134"/>
+      <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -10515,7 +10518,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="134"/>
+      <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -10541,7 +10544,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="134"/>
+      <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -10567,7 +10570,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="134"/>
+      <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -10593,7 +10596,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="134"/>
+      <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -10619,7 +10622,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="134"/>
+      <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -10645,7 +10648,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="134"/>
+      <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -10671,7 +10674,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="134"/>
+      <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -10710,7 +10713,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -10738,7 +10741,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="134"/>
+      <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -10764,7 +10767,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="134"/>
+      <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -10790,7 +10793,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="134"/>
+      <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -10816,7 +10819,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="134"/>
+      <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -10842,7 +10845,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="134"/>
+      <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -10868,7 +10871,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="134"/>
+      <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -10894,7 +10897,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="134"/>
+      <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -10920,7 +10923,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="134"/>
+      <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -10946,7 +10949,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="134"/>
+      <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -10972,7 +10975,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="134"/>
+      <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -10998,7 +11001,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="134"/>
+      <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -11024,7 +11027,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="134"/>
+      <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -11050,7 +11053,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="134"/>
+      <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -11076,7 +11079,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="134"/>
+      <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -11102,7 +11105,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="134"/>
+      <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -11132,7 +11135,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="134"/>
+      <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -11158,7 +11161,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="134"/>
+      <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -11184,7 +11187,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="134"/>
+      <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -11210,7 +11213,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="134"/>
+      <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -11236,7 +11239,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="134"/>
+      <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -11262,7 +11265,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="134"/>
+      <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -11288,7 +11291,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="134"/>
+      <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -11314,7 +11317,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="134"/>
+      <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -11340,7 +11343,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="134"/>
+      <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -11366,7 +11369,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="134"/>
+      <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -11392,7 +11395,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="134"/>
+      <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -11418,7 +11421,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="134"/>
+      <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -11444,7 +11447,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="134"/>
+      <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -11470,7 +11473,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="134"/>
+      <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -11510,7 +11513,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -11538,7 +11541,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="134"/>
+      <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -11564,7 +11567,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="134"/>
+      <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -11590,7 +11593,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="134"/>
+      <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -11616,7 +11619,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="134"/>
+      <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -11642,7 +11645,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="134"/>
+      <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -11668,7 +11671,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="134"/>
+      <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -11694,7 +11697,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="134"/>
+      <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -11720,7 +11723,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="134"/>
+      <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -11746,7 +11749,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="134"/>
+      <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -11772,7 +11775,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="134"/>
+      <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -11798,7 +11801,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="134"/>
+      <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -11824,7 +11827,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="134"/>
+      <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -11850,7 +11853,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="134"/>
+      <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -11876,7 +11879,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="134"/>
+      <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -11902,7 +11905,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="134"/>
+      <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -11928,7 +11931,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="134"/>
+      <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -11954,7 +11957,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="134"/>
+      <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -11980,7 +11983,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="134"/>
+      <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -12006,7 +12009,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="134"/>
+      <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -12032,7 +12035,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="134"/>
+      <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -12058,7 +12061,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="134"/>
+      <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -12084,7 +12087,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="134"/>
+      <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -12110,7 +12113,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="134"/>
+      <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -12136,7 +12139,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="134"/>
+      <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -12162,7 +12165,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="134"/>
+      <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -12188,7 +12191,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="134"/>
+      <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -12214,7 +12217,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="134"/>
+      <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -12240,7 +12243,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="134"/>
+      <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -12266,7 +12269,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="134"/>
+      <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -12292,7 +12295,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="134"/>
+      <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -12332,7 +12335,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="131" t="s">
+      <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -12360,7 +12363,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="132"/>
+      <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -12386,7 +12389,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="132"/>
+      <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -12412,7 +12415,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="132"/>
+      <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -12438,7 +12441,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="132"/>
+      <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -12464,7 +12467,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="132"/>
+      <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -12490,7 +12493,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="132"/>
+      <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -12516,7 +12519,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="132"/>
+      <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -12542,7 +12545,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="132"/>
+      <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -12568,7 +12571,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="132"/>
+      <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -12594,7 +12597,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="132"/>
+      <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -12620,7 +12623,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="132"/>
+      <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -12646,7 +12649,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="132"/>
+      <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -12672,7 +12675,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="132"/>
+      <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -12698,7 +12701,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="132"/>
+      <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -12724,7 +12727,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="132"/>
+      <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -12750,7 +12753,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="132"/>
+      <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -12776,7 +12779,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="132"/>
+      <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -12802,7 +12805,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="132"/>
+      <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -12828,7 +12831,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="132"/>
+      <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -12854,7 +12857,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="132"/>
+      <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -12880,7 +12883,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="133"/>
+      <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -12907,17 +12910,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
@@ -13006,52 +13009,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="F2" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="127"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="L2" s="129" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="130"/>
-      <c r="R2" s="120" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -13083,7 +13086,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
+      <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -13113,7 +13116,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="132"/>
+      <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -13143,7 +13146,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
+      <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -13173,7 +13176,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
+      <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -13205,7 +13208,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="132"/>
+      <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -13235,7 +13238,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="132"/>
+      <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -13265,7 +13268,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="132"/>
+      <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -13297,7 +13300,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="132"/>
+      <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -13327,7 +13330,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
+      <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -13357,7 +13360,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="132"/>
+      <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -13387,7 +13390,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="132"/>
+      <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -13419,7 +13422,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="132"/>
+      <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -13449,7 +13452,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="132"/>
+      <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -13479,7 +13482,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="132"/>
+      <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -13509,7 +13512,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="133"/>
+      <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -13556,7 +13559,7 @@
       <c r="S21" s="116"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -13588,7 +13591,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="134"/>
+      <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -13618,7 +13621,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="134"/>
+      <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -13648,7 +13651,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="134"/>
+      <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -13678,7 +13681,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="134"/>
+      <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -13708,7 +13711,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="134"/>
+      <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -13740,7 +13743,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="134"/>
+      <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -13770,7 +13773,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="134"/>
+      <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -13800,7 +13803,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134"/>
+      <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -13830,7 +13833,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="134"/>
+      <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -13862,7 +13865,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="134"/>
+      <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -13892,7 +13895,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="134"/>
+      <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -13922,7 +13925,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134"/>
+      <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -13954,7 +13957,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134"/>
+      <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -13984,7 +13987,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="134"/>
+      <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -14014,7 +14017,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="134"/>
+      <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -14044,7 +14047,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="134"/>
+      <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -14076,7 +14079,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="134"/>
+      <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -14108,7 +14111,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="134"/>
+      <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -14138,7 +14141,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="134"/>
+      <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -14170,7 +14173,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="134"/>
+      <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -14200,7 +14203,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="134"/>
+      <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -14230,7 +14233,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="134"/>
+      <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -14260,7 +14263,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="134"/>
+      <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -14294,7 +14297,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="134"/>
+      <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -14324,7 +14327,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="134"/>
+      <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -14354,7 +14357,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="134"/>
+      <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -14384,7 +14387,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="134"/>
+      <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -14414,7 +14417,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="134"/>
+      <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -14444,7 +14447,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="134"/>
+      <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -14474,7 +14477,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="134"/>
+      <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -14521,7 +14524,7 @@
       <c r="S53" s="116"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -14553,7 +14556,7 @@
       <c r="S54" s="74"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="134"/>
+      <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -14583,7 +14586,7 @@
       <c r="S55" s="74"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="134"/>
+      <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -14613,7 +14616,7 @@
       <c r="S56" s="74"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="134"/>
+      <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -14643,7 +14646,7 @@
       <c r="S57" s="74"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="134"/>
+      <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -14673,7 +14676,7 @@
       <c r="S58" s="74"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="134"/>
+      <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -14703,7 +14706,7 @@
       <c r="S59" s="74"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="134"/>
+      <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -14733,7 +14736,7 @@
       <c r="S60" s="74"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="134"/>
+      <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -14763,7 +14766,7 @@
       <c r="S61" s="74"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="134"/>
+      <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -14793,7 +14796,7 @@
       <c r="S62" s="74"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="134"/>
+      <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -14823,7 +14826,7 @@
       <c r="S63" s="74"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="134"/>
+      <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -14853,7 +14856,7 @@
       <c r="S64" s="74"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="134"/>
+      <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -14883,7 +14886,7 @@
       <c r="S65" s="74"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="134"/>
+      <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -14913,7 +14916,7 @@
       <c r="S66" s="74"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="134"/>
+      <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -14943,7 +14946,7 @@
       <c r="S67" s="74"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="134"/>
+      <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -14973,7 +14976,7 @@
       <c r="S68" s="74"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="134"/>
+      <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -15007,7 +15010,7 @@
       <c r="S69" s="74"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="134"/>
+      <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -15037,7 +15040,7 @@
       <c r="S70" s="74"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="134"/>
+      <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -15067,7 +15070,7 @@
       <c r="S71" s="74"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="134"/>
+      <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -15097,7 +15100,7 @@
       <c r="S72" s="74"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="134"/>
+      <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -15127,7 +15130,7 @@
       <c r="S73" s="74"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="134"/>
+      <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -15157,7 +15160,7 @@
       <c r="S74" s="74"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="134"/>
+      <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -15187,7 +15190,7 @@
       <c r="S75" s="74"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="134"/>
+      <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -15217,7 +15220,7 @@
       <c r="S76" s="74"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="134"/>
+      <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -15247,7 +15250,7 @@
       <c r="S77" s="74"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="134"/>
+      <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -15277,7 +15280,7 @@
       <c r="S78" s="74"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="134"/>
+      <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -15307,7 +15310,7 @@
       <c r="S79" s="74"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="134"/>
+      <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -15337,7 +15340,7 @@
       <c r="S80" s="74"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="134"/>
+      <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -15367,7 +15370,7 @@
       <c r="S81" s="74"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="134"/>
+      <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -15397,7 +15400,7 @@
       <c r="S82" s="74"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="134"/>
+      <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -15445,7 +15448,7 @@
       <c r="S84" s="116"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -15477,7 +15480,7 @@
       <c r="S85" s="74"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="134"/>
+      <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -15507,7 +15510,7 @@
       <c r="S86" s="74"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="134"/>
+      <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -15537,7 +15540,7 @@
       <c r="S87" s="74"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="134"/>
+      <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -15567,7 +15570,7 @@
       <c r="S88" s="74"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="134"/>
+      <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -15597,7 +15600,7 @@
       <c r="S89" s="74"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="134"/>
+      <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -15627,7 +15630,7 @@
       <c r="S90" s="74"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="134"/>
+      <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -15657,7 +15660,7 @@
       <c r="S91" s="74"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="134"/>
+      <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -15687,7 +15690,7 @@
       <c r="S92" s="74"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="134"/>
+      <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -15717,7 +15720,7 @@
       <c r="S93" s="74"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="134"/>
+      <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -15747,7 +15750,7 @@
       <c r="S94" s="74"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="134"/>
+      <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -15777,7 +15780,7 @@
       <c r="S95" s="74"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="134"/>
+      <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -15807,7 +15810,7 @@
       <c r="S96" s="74"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="134"/>
+      <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -15837,7 +15840,7 @@
       <c r="S97" s="74"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="134"/>
+      <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -15867,7 +15870,7 @@
       <c r="S98" s="74"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="134"/>
+      <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -15897,7 +15900,7 @@
       <c r="S99" s="74"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="134"/>
+      <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -15927,7 +15930,7 @@
       <c r="S100" s="74"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="134"/>
+      <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -15957,7 +15960,7 @@
       <c r="S101" s="74"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="134"/>
+      <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -15987,7 +15990,7 @@
       <c r="S102" s="74"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="134"/>
+      <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -16017,7 +16020,7 @@
       <c r="S103" s="74"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="134"/>
+      <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -16047,7 +16050,7 @@
       <c r="S104" s="74"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="134"/>
+      <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -16077,7 +16080,7 @@
       <c r="S105" s="74"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="134"/>
+      <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -16107,7 +16110,7 @@
       <c r="S106" s="74"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="134"/>
+      <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -16137,7 +16140,7 @@
       <c r="S107" s="74"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="134"/>
+      <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -16167,7 +16170,7 @@
       <c r="S108" s="74"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="134"/>
+      <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -16197,7 +16200,7 @@
       <c r="S109" s="74"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="134"/>
+      <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -16227,7 +16230,7 @@
       <c r="S110" s="74"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="134"/>
+      <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -16257,7 +16260,7 @@
       <c r="S111" s="74"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="134"/>
+      <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -16287,7 +16290,7 @@
       <c r="S112" s="74"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="134"/>
+      <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -16317,7 +16320,7 @@
       <c r="S113" s="74"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="134"/>
+      <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -16347,7 +16350,7 @@
       <c r="S114" s="74"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="134"/>
+      <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -16395,7 +16398,7 @@
       <c r="S116" s="116"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="131" t="s">
+      <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -16427,7 +16430,7 @@
       <c r="S117" s="74"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="132"/>
+      <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -16457,7 +16460,7 @@
       <c r="S118" s="74"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="132"/>
+      <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -16487,7 +16490,7 @@
       <c r="S119" s="74"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="132"/>
+      <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -16517,7 +16520,7 @@
       <c r="S120" s="74"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="132"/>
+      <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -16547,7 +16550,7 @@
       <c r="S121" s="74"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="132"/>
+      <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -16577,7 +16580,7 @@
       <c r="S122" s="74"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="132"/>
+      <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -16607,7 +16610,7 @@
       <c r="S123" s="74"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="132"/>
+      <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -16637,7 +16640,7 @@
       <c r="S124" s="74"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="132"/>
+      <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -16667,7 +16670,7 @@
       <c r="S125" s="74"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="132"/>
+      <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -16697,7 +16700,7 @@
       <c r="S126" s="74"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="132"/>
+      <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -16727,7 +16730,7 @@
       <c r="S127" s="74"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="132"/>
+      <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -16757,7 +16760,7 @@
       <c r="S128" s="74"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="132"/>
+      <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -16787,7 +16790,7 @@
       <c r="S129" s="74"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="132"/>
+      <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -16817,7 +16820,7 @@
       <c r="S130" s="74"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="132"/>
+      <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -16847,7 +16850,7 @@
       <c r="S131" s="74"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="132"/>
+      <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -16877,7 +16880,7 @@
       <c r="S132" s="74"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="132"/>
+      <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -16907,7 +16910,7 @@
       <c r="S133" s="74"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="132"/>
+      <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -16937,7 +16940,7 @@
       <c r="S134" s="74"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="132"/>
+      <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -16967,7 +16970,7 @@
       <c r="S135" s="74"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="132"/>
+      <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -16997,7 +17000,7 @@
       <c r="S136" s="74"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="132"/>
+      <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -17027,7 +17030,7 @@
       <c r="S137" s="74"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="133"/>
+      <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -17058,17 +17061,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
@@ -17157,52 +17160,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="F2" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="127"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="L2" s="129" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="130"/>
-      <c r="R2" s="120" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -17230,7 +17233,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
+      <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -17256,7 +17259,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="132"/>
+      <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -17282,7 +17285,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
+      <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -17308,7 +17311,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
+      <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -17336,7 +17339,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="132"/>
+      <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -17362,7 +17365,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="132"/>
+      <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -17388,7 +17391,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="132"/>
+      <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -17416,7 +17419,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="132"/>
+      <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -17442,7 +17445,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
+      <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -17468,7 +17471,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="132"/>
+      <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -17494,7 +17497,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="132"/>
+      <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -17522,7 +17525,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="132"/>
+      <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -17548,7 +17551,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="132"/>
+      <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -17574,7 +17577,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="132"/>
+      <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -17600,7 +17603,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="133"/>
+      <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -17639,7 +17642,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -17667,7 +17670,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="134"/>
+      <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -17693,7 +17696,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="134"/>
+      <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -17719,7 +17722,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="134"/>
+      <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -17745,7 +17748,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="134"/>
+      <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -17771,7 +17774,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="134"/>
+      <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -17799,7 +17802,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="134"/>
+      <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -17825,7 +17828,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="134"/>
+      <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -17851,7 +17854,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134"/>
+      <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -17877,7 +17880,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="134"/>
+      <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -17905,7 +17908,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="134"/>
+      <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -17931,7 +17934,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="134"/>
+      <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -17957,7 +17960,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134"/>
+      <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -17985,7 +17988,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134"/>
+      <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -18011,7 +18014,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="134"/>
+      <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -18037,7 +18040,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="134"/>
+      <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -18063,7 +18066,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="134"/>
+      <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -18093,7 +18096,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="134"/>
+      <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -18119,7 +18122,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="134"/>
+      <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -18145,7 +18148,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="134"/>
+      <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -18173,7 +18176,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="134"/>
+      <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -18199,7 +18202,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="134"/>
+      <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -18225,7 +18228,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="134"/>
+      <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -18251,7 +18254,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="134"/>
+      <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -18281,7 +18284,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="134"/>
+      <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -18307,7 +18310,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="134"/>
+      <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -18333,7 +18336,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="134"/>
+      <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -18359,7 +18362,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="134"/>
+      <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -18385,7 +18388,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="134"/>
+      <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -18411,7 +18414,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="134"/>
+      <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -18437,7 +18440,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="134"/>
+      <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -18476,7 +18479,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -18504,7 +18507,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="134"/>
+      <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -18530,7 +18533,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="134"/>
+      <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -18556,7 +18559,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="134"/>
+      <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -18582,7 +18585,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="134"/>
+      <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -18608,7 +18611,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="134"/>
+      <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -18634,7 +18637,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="134"/>
+      <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -18660,7 +18663,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="134"/>
+      <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -18686,7 +18689,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="134"/>
+      <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -18712,7 +18715,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="134"/>
+      <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -18738,7 +18741,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="134"/>
+      <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -18764,7 +18767,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="134"/>
+      <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -18790,7 +18793,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="134"/>
+      <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -18816,7 +18819,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="134"/>
+      <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -18842,7 +18845,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="134"/>
+      <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -18872,7 +18875,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="134"/>
+      <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -18898,7 +18901,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="134"/>
+      <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -18924,7 +18927,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="134"/>
+      <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -18950,7 +18953,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="134"/>
+      <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -18976,7 +18979,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="134"/>
+      <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -19002,7 +19005,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="134"/>
+      <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -19028,7 +19031,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="134"/>
+      <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -19054,7 +19057,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="134"/>
+      <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -19080,7 +19083,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="134"/>
+      <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -19106,7 +19109,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="134"/>
+      <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -19132,7 +19135,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="134"/>
+      <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -19158,7 +19161,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="134"/>
+      <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -19184,7 +19187,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="134"/>
+      <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -19210,7 +19213,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="134"/>
+      <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -19236,7 +19239,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="134"/>
+      <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -19276,7 +19279,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -19304,7 +19307,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="134"/>
+      <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -19330,7 +19333,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="134"/>
+      <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -19356,7 +19359,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="134"/>
+      <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -19382,7 +19385,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="134"/>
+      <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -19408,7 +19411,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="134"/>
+      <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -19434,7 +19437,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="134"/>
+      <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -19460,7 +19463,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="134"/>
+      <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -19486,7 +19489,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="134"/>
+      <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -19512,7 +19515,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="134"/>
+      <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -19538,7 +19541,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="134"/>
+      <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -19564,7 +19567,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="134"/>
+      <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -19590,7 +19593,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="134"/>
+      <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -19616,7 +19619,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="134"/>
+      <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -19642,7 +19645,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="134"/>
+      <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -19668,7 +19671,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="134"/>
+      <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -19694,7 +19697,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="134"/>
+      <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -19720,7 +19723,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="134"/>
+      <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -19746,7 +19749,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="134"/>
+      <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -19772,7 +19775,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="134"/>
+      <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -19798,7 +19801,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="134"/>
+      <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -19824,7 +19827,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="134"/>
+      <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -19850,7 +19853,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="134"/>
+      <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -19876,7 +19879,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="134"/>
+      <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -19902,7 +19905,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="134"/>
+      <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -19928,7 +19931,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="134"/>
+      <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -19954,7 +19957,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="134"/>
+      <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -19980,7 +19983,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="134"/>
+      <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -20006,7 +20009,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="134"/>
+      <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -20032,7 +20035,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="134"/>
+      <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -20058,7 +20061,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="134"/>
+      <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -20098,7 +20101,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="131" t="s">
+      <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -20126,7 +20129,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="132"/>
+      <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -20152,7 +20155,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="132"/>
+      <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -20178,7 +20181,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="132"/>
+      <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -20204,7 +20207,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="132"/>
+      <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -20230,7 +20233,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="132"/>
+      <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -20256,7 +20259,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="132"/>
+      <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -20282,7 +20285,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="132"/>
+      <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -20308,7 +20311,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="132"/>
+      <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -20334,7 +20337,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="132"/>
+      <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -20360,7 +20363,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="132"/>
+      <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -20386,7 +20389,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="132"/>
+      <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -20412,7 +20415,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="132"/>
+      <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -20438,7 +20441,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="132"/>
+      <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -20464,7 +20467,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="132"/>
+      <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -20490,7 +20493,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="132"/>
+      <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -20516,7 +20519,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="132"/>
+      <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -20542,7 +20545,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="132"/>
+      <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -20568,7 +20571,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="132"/>
+      <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -20594,7 +20597,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="132"/>
+      <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -20620,7 +20623,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="132"/>
+      <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -20646,7 +20649,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="133"/>
+      <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -20673,17 +20676,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
@@ -20772,52 +20775,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="F2" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="127"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="L2" s="129" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="130"/>
-      <c r="R2" s="120" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -20845,7 +20848,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
+      <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -20871,7 +20874,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="132"/>
+      <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -20897,7 +20900,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
+      <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -20923,7 +20926,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
+      <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -20951,7 +20954,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="132"/>
+      <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -20977,7 +20980,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="132"/>
+      <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -21003,7 +21006,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="132"/>
+      <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -21031,7 +21034,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="132"/>
+      <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -21057,7 +21060,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
+      <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -21083,7 +21086,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="132"/>
+      <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -21109,7 +21112,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="132"/>
+      <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -21137,7 +21140,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="132"/>
+      <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -21163,7 +21166,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="132"/>
+      <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -21189,7 +21192,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="132"/>
+      <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -21215,7 +21218,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="133"/>
+      <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -21254,7 +21257,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -21282,7 +21285,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="134"/>
+      <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -21308,7 +21311,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="134"/>
+      <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -21334,7 +21337,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="134"/>
+      <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -21360,7 +21363,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="134"/>
+      <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -21386,7 +21389,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="134"/>
+      <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -21414,7 +21417,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="134"/>
+      <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -21440,7 +21443,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="134"/>
+      <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -21466,7 +21469,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134"/>
+      <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -21492,7 +21495,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="134"/>
+      <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -21520,7 +21523,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="134"/>
+      <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -21546,7 +21549,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="134"/>
+      <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -21572,7 +21575,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134"/>
+      <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -21600,7 +21603,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134"/>
+      <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -21626,7 +21629,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="134"/>
+      <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -21652,7 +21655,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="134"/>
+      <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -21682,7 +21685,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="134"/>
+      <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -21710,7 +21713,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="134"/>
+      <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -21736,7 +21739,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="134"/>
+      <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -21764,7 +21767,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="134"/>
+      <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -21792,7 +21795,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="134"/>
+      <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -21818,7 +21821,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="134"/>
+      <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -21844,7 +21847,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="134"/>
+      <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -21870,7 +21873,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="134"/>
+      <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -21900,7 +21903,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="134"/>
+      <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -21926,7 +21929,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="134"/>
+      <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -21952,7 +21955,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="134"/>
+      <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -21978,7 +21981,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="134"/>
+      <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -22004,7 +22007,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="134"/>
+      <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -22030,7 +22033,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="134"/>
+      <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -22056,7 +22059,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="134"/>
+      <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -22095,7 +22098,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -22123,7 +22126,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="134"/>
+      <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -22149,7 +22152,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="134"/>
+      <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -22175,7 +22178,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="134"/>
+      <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -22201,7 +22204,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="134"/>
+      <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -22227,7 +22230,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="134"/>
+      <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -22253,7 +22256,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="134"/>
+      <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -22279,7 +22282,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="134"/>
+      <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -22305,7 +22308,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="134"/>
+      <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -22331,7 +22334,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="134"/>
+      <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -22357,7 +22360,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="134"/>
+      <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -22383,7 +22386,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="134"/>
+      <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -22409,7 +22412,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="134"/>
+      <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -22435,7 +22438,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="134"/>
+      <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -22461,7 +22464,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="134"/>
+      <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -22487,7 +22490,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="134"/>
+      <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -22513,7 +22516,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="134"/>
+      <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -22539,7 +22542,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="134"/>
+      <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -22565,7 +22568,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="134"/>
+      <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -22591,7 +22594,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="134"/>
+      <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -22617,7 +22620,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="134"/>
+      <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -22643,7 +22646,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="134"/>
+      <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -22669,7 +22672,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="134"/>
+      <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -22695,7 +22698,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="134"/>
+      <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -22721,7 +22724,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="134"/>
+      <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -22747,7 +22750,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="134"/>
+      <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -22773,7 +22776,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="134"/>
+      <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -22799,7 +22802,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="134"/>
+      <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -22825,7 +22828,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="134"/>
+      <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -22851,7 +22854,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="134"/>
+      <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -22891,7 +22894,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -22919,7 +22922,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="134"/>
+      <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -22945,7 +22948,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="134"/>
+      <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -22971,7 +22974,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="134"/>
+      <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -22997,7 +23000,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="134"/>
+      <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -23023,7 +23026,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="134"/>
+      <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -23049,7 +23052,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="134"/>
+      <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -23075,7 +23078,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="134"/>
+      <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -23101,7 +23104,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="134"/>
+      <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -23127,7 +23130,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="134"/>
+      <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -23153,7 +23156,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="134"/>
+      <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -23179,7 +23182,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="134"/>
+      <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -23205,7 +23208,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="134"/>
+      <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -23231,7 +23234,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="134"/>
+      <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -23257,7 +23260,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="134"/>
+      <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -23283,7 +23286,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="134"/>
+      <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -23309,7 +23312,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="134"/>
+      <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -23335,7 +23338,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="134"/>
+      <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -23361,7 +23364,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="134"/>
+      <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -23387,7 +23390,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="134"/>
+      <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -23413,7 +23416,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="134"/>
+      <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -23439,7 +23442,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="134"/>
+      <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -23465,7 +23468,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="134"/>
+      <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -23491,7 +23494,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="134"/>
+      <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -23517,7 +23520,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="134"/>
+      <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -23543,7 +23546,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="134"/>
+      <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -23569,7 +23572,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="134"/>
+      <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -23595,7 +23598,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="134"/>
+      <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -23621,7 +23624,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="134"/>
+      <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -23647,7 +23650,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="134"/>
+      <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -23673,7 +23676,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="134"/>
+      <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -23713,7 +23716,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="131" t="s">
+      <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -23741,7 +23744,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="132"/>
+      <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -23767,7 +23770,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="132"/>
+      <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -23793,7 +23796,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="132"/>
+      <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -23819,7 +23822,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="132"/>
+      <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -23845,7 +23848,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="132"/>
+      <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -23871,7 +23874,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="132"/>
+      <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -23897,7 +23900,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="132"/>
+      <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -23923,7 +23926,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="132"/>
+      <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -23949,7 +23952,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="132"/>
+      <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -23975,7 +23978,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="132"/>
+      <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -24001,7 +24004,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="132"/>
+      <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -24027,7 +24030,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="132"/>
+      <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -24053,7 +24056,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="132"/>
+      <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -24079,7 +24082,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="132"/>
+      <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -24105,7 +24108,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="132"/>
+      <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -24131,7 +24134,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="132"/>
+      <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -24157,7 +24160,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="132"/>
+      <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -24183,7 +24186,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="132"/>
+      <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -24209,7 +24212,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="132"/>
+      <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -24235,7 +24238,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="132"/>
+      <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -24261,7 +24264,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="133"/>
+      <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -24388,52 +24391,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="F2" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="127"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="F2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="L2" s="129" t="s">
+      <c r="J2" s="132"/>
+      <c r="L2" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="M2" s="133"/>
+      <c r="O2" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="130"/>
-      <c r="R2" s="120" t="s">
+      <c r="P2" s="134"/>
+      <c r="R2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -24461,7 +24464,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
+      <c r="B6" s="121"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -24487,7 +24490,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="132"/>
+      <c r="B7" s="121"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -24513,7 +24516,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
+      <c r="B8" s="121"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -24539,7 +24542,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
+      <c r="B9" s="121"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -24567,7 +24570,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="132"/>
+      <c r="B10" s="121"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -24593,7 +24596,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="132"/>
+      <c r="B11" s="121"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -24619,7 +24622,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="132"/>
+      <c r="B12" s="121"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -24647,7 +24650,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="132"/>
+      <c r="B13" s="121"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -24673,7 +24676,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
+      <c r="B14" s="121"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -24699,7 +24702,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="132"/>
+      <c r="B15" s="121"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -24725,7 +24728,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="132"/>
+      <c r="B16" s="121"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -24753,7 +24756,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="132"/>
+      <c r="B17" s="121"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -24779,7 +24782,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="132"/>
+      <c r="B18" s="121"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -24805,7 +24808,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="132"/>
+      <c r="B19" s="121"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -24831,7 +24834,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="133"/>
+      <c r="B20" s="122"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -24870,7 +24873,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -24898,7 +24901,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="134"/>
+      <c r="B23" s="123"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -24924,7 +24927,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="134"/>
+      <c r="B24" s="123"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -24950,7 +24953,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="134"/>
+      <c r="B25" s="123"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -24976,7 +24979,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="134"/>
+      <c r="B26" s="123"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -25002,7 +25005,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="134"/>
+      <c r="B27" s="123"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -25030,7 +25033,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="134"/>
+      <c r="B28" s="123"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -25056,7 +25059,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="134"/>
+      <c r="B29" s="123"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -25082,7 +25085,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134"/>
+      <c r="B30" s="123"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -25108,7 +25111,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="134"/>
+      <c r="B31" s="123"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -25136,7 +25139,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="134"/>
+      <c r="B32" s="123"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -25162,7 +25165,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="134"/>
+      <c r="B33" s="123"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -25188,7 +25191,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134"/>
+      <c r="B34" s="123"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -25216,7 +25219,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134"/>
+      <c r="B35" s="123"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -25242,7 +25245,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="134"/>
+      <c r="B36" s="123"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -25268,7 +25271,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="134"/>
+      <c r="B37" s="123"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -25294,7 +25297,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="134"/>
+      <c r="B38" s="123"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -25322,7 +25325,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="134"/>
+      <c r="B39" s="123"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -25350,7 +25353,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="134"/>
+      <c r="B40" s="123"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -25380,7 +25383,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="134"/>
+      <c r="B41" s="123"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -25408,7 +25411,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="134"/>
+      <c r="B42" s="123"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -25434,7 +25437,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="134"/>
+      <c r="B43" s="123"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -25460,7 +25463,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="134"/>
+      <c r="B44" s="123"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -25486,7 +25489,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="134"/>
+      <c r="B45" s="123"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -25516,7 +25519,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="134"/>
+      <c r="B46" s="123"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -25542,7 +25545,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="134"/>
+      <c r="B47" s="123"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -25568,7 +25571,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="134"/>
+      <c r="B48" s="123"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -25594,7 +25597,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="134"/>
+      <c r="B49" s="123"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -25620,7 +25623,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="134"/>
+      <c r="B50" s="123"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -25646,7 +25649,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="134"/>
+      <c r="B51" s="123"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -25672,7 +25675,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="134"/>
+      <c r="B52" s="123"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -25711,7 +25714,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="123" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -25739,7 +25742,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="134"/>
+      <c r="B55" s="123"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -25765,7 +25768,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="134"/>
+      <c r="B56" s="123"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -25791,7 +25794,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="134"/>
+      <c r="B57" s="123"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -25819,7 +25822,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="134"/>
+      <c r="B58" s="123"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -25847,7 +25850,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="134"/>
+      <c r="B59" s="123"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -25873,7 +25876,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="134"/>
+      <c r="B60" s="123"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -25899,7 +25902,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="134"/>
+      <c r="B61" s="123"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -25925,7 +25928,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="134"/>
+      <c r="B62" s="123"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -25951,7 +25954,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="134"/>
+      <c r="B63" s="123"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -25977,7 +25980,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="134"/>
+      <c r="B64" s="123"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -26003,7 +26006,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="134"/>
+      <c r="B65" s="123"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -26029,7 +26032,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="134"/>
+      <c r="B66" s="123"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -26055,7 +26058,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="134"/>
+      <c r="B67" s="123"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -26081,7 +26084,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="134"/>
+      <c r="B68" s="123"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -26107,7 +26110,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="134"/>
+      <c r="B69" s="123"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -26137,7 +26140,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="134"/>
+      <c r="B70" s="123"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -26163,7 +26166,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="134"/>
+      <c r="B71" s="123"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -26189,7 +26192,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="134"/>
+      <c r="B72" s="123"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -26217,7 +26220,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="134"/>
+      <c r="B73" s="123"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -26243,7 +26246,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="134"/>
+      <c r="B74" s="123"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -26269,7 +26272,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="134"/>
+      <c r="B75" s="123"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -26295,7 +26298,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="134"/>
+      <c r="B76" s="123"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -26321,7 +26324,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="134"/>
+      <c r="B77" s="123"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -26342,12 +26345,14 @@
       </c>
       <c r="P77" s="73"/>
       <c r="R77" s="95">
-        <v>0</v>
-      </c>
-      <c r="S77" s="75"/>
+        <v>2</v>
+      </c>
+      <c r="S77" s="75" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="134"/>
+      <c r="B78" s="123"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -26373,7 +26378,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="134"/>
+      <c r="B79" s="123"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -26399,7 +26404,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="134"/>
+      <c r="B80" s="123"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -26425,7 +26430,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="134"/>
+      <c r="B81" s="123"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -26451,7 +26456,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="134"/>
+      <c r="B82" s="123"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -26472,12 +26477,14 @@
       </c>
       <c r="P82" s="73"/>
       <c r="R82" s="95">
-        <v>0</v>
-      </c>
-      <c r="S82" s="75"/>
+        <v>2</v>
+      </c>
+      <c r="S82" s="75" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="134"/>
+      <c r="B83" s="123"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -26517,7 +26524,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="123" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -26545,7 +26552,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="134"/>
+      <c r="B86" s="123"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -26571,7 +26578,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="134"/>
+      <c r="B87" s="123"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -26597,7 +26604,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="134"/>
+      <c r="B88" s="123"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -26623,7 +26630,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="134"/>
+      <c r="B89" s="123"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -26649,7 +26656,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="134"/>
+      <c r="B90" s="123"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -26675,7 +26682,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="134"/>
+      <c r="B91" s="123"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -26701,7 +26708,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="134"/>
+      <c r="B92" s="123"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -26727,7 +26734,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="134"/>
+      <c r="B93" s="123"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -26753,7 +26760,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="134"/>
+      <c r="B94" s="123"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -26779,7 +26786,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="134"/>
+      <c r="B95" s="123"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -26805,7 +26812,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="134"/>
+      <c r="B96" s="123"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -26831,7 +26838,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="134"/>
+      <c r="B97" s="123"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -26857,7 +26864,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="134"/>
+      <c r="B98" s="123"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -26883,7 +26890,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="134"/>
+      <c r="B99" s="123"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -26909,7 +26916,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="134"/>
+      <c r="B100" s="123"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -26935,7 +26942,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="134"/>
+      <c r="B101" s="123"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -26961,7 +26968,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="134"/>
+      <c r="B102" s="123"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -26987,7 +26994,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="134"/>
+      <c r="B103" s="123"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -27013,7 +27020,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="134"/>
+      <c r="B104" s="123"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -27039,7 +27046,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="134"/>
+      <c r="B105" s="123"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -27065,7 +27072,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="134"/>
+      <c r="B106" s="123"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -27091,7 +27098,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="134"/>
+      <c r="B107" s="123"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -27117,7 +27124,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="134"/>
+      <c r="B108" s="123"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -27143,7 +27150,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="134"/>
+      <c r="B109" s="123"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -27169,7 +27176,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="134"/>
+      <c r="B110" s="123"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -27195,7 +27202,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="134"/>
+      <c r="B111" s="123"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -27221,7 +27228,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="134"/>
+      <c r="B112" s="123"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -27247,7 +27254,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="134"/>
+      <c r="B113" s="123"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -27273,7 +27280,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="134"/>
+      <c r="B114" s="123"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -27299,7 +27306,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="134"/>
+      <c r="B115" s="123"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -27339,7 +27346,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="131" t="s">
+      <c r="B117" s="120" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -27367,7 +27374,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="132"/>
+      <c r="B118" s="121"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -27393,7 +27400,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="132"/>
+      <c r="B119" s="121"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -27419,7 +27426,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="132"/>
+      <c r="B120" s="121"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -27445,7 +27452,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="132"/>
+      <c r="B121" s="121"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -27471,7 +27478,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="132"/>
+      <c r="B122" s="121"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -27497,7 +27504,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="132"/>
+      <c r="B123" s="121"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -27523,7 +27530,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="132"/>
+      <c r="B124" s="121"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -27549,7 +27556,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="132"/>
+      <c r="B125" s="121"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -27575,7 +27582,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="132"/>
+      <c r="B126" s="121"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -27601,7 +27608,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="132"/>
+      <c r="B127" s="121"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -27627,7 +27634,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="132"/>
+      <c r="B128" s="121"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -27653,7 +27660,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="132"/>
+      <c r="B129" s="121"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -27679,7 +27686,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="132"/>
+      <c r="B130" s="121"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -27705,7 +27712,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="132"/>
+      <c r="B131" s="121"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -27731,7 +27738,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="132"/>
+      <c r="B132" s="121"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -27757,7 +27764,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="132"/>
+      <c r="B133" s="121"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -27783,7 +27790,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="132"/>
+      <c r="B134" s="121"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -27809,7 +27816,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="132"/>
+      <c r="B135" s="121"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -27835,7 +27842,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="132"/>
+      <c r="B136" s="121"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -27861,7 +27868,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="132"/>
+      <c r="B137" s="121"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -27887,7 +27894,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="133"/>
+      <c r="B138" s="122"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -27914,17 +27921,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C95C014-ED4F-472B-9B57-5F33BD01DA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEA4571-40F9-493D-AABF-0A125545A3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="93">
   <si>
     <t>BACKEND</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>devops</t>
+  </si>
+  <si>
+    <t>Joi fixes</t>
+  </si>
+  <si>
+    <t>Posts page implemented</t>
   </si>
 </sst>
 </file>
@@ -1707,18 +1713,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1751,6 +1745,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2475,10 +2481,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>80.5</c:v>
+                  <c:v>81.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.5</c:v>
+                  <c:v>27.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>21.5</c:v>
@@ -4529,10 +4535,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.5</c:v>
@@ -9117,12 +9123,12 @@
       </c>
       <c r="H6" s="78">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="40"/>
       <c r="J6" s="41">
         <f>SUM(D6:H6)</f>
-        <v>80.5</v>
+        <v>81.5</v>
       </c>
       <c r="K6" s="30"/>
     </row>
@@ -9161,12 +9167,12 @@
       </c>
       <c r="H8" s="81">
         <f>SUM(WENJIE!I5:I138)</f>
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="I8" s="47"/>
       <c r="J8" s="48">
         <f>SUM(D8:H8)</f>
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
       <c r="K8" s="30"/>
     </row>
@@ -9336,12 +9342,12 @@
       </c>
       <c r="H16" s="28">
         <f>SUM(H6:H14)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I16" s="33"/>
       <c r="J16" s="28">
         <f>SUM(D16:H16)</f>
-        <v>167.5</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9394,52 +9400,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -9467,7 +9473,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -9493,7 +9499,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -9519,7 +9525,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -9545,7 +9551,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -9573,7 +9579,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -9599,7 +9605,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -9625,7 +9631,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -9653,7 +9659,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -9679,7 +9685,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -9705,7 +9711,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -9731,7 +9737,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -9759,7 +9765,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -9785,7 +9791,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -9811,7 +9817,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -9837,7 +9843,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -9876,7 +9882,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -9904,7 +9910,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -9930,7 +9936,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -9956,7 +9962,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -9982,7 +9988,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -10008,7 +10014,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -10036,7 +10042,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -10062,7 +10068,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -10088,7 +10094,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -10114,7 +10120,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -10142,7 +10148,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -10168,7 +10174,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -10194,7 +10200,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -10222,7 +10228,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -10248,7 +10254,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -10274,7 +10280,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -10300,7 +10306,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -10328,7 +10334,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -10356,7 +10362,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -10382,7 +10388,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -10410,7 +10416,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -10436,7 +10442,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -10462,7 +10468,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -10488,7 +10494,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -10518,7 +10524,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -10544,7 +10550,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -10570,7 +10576,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -10596,7 +10602,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -10622,7 +10628,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -10648,7 +10654,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -10674,7 +10680,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -10713,7 +10719,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -10741,7 +10747,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -10767,7 +10773,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -10793,7 +10799,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -10819,7 +10825,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -10845,7 +10851,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -10871,7 +10877,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -10897,7 +10903,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -10923,7 +10929,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -10949,7 +10955,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -10975,7 +10981,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -11001,7 +11007,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -11027,7 +11033,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -11053,7 +11059,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -11079,7 +11085,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -11105,7 +11111,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -11135,7 +11141,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -11161,7 +11167,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -11187,7 +11193,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -11213,7 +11219,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -11239,7 +11245,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -11265,7 +11271,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -11291,7 +11297,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -11317,7 +11323,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -11343,7 +11349,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -11369,7 +11375,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -11395,7 +11401,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -11421,7 +11427,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -11447,7 +11453,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -11473,7 +11479,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -11513,7 +11519,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -11541,7 +11547,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -11567,7 +11573,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -11593,7 +11599,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -11619,7 +11625,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -11645,7 +11651,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -11671,7 +11677,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -11697,7 +11703,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -11723,7 +11729,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -11749,7 +11755,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -11775,7 +11781,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -11801,7 +11807,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -11827,7 +11833,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -11853,7 +11859,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -11879,7 +11885,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -11905,7 +11911,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -11931,7 +11937,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -11957,7 +11963,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -11983,7 +11989,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -12009,7 +12015,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -12035,7 +12041,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -12061,7 +12067,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -12087,7 +12093,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -12113,7 +12119,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -12139,7 +12145,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -12165,7 +12171,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -12191,7 +12197,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -12217,7 +12223,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -12243,7 +12249,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -12269,7 +12275,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -12295,7 +12301,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -12335,7 +12341,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -12363,7 +12369,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -12389,7 +12395,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -12415,7 +12421,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -12441,7 +12447,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -12467,7 +12473,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -12493,7 +12499,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -12519,7 +12525,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -12545,7 +12551,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -12571,7 +12577,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -12597,7 +12603,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -12623,7 +12629,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -12649,7 +12655,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -12675,7 +12681,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -12701,7 +12707,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -12727,7 +12733,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -12753,7 +12759,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -12779,7 +12785,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -12805,7 +12811,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -12831,7 +12837,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -12857,7 +12863,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -12883,7 +12889,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -12910,17 +12916,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
@@ -13009,52 +13015,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -13086,7 +13092,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -13116,7 +13122,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -13146,7 +13152,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -13176,7 +13182,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -13208,7 +13214,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -13238,7 +13244,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -13268,7 +13274,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -13300,7 +13306,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -13330,7 +13336,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -13360,7 +13366,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -13390,7 +13396,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -13422,7 +13428,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -13452,7 +13458,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -13482,7 +13488,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -13512,7 +13518,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -13559,7 +13565,7 @@
       <c r="S21" s="116"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -13591,7 +13597,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -13621,7 +13627,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -13651,7 +13657,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -13681,7 +13687,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -13711,7 +13717,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -13743,7 +13749,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -13773,7 +13779,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -13803,7 +13809,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -13833,7 +13839,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -13865,7 +13871,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -13895,7 +13901,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -13925,7 +13931,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -13957,7 +13963,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -13987,7 +13993,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -14017,7 +14023,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -14047,7 +14053,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -14079,7 +14085,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -14111,7 +14117,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -14141,7 +14147,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -14173,7 +14179,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -14203,7 +14209,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -14233,7 +14239,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -14263,7 +14269,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -14297,7 +14303,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -14327,7 +14333,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -14357,7 +14363,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -14387,7 +14393,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -14417,7 +14423,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -14447,7 +14453,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -14477,7 +14483,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -14524,7 +14530,7 @@
       <c r="S53" s="116"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -14556,7 +14562,7 @@
       <c r="S54" s="74"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -14586,7 +14592,7 @@
       <c r="S55" s="74"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -14616,7 +14622,7 @@
       <c r="S56" s="74"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -14646,7 +14652,7 @@
       <c r="S57" s="74"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -14676,7 +14682,7 @@
       <c r="S58" s="74"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -14706,7 +14712,7 @@
       <c r="S59" s="74"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -14736,7 +14742,7 @@
       <c r="S60" s="74"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -14766,7 +14772,7 @@
       <c r="S61" s="74"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -14796,7 +14802,7 @@
       <c r="S62" s="74"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -14826,7 +14832,7 @@
       <c r="S63" s="74"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -14856,7 +14862,7 @@
       <c r="S64" s="74"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -14886,7 +14892,7 @@
       <c r="S65" s="74"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -14916,7 +14922,7 @@
       <c r="S66" s="74"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -14946,7 +14952,7 @@
       <c r="S67" s="74"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -14976,7 +14982,7 @@
       <c r="S68" s="74"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -15010,7 +15016,7 @@
       <c r="S69" s="74"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -15040,7 +15046,7 @@
       <c r="S70" s="74"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -15070,7 +15076,7 @@
       <c r="S71" s="74"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -15100,7 +15106,7 @@
       <c r="S72" s="74"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -15130,7 +15136,7 @@
       <c r="S73" s="74"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -15160,7 +15166,7 @@
       <c r="S74" s="74"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -15190,7 +15196,7 @@
       <c r="S75" s="74"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -15220,7 +15226,7 @@
       <c r="S76" s="74"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -15250,7 +15256,7 @@
       <c r="S77" s="74"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -15280,7 +15286,7 @@
       <c r="S78" s="74"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -15310,7 +15316,7 @@
       <c r="S79" s="74"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -15340,7 +15346,7 @@
       <c r="S80" s="74"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -15370,7 +15376,7 @@
       <c r="S81" s="74"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -15400,7 +15406,7 @@
       <c r="S82" s="74"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -15448,7 +15454,7 @@
       <c r="S84" s="116"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -15480,7 +15486,7 @@
       <c r="S85" s="74"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -15510,7 +15516,7 @@
       <c r="S86" s="74"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -15540,7 +15546,7 @@
       <c r="S87" s="74"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -15570,7 +15576,7 @@
       <c r="S88" s="74"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -15600,7 +15606,7 @@
       <c r="S89" s="74"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -15630,7 +15636,7 @@
       <c r="S90" s="74"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -15660,7 +15666,7 @@
       <c r="S91" s="74"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -15690,7 +15696,7 @@
       <c r="S92" s="74"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -15720,7 +15726,7 @@
       <c r="S93" s="74"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -15750,7 +15756,7 @@
       <c r="S94" s="74"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -15780,7 +15786,7 @@
       <c r="S95" s="74"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -15810,7 +15816,7 @@
       <c r="S96" s="74"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -15840,7 +15846,7 @@
       <c r="S97" s="74"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -15870,7 +15876,7 @@
       <c r="S98" s="74"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -15900,7 +15906,7 @@
       <c r="S99" s="74"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -15930,7 +15936,7 @@
       <c r="S100" s="74"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -15960,7 +15966,7 @@
       <c r="S101" s="74"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -15990,7 +15996,7 @@
       <c r="S102" s="74"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -16020,7 +16026,7 @@
       <c r="S103" s="74"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -16050,7 +16056,7 @@
       <c r="S104" s="74"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -16080,7 +16086,7 @@
       <c r="S105" s="74"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -16110,7 +16116,7 @@
       <c r="S106" s="74"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -16140,7 +16146,7 @@
       <c r="S107" s="74"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -16170,7 +16176,7 @@
       <c r="S108" s="74"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -16200,7 +16206,7 @@
       <c r="S109" s="74"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -16230,7 +16236,7 @@
       <c r="S110" s="74"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -16260,7 +16266,7 @@
       <c r="S111" s="74"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -16290,7 +16296,7 @@
       <c r="S112" s="74"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -16320,7 +16326,7 @@
       <c r="S113" s="74"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -16350,7 +16356,7 @@
       <c r="S114" s="74"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -16398,7 +16404,7 @@
       <c r="S116" s="116"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -16430,7 +16436,7 @@
       <c r="S117" s="74"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -16460,7 +16466,7 @@
       <c r="S118" s="74"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -16490,7 +16496,7 @@
       <c r="S119" s="74"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -16520,7 +16526,7 @@
       <c r="S120" s="74"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -16550,7 +16556,7 @@
       <c r="S121" s="74"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -16580,7 +16586,7 @@
       <c r="S122" s="74"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -16610,7 +16616,7 @@
       <c r="S123" s="74"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -16640,7 +16646,7 @@
       <c r="S124" s="74"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -16670,7 +16676,7 @@
       <c r="S125" s="74"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -16700,7 +16706,7 @@
       <c r="S126" s="74"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -16730,7 +16736,7 @@
       <c r="S127" s="74"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -16760,7 +16766,7 @@
       <c r="S128" s="74"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -16790,7 +16796,7 @@
       <c r="S129" s="74"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -16820,7 +16826,7 @@
       <c r="S130" s="74"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -16850,7 +16856,7 @@
       <c r="S131" s="74"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -16880,7 +16886,7 @@
       <c r="S132" s="74"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -16910,7 +16916,7 @@
       <c r="S133" s="74"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -16940,7 +16946,7 @@
       <c r="S134" s="74"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -16970,7 +16976,7 @@
       <c r="S135" s="74"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -17000,7 +17006,7 @@
       <c r="S136" s="74"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -17030,7 +17036,7 @@
       <c r="S137" s="74"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -17061,17 +17067,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
@@ -17160,52 +17166,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -17233,7 +17239,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -17259,7 +17265,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -17285,7 +17291,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -17311,7 +17317,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -17339,7 +17345,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -17365,7 +17371,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -17391,7 +17397,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -17419,7 +17425,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -17445,7 +17451,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -17471,7 +17477,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -17497,7 +17503,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -17525,7 +17531,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -17551,7 +17557,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -17577,7 +17583,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -17603,7 +17609,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -17642,7 +17648,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -17670,7 +17676,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -17696,7 +17702,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -17722,7 +17728,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -17748,7 +17754,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -17774,7 +17780,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -17802,7 +17808,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -17828,7 +17834,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -17854,7 +17860,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -17880,7 +17886,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -17908,7 +17914,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -17934,7 +17940,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -17960,7 +17966,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -17988,7 +17994,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -18014,7 +18020,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -18040,7 +18046,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -18066,7 +18072,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -18096,7 +18102,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -18122,7 +18128,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -18148,7 +18154,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -18176,7 +18182,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -18202,7 +18208,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -18228,7 +18234,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -18254,7 +18260,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -18284,7 +18290,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -18310,7 +18316,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -18336,7 +18342,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -18362,7 +18368,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -18388,7 +18394,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -18414,7 +18420,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -18440,7 +18446,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -18479,7 +18485,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -18507,7 +18513,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -18533,7 +18539,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -18559,7 +18565,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -18585,7 +18591,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -18611,7 +18617,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -18637,7 +18643,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -18663,7 +18669,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -18689,7 +18695,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -18715,7 +18721,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -18741,7 +18747,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -18767,7 +18773,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -18793,7 +18799,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -18819,7 +18825,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -18845,7 +18851,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -18875,7 +18881,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -18901,7 +18907,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -18927,7 +18933,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -18953,7 +18959,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -18979,7 +18985,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -19005,7 +19011,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -19031,7 +19037,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -19057,7 +19063,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -19083,7 +19089,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -19109,7 +19115,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -19135,7 +19141,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -19161,7 +19167,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -19187,7 +19193,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -19213,7 +19219,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -19239,7 +19245,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -19279,7 +19285,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -19307,7 +19313,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -19333,7 +19339,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -19359,7 +19365,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -19385,7 +19391,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -19411,7 +19417,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -19437,7 +19443,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -19463,7 +19469,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -19489,7 +19495,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -19515,7 +19521,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -19541,7 +19547,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -19567,7 +19573,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -19593,7 +19599,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -19619,7 +19625,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -19645,7 +19651,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -19671,7 +19677,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -19697,7 +19703,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -19723,7 +19729,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -19749,7 +19755,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -19775,7 +19781,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -19801,7 +19807,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -19827,7 +19833,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -19853,7 +19859,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -19879,7 +19885,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -19905,7 +19911,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -19931,7 +19937,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -19957,7 +19963,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -19983,7 +19989,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -20009,7 +20015,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -20035,7 +20041,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -20061,7 +20067,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -20101,7 +20107,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -20129,7 +20135,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -20155,7 +20161,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -20181,7 +20187,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -20207,7 +20213,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -20233,7 +20239,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -20259,7 +20265,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -20285,7 +20291,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -20311,7 +20317,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -20337,7 +20343,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -20363,7 +20369,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -20389,7 +20395,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -20415,7 +20421,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -20441,7 +20447,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -20467,7 +20473,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -20493,7 +20499,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -20519,7 +20525,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -20545,7 +20551,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -20571,7 +20577,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -20597,7 +20603,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -20623,7 +20629,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -20649,7 +20655,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -20676,17 +20682,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
@@ -20775,52 +20781,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -20848,7 +20854,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -20874,7 +20880,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -20900,7 +20906,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -20926,7 +20932,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -20954,7 +20960,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -20980,7 +20986,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -21006,7 +21012,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -21034,7 +21040,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -21060,7 +21066,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -21086,7 +21092,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -21112,7 +21118,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -21140,7 +21146,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -21166,7 +21172,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -21192,7 +21198,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -21218,7 +21224,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -21257,7 +21263,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -21285,7 +21291,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -21311,7 +21317,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -21337,7 +21343,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -21363,7 +21369,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -21389,7 +21395,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -21417,7 +21423,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -21443,7 +21449,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -21469,7 +21475,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -21495,7 +21501,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -21523,7 +21529,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -21549,7 +21555,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -21575,7 +21581,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -21603,7 +21609,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -21629,7 +21635,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -21655,7 +21661,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -21685,7 +21691,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -21713,7 +21719,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -21739,7 +21745,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -21767,7 +21773,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -21795,7 +21801,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -21821,7 +21827,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -21847,7 +21853,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -21873,7 +21879,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -21903,7 +21909,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -21929,7 +21935,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -21955,7 +21961,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -21981,7 +21987,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -22007,7 +22013,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -22033,7 +22039,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -22059,7 +22065,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -22098,7 +22104,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -22126,7 +22132,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -22152,7 +22158,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -22178,7 +22184,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -22204,7 +22210,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -22230,7 +22236,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -22256,7 +22262,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -22282,7 +22288,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -22308,7 +22314,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -22334,7 +22340,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -22360,7 +22366,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -22386,7 +22392,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -22412,7 +22418,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -22438,7 +22444,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -22464,7 +22470,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -22490,7 +22496,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -22516,7 +22522,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -22542,7 +22548,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -22568,7 +22574,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -22594,7 +22600,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -22620,7 +22626,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -22646,7 +22652,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -22672,7 +22678,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -22698,7 +22704,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -22724,7 +22730,7 @@
       <c r="S77" s="75"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -22750,7 +22756,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -22776,7 +22782,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -22802,7 +22808,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -22828,7 +22834,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -22854,7 +22860,7 @@
       <c r="S82" s="75"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -22894,7 +22900,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -22922,7 +22928,7 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
@@ -22948,7 +22954,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -22974,7 +22980,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -23000,7 +23006,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -23026,7 +23032,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -23052,7 +23058,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -23078,7 +23084,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -23104,7 +23110,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -23130,7 +23136,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -23156,7 +23162,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -23182,7 +23188,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -23208,7 +23214,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -23234,7 +23240,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -23260,7 +23266,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -23286,7 +23292,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -23312,7 +23318,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -23338,7 +23344,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -23364,7 +23370,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -23390,7 +23396,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -23416,7 +23422,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -23442,7 +23448,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -23468,7 +23474,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -23494,7 +23500,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -23520,7 +23526,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -23546,7 +23552,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -23572,7 +23578,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -23598,7 +23604,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -23624,7 +23630,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -23650,7 +23656,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -23676,7 +23682,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -23716,7 +23722,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -23744,7 +23750,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -23770,7 +23776,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -23796,7 +23802,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -23822,7 +23828,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -23848,7 +23854,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -23874,7 +23880,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -23900,7 +23906,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -23926,7 +23932,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -23952,7 +23958,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -23978,7 +23984,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -24004,7 +24010,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -24030,7 +24036,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -24056,7 +24062,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -24082,7 +24088,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -24108,7 +24114,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -24134,7 +24140,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -24160,7 +24166,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -24186,7 +24192,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -24212,7 +24218,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -24238,7 +24244,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -24264,7 +24270,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -24391,52 +24397,52 @@
     </row>
     <row r="2" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="127"/>
-      <c r="F2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="131"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="F2" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="127"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="128"/>
+      <c r="L2" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="133"/>
-      <c r="O2" s="134" t="s">
+      <c r="M2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="R2" s="124" t="s">
+      <c r="P2" s="130"/>
+      <c r="R2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="124"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="131" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="32">
@@ -24464,7 +24470,7 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="32">
         <v>14</v>
       </c>
@@ -24490,7 +24496,7 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="32">
         <v>15</v>
       </c>
@@ -24516,7 +24522,7 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="32">
         <v>16</v>
       </c>
@@ -24542,7 +24548,7 @@
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="32">
         <v>17</v>
       </c>
@@ -24570,7 +24576,7 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="32">
         <v>18</v>
       </c>
@@ -24596,7 +24602,7 @@
       <c r="S10" s="74"/>
     </row>
     <row r="11" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="32">
         <v>19</v>
       </c>
@@ -24622,7 +24628,7 @@
       <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="32">
         <v>20</v>
       </c>
@@ -24650,7 +24656,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="32">
         <v>21</v>
       </c>
@@ -24676,7 +24682,7 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="32">
         <v>22</v>
       </c>
@@ -24702,7 +24708,7 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="32">
         <v>23</v>
       </c>
@@ -24728,7 +24734,7 @@
       <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121"/>
+      <c r="B16" s="132"/>
       <c r="D16" s="32">
         <v>24</v>
       </c>
@@ -24756,7 +24762,7 @@
       <c r="S16" s="74"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
+      <c r="B17" s="132"/>
       <c r="D17" s="32">
         <v>25</v>
       </c>
@@ -24782,7 +24788,7 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
+      <c r="B18" s="132"/>
       <c r="D18" s="32">
         <v>26</v>
       </c>
@@ -24808,7 +24814,7 @@
       <c r="S18" s="74"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121"/>
+      <c r="B19" s="132"/>
       <c r="D19" s="32">
         <v>27</v>
       </c>
@@ -24834,7 +24840,7 @@
       <c r="S19" s="74"/>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122"/>
+      <c r="B20" s="133"/>
       <c r="D20" s="32">
         <v>28</v>
       </c>
@@ -24873,7 +24879,7 @@
       <c r="S21" s="23"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="134" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="32">
@@ -24901,7 +24907,7 @@
       <c r="S22" s="74"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="123"/>
+      <c r="B23" s="134"/>
       <c r="D23" s="32">
         <v>2</v>
       </c>
@@ -24927,7 +24933,7 @@
       <c r="S23" s="74"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="123"/>
+      <c r="B24" s="134"/>
       <c r="D24" s="32">
         <v>3</v>
       </c>
@@ -24953,7 +24959,7 @@
       <c r="S24" s="74"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="123"/>
+      <c r="B25" s="134"/>
       <c r="D25" s="32">
         <v>4</v>
       </c>
@@ -24979,7 +24985,7 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="123"/>
+      <c r="B26" s="134"/>
       <c r="D26" s="32">
         <v>5</v>
       </c>
@@ -25005,7 +25011,7 @@
       <c r="S26" s="74"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="123"/>
+      <c r="B27" s="134"/>
       <c r="D27" s="32">
         <v>6</v>
       </c>
@@ -25033,7 +25039,7 @@
       <c r="S27" s="74"/>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="123"/>
+      <c r="B28" s="134"/>
       <c r="D28" s="32">
         <v>7</v>
       </c>
@@ -25059,7 +25065,7 @@
       <c r="S28" s="74"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="123"/>
+      <c r="B29" s="134"/>
       <c r="D29" s="32">
         <v>8</v>
       </c>
@@ -25085,7 +25091,7 @@
       <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="123"/>
+      <c r="B30" s="134"/>
       <c r="D30" s="32">
         <v>9</v>
       </c>
@@ -25111,7 +25117,7 @@
       <c r="S30" s="74"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="123"/>
+      <c r="B31" s="134"/>
       <c r="D31" s="32">
         <v>10</v>
       </c>
@@ -25139,7 +25145,7 @@
       <c r="S31" s="74"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="123"/>
+      <c r="B32" s="134"/>
       <c r="D32" s="32">
         <v>11</v>
       </c>
@@ -25165,7 +25171,7 @@
       <c r="S32" s="74"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="123"/>
+      <c r="B33" s="134"/>
       <c r="D33" s="32">
         <v>12</v>
       </c>
@@ -25191,7 +25197,7 @@
       <c r="S33" s="74"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="123"/>
+      <c r="B34" s="134"/>
       <c r="D34" s="32">
         <v>13</v>
       </c>
@@ -25219,7 +25225,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="123"/>
+      <c r="B35" s="134"/>
       <c r="D35" s="32">
         <v>14</v>
       </c>
@@ -25245,7 +25251,7 @@
       <c r="S35" s="74"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="123"/>
+      <c r="B36" s="134"/>
       <c r="D36" s="32">
         <v>15</v>
       </c>
@@ -25271,7 +25277,7 @@
       <c r="S36" s="74"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
+      <c r="B37" s="134"/>
       <c r="D37" s="32">
         <v>16</v>
       </c>
@@ -25297,7 +25303,7 @@
       <c r="S37" s="74"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="123"/>
+      <c r="B38" s="134"/>
       <c r="D38" s="32">
         <v>17</v>
       </c>
@@ -25325,7 +25331,7 @@
       <c r="S38" s="74"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="123"/>
+      <c r="B39" s="134"/>
       <c r="D39" s="32">
         <v>18</v>
       </c>
@@ -25353,7 +25359,7 @@
       <c r="S39" s="74"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="123"/>
+      <c r="B40" s="134"/>
       <c r="D40" s="32">
         <v>19</v>
       </c>
@@ -25383,7 +25389,7 @@
       <c r="S40" s="74"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="123"/>
+      <c r="B41" s="134"/>
       <c r="D41" s="66">
         <v>20</v>
       </c>
@@ -25411,7 +25417,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123"/>
+      <c r="B42" s="134"/>
       <c r="D42" s="32">
         <v>21</v>
       </c>
@@ -25437,7 +25443,7 @@
       <c r="S42" s="74"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="123"/>
+      <c r="B43" s="134"/>
       <c r="D43" s="32">
         <v>22</v>
       </c>
@@ -25463,7 +25469,7 @@
       <c r="S43" s="74"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="123"/>
+      <c r="B44" s="134"/>
       <c r="D44" s="32">
         <v>23</v>
       </c>
@@ -25489,7 +25495,7 @@
       <c r="S44" s="74"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="123"/>
+      <c r="B45" s="134"/>
       <c r="D45" s="32">
         <v>24</v>
       </c>
@@ -25519,7 +25525,7 @@
       <c r="S45" s="74"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="123"/>
+      <c r="B46" s="134"/>
       <c r="D46" s="32">
         <v>25</v>
       </c>
@@ -25545,7 +25551,7 @@
       <c r="S46" s="74"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
+      <c r="B47" s="134"/>
       <c r="D47" s="32">
         <v>26</v>
       </c>
@@ -25571,7 +25577,7 @@
       <c r="S47" s="74"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
+      <c r="B48" s="134"/>
       <c r="D48" s="32">
         <v>27</v>
       </c>
@@ -25597,7 +25603,7 @@
       <c r="S48" s="74"/>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
+      <c r="B49" s="134"/>
       <c r="D49" s="32">
         <v>28</v>
       </c>
@@ -25623,7 +25629,7 @@
       <c r="S49" s="74"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="123"/>
+      <c r="B50" s="134"/>
       <c r="D50" s="32">
         <v>29</v>
       </c>
@@ -25649,7 +25655,7 @@
       <c r="S50" s="74"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="123"/>
+      <c r="B51" s="134"/>
       <c r="D51" s="32">
         <v>30</v>
       </c>
@@ -25675,7 +25681,7 @@
       <c r="S51" s="74"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="123"/>
+      <c r="B52" s="134"/>
       <c r="D52" s="32">
         <v>31</v>
       </c>
@@ -25714,7 +25720,7 @@
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="134" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="32">
@@ -25742,7 +25748,7 @@
       <c r="S54" s="75"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="123"/>
+      <c r="B55" s="134"/>
       <c r="D55" s="32">
         <v>2</v>
       </c>
@@ -25768,7 +25774,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="123"/>
+      <c r="B56" s="134"/>
       <c r="D56" s="32">
         <v>3</v>
       </c>
@@ -25794,7 +25800,7 @@
       <c r="S56" s="75"/>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="123"/>
+      <c r="B57" s="134"/>
       <c r="D57" s="32">
         <v>4</v>
       </c>
@@ -25822,7 +25828,7 @@
       <c r="S57" s="75"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="123"/>
+      <c r="B58" s="134"/>
       <c r="D58" s="32">
         <v>5</v>
       </c>
@@ -25850,7 +25856,7 @@
       <c r="S58" s="75"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
+      <c r="B59" s="134"/>
       <c r="D59" s="32">
         <v>6</v>
       </c>
@@ -25876,7 +25882,7 @@
       <c r="S59" s="75"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="123"/>
+      <c r="B60" s="134"/>
       <c r="D60" s="32">
         <v>7</v>
       </c>
@@ -25902,7 +25908,7 @@
       <c r="S60" s="75"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="123"/>
+      <c r="B61" s="134"/>
       <c r="D61" s="32">
         <v>8</v>
       </c>
@@ -25928,7 +25934,7 @@
       <c r="S61" s="75"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="123"/>
+      <c r="B62" s="134"/>
       <c r="D62" s="32">
         <v>9</v>
       </c>
@@ -25954,7 +25960,7 @@
       <c r="S62" s="75"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="123"/>
+      <c r="B63" s="134"/>
       <c r="D63" s="32">
         <v>10</v>
       </c>
@@ -25980,7 +25986,7 @@
       <c r="S63" s="75"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="123"/>
+      <c r="B64" s="134"/>
       <c r="D64" s="32">
         <v>11</v>
       </c>
@@ -26006,7 +26012,7 @@
       <c r="S64" s="75"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="123"/>
+      <c r="B65" s="134"/>
       <c r="D65" s="32">
         <v>12</v>
       </c>
@@ -26032,7 +26038,7 @@
       <c r="S65" s="75"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="123"/>
+      <c r="B66" s="134"/>
       <c r="D66" s="32">
         <v>13</v>
       </c>
@@ -26058,7 +26064,7 @@
       <c r="S66" s="75"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="123"/>
+      <c r="B67" s="134"/>
       <c r="D67" s="32">
         <v>14</v>
       </c>
@@ -26084,7 +26090,7 @@
       <c r="S67" s="75"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="123"/>
+      <c r="B68" s="134"/>
       <c r="D68" s="32">
         <v>15</v>
       </c>
@@ -26110,7 +26116,7 @@
       <c r="S68" s="75"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="123"/>
+      <c r="B69" s="134"/>
       <c r="D69" s="32">
         <v>16</v>
       </c>
@@ -26140,7 +26146,7 @@
       <c r="S69" s="75"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="123"/>
+      <c r="B70" s="134"/>
       <c r="D70" s="66">
         <v>17</v>
       </c>
@@ -26166,7 +26172,7 @@
       <c r="S70" s="75"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="123"/>
+      <c r="B71" s="134"/>
       <c r="D71" s="32">
         <v>18</v>
       </c>
@@ -26192,7 +26198,7 @@
       <c r="S71" s="75"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="123"/>
+      <c r="B72" s="134"/>
       <c r="D72" s="32">
         <v>19</v>
       </c>
@@ -26220,7 +26226,7 @@
       <c r="S72" s="75"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="123"/>
+      <c r="B73" s="134"/>
       <c r="D73" s="32">
         <v>20</v>
       </c>
@@ -26246,7 +26252,7 @@
       <c r="S73" s="75"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="123"/>
+      <c r="B74" s="134"/>
       <c r="D74" s="32">
         <v>21</v>
       </c>
@@ -26272,7 +26278,7 @@
       <c r="S74" s="75"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="123"/>
+      <c r="B75" s="134"/>
       <c r="D75" s="32">
         <v>22</v>
       </c>
@@ -26298,7 +26304,7 @@
       <c r="S75" s="75"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="123"/>
+      <c r="B76" s="134"/>
       <c r="D76" s="32">
         <v>23</v>
       </c>
@@ -26324,7 +26330,7 @@
       <c r="S76" s="75"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="123"/>
+      <c r="B77" s="134"/>
       <c r="D77" s="32">
         <v>24</v>
       </c>
@@ -26352,7 +26358,7 @@
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="123"/>
+      <c r="B78" s="134"/>
       <c r="D78" s="32">
         <v>25</v>
       </c>
@@ -26378,7 +26384,7 @@
       <c r="S78" s="75"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="123"/>
+      <c r="B79" s="134"/>
       <c r="D79" s="32">
         <v>26</v>
       </c>
@@ -26404,7 +26410,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="123"/>
+      <c r="B80" s="134"/>
       <c r="D80" s="32">
         <v>27</v>
       </c>
@@ -26430,7 +26436,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="123"/>
+      <c r="B81" s="134"/>
       <c r="D81" s="32">
         <v>28</v>
       </c>
@@ -26456,7 +26462,7 @@
       <c r="S81" s="75"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="123"/>
+      <c r="B82" s="134"/>
       <c r="D82" s="32">
         <v>29</v>
       </c>
@@ -26484,7 +26490,7 @@
       </c>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="123"/>
+      <c r="B83" s="134"/>
       <c r="D83" s="32">
         <v>30</v>
       </c>
@@ -26524,7 +26530,7 @@
       <c r="S84" s="23"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="123" t="s">
+      <c r="B85" s="134" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="32">
@@ -26552,18 +26558,22 @@
       <c r="S85" s="75"/>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="123"/>
+      <c r="B86" s="134"/>
       <c r="D86" s="32">
         <v>2</v>
       </c>
       <c r="F86" s="91">
-        <v>0</v>
-      </c>
-      <c r="G86" s="67"/>
+        <v>1</v>
+      </c>
+      <c r="G86" s="67" t="s">
+        <v>91</v>
+      </c>
       <c r="I86" s="92">
-        <v>0</v>
-      </c>
-      <c r="J86" s="69"/>
+        <v>2</v>
+      </c>
+      <c r="J86" s="69" t="s">
+        <v>92</v>
+      </c>
       <c r="L86" s="93">
         <v>0</v>
       </c>
@@ -26578,7 +26588,7 @@
       <c r="S86" s="75"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="123"/>
+      <c r="B87" s="134"/>
       <c r="D87" s="32">
         <v>3</v>
       </c>
@@ -26604,7 +26614,7 @@
       <c r="S87" s="75"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="123"/>
+      <c r="B88" s="134"/>
       <c r="D88" s="32">
         <v>4</v>
       </c>
@@ -26630,7 +26640,7 @@
       <c r="S88" s="75"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="123"/>
+      <c r="B89" s="134"/>
       <c r="D89" s="32">
         <v>5</v>
       </c>
@@ -26656,7 +26666,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="123"/>
+      <c r="B90" s="134"/>
       <c r="D90" s="32">
         <v>6</v>
       </c>
@@ -26682,7 +26692,7 @@
       <c r="S90" s="75"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="123"/>
+      <c r="B91" s="134"/>
       <c r="D91" s="32">
         <v>7</v>
       </c>
@@ -26708,7 +26718,7 @@
       <c r="S91" s="75"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="123"/>
+      <c r="B92" s="134"/>
       <c r="D92" s="32">
         <v>8</v>
       </c>
@@ -26734,7 +26744,7 @@
       <c r="S92" s="75"/>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="123"/>
+      <c r="B93" s="134"/>
       <c r="D93" s="32">
         <v>9</v>
       </c>
@@ -26760,7 +26770,7 @@
       <c r="S93" s="75"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="123"/>
+      <c r="B94" s="134"/>
       <c r="D94" s="32">
         <v>10</v>
       </c>
@@ -26786,7 +26796,7 @@
       <c r="S94" s="75"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="123"/>
+      <c r="B95" s="134"/>
       <c r="D95" s="32">
         <v>11</v>
       </c>
@@ -26812,7 +26822,7 @@
       <c r="S95" s="75"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="123"/>
+      <c r="B96" s="134"/>
       <c r="D96" s="32">
         <v>12</v>
       </c>
@@ -26838,7 +26848,7 @@
       <c r="S96" s="75"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="123"/>
+      <c r="B97" s="134"/>
       <c r="D97" s="32">
         <v>13</v>
       </c>
@@ -26864,7 +26874,7 @@
       <c r="S97" s="75"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="123"/>
+      <c r="B98" s="134"/>
       <c r="D98" s="32">
         <v>14</v>
       </c>
@@ -26890,7 +26900,7 @@
       <c r="S98" s="75"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="123"/>
+      <c r="B99" s="134"/>
       <c r="D99" s="32">
         <v>15</v>
       </c>
@@ -26916,7 +26926,7 @@
       <c r="S99" s="75"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="123"/>
+      <c r="B100" s="134"/>
       <c r="D100" s="32">
         <v>16</v>
       </c>
@@ -26942,7 +26952,7 @@
       <c r="S100" s="75"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="123"/>
+      <c r="B101" s="134"/>
       <c r="D101" s="32">
         <v>17</v>
       </c>
@@ -26968,7 +26978,7 @@
       <c r="S101" s="75"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="123"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="32">
         <v>18</v>
       </c>
@@ -26994,7 +27004,7 @@
       <c r="S102" s="75"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="123"/>
+      <c r="B103" s="134"/>
       <c r="D103" s="66">
         <v>19</v>
       </c>
@@ -27020,7 +27030,7 @@
       <c r="S103" s="75"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="123"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="32">
         <v>20</v>
       </c>
@@ -27046,7 +27056,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="123"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="32">
         <v>21</v>
       </c>
@@ -27072,7 +27082,7 @@
       <c r="S105" s="75"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="123"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="32">
         <v>22</v>
       </c>
@@ -27098,7 +27108,7 @@
       <c r="S106" s="75"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="123"/>
+      <c r="B107" s="134"/>
       <c r="D107" s="32">
         <v>23</v>
       </c>
@@ -27124,7 +27134,7 @@
       <c r="S107" s="75"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="123"/>
+      <c r="B108" s="134"/>
       <c r="D108" s="32">
         <v>24</v>
       </c>
@@ -27150,7 +27160,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="123"/>
+      <c r="B109" s="134"/>
       <c r="D109" s="32">
         <v>25</v>
       </c>
@@ -27176,7 +27186,7 @@
       <c r="S109" s="75"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="123"/>
+      <c r="B110" s="134"/>
       <c r="D110" s="32">
         <v>26</v>
       </c>
@@ -27202,7 +27212,7 @@
       <c r="S110" s="75"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="123"/>
+      <c r="B111" s="134"/>
       <c r="D111" s="32">
         <v>27</v>
       </c>
@@ -27228,7 +27238,7 @@
       <c r="S111" s="75"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="123"/>
+      <c r="B112" s="134"/>
       <c r="D112" s="32">
         <v>28</v>
       </c>
@@ -27254,7 +27264,7 @@
       <c r="S112" s="75"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="123"/>
+      <c r="B113" s="134"/>
       <c r="D113" s="32">
         <v>29</v>
       </c>
@@ -27280,7 +27290,7 @@
       <c r="S113" s="75"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="123"/>
+      <c r="B114" s="134"/>
       <c r="D114" s="32">
         <v>30</v>
       </c>
@@ -27306,7 +27316,7 @@
       <c r="S114" s="75"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="123"/>
+      <c r="B115" s="134"/>
       <c r="D115" s="32">
         <v>31</v>
       </c>
@@ -27346,7 +27356,7 @@
       <c r="S116" s="23"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="131" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="32">
@@ -27374,7 +27384,7 @@
       <c r="S117" s="75"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="121"/>
+      <c r="B118" s="132"/>
       <c r="D118" s="32">
         <v>2</v>
       </c>
@@ -27400,7 +27410,7 @@
       <c r="S118" s="75"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="121"/>
+      <c r="B119" s="132"/>
       <c r="D119" s="32">
         <v>3</v>
       </c>
@@ -27426,7 +27436,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="121"/>
+      <c r="B120" s="132"/>
       <c r="D120" s="32">
         <v>4</v>
       </c>
@@ -27452,7 +27462,7 @@
       <c r="S120" s="75"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="121"/>
+      <c r="B121" s="132"/>
       <c r="D121" s="32">
         <v>5</v>
       </c>
@@ -27478,7 +27488,7 @@
       <c r="S121" s="75"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="121"/>
+      <c r="B122" s="132"/>
       <c r="D122" s="32">
         <v>6</v>
       </c>
@@ -27504,7 +27514,7 @@
       <c r="S122" s="75"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="121"/>
+      <c r="B123" s="132"/>
       <c r="D123" s="32">
         <v>7</v>
       </c>
@@ -27530,7 +27540,7 @@
       <c r="S123" s="75"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="121"/>
+      <c r="B124" s="132"/>
       <c r="D124" s="32">
         <v>8</v>
       </c>
@@ -27556,7 +27566,7 @@
       <c r="S124" s="75"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="121"/>
+      <c r="B125" s="132"/>
       <c r="D125" s="32">
         <v>9</v>
       </c>
@@ -27582,7 +27592,7 @@
       <c r="S125" s="75"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="121"/>
+      <c r="B126" s="132"/>
       <c r="D126" s="32">
         <v>10</v>
       </c>
@@ -27608,7 +27618,7 @@
       <c r="S126" s="75"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="121"/>
+      <c r="B127" s="132"/>
       <c r="D127" s="32">
         <v>11</v>
       </c>
@@ -27634,7 +27644,7 @@
       <c r="S127" s="75"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="121"/>
+      <c r="B128" s="132"/>
       <c r="D128" s="32">
         <v>12</v>
       </c>
@@ -27660,7 +27670,7 @@
       <c r="S128" s="75"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="121"/>
+      <c r="B129" s="132"/>
       <c r="D129" s="32">
         <v>13</v>
       </c>
@@ -27686,7 +27696,7 @@
       <c r="S129" s="75"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="121"/>
+      <c r="B130" s="132"/>
       <c r="D130" s="32">
         <v>14</v>
       </c>
@@ -27712,7 +27722,7 @@
       <c r="S130" s="75"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="121"/>
+      <c r="B131" s="132"/>
       <c r="D131" s="32">
         <v>15</v>
       </c>
@@ -27738,7 +27748,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="121"/>
+      <c r="B132" s="132"/>
       <c r="D132" s="32">
         <v>16</v>
       </c>
@@ -27764,7 +27774,7 @@
       <c r="S132" s="75"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="121"/>
+      <c r="B133" s="132"/>
       <c r="D133" s="32">
         <v>17</v>
       </c>
@@ -27790,7 +27800,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="121"/>
+      <c r="B134" s="132"/>
       <c r="D134" s="32">
         <v>18</v>
       </c>
@@ -27816,7 +27826,7 @@
       <c r="S134" s="75"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="121"/>
+      <c r="B135" s="132"/>
       <c r="D135" s="32">
         <v>19</v>
       </c>
@@ -27842,7 +27852,7 @@
       <c r="S135" s="75"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="121"/>
+      <c r="B136" s="132"/>
       <c r="D136" s="32">
         <v>20</v>
       </c>
@@ -27868,7 +27878,7 @@
       <c r="S136" s="75"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="121"/>
+      <c r="B137" s="132"/>
       <c r="D137" s="32">
         <v>21</v>
       </c>
@@ -27894,7 +27904,7 @@
       <c r="S137" s="75"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="122"/>
+      <c r="B138" s="133"/>
       <c r="D138" s="66">
         <v>22</v>
       </c>
@@ -27921,17 +27931,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UPC\Curso QP2526\EA\EA_ViveBook_TeamManagement\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C9EF1EE-E563-4AE7-BA9D-AD6B49CD6BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{42C71FD0-A47D-440F-8008-A765A550E6B0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
     <sheet name="WENJIE" sheetId="6" r:id="rId6"/>
     <sheet name="SCRUM" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -331,11 +325,26 @@
   <si>
     <t>Como usuario, quiero una interfaz clara y usable para navegar y utilizar la aplicación de forma sencilla.</t>
   </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Backend Validation fix</t>
+  </si>
+  <si>
+    <t>Posts page updated</t>
+  </si>
+  <si>
+    <t>Posts section implemented</t>
+  </si>
+  <si>
+    <t>Actualizar imagen Vivebook-Backend</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="52">
     <font>
       <sz val="11"/>
@@ -1651,6 +1660,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1684,18 +1705,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1713,7 +1722,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="120">
@@ -2597,9 +2606,9 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2636,6 +2645,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2644,26 +2654,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2696,7 +2686,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-0202-4B67-923C-40E83170638C}"/>
               </c:ext>
@@ -2720,7 +2710,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-0202-4B67-923C-40E83170638C}"/>
               </c:ext>
@@ -2744,7 +2734,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-0202-4B67-923C-40E83170638C}"/>
               </c:ext>
@@ -2768,7 +2758,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-0202-4B67-923C-40E83170638C}"/>
               </c:ext>
@@ -2792,7 +2782,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-0202-4B67-923C-40E83170638C}"/>
               </c:ext>
@@ -2841,7 +2831,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -2852,7 +2842,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -2915,18 +2905,18 @@
                   <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>31.5</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>62</c:v>
+                  <c:v>68.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>113</c:v>
+                  <c:v>116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-74A7-468D-8D7D-38DDB2193E63}"/>
             </c:ext>
@@ -2954,7 +2944,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3000,7 +2990,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3012,9 +3002,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3051,6 +3041,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3059,26 +3050,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3106,7 +3077,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-21A0-45C2-AA91-1B64D56EB349}"/>
               </c:ext>
@@ -3130,7 +3101,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-21A0-45C2-AA91-1B64D56EB349}"/>
               </c:ext>
@@ -3154,7 +3125,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-21A0-45C2-AA91-1B64D56EB349}"/>
               </c:ext>
@@ -3178,7 +3149,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-21A0-45C2-AA91-1B64D56EB349}"/>
               </c:ext>
@@ -3202,7 +3173,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-21A0-45C2-AA91-1B64D56EB349}"/>
               </c:ext>
@@ -3251,7 +3222,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -3262,7 +3233,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -3336,7 +3307,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-21A0-45C2-AA91-1B64D56EB349}"/>
             </c:ext>
@@ -3364,7 +3335,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3410,7 +3381,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3422,9 +3393,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3461,6 +3432,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3469,26 +3441,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3516,7 +3468,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-363C-448D-96B4-13656258F8BC}"/>
               </c:ext>
@@ -3540,7 +3492,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-363C-448D-96B4-13656258F8BC}"/>
               </c:ext>
@@ -3564,7 +3516,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-363C-448D-96B4-13656258F8BC}"/>
               </c:ext>
@@ -3588,7 +3540,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-363C-448D-96B4-13656258F8BC}"/>
               </c:ext>
@@ -3612,7 +3564,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-363C-448D-96B4-13656258F8BC}"/>
               </c:ext>
@@ -3661,7 +3613,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3671,7 +3623,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -3745,7 +3697,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-363C-448D-96B4-13656258F8BC}"/>
             </c:ext>
@@ -3773,7 +3725,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3819,7 +3771,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3831,9 +3783,9 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3870,6 +3822,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3878,26 +3831,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3925,7 +3858,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-56A7-4880-B2D2-9B38B2857788}"/>
               </c:ext>
@@ -3949,7 +3882,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-56A7-4880-B2D2-9B38B2857788}"/>
               </c:ext>
@@ -3973,7 +3906,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-56A7-4880-B2D2-9B38B2857788}"/>
               </c:ext>
@@ -3997,7 +3930,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-56A7-4880-B2D2-9B38B2857788}"/>
               </c:ext>
@@ -4021,7 +3954,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-56A7-4880-B2D2-9B38B2857788}"/>
               </c:ext>
@@ -4070,7 +4003,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -4081,7 +4014,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -4155,7 +4088,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-56A7-4880-B2D2-9B38B2857788}"/>
             </c:ext>
@@ -4183,7 +4116,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -4229,7 +4162,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4241,9 +4174,9 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4280,6 +4213,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4288,26 +4222,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4340,7 +4254,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
               </c:ext>
@@ -4364,7 +4278,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
               </c:ext>
@@ -4388,7 +4302,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
               </c:ext>
@@ -4412,7 +4326,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
               </c:ext>
@@ -4436,7 +4350,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
               </c:ext>
@@ -4485,7 +4399,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -4496,7 +4410,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -4570,7 +4484,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-8E38-4DB5-ACBE-F5EB69E3F75F}"/>
             </c:ext>
@@ -4598,7 +4512,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -4644,7 +4558,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4656,9 +4570,9 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4695,6 +4609,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4703,26 +4618,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4750,7 +4645,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-E1B6-4A9C-B4E4-BF935837EC3B}"/>
               </c:ext>
@@ -4774,7 +4669,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-E1B6-4A9C-B4E4-BF935837EC3B}"/>
               </c:ext>
@@ -4798,7 +4693,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-E1B6-4A9C-B4E4-BF935837EC3B}"/>
               </c:ext>
@@ -4822,7 +4717,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-E1B6-4A9C-B4E4-BF935837EC3B}"/>
               </c:ext>
@@ -4846,7 +4741,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-E1B6-4A9C-B4E4-BF935837EC3B}"/>
               </c:ext>
@@ -4895,7 +4790,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-ES"/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -4906,7 +4801,7 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <a:prstGeom prst="wedgeRectCallout">
@@ -4969,18 +4864,18 @@
                   <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6</c:v>
+                  <c:v>12.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-E1B6-4A9C-B4E4-BF935837EC3B}"/>
             </c:ext>
@@ -5008,7 +4903,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -5054,7 +4949,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -8931,7 +8826,7 @@
         <xdr:cNvPr id="3" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CEA09F4-D4FE-9445-6FD0-12C5BE0ED95F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CEA09F4-D4FE-9445-6FD0-12C5BE0ED95F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8967,7 +8862,7 @@
         <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02D6247F-43EA-45A4-8278-9AD8FE8658B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{02D6247F-43EA-45A4-8278-9AD8FE8658B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9005,7 +8900,7 @@
         <xdr:cNvPr id="5" name="Gráfico 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC29DC6-0B93-446F-8E9E-116E1D18528B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3BC29DC6-0B93-446F-8E9E-116E1D18528B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9043,7 +8938,7 @@
         <xdr:cNvPr id="6" name="Gráfico 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26738762-9A3C-4AE2-B035-ABDE35DC7BF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{26738762-9A3C-4AE2-B035-ABDE35DC7BF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9081,7 +8976,7 @@
         <xdr:cNvPr id="7" name="Gráfico 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE52FBF1-DEC6-4509-B79C-91D51A194682}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AE52FBF1-DEC6-4509-B79C-91D51A194682}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9119,7 +9014,7 @@
         <xdr:cNvPr id="8" name="Gráfico 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE1E114-D70A-4221-AF24-13B56C9E1B46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CCE1E114-D70A-4221-AF24-13B56C9E1B46}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9451,25 +9346,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469259-10C4-451F-B658-7DCDC5640A2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:P22"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="16" customWidth="1"/>
-    <col min="4" max="8" width="10.85546875" style="16"/>
-    <col min="9" max="9" width="2.5703125" style="21" customWidth="1"/>
-    <col min="10" max="15" width="10.85546875" style="16"/>
-    <col min="16" max="16" width="7.85546875" style="16" customWidth="1"/>
-    <col min="17" max="16384" width="10.85546875" style="16"/>
+    <col min="1" max="1" width="2.625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="16" customWidth="1"/>
+    <col min="4" max="8" width="10.875" style="16"/>
+    <col min="9" max="9" width="2.625" style="21" customWidth="1"/>
+    <col min="10" max="15" width="10.875" style="16"/>
+    <col min="16" max="16" width="7.875" style="16" customWidth="1"/>
+    <col min="17" max="16384" width="10.875" style="16"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1">
@@ -9639,12 +9534,12 @@
       </c>
       <c r="H10" s="69">
         <f>SUM(WENJIE!L5:L138)</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I10" s="41"/>
       <c r="J10" s="42">
         <f>SUM(D10:H10)</f>
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="K10" s="20"/>
     </row>
@@ -9683,12 +9578,12 @@
       </c>
       <c r="H12" s="72">
         <f>SUM(WENJIE!O5:O138)</f>
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="I12" s="45"/>
       <c r="J12" s="46">
         <f>SUM(D12:H12)</f>
-        <v>62</v>
+        <v>68.5</v>
       </c>
       <c r="K12" s="20"/>
     </row>
@@ -9727,12 +9622,12 @@
       </c>
       <c r="H14" s="75">
         <f>SUM(WENJIE!R5:R138)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I14" s="49"/>
       <c r="J14" s="50">
         <f>SUM(D14:H14)</f>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K14" s="20"/>
     </row>
@@ -9770,12 +9665,12 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>352.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row r="22" spans="5:11">
@@ -9797,80 +9692,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2CD9D50-0C20-46D0-8F5B-32DDB5716BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:S138"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.625" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1"/>
     <row r="2" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:19" ht="14.45" customHeight="1"/>
     <row r="5" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9902,7 +9797,7 @@
       <c r="S5" s="60"/>
     </row>
     <row r="6" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9932,7 +9827,7 @@
       <c r="S6" s="60"/>
     </row>
     <row r="7" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9962,7 +9857,7 @@
       <c r="S7" s="60"/>
     </row>
     <row r="8" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9992,7 +9887,7 @@
       <c r="S8" s="60"/>
     </row>
     <row r="9" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -10024,7 +9919,7 @@
       <c r="S9" s="60"/>
     </row>
     <row r="10" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -10054,7 +9949,7 @@
       <c r="S10" s="60"/>
     </row>
     <row r="11" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -10084,7 +9979,7 @@
       <c r="S11" s="60"/>
     </row>
     <row r="12" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -10116,7 +10011,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -10146,7 +10041,7 @@
       <c r="S13" s="60"/>
     </row>
     <row r="14" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -10176,7 +10071,7 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -10206,7 +10101,7 @@
       <c r="S15" s="60"/>
     </row>
     <row r="16" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -10238,7 +10133,7 @@
       <c r="S16" s="60"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -10268,7 +10163,7 @@
       <c r="S17" s="60"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -10298,7 +10193,7 @@
       <c r="S18" s="60"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -10330,7 +10225,7 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -10377,7 +10272,7 @@
       <c r="S21" s="101"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10409,7 +10304,7 @@
       <c r="S22" s="60"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10439,7 +10334,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10469,7 +10364,7 @@
       <c r="S24" s="60"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10499,7 +10394,7 @@
       <c r="S25" s="60"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10529,7 +10424,7 @@
       <c r="S26" s="60"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10563,7 +10458,7 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10593,7 +10488,7 @@
       <c r="S28" s="60"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10623,7 +10518,7 @@
       <c r="S29" s="60"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10653,7 +10548,7 @@
       <c r="S30" s="60"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10685,7 +10580,7 @@
       <c r="S31" s="60"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10715,7 +10610,7 @@
       <c r="S32" s="60"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10745,7 +10640,7 @@
       <c r="S33" s="60"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10777,7 +10672,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10807,7 +10702,7 @@
       <c r="S35" s="60"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10837,7 +10732,7 @@
       <c r="S36" s="60"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10867,7 +10762,7 @@
       <c r="S37" s="60"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10899,7 +10794,7 @@
       <c r="S38" s="60"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10931,7 +10826,7 @@
       <c r="S39" s="60"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10961,7 +10856,7 @@
       <c r="S40" s="60"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10993,7 +10888,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -11023,7 +10918,7 @@
       <c r="S42" s="60"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -11053,7 +10948,7 @@
       <c r="S43" s="60"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -11083,7 +10978,7 @@
       <c r="S44" s="60"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -11117,7 +11012,7 @@
       <c r="S45" s="60"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -11147,7 +11042,7 @@
       <c r="S46" s="60"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -11177,7 +11072,7 @@
       <c r="S47" s="60"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -11209,7 +11104,7 @@
       </c>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -11239,7 +11134,7 @@
       <c r="S49" s="60"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -11269,7 +11164,7 @@
       <c r="S50" s="60"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -11299,7 +11194,7 @@
       <c r="S51" s="60"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -11346,7 +11241,7 @@
       <c r="S53" s="101"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11378,7 +11273,7 @@
       <c r="S54" s="60"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11408,7 +11303,7 @@
       <c r="S55" s="60"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11440,7 +11335,7 @@
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11470,7 +11365,7 @@
       <c r="S57" s="60"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11500,7 +11395,7 @@
       <c r="S58" s="60"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11530,7 +11425,7 @@
       <c r="S59" s="60"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11560,7 +11455,7 @@
       <c r="S60" s="60"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11590,7 +11485,7 @@
       <c r="S61" s="60"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11619,8 +11514,8 @@
       </c>
       <c r="S62" s="60"/>
     </row>
-    <row r="63" spans="2:19">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:19" ht="14.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11649,8 +11544,8 @@
       </c>
       <c r="S63" s="60"/>
     </row>
-    <row r="64" spans="2:19">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:19" ht="14.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11681,8 +11576,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="2:19">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:19" ht="14.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11711,8 +11606,8 @@
       </c>
       <c r="S65" s="60"/>
     </row>
-    <row r="66" spans="2:19">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:19" ht="14.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11741,8 +11636,8 @@
       </c>
       <c r="S66" s="60"/>
     </row>
-    <row r="67" spans="2:19">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:19" ht="14.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11771,8 +11666,8 @@
       </c>
       <c r="S67" s="60"/>
     </row>
-    <row r="68" spans="2:19">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:19" ht="14.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11801,8 +11696,8 @@
       </c>
       <c r="S68" s="60"/>
     </row>
-    <row r="69" spans="2:19">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:19" ht="14.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11835,8 +11730,8 @@
       </c>
       <c r="S69" s="60"/>
     </row>
-    <row r="70" spans="2:19">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:19" ht="14.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11867,8 +11762,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="2:19">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:19" ht="14.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11897,8 +11792,8 @@
       </c>
       <c r="S71" s="60"/>
     </row>
-    <row r="72" spans="2:19">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:19" ht="14.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11927,8 +11822,8 @@
       </c>
       <c r="S72" s="60"/>
     </row>
-    <row r="73" spans="2:19">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:19" ht="14.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11957,8 +11852,8 @@
       </c>
       <c r="S73" s="60"/>
     </row>
-    <row r="74" spans="2:19">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:19" ht="14.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11989,8 +11884,8 @@
       </c>
       <c r="S74" s="60"/>
     </row>
-    <row r="75" spans="2:19">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:19" ht="14.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -12019,8 +11914,8 @@
       </c>
       <c r="S75" s="60"/>
     </row>
-    <row r="76" spans="2:19">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:19" ht="14.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -12049,8 +11944,8 @@
       </c>
       <c r="S76" s="60"/>
     </row>
-    <row r="77" spans="2:19">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:19" ht="14.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -12081,8 +11976,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="2:19">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:19" ht="14.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -12111,8 +12006,8 @@
       </c>
       <c r="S78" s="60"/>
     </row>
-    <row r="79" spans="2:19">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:19" ht="14.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -12141,8 +12036,8 @@
       </c>
       <c r="S79" s="60"/>
     </row>
-    <row r="80" spans="2:19">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:19" ht="14.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -12171,8 +12066,8 @@
       </c>
       <c r="S80" s="60"/>
     </row>
-    <row r="81" spans="2:19">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:19" ht="14.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -12201,8 +12096,8 @@
       </c>
       <c r="S81" s="60"/>
     </row>
-    <row r="82" spans="2:19">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:19" ht="14.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -12231,8 +12126,8 @@
       </c>
       <c r="S82" s="60"/>
     </row>
-    <row r="83" spans="2:19">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:19" ht="14.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -12279,8 +12174,8 @@
       <c r="R84" s="100"/>
       <c r="S84" s="101"/>
     </row>
-    <row r="85" spans="2:19">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:19" ht="14.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -12313,8 +12208,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="2:19">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:19" ht="14.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -12343,8 +12238,8 @@
       </c>
       <c r="S86" s="60"/>
     </row>
-    <row r="87" spans="2:19">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:19" ht="14.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12373,8 +12268,8 @@
       </c>
       <c r="S87" s="60"/>
     </row>
-    <row r="88" spans="2:19">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:19" ht="14.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12403,8 +12298,8 @@
       </c>
       <c r="S88" s="60"/>
     </row>
-    <row r="89" spans="2:19">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:19" ht="14.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12435,8 +12330,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="2:19">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:19" ht="14.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12463,8 +12358,8 @@
       </c>
       <c r="S90" s="60"/>
     </row>
-    <row r="91" spans="2:19">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:19" ht="14.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12493,8 +12388,8 @@
       </c>
       <c r="S91" s="60"/>
     </row>
-    <row r="92" spans="2:19">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:19" ht="14.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12525,8 +12420,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="2:19">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:19" ht="14.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12555,8 +12450,8 @@
       </c>
       <c r="S93" s="60"/>
     </row>
-    <row r="94" spans="2:19">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:19" ht="14.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12585,8 +12480,8 @@
       </c>
       <c r="S94" s="60"/>
     </row>
-    <row r="95" spans="2:19">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:19" ht="14.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12615,8 +12510,8 @@
       </c>
       <c r="S95" s="60"/>
     </row>
-    <row r="96" spans="2:19">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:19" ht="14.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12645,8 +12540,8 @@
       </c>
       <c r="S96" s="60"/>
     </row>
-    <row r="97" spans="2:19">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:19" ht="14.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12675,8 +12570,8 @@
       </c>
       <c r="S97" s="60"/>
     </row>
-    <row r="98" spans="2:19">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:19" ht="14.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12705,8 +12600,8 @@
       </c>
       <c r="S98" s="60"/>
     </row>
-    <row r="99" spans="2:19">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:19" ht="14.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12735,8 +12630,8 @@
       </c>
       <c r="S99" s="60"/>
     </row>
-    <row r="100" spans="2:19">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:19" ht="14.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12765,8 +12660,8 @@
       </c>
       <c r="S100" s="60"/>
     </row>
-    <row r="101" spans="2:19">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:19" ht="14.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12795,8 +12690,8 @@
       </c>
       <c r="S101" s="60"/>
     </row>
-    <row r="102" spans="2:19">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:19" ht="14.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12825,8 +12720,8 @@
       </c>
       <c r="S102" s="60"/>
     </row>
-    <row r="103" spans="2:19">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:19" ht="14.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12855,8 +12750,8 @@
       </c>
       <c r="S103" s="60"/>
     </row>
-    <row r="104" spans="2:19">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:19" ht="14.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12885,8 +12780,8 @@
       </c>
       <c r="S104" s="60"/>
     </row>
-    <row r="105" spans="2:19">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:19" ht="14.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12915,8 +12810,8 @@
       </c>
       <c r="S105" s="60"/>
     </row>
-    <row r="106" spans="2:19">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:19" ht="14.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12945,8 +12840,8 @@
       </c>
       <c r="S106" s="60"/>
     </row>
-    <row r="107" spans="2:19">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:19" ht="14.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12975,8 +12870,8 @@
       </c>
       <c r="S107" s="60"/>
     </row>
-    <row r="108" spans="2:19">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:19" ht="14.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -13005,8 +12900,8 @@
       </c>
       <c r="S108" s="60"/>
     </row>
-    <row r="109" spans="2:19">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:19" ht="14.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -13035,8 +12930,8 @@
       </c>
       <c r="S109" s="60"/>
     </row>
-    <row r="110" spans="2:19">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:19" ht="14.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -13065,8 +12960,8 @@
       </c>
       <c r="S110" s="60"/>
     </row>
-    <row r="111" spans="2:19">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:19" ht="14.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -13095,8 +12990,8 @@
       </c>
       <c r="S111" s="60"/>
     </row>
-    <row r="112" spans="2:19">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:19" ht="14.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -13125,8 +13020,8 @@
       </c>
       <c r="S112" s="60"/>
     </row>
-    <row r="113" spans="2:19">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:19" ht="14.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -13155,8 +13050,8 @@
       </c>
       <c r="S113" s="60"/>
     </row>
-    <row r="114" spans="2:19">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:19" ht="14.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -13185,8 +13080,8 @@
       </c>
       <c r="S114" s="60"/>
     </row>
-    <row r="115" spans="2:19">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:19" ht="14.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -13234,7 +13129,7 @@
       <c r="S116" s="101"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -13265,8 +13160,8 @@
       </c>
       <c r="S117" s="60"/>
     </row>
-    <row r="118" spans="2:19">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:19" ht="14.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -13295,8 +13190,8 @@
       </c>
       <c r="S118" s="60"/>
     </row>
-    <row r="119" spans="2:19">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:19" ht="14.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -13325,8 +13220,8 @@
       </c>
       <c r="S119" s="60"/>
     </row>
-    <row r="120" spans="2:19">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:19" ht="14.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -13355,8 +13250,8 @@
       </c>
       <c r="S120" s="60"/>
     </row>
-    <row r="121" spans="2:19">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:19" ht="14.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13385,8 +13280,8 @@
       </c>
       <c r="S121" s="60"/>
     </row>
-    <row r="122" spans="2:19">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:19" ht="14.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13415,8 +13310,8 @@
       </c>
       <c r="S122" s="60"/>
     </row>
-    <row r="123" spans="2:19">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:19" ht="14.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13445,8 +13340,8 @@
       </c>
       <c r="S123" s="60"/>
     </row>
-    <row r="124" spans="2:19">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:19" ht="14.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13475,8 +13370,8 @@
       </c>
       <c r="S124" s="60"/>
     </row>
-    <row r="125" spans="2:19">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:19" ht="14.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13505,8 +13400,8 @@
       </c>
       <c r="S125" s="60"/>
     </row>
-    <row r="126" spans="2:19">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:19" ht="14.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13535,8 +13430,8 @@
       </c>
       <c r="S126" s="60"/>
     </row>
-    <row r="127" spans="2:19">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:19" ht="14.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13565,8 +13460,8 @@
       </c>
       <c r="S127" s="60"/>
     </row>
-    <row r="128" spans="2:19">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:19" ht="14.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13595,8 +13490,8 @@
       </c>
       <c r="S128" s="60"/>
     </row>
-    <row r="129" spans="2:19">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:19" ht="14.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13625,8 +13520,8 @@
       </c>
       <c r="S129" s="60"/>
     </row>
-    <row r="130" spans="2:19">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:19" ht="14.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13655,8 +13550,8 @@
       </c>
       <c r="S130" s="60"/>
     </row>
-    <row r="131" spans="2:19">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:19" ht="14.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13685,8 +13580,8 @@
       </c>
       <c r="S131" s="60"/>
     </row>
-    <row r="132" spans="2:19">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:19" ht="14.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13715,8 +13610,8 @@
       </c>
       <c r="S132" s="60"/>
     </row>
-    <row r="133" spans="2:19">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:19" ht="14.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13745,8 +13640,8 @@
       </c>
       <c r="S133" s="60"/>
     </row>
-    <row r="134" spans="2:19">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:19" ht="14.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13775,8 +13670,8 @@
       </c>
       <c r="S134" s="60"/>
     </row>
-    <row r="135" spans="2:19">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:19" ht="14.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13805,8 +13700,8 @@
       </c>
       <c r="S135" s="60"/>
     </row>
-    <row r="136" spans="2:19">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:19" ht="14.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13835,8 +13730,8 @@
       </c>
       <c r="S136" s="60"/>
     </row>
-    <row r="137" spans="2:19">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:19" ht="14.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13865,8 +13760,8 @@
       </c>
       <c r="S137" s="60"/>
     </row>
-    <row r="138" spans="2:19">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:19" ht="14.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13897,17 +13792,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="119" priority="5" operator="equal">
@@ -13965,80 +13860,80 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88D3A4C-A797-4BB6-9317-62E07FE783D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.625" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -14072,7 +13967,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -14104,7 +13999,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -14136,7 +14031,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -14168,7 +14063,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -14202,7 +14097,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -14234,7 +14129,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -14266,7 +14161,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -14300,7 +14195,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -14332,7 +14227,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14364,7 +14259,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14396,7 +14291,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14430,7 +14325,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14462,7 +14357,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14494,7 +14389,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14528,7 +14423,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14579,7 +14474,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14613,7 +14508,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14645,7 +14540,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14677,7 +14572,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14709,7 +14604,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14741,7 +14636,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14777,7 +14672,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14809,7 +14704,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14841,7 +14736,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14873,7 +14768,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14907,7 +14802,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14939,7 +14834,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14971,7 +14866,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -15005,7 +14900,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -15037,7 +14932,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -15069,7 +14964,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -15101,7 +14996,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -15135,7 +15030,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -15169,7 +15064,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -15201,7 +15096,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -15235,7 +15130,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -15267,7 +15162,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -15299,7 +15194,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -15331,7 +15226,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15367,7 +15262,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15399,7 +15294,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15431,7 +15326,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15465,7 +15360,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15497,7 +15392,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15529,7 +15424,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15561,7 +15456,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15612,7 +15507,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15646,7 +15541,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15678,7 +15573,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15712,7 +15607,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15744,7 +15639,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15776,7 +15671,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15808,7 +15703,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15840,7 +15735,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15872,7 +15767,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15903,8 +15798,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" ht="14.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15935,8 +15830,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" ht="14.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15969,8 +15864,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" ht="14.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -16001,8 +15896,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" ht="14.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -16033,8 +15928,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" ht="14.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -16065,8 +15960,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" ht="14.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -16097,8 +15992,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" ht="14.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -16133,8 +16028,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" ht="14.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -16167,8 +16062,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" ht="14.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -16199,8 +16094,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" ht="14.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -16231,8 +16126,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" ht="14.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -16263,8 +16158,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" ht="14.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -16297,8 +16192,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" ht="14.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -16329,8 +16224,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" ht="14.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -16361,8 +16256,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" ht="14.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16395,8 +16290,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" ht="14.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16427,8 +16322,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" ht="14.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16459,8 +16354,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" ht="14.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16491,8 +16386,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" ht="14.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16523,8 +16418,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" ht="14.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16555,8 +16450,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" ht="14.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16607,8 +16502,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" ht="14.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16643,8 +16538,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" ht="14.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16675,8 +16570,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" ht="14.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16707,8 +16602,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" ht="14.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16739,8 +16634,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" ht="14.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16773,8 +16668,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" ht="14.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16805,8 +16700,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" ht="14.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16837,8 +16732,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" ht="14.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16871,8 +16766,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" ht="14.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16903,8 +16798,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" ht="14.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16935,8 +16830,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" ht="14.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16967,8 +16862,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" ht="14.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16999,8 +16894,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" ht="14.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -17031,8 +16926,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" ht="14.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -17063,8 +16958,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" ht="14.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -17095,8 +16990,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" ht="14.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -17127,8 +17022,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" ht="14.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -17159,8 +17054,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" ht="14.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -17191,8 +17086,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" ht="14.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -17223,8 +17118,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" ht="14.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -17255,8 +17150,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" ht="14.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -17287,8 +17182,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" ht="14.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -17319,8 +17214,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" ht="14.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -17351,8 +17246,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" ht="14.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17383,8 +17278,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" ht="14.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17415,8 +17310,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" ht="14.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17447,8 +17342,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" ht="14.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17479,8 +17374,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" ht="14.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17511,8 +17406,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" ht="14.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17543,8 +17438,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" ht="14.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17575,8 +17470,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" ht="14.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17628,7 +17523,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17661,8 +17556,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" ht="14.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17693,8 +17588,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" ht="14.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17725,8 +17620,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" ht="14.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17757,8 +17652,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" ht="14.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17789,8 +17684,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" ht="14.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17821,8 +17716,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" ht="14.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17853,8 +17748,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" ht="14.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17885,8 +17780,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" ht="14.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17917,8 +17812,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" ht="14.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17949,8 +17844,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" ht="14.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17981,8 +17876,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" ht="14.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -18013,8 +17908,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" ht="14.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -18045,8 +17940,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" ht="14.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -18077,8 +17972,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" ht="14.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -18109,8 +18004,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" ht="14.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -18141,8 +18036,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" ht="14.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -18173,8 +18068,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" ht="14.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -18205,8 +18100,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" ht="14.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -18237,8 +18132,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" ht="14.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -18269,8 +18164,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" ht="14.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -18301,8 +18196,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" ht="14.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -18335,17 +18230,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="109" priority="25" operator="equal">
@@ -18493,80 +18388,80 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19BC2A3-3CFD-4E99-B7D2-ED7A63008A84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.625" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18600,7 +18495,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18632,7 +18527,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18664,7 +18559,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18696,7 +18591,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18730,7 +18625,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18762,7 +18657,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18794,7 +18689,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18828,7 +18723,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18860,7 +18755,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18892,7 +18787,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18924,7 +18819,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18958,7 +18853,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18990,7 +18885,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -19022,7 +18917,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -19056,7 +18951,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -19107,7 +19002,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -19141,7 +19036,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -19173,7 +19068,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -19205,7 +19100,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -19237,7 +19132,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -19269,7 +19164,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -19305,7 +19200,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -19337,7 +19232,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -19369,7 +19264,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -19401,7 +19296,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19435,7 +19330,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19467,7 +19362,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19499,7 +19394,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19533,7 +19428,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19565,7 +19460,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19597,7 +19492,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19629,7 +19524,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19665,7 +19560,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19697,7 +19592,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19729,7 +19624,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19763,7 +19658,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19795,7 +19690,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19827,7 +19722,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19859,7 +19754,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19895,7 +19790,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19927,7 +19822,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19959,7 +19854,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19993,7 +19888,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -20025,7 +19920,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -20057,7 +19952,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -20089,7 +19984,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -20140,7 +20035,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -20174,7 +20069,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -20206,7 +20101,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -20240,7 +20135,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -20272,7 +20167,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -20304,7 +20199,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -20336,7 +20231,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -20368,7 +20263,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -20400,7 +20295,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -20431,8 +20326,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" ht="14.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20463,8 +20358,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" ht="14.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20497,8 +20392,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" ht="14.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20529,8 +20424,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" ht="14.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20561,8 +20456,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" ht="14.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20593,8 +20488,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" ht="14.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20629,8 +20524,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" ht="14.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20661,8 +20556,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" ht="14.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20695,8 +20590,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" ht="14.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20727,8 +20622,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" ht="14.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20759,8 +20654,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" ht="14.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20791,8 +20686,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" ht="14.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20825,8 +20720,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" ht="14.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20857,8 +20752,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" ht="14.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20889,8 +20784,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" ht="14.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20923,8 +20818,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" ht="14.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20955,8 +20850,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" ht="14.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20987,8 +20882,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" ht="14.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -21019,8 +20914,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" ht="14.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -21051,8 +20946,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" ht="14.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -21083,8 +20978,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" ht="14.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -21135,8 +21030,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" ht="14.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -21171,8 +21066,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" ht="14.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -21203,8 +21098,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" ht="14.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -21235,8 +21130,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" ht="14.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -21267,8 +21162,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" ht="14.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -21301,8 +21196,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" ht="14.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -21333,8 +21228,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" ht="14.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -21365,8 +21260,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" ht="14.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -21399,8 +21294,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" ht="14.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -21431,8 +21326,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" ht="14.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21463,8 +21358,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" ht="14.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21495,8 +21390,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" ht="14.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21527,8 +21422,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" ht="14.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21559,8 +21454,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" ht="14.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21591,8 +21486,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" ht="14.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21623,8 +21518,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" ht="14.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21655,8 +21550,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" ht="14.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21687,8 +21582,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" ht="14.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21719,8 +21614,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" ht="14.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21751,8 +21646,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" ht="14.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21783,8 +21678,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" ht="14.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21815,8 +21710,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" ht="14.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21847,8 +21742,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" ht="14.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21879,8 +21774,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" ht="14.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21911,8 +21806,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" ht="14.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21943,8 +21838,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" ht="14.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21975,8 +21870,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" ht="14.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -22007,8 +21902,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" ht="14.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -22039,8 +21934,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" ht="14.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -22071,8 +21966,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" ht="14.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -22103,8 +21998,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" ht="14.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -22156,7 +22051,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -22189,8 +22084,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" ht="14.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -22221,8 +22116,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" ht="14.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -22253,8 +22148,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" ht="14.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -22285,8 +22180,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" ht="14.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -22317,8 +22212,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" ht="14.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -22349,8 +22244,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" ht="14.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -22381,8 +22276,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" ht="14.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -22413,8 +22308,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" ht="14.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22445,8 +22340,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" ht="14.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22477,8 +22372,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" ht="14.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22509,8 +22404,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" ht="14.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22541,8 +22436,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" ht="14.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22573,8 +22468,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" ht="14.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22605,8 +22500,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" ht="14.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22637,8 +22532,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" ht="14.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22669,8 +22564,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" ht="14.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22701,8 +22596,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" ht="14.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22733,8 +22628,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" ht="14.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22765,8 +22660,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" ht="14.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -22797,8 +22692,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" ht="14.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -22829,8 +22724,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" ht="14.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -22863,17 +22758,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="81" priority="25" operator="equal">
@@ -23021,80 +22916,80 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1808E512-9086-4256-BF9F-9A0636DA67FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:V190"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.625" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -23128,7 +23023,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -23160,7 +23055,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -23192,7 +23087,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -23224,7 +23119,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -23258,7 +23153,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -23290,7 +23185,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -23322,7 +23217,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -23356,7 +23251,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -23388,7 +23283,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -23420,7 +23315,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -23452,7 +23347,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -23486,7 +23381,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -23518,7 +23413,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -23550,7 +23445,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -23584,7 +23479,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -23635,7 +23530,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -23669,7 +23564,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -23701,7 +23596,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -23733,7 +23628,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -23765,7 +23660,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -23797,7 +23692,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -23833,7 +23728,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -23865,7 +23760,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -23897,7 +23792,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -23929,7 +23824,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -23963,7 +23858,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -23995,7 +23890,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -24027,7 +23922,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -24061,7 +23956,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -24093,7 +23988,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -24125,7 +24020,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -24161,7 +24056,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -24195,7 +24090,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -24227,7 +24122,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -24261,7 +24156,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -24295,7 +24190,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -24327,7 +24222,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -24359,7 +24254,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -24391,7 +24286,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -24427,7 +24322,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -24459,7 +24354,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -24491,7 +24386,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -24525,7 +24420,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -24557,7 +24452,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -24589,7 +24484,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -24621,7 +24516,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -24672,7 +24567,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -24706,7 +24601,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -24738,7 +24633,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -24772,7 +24667,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -24804,7 +24699,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -24836,7 +24731,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -24868,7 +24763,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -24900,7 +24795,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -24932,7 +24827,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -24963,8 +24858,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" ht="14.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -24995,8 +24890,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" ht="14.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -25029,8 +24924,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" ht="14.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -25061,8 +24956,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" ht="14.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -25093,8 +24988,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" ht="14.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -25125,8 +25020,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" ht="14.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -25157,8 +25052,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" ht="14.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -25189,8 +25084,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" ht="14.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -25223,8 +25118,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" ht="14.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -25255,8 +25150,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" ht="14.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -25287,8 +25182,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" ht="14.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -25319,8 +25214,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" ht="14.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -25353,8 +25248,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" ht="14.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -25385,8 +25280,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" ht="14.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -25417,8 +25312,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" ht="14.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -25451,8 +25346,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" ht="14.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -25483,8 +25378,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" ht="14.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -25515,8 +25410,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" ht="14.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -25547,8 +25442,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" ht="14.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -25579,8 +25474,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" ht="14.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -25611,8 +25506,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" ht="14.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -25663,8 +25558,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" ht="14.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -25697,8 +25592,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" ht="14.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -25727,8 +25622,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" ht="14.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -25759,8 +25654,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" ht="14.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -25791,8 +25686,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" ht="14.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -25825,8 +25720,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" ht="14.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -25857,8 +25752,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" ht="14.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -25889,8 +25784,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" ht="14.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -25923,8 +25818,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" ht="14.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -25955,8 +25850,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" ht="14.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -25987,8 +25882,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" ht="14.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -26019,8 +25914,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" ht="14.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -26051,8 +25946,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" ht="14.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -26083,8 +25978,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" ht="14.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -26115,8 +26010,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" ht="14.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -26147,8 +26042,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" ht="14.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -26179,8 +26074,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" ht="14.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -26211,8 +26106,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" ht="14.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -26243,8 +26138,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" ht="14.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -26275,8 +26170,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" ht="14.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -26307,8 +26202,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" ht="14.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -26339,8 +26234,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" ht="14.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -26371,8 +26266,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" ht="14.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -26403,8 +26298,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" ht="14.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -26435,8 +26330,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" ht="14.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -26467,8 +26362,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" ht="14.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -26499,8 +26394,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" ht="14.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -26531,8 +26426,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" ht="14.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -26563,8 +26458,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" ht="14.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -26595,8 +26490,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" ht="14.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -26627,8 +26522,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" ht="14.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -26680,7 +26575,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -26713,8 +26608,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" ht="14.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -26745,8 +26640,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" ht="14.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -26777,8 +26672,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" ht="14.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -26809,8 +26704,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" ht="14.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -26841,8 +26736,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" ht="14.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -26873,8 +26768,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" ht="14.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -26905,8 +26800,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" ht="14.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -26937,8 +26832,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" ht="14.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -26969,8 +26864,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" ht="14.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -27001,8 +26896,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" ht="14.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -27033,8 +26928,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" ht="14.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -27065,8 +26960,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" ht="14.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -27097,8 +26992,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" ht="14.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -27129,8 +27024,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" ht="14.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -27161,8 +27056,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" ht="14.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -27193,8 +27088,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" ht="14.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -27225,8 +27120,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" ht="14.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -27257,8 +27152,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" ht="14.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -27289,8 +27184,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" ht="14.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -27321,8 +27216,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" ht="14.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -27353,8 +27248,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" ht="14.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -27754,80 +27649,80 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9F5440-2F33-4399-87DF-E31A71076149}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.625" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -27861,7 +27756,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -27893,7 +27788,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -27925,7 +27820,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -27957,7 +27852,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -27991,7 +27886,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -28023,7 +27918,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -28055,7 +27950,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -28089,7 +27984,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -28121,7 +28016,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -28153,7 +28048,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -28185,7 +28080,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -28219,7 +28114,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -28251,7 +28146,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -28283,7 +28178,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -28317,7 +28212,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -28368,7 +28263,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -28402,7 +28297,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -28434,7 +28329,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -28466,7 +28361,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -28498,7 +28393,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -28530,7 +28425,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -28566,7 +28461,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -28598,7 +28493,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -28630,7 +28525,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -28662,7 +28557,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -28696,7 +28591,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -28728,7 +28623,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -28760,7 +28655,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -28794,7 +28689,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -28826,7 +28721,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -28858,7 +28753,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -28890,7 +28785,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -28924,7 +28819,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -28958,7 +28853,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -28994,7 +28889,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -29028,7 +28923,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -29060,7 +28955,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -29092,7 +28987,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -29124,7 +29019,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -29139,14 +29034,14 @@
       <c r="J45" s="57"/>
       <c r="K45" s="90"/>
       <c r="L45" s="78">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M45" s="58" t="s">
         <v>32</v>
       </c>
       <c r="N45" s="90"/>
       <c r="O45" s="79">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P45" s="59" t="s">
         <v>33</v>
@@ -29160,7 +29055,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -29192,7 +29087,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -29224,7 +29119,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -29258,7 +29153,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -29290,7 +29185,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -29322,7 +29217,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -29354,7 +29249,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -29405,7 +29300,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -29439,7 +29334,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -29471,7 +29366,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -29505,7 +29400,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -29539,7 +29434,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -29573,7 +29468,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -29605,7 +29500,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -29637,7 +29532,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -29669,7 +29564,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -29700,8 +29595,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" ht="14.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -29732,8 +29627,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" ht="14.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -29766,8 +29661,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" ht="14.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -29798,8 +29693,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" ht="14.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -29830,8 +29725,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" ht="14.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -29862,8 +29757,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" ht="14.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -29894,8 +29789,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" ht="14.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -29930,8 +29825,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" ht="14.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -29964,8 +29859,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" ht="14.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -29996,8 +29891,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" ht="14.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -30030,8 +29925,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" ht="14.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -30062,8 +29957,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" ht="14.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -30083,7 +29978,7 @@
       <c r="M74" s="58"/>
       <c r="N74" s="90"/>
       <c r="O74" s="79">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P74" s="59" t="s">
         <v>37</v>
@@ -30096,8 +29991,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" ht="14.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -30128,8 +30023,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" ht="14.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -30160,8 +30055,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" ht="14.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -30194,8 +30089,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" ht="14.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -30226,8 +30121,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" ht="14.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -30258,8 +30153,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" ht="14.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -30290,8 +30185,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" ht="14.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -30322,8 +30217,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" ht="14.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -30356,8 +30251,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" ht="14.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -30408,8 +30303,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" ht="14.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -30444,8 +30339,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" ht="14.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -30480,8 +30375,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" ht="14.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -30512,8 +30407,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" ht="14.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -30544,8 +30439,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" ht="14.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -30570,7 +30465,7 @@
       <c r="P89" s="59"/>
       <c r="Q89" s="90"/>
       <c r="R89" s="80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S89" s="60" t="s">
         <v>39</v>
@@ -30578,8 +30473,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" ht="14.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -30610,8 +30505,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" ht="14.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -30642,25 +30537,31 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" ht="14.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
-      <c r="F92" s="76">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4"/>
+      <c r="F92" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="H92" s="90"/>
-      <c r="I92" s="77">
-        <v>0</v>
-      </c>
-      <c r="J92" s="57"/>
+      <c r="I92" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="J92" s="57" t="s">
+        <v>98</v>
+      </c>
       <c r="K92" s="90"/>
-      <c r="L92" s="78">
-        <v>0</v>
-      </c>
-      <c r="M92" s="58"/>
+      <c r="L92" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="M92" s="58" t="s">
+        <v>99</v>
+      </c>
       <c r="N92" s="90"/>
       <c r="O92" s="79">
         <v>0</v>
@@ -30676,8 +30577,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" ht="14.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -30708,8 +30609,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" ht="14.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -30740,8 +30641,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" ht="14.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -30766,14 +30667,16 @@
       <c r="P95" s="59"/>
       <c r="Q95" s="90"/>
       <c r="R95" s="80">
-        <v>0</v>
-      </c>
-      <c r="S95" s="60"/>
+        <v>1</v>
+      </c>
+      <c r="S95" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" ht="14.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -30804,8 +30707,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" ht="14.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -30836,8 +30739,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" ht="14.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -30868,8 +30771,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" ht="14.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -30900,8 +30803,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" ht="14.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -30932,8 +30835,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" ht="14.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -30964,8 +30867,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" ht="14.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -30996,8 +30899,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" ht="14.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -31028,8 +30931,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" ht="14.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -31060,8 +30963,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" ht="14.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -31092,8 +30995,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" ht="14.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -31124,8 +31027,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" ht="14.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -31156,8 +31059,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" ht="14.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -31188,8 +31091,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" ht="14.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -31220,8 +31123,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" ht="14.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -31252,8 +31155,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" ht="14.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -31284,8 +31187,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" ht="14.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -31316,8 +31219,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" ht="14.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -31348,8 +31251,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" ht="14.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -31380,8 +31283,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" ht="14.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -31433,7 +31336,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -31466,8 +31369,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" ht="14.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -31498,8 +31401,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" ht="14.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -31530,8 +31433,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" ht="14.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -31562,8 +31465,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" ht="14.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -31594,8 +31497,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" ht="14.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -31626,8 +31529,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" ht="14.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -31658,8 +31561,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" ht="14.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -31690,8 +31593,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" ht="14.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -31722,8 +31625,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" ht="14.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -31754,8 +31657,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" ht="14.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -31786,8 +31689,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" ht="14.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -31818,8 +31721,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" ht="14.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -31850,8 +31753,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" ht="14.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -31882,8 +31785,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" ht="14.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -31914,8 +31817,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" ht="14.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -31946,8 +31849,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" ht="14.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -31978,8 +31881,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" ht="14.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -32010,8 +31913,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" ht="14.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -32042,8 +31945,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" ht="14.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -32074,8 +31977,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" ht="14.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -32106,8 +32009,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" ht="14.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -32140,17 +32043,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
@@ -32288,19 +32191,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653D0077-DF0B-4D1F-9CC1-B4A9B63AFE0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:H119"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="14" customWidth="1"/>
     <col min="4" max="4" width="13" style="14" customWidth="1"/>
-    <col min="5" max="5" width="150.5703125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="2.5703125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" style="14" customWidth="1"/>
-    <col min="9" max="16384" width="10.85546875" style="14"/>
+    <col min="5" max="5" width="150.625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="2.625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="10.875" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="12" customHeight="1"/>
@@ -32607,10 +32510,10 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E12" r:id="rId1" xr:uid="{18FEECD5-C155-4CC9-AA11-621E630C9E55}"/>
-    <hyperlink ref="E13" r:id="rId2" xr:uid="{78ABA37A-638D-4094-AC36-FFAFEECCA06C}"/>
-    <hyperlink ref="E14" r:id="rId3" xr:uid="{29BAD511-7466-4514-8442-4E4FC306B87F}"/>
-    <hyperlink ref="E15" r:id="rId4" xr:uid="{1A21F5A7-AECE-4A82-A236-DC8AAAF85D52}"/>
+    <hyperlink ref="E12" r:id="rId1"/>
+    <hyperlink ref="E13" r:id="rId2"/>
+    <hyperlink ref="E14" r:id="rId3"/>
+    <hyperlink ref="E15" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UPC\Curso QP2526\EA\EA_ViveBook_TeamManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D02898-24BC-4BA1-9FC9-94F2F5CF2388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C0A6F-5972-4142-A727-B64E39E4BCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>Actualizar imagen Vivebook-Backend</t>
+  </si>
+  <si>
+    <t>Busqueda por indice para usuarios, libros y posts</t>
   </si>
 </sst>
 </file>
@@ -1666,6 +1669,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1699,18 +1714,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1728,7 +1731,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="66">
@@ -2236,7 +2239,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2546,7 +2549,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>106.5</c:v>
+                  <c:v>109.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39.5</c:v>
@@ -2651,7 +2654,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3061,7 +3064,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3470,7 +3473,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3880,7 +3883,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4295,7 +4298,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4600,7 +4603,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
@@ -9097,19 +9100,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:P22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="24.08984375" style="16" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="16" customWidth="1"/>
-    <col min="4" max="8" width="10.90625" style="16"/>
-    <col min="9" max="9" width="2.6328125" style="21" customWidth="1"/>
-    <col min="10" max="15" width="10.90625" style="16"/>
-    <col min="16" max="16" width="7.90625" style="16" customWidth="1"/>
-    <col min="17" max="16384" width="10.90625" style="16"/>
+    <col min="1" max="1" width="2.5703125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="16" customWidth="1"/>
+    <col min="4" max="8" width="10.85546875" style="16"/>
+    <col min="9" max="9" width="2.5703125" style="21" customWidth="1"/>
+    <col min="10" max="15" width="10.85546875" style="16"/>
+    <col min="16" max="16" width="7.85546875" style="16" customWidth="1"/>
+    <col min="17" max="16384" width="10.85546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="102" t="s">
         <v>0</v>
       </c>
@@ -9128,7 +9131,7 @@
       <c r="O2" s="103"/>
       <c r="P2" s="104"/>
     </row>
-    <row r="4" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
         <v>1</v>
       </c>
@@ -9153,7 +9156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="25"/>
       <c r="C5" s="17"/>
       <c r="D5" s="26"/>
@@ -9164,7 +9167,7 @@
       <c r="I5" s="27"/>
       <c r="J5" s="26"/>
     </row>
-    <row r="6" spans="1:16" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19"/>
       <c r="B6" s="28" t="s">
         <v>8</v>
@@ -9188,16 +9191,16 @@
       </c>
       <c r="H6" s="63">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="31">
         <f>SUM(D6:H6)</f>
-        <v>106.5</v>
+        <v>109.5</v>
       </c>
       <c r="K6" s="20"/>
     </row>
-    <row r="7" spans="1:16" s="21" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" s="21" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="33"/>
       <c r="D7" s="34"/>
@@ -9208,7 +9211,7 @@
       <c r="I7" s="34"/>
       <c r="J7" s="35"/>
     </row>
-    <row r="8" spans="1:16" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="B8" s="36" t="s">
         <v>9</v>
@@ -9241,7 +9244,7 @@
       </c>
       <c r="K8" s="20"/>
     </row>
-    <row r="9" spans="1:16" s="21" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" s="21" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="39"/>
       <c r="C9" s="33"/>
       <c r="D9" s="34"/>
@@ -9252,7 +9255,7 @@
       <c r="I9" s="34"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:16" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="40" t="s">
         <v>10</v>
@@ -9285,7 +9288,7 @@
       </c>
       <c r="K10" s="20"/>
     </row>
-    <row r="11" spans="1:16" s="21" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" s="21" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="43"/>
       <c r="C11" s="33"/>
       <c r="D11" s="34"/>
@@ -9296,7 +9299,7 @@
       <c r="I11" s="34"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:16" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="44" t="s">
         <v>11</v>
@@ -9329,7 +9332,7 @@
       </c>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:16" s="21" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" s="21" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="47"/>
       <c r="C13" s="33"/>
       <c r="D13" s="34"/>
@@ -9340,7 +9343,7 @@
       <c r="I13" s="34"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:16" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
       <c r="B14" s="48" t="s">
         <v>12</v>
@@ -9373,7 +9376,7 @@
       </c>
       <c r="K14" s="20"/>
     </row>
-    <row r="15" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="51"/>
@@ -9384,7 +9387,7 @@
       <c r="I15" s="53"/>
       <c r="J15" s="54"/>
     </row>
-    <row r="16" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
         <v>13</v>
       </c>
@@ -9407,15 +9410,15 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>362.5</v>
-      </c>
-    </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.35">
+        <v>365.5</v>
+      </c>
+    </row>
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
@@ -9436,78 +9439,78 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:S138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+    <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
-    </row>
-    <row r="3" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="S2" s="109"/>
+    </row>
+    <row r="3" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-    </row>
-    <row r="4" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+    </row>
+    <row r="4" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9538,8 +9541,8 @@
       </c>
       <c r="S5" s="60"/>
     </row>
-    <row r="6" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117"/>
+    <row r="6" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9568,8 +9571,8 @@
       </c>
       <c r="S6" s="60"/>
     </row>
-    <row r="7" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
+    <row r="7" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9598,8 +9601,8 @@
       </c>
       <c r="S7" s="60"/>
     </row>
-    <row r="8" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="117"/>
+    <row r="8" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9628,8 +9631,8 @@
       </c>
       <c r="S8" s="60"/>
     </row>
-    <row r="9" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="117"/>
+    <row r="9" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -9660,8 +9663,8 @@
       </c>
       <c r="S9" s="60"/>
     </row>
-    <row r="10" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="117"/>
+    <row r="10" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -9690,8 +9693,8 @@
       </c>
       <c r="S10" s="60"/>
     </row>
-    <row r="11" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="117"/>
+    <row r="11" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -9720,8 +9723,8 @@
       </c>
       <c r="S11" s="60"/>
     </row>
-    <row r="12" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="117"/>
+    <row r="12" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -9752,8 +9755,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117"/>
+    <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -9782,8 +9785,8 @@
       </c>
       <c r="S13" s="60"/>
     </row>
-    <row r="14" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117"/>
+    <row r="14" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -9812,8 +9815,8 @@
       </c>
       <c r="S14" s="60"/>
     </row>
-    <row r="15" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117"/>
+    <row r="15" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -9842,8 +9845,8 @@
       </c>
       <c r="S15" s="60"/>
     </row>
-    <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117"/>
+    <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -9874,8 +9877,8 @@
       </c>
       <c r="S16" s="60"/>
     </row>
-    <row r="17" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117"/>
+    <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -9904,8 +9907,8 @@
       </c>
       <c r="S17" s="60"/>
     </row>
-    <row r="18" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117"/>
+    <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -9934,8 +9937,8 @@
       </c>
       <c r="S18" s="60"/>
     </row>
-    <row r="19" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117"/>
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -9966,8 +9969,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="118"/>
+    <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -9996,7 +9999,7 @@
       </c>
       <c r="S20" s="60"/>
     </row>
-    <row r="21" spans="2:19" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="11"/>
       <c r="F21" s="91"/>
       <c r="G21" s="92"/>
@@ -10013,8 +10016,8 @@
       <c r="R21" s="100"/>
       <c r="S21" s="101"/>
     </row>
-    <row r="22" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+    <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10045,8 +10048,8 @@
       </c>
       <c r="S22" s="60"/>
     </row>
-    <row r="23" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
+    <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10075,8 +10078,8 @@
       </c>
       <c r="S23" s="60"/>
     </row>
-    <row r="24" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119"/>
+    <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10105,8 +10108,8 @@
       </c>
       <c r="S24" s="60"/>
     </row>
-    <row r="25" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119"/>
+    <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10135,8 +10138,8 @@
       </c>
       <c r="S25" s="60"/>
     </row>
-    <row r="26" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
+    <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10165,8 +10168,8 @@
       </c>
       <c r="S26" s="60"/>
     </row>
-    <row r="27" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119"/>
+    <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10199,8 +10202,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119"/>
+    <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10229,8 +10232,8 @@
       </c>
       <c r="S28" s="60"/>
     </row>
-    <row r="29" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119"/>
+    <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10259,8 +10262,8 @@
       </c>
       <c r="S29" s="60"/>
     </row>
-    <row r="30" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119"/>
+    <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10289,8 +10292,8 @@
       </c>
       <c r="S30" s="60"/>
     </row>
-    <row r="31" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119"/>
+    <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10321,8 +10324,8 @@
       </c>
       <c r="S31" s="60"/>
     </row>
-    <row r="32" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
+    <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10351,8 +10354,8 @@
       </c>
       <c r="S32" s="60"/>
     </row>
-    <row r="33" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119"/>
+    <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10381,8 +10384,8 @@
       </c>
       <c r="S33" s="60"/>
     </row>
-    <row r="34" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119"/>
+    <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10413,8 +10416,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119"/>
+    <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10443,8 +10446,8 @@
       </c>
       <c r="S35" s="60"/>
     </row>
-    <row r="36" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119"/>
+    <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10473,8 +10476,8 @@
       </c>
       <c r="S36" s="60"/>
     </row>
-    <row r="37" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119"/>
+    <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10503,8 +10506,8 @@
       </c>
       <c r="S37" s="60"/>
     </row>
-    <row r="38" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119"/>
+    <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10535,8 +10538,8 @@
       </c>
       <c r="S38" s="60"/>
     </row>
-    <row r="39" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
+    <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10567,8 +10570,8 @@
       </c>
       <c r="S39" s="60"/>
     </row>
-    <row r="40" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119"/>
+    <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10597,8 +10600,8 @@
       </c>
       <c r="S40" s="60"/>
     </row>
-    <row r="41" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119"/>
+    <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10629,8 +10632,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119"/>
+    <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -10659,8 +10662,8 @@
       </c>
       <c r="S42" s="60"/>
     </row>
-    <row r="43" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="119"/>
+    <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -10689,8 +10692,8 @@
       </c>
       <c r="S43" s="60"/>
     </row>
-    <row r="44" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="119"/>
+    <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -10719,8 +10722,8 @@
       </c>
       <c r="S44" s="60"/>
     </row>
-    <row r="45" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
+    <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -10753,8 +10756,8 @@
       </c>
       <c r="S45" s="60"/>
     </row>
-    <row r="46" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="119"/>
+    <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -10783,8 +10786,8 @@
       </c>
       <c r="S46" s="60"/>
     </row>
-    <row r="47" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
+    <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -10813,8 +10816,8 @@
       </c>
       <c r="S47" s="60"/>
     </row>
-    <row r="48" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="119"/>
+    <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -10845,8 +10848,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="119"/>
+    <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -10875,8 +10878,8 @@
       </c>
       <c r="S49" s="60"/>
     </row>
-    <row r="50" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="119"/>
+    <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -10905,8 +10908,8 @@
       </c>
       <c r="S50" s="60"/>
     </row>
-    <row r="51" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119"/>
+    <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -10935,8 +10938,8 @@
       </c>
       <c r="S51" s="60"/>
     </row>
-    <row r="52" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="119"/>
+    <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -10965,7 +10968,7 @@
       </c>
       <c r="S52" s="60"/>
     </row>
-    <row r="53" spans="2:19" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:19" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="11"/>
       <c r="F53" s="91"/>
       <c r="G53" s="92"/>
@@ -10982,8 +10985,8 @@
       <c r="R53" s="100"/>
       <c r="S53" s="101"/>
     </row>
-    <row r="54" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11014,8 +11017,8 @@
       </c>
       <c r="S54" s="60"/>
     </row>
-    <row r="55" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="119"/>
+    <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11044,8 +11047,8 @@
       </c>
       <c r="S55" s="60"/>
     </row>
-    <row r="56" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="119"/>
+    <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11076,8 +11079,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="119"/>
+    <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11106,8 +11109,8 @@
       </c>
       <c r="S57" s="60"/>
     </row>
-    <row r="58" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="119"/>
+    <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11136,8 +11139,8 @@
       </c>
       <c r="S58" s="60"/>
     </row>
-    <row r="59" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="119"/>
+    <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11166,8 +11169,8 @@
       </c>
       <c r="S59" s="60"/>
     </row>
-    <row r="60" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="119"/>
+    <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11196,8 +11199,8 @@
       </c>
       <c r="S60" s="60"/>
     </row>
-    <row r="61" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="119"/>
+    <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11226,8 +11229,8 @@
       </c>
       <c r="S61" s="60"/>
     </row>
-    <row r="62" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="119"/>
+    <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11256,8 +11259,8 @@
       </c>
       <c r="S62" s="60"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11286,8 +11289,8 @@
       </c>
       <c r="S63" s="60"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11318,8 +11321,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11348,8 +11351,8 @@
       </c>
       <c r="S65" s="60"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11378,8 +11381,8 @@
       </c>
       <c r="S66" s="60"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11408,8 +11411,8 @@
       </c>
       <c r="S67" s="60"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11438,8 +11441,8 @@
       </c>
       <c r="S68" s="60"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11472,8 +11475,8 @@
       </c>
       <c r="S69" s="60"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11504,8 +11507,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11534,8 +11537,8 @@
       </c>
       <c r="S71" s="60"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11564,8 +11567,8 @@
       </c>
       <c r="S72" s="60"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11594,8 +11597,8 @@
       </c>
       <c r="S73" s="60"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11626,8 +11629,8 @@
       </c>
       <c r="S74" s="60"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -11656,8 +11659,8 @@
       </c>
       <c r="S75" s="60"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -11686,8 +11689,8 @@
       </c>
       <c r="S76" s="60"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -11718,8 +11721,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -11748,8 +11751,8 @@
       </c>
       <c r="S78" s="60"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -11778,8 +11781,8 @@
       </c>
       <c r="S79" s="60"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -11808,8 +11811,8 @@
       </c>
       <c r="S80" s="60"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -11838,8 +11841,8 @@
       </c>
       <c r="S81" s="60"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -11868,8 +11871,8 @@
       </c>
       <c r="S82" s="60"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -11898,7 +11901,7 @@
       </c>
       <c r="S83" s="60"/>
     </row>
-    <row r="84" spans="2:19" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="12"/>
       <c r="D84" s="11"/>
       <c r="F84" s="91"/>
@@ -11916,8 +11919,8 @@
       <c r="R84" s="100"/>
       <c r="S84" s="101"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -11950,8 +11953,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -11980,8 +11983,8 @@
       </c>
       <c r="S86" s="60"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12010,8 +12013,8 @@
       </c>
       <c r="S87" s="60"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12040,8 +12043,8 @@
       </c>
       <c r="S88" s="60"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12072,8 +12075,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12100,8 +12103,8 @@
       </c>
       <c r="S90" s="60"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12130,8 +12133,8 @@
       </c>
       <c r="S91" s="60"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12162,8 +12165,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12192,8 +12195,8 @@
       </c>
       <c r="S93" s="60"/>
     </row>
-    <row r="94" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12222,8 +12225,8 @@
       </c>
       <c r="S94" s="60"/>
     </row>
-    <row r="95" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12252,8 +12255,8 @@
       </c>
       <c r="S95" s="60"/>
     </row>
-    <row r="96" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12282,8 +12285,8 @@
       </c>
       <c r="S96" s="60"/>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12312,8 +12315,8 @@
       </c>
       <c r="S97" s="60"/>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12342,8 +12345,8 @@
       </c>
       <c r="S98" s="60"/>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12372,8 +12375,8 @@
       </c>
       <c r="S99" s="60"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12402,8 +12405,8 @@
       </c>
       <c r="S100" s="60"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12432,8 +12435,8 @@
       </c>
       <c r="S101" s="60"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12462,8 +12465,8 @@
       </c>
       <c r="S102" s="60"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12492,8 +12495,8 @@
       </c>
       <c r="S103" s="60"/>
     </row>
-    <row r="104" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12522,8 +12525,8 @@
       </c>
       <c r="S104" s="60"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12552,8 +12555,8 @@
       </c>
       <c r="S105" s="60"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12582,8 +12585,8 @@
       </c>
       <c r="S106" s="60"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12612,8 +12615,8 @@
       </c>
       <c r="S107" s="60"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -12642,8 +12645,8 @@
       </c>
       <c r="S108" s="60"/>
     </row>
-    <row r="109" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -12672,8 +12675,8 @@
       </c>
       <c r="S109" s="60"/>
     </row>
-    <row r="110" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -12702,8 +12705,8 @@
       </c>
       <c r="S110" s="60"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -12732,8 +12735,8 @@
       </c>
       <c r="S111" s="60"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -12762,8 +12765,8 @@
       </c>
       <c r="S112" s="60"/>
     </row>
-    <row r="113" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -12792,8 +12795,8 @@
       </c>
       <c r="S113" s="60"/>
     </row>
-    <row r="114" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -12822,8 +12825,8 @@
       </c>
       <c r="S114" s="60"/>
     </row>
-    <row r="115" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -12852,7 +12855,7 @@
       </c>
       <c r="S115" s="60"/>
     </row>
-    <row r="116" spans="2:19" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="12"/>
       <c r="D116" s="11"/>
       <c r="F116" s="91"/>
@@ -12870,8 +12873,8 @@
       <c r="R116" s="100"/>
       <c r="S116" s="101"/>
     </row>
-    <row r="117" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="116" t="s">
+    <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -12902,8 +12905,8 @@
       </c>
       <c r="S117" s="60"/>
     </row>
-    <row r="118" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -12932,8 +12935,8 @@
       </c>
       <c r="S118" s="60"/>
     </row>
-    <row r="119" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -12962,8 +12965,8 @@
       </c>
       <c r="S119" s="60"/>
     </row>
-    <row r="120" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -12992,8 +12995,8 @@
       </c>
       <c r="S120" s="60"/>
     </row>
-    <row r="121" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13022,8 +13025,8 @@
       </c>
       <c r="S121" s="60"/>
     </row>
-    <row r="122" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13052,8 +13055,8 @@
       </c>
       <c r="S122" s="60"/>
     </row>
-    <row r="123" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13082,8 +13085,8 @@
       </c>
       <c r="S123" s="60"/>
     </row>
-    <row r="124" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13112,8 +13115,8 @@
       </c>
       <c r="S124" s="60"/>
     </row>
-    <row r="125" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13142,8 +13145,8 @@
       </c>
       <c r="S125" s="60"/>
     </row>
-    <row r="126" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13172,8 +13175,8 @@
       </c>
       <c r="S126" s="60"/>
     </row>
-    <row r="127" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13202,8 +13205,8 @@
       </c>
       <c r="S127" s="60"/>
     </row>
-    <row r="128" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13232,8 +13235,8 @@
       </c>
       <c r="S128" s="60"/>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13262,8 +13265,8 @@
       </c>
       <c r="S129" s="60"/>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13292,8 +13295,8 @@
       </c>
       <c r="S130" s="60"/>
     </row>
-    <row r="131" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13322,8 +13325,8 @@
       </c>
       <c r="S131" s="60"/>
     </row>
-    <row r="132" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13352,8 +13355,8 @@
       </c>
       <c r="S132" s="60"/>
     </row>
-    <row r="133" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13382,8 +13385,8 @@
       </c>
       <c r="S133" s="60"/>
     </row>
-    <row r="134" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13412,8 +13415,8 @@
       </c>
       <c r="S134" s="60"/>
     </row>
-    <row r="135" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13442,8 +13445,8 @@
       </c>
       <c r="S135" s="60"/>
     </row>
-    <row r="136" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13472,8 +13475,8 @@
       </c>
       <c r="S136" s="60"/>
     </row>
-    <row r="137" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13502,8 +13505,8 @@
       </c>
       <c r="S137" s="60"/>
     </row>
-    <row r="138" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13534,17 +13537,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
@@ -13604,78 +13607,78 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
-    </row>
-    <row r="3" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="S2" s="109"/>
+    </row>
+    <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-    </row>
-    <row r="4" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+    </row>
+    <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -13708,8 +13711,8 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
     </row>
-    <row r="6" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117"/>
+    <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -13740,8 +13743,8 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
     </row>
-    <row r="7" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
+    <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -13772,8 +13775,8 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
     </row>
-    <row r="8" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="117"/>
+    <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -13804,8 +13807,8 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
     </row>
-    <row r="9" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="117"/>
+    <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -13838,8 +13841,8 @@
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
     </row>
-    <row r="10" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="117"/>
+    <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -13870,8 +13873,8 @@
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
     </row>
-    <row r="11" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="117"/>
+    <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -13902,8 +13905,8 @@
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
     </row>
-    <row r="12" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="117"/>
+    <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -13936,8 +13939,8 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
     </row>
-    <row r="13" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117"/>
+    <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -13968,8 +13971,8 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
     </row>
-    <row r="14" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117"/>
+    <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14000,8 +14003,8 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
     </row>
-    <row r="15" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117"/>
+    <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14032,8 +14035,8 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
     </row>
-    <row r="16" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117"/>
+    <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14066,8 +14069,8 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
     </row>
-    <row r="17" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117"/>
+    <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14098,8 +14101,8 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
     </row>
-    <row r="18" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117"/>
+    <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14130,8 +14133,8 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117"/>
+    <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14164,8 +14167,8 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="118"/>
+    <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14196,7 +14199,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="11"/>
       <c r="F21" s="91"/>
       <c r="G21" s="92"/>
@@ -14215,8 +14218,8 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
     </row>
-    <row r="22" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+    <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14249,8 +14252,8 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
     </row>
-    <row r="23" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
+    <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14281,8 +14284,8 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
     </row>
-    <row r="24" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119"/>
+    <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14313,8 +14316,8 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
     </row>
-    <row r="25" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119"/>
+    <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14345,8 +14348,8 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
     </row>
-    <row r="26" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
+    <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14377,8 +14380,8 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119"/>
+    <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14413,8 +14416,8 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
     </row>
-    <row r="28" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119"/>
+    <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14445,8 +14448,8 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
     </row>
-    <row r="29" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119"/>
+    <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14477,8 +14480,8 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119"/>
+    <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14509,8 +14512,8 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
     </row>
-    <row r="31" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119"/>
+    <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14543,8 +14546,8 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
     </row>
-    <row r="32" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
+    <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14575,8 +14578,8 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
     </row>
-    <row r="33" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119"/>
+    <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14607,8 +14610,8 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
     </row>
-    <row r="34" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119"/>
+    <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -14641,8 +14644,8 @@
       <c r="U34" s="14"/>
       <c r="V34" s="14"/>
     </row>
-    <row r="35" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119"/>
+    <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -14673,8 +14676,8 @@
       <c r="U35" s="14"/>
       <c r="V35" s="14"/>
     </row>
-    <row r="36" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119"/>
+    <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -14705,8 +14708,8 @@
       <c r="U36" s="14"/>
       <c r="V36" s="14"/>
     </row>
-    <row r="37" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119"/>
+    <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -14737,8 +14740,8 @@
       <c r="U37" s="14"/>
       <c r="V37" s="14"/>
     </row>
-    <row r="38" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119"/>
+    <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -14771,8 +14774,8 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
     </row>
-    <row r="39" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
+    <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -14805,8 +14808,8 @@
       <c r="U39" s="14"/>
       <c r="V39" s="14"/>
     </row>
-    <row r="40" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119"/>
+    <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -14837,8 +14840,8 @@
       <c r="U40" s="14"/>
       <c r="V40" s="14"/>
     </row>
-    <row r="41" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119"/>
+    <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -14871,8 +14874,8 @@
       <c r="U41" s="14"/>
       <c r="V41" s="14"/>
     </row>
-    <row r="42" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119"/>
+    <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -14903,8 +14906,8 @@
       <c r="U42" s="14"/>
       <c r="V42" s="14"/>
     </row>
-    <row r="43" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="119"/>
+    <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -14935,8 +14938,8 @@
       <c r="U43" s="14"/>
       <c r="V43" s="14"/>
     </row>
-    <row r="44" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="119"/>
+    <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -14967,8 +14970,8 @@
       <c r="U44" s="14"/>
       <c r="V44" s="14"/>
     </row>
-    <row r="45" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
+    <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15003,8 +15006,8 @@
       <c r="U45" s="14"/>
       <c r="V45" s="14"/>
     </row>
-    <row r="46" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="119"/>
+    <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15035,8 +15038,8 @@
       <c r="U46" s="14"/>
       <c r="V46" s="14"/>
     </row>
-    <row r="47" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
+    <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15067,8 +15070,8 @@
       <c r="U47" s="14"/>
       <c r="V47" s="14"/>
     </row>
-    <row r="48" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="119"/>
+    <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15101,8 +15104,8 @@
       <c r="U48" s="14"/>
       <c r="V48" s="14"/>
     </row>
-    <row r="49" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="119"/>
+    <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15133,8 +15136,8 @@
       <c r="U49" s="14"/>
       <c r="V49" s="14"/>
     </row>
-    <row r="50" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="119"/>
+    <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15165,8 +15168,8 @@
       <c r="U50" s="14"/>
       <c r="V50" s="14"/>
     </row>
-    <row r="51" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119"/>
+    <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15197,8 +15200,8 @@
       <c r="U51" s="14"/>
       <c r="V51" s="14"/>
     </row>
-    <row r="52" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="119"/>
+    <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15229,7 +15232,7 @@
       <c r="U52" s="14"/>
       <c r="V52" s="14"/>
     </row>
-    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="11"/>
       <c r="F53" s="91"/>
       <c r="G53" s="92"/>
@@ -15248,8 +15251,8 @@
       <c r="U53" s="14"/>
       <c r="V53" s="14"/>
     </row>
-    <row r="54" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15282,8 +15285,8 @@
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
     </row>
-    <row r="55" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="119"/>
+    <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15314,8 +15317,8 @@
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
     </row>
-    <row r="56" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="119"/>
+    <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15348,8 +15351,8 @@
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
     </row>
-    <row r="57" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="119"/>
+    <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15380,8 +15383,8 @@
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
     </row>
-    <row r="58" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="119"/>
+    <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15412,8 +15415,8 @@
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
     </row>
-    <row r="59" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="119"/>
+    <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15444,8 +15447,8 @@
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
     </row>
-    <row r="60" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="119"/>
+    <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15476,8 +15479,8 @@
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
     </row>
-    <row r="61" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="119"/>
+    <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15508,8 +15511,8 @@
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
     </row>
-    <row r="62" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="119"/>
+    <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15540,8 +15543,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15572,8 +15575,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15606,8 +15609,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -15638,8 +15641,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -15670,8 +15673,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -15702,8 +15705,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -15734,8 +15737,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -15770,8 +15773,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -15804,8 +15807,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -15836,8 +15839,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -15868,8 +15871,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -15900,8 +15903,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -15934,8 +15937,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -15966,8 +15969,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -15998,8 +16001,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16032,8 +16035,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16064,8 +16067,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16096,8 +16099,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16128,8 +16131,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16160,8 +16163,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16192,8 +16195,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16224,7 +16227,7 @@
       <c r="U83" s="14"/>
       <c r="V83" s="14"/>
     </row>
-    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="12"/>
       <c r="D84" s="11"/>
       <c r="F84" s="91"/>
@@ -16244,8 +16247,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16280,8 +16283,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16312,8 +16315,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16344,8 +16347,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16376,8 +16379,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16410,8 +16413,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16442,8 +16445,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16474,8 +16477,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16508,8 +16511,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16540,8 +16543,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16572,8 +16575,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16604,8 +16607,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16636,8 +16639,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -16668,8 +16671,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -16700,8 +16703,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -16732,8 +16735,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -16764,8 +16767,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -16796,8 +16799,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -16828,8 +16831,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -16860,8 +16863,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -16892,8 +16895,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -16924,8 +16927,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -16956,8 +16959,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -16988,8 +16991,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17020,8 +17023,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17052,8 +17055,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17084,8 +17087,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17116,8 +17119,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17148,8 +17151,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17180,8 +17183,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17212,8 +17215,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17244,7 +17247,7 @@
       <c r="U115" s="14"/>
       <c r="V115" s="14"/>
     </row>
-    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="12"/>
       <c r="D116" s="11"/>
       <c r="F116" s="91"/>
@@ -17264,8 +17267,8 @@
       <c r="U116" s="14"/>
       <c r="V116" s="14"/>
     </row>
-    <row r="117" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="116" t="s">
+    <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17298,8 +17301,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17330,8 +17333,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17362,8 +17365,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17394,8 +17397,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17426,8 +17429,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17458,8 +17461,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17490,8 +17493,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17522,8 +17525,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17554,8 +17557,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17586,8 +17589,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17618,8 +17621,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -17650,8 +17653,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -17682,8 +17685,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -17714,8 +17717,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -17746,8 +17749,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -17778,8 +17781,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -17810,8 +17813,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -17842,8 +17845,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -17874,8 +17877,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -17906,8 +17909,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -17938,8 +17941,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -17972,17 +17975,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
@@ -18062,78 +18065,78 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
-    </row>
-    <row r="3" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="S2" s="109"/>
+    </row>
+    <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-    </row>
-    <row r="4" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+    </row>
+    <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18166,8 +18169,8 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
     </row>
-    <row r="6" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117"/>
+    <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18198,8 +18201,8 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
     </row>
-    <row r="7" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
+    <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18230,8 +18233,8 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
     </row>
-    <row r="8" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="117"/>
+    <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18262,8 +18265,8 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
     </row>
-    <row r="9" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="117"/>
+    <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18296,8 +18299,8 @@
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
     </row>
-    <row r="10" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="117"/>
+    <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18328,8 +18331,8 @@
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
     </row>
-    <row r="11" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="117"/>
+    <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18360,8 +18363,8 @@
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
     </row>
-    <row r="12" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="117"/>
+    <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18394,8 +18397,8 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
     </row>
-    <row r="13" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117"/>
+    <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18426,8 +18429,8 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
     </row>
-    <row r="14" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117"/>
+    <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18458,8 +18461,8 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
     </row>
-    <row r="15" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117"/>
+    <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18490,8 +18493,8 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
     </row>
-    <row r="16" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117"/>
+    <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18524,8 +18527,8 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
     </row>
-    <row r="17" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117"/>
+    <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18556,8 +18559,8 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
     </row>
-    <row r="18" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117"/>
+    <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -18588,8 +18591,8 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117"/>
+    <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -18622,8 +18625,8 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="118"/>
+    <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -18654,7 +18657,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="11"/>
       <c r="F21" s="91"/>
       <c r="G21" s="92"/>
@@ -18673,8 +18676,8 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
     </row>
-    <row r="22" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+    <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -18707,8 +18710,8 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
     </row>
-    <row r="23" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
+    <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -18739,8 +18742,8 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
     </row>
-    <row r="24" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119"/>
+    <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -18771,8 +18774,8 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
     </row>
-    <row r="25" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119"/>
+    <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -18803,8 +18806,8 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
     </row>
-    <row r="26" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
+    <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -18835,8 +18838,8 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119"/>
+    <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -18871,8 +18874,8 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
     </row>
-    <row r="28" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119"/>
+    <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -18903,8 +18906,8 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
     </row>
-    <row r="29" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119"/>
+    <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -18935,8 +18938,8 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119"/>
+    <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -18967,8 +18970,8 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
     </row>
-    <row r="31" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119"/>
+    <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19001,8 +19004,8 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
     </row>
-    <row r="32" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
+    <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19033,8 +19036,8 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
     </row>
-    <row r="33" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119"/>
+    <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19065,8 +19068,8 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
     </row>
-    <row r="34" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119"/>
+    <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19099,8 +19102,8 @@
       <c r="U34" s="14"/>
       <c r="V34" s="14"/>
     </row>
-    <row r="35" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119"/>
+    <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19131,8 +19134,8 @@
       <c r="U35" s="14"/>
       <c r="V35" s="14"/>
     </row>
-    <row r="36" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119"/>
+    <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19163,8 +19166,8 @@
       <c r="U36" s="14"/>
       <c r="V36" s="14"/>
     </row>
-    <row r="37" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119"/>
+    <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19195,8 +19198,8 @@
       <c r="U37" s="14"/>
       <c r="V37" s="14"/>
     </row>
-    <row r="38" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119"/>
+    <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19231,8 +19234,8 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
     </row>
-    <row r="39" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
+    <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19263,8 +19266,8 @@
       <c r="U39" s="14"/>
       <c r="V39" s="14"/>
     </row>
-    <row r="40" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119"/>
+    <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19295,8 +19298,8 @@
       <c r="U40" s="14"/>
       <c r="V40" s="14"/>
     </row>
-    <row r="41" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119"/>
+    <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19329,8 +19332,8 @@
       <c r="U41" s="14"/>
       <c r="V41" s="14"/>
     </row>
-    <row r="42" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119"/>
+    <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19361,8 +19364,8 @@
       <c r="U42" s="14"/>
       <c r="V42" s="14"/>
     </row>
-    <row r="43" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="119"/>
+    <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19393,8 +19396,8 @@
       <c r="U43" s="14"/>
       <c r="V43" s="14"/>
     </row>
-    <row r="44" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="119"/>
+    <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19425,8 +19428,8 @@
       <c r="U44" s="14"/>
       <c r="V44" s="14"/>
     </row>
-    <row r="45" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
+    <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19461,8 +19464,8 @@
       <c r="U45" s="14"/>
       <c r="V45" s="14"/>
     </row>
-    <row r="46" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="119"/>
+    <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19493,8 +19496,8 @@
       <c r="U46" s="14"/>
       <c r="V46" s="14"/>
     </row>
-    <row r="47" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
+    <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19525,8 +19528,8 @@
       <c r="U47" s="14"/>
       <c r="V47" s="14"/>
     </row>
-    <row r="48" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="119"/>
+    <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19559,8 +19562,8 @@
       <c r="U48" s="14"/>
       <c r="V48" s="14"/>
     </row>
-    <row r="49" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="119"/>
+    <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -19591,8 +19594,8 @@
       <c r="U49" s="14"/>
       <c r="V49" s="14"/>
     </row>
-    <row r="50" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="119"/>
+    <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -19623,8 +19626,8 @@
       <c r="U50" s="14"/>
       <c r="V50" s="14"/>
     </row>
-    <row r="51" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119"/>
+    <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -19655,8 +19658,8 @@
       <c r="U51" s="14"/>
       <c r="V51" s="14"/>
     </row>
-    <row r="52" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="119"/>
+    <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -19687,7 +19690,7 @@
       <c r="U52" s="14"/>
       <c r="V52" s="14"/>
     </row>
-    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="11"/>
       <c r="F53" s="91"/>
       <c r="G53" s="92"/>
@@ -19706,8 +19709,8 @@
       <c r="U53" s="14"/>
       <c r="V53" s="14"/>
     </row>
-    <row r="54" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -19740,8 +19743,8 @@
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
     </row>
-    <row r="55" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="119"/>
+    <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -19772,8 +19775,8 @@
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
     </row>
-    <row r="56" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="119"/>
+    <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -19806,8 +19809,8 @@
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
     </row>
-    <row r="57" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="119"/>
+    <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -19838,8 +19841,8 @@
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
     </row>
-    <row r="58" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="119"/>
+    <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -19870,8 +19873,8 @@
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
     </row>
-    <row r="59" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="119"/>
+    <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -19902,8 +19905,8 @@
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
     </row>
-    <row r="60" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="119"/>
+    <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -19934,8 +19937,8 @@
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
     </row>
-    <row r="61" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="119"/>
+    <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -19966,8 +19969,8 @@
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
     </row>
-    <row r="62" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="119"/>
+    <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -19998,8 +20001,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20030,8 +20033,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20064,8 +20067,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20096,8 +20099,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20128,8 +20131,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20160,8 +20163,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20196,8 +20199,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20228,8 +20231,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20262,8 +20265,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20294,8 +20297,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20326,8 +20329,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20358,8 +20361,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20392,8 +20395,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20424,8 +20427,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20456,8 +20459,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20490,8 +20493,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20522,8 +20525,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20554,8 +20557,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -20586,8 +20589,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -20618,8 +20621,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -20650,8 +20653,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -20682,7 +20685,7 @@
       <c r="U83" s="14"/>
       <c r="V83" s="14"/>
     </row>
-    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="12"/>
       <c r="D84" s="11"/>
       <c r="F84" s="91"/>
@@ -20702,8 +20705,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -20738,8 +20741,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -20770,8 +20773,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -20802,8 +20805,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -20834,8 +20837,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -20868,8 +20871,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -20900,8 +20903,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -20932,8 +20935,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -20966,8 +20969,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -20998,8 +21001,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21030,8 +21033,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21062,8 +21065,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21094,8 +21097,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21126,8 +21129,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21158,8 +21161,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21190,8 +21193,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21222,8 +21225,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21254,8 +21257,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21286,8 +21289,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21318,8 +21321,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21350,8 +21353,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21382,8 +21385,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21414,8 +21417,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21446,8 +21449,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21478,8 +21481,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21510,8 +21513,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21542,8 +21545,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -21574,8 +21577,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -21606,8 +21609,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -21638,8 +21641,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -21670,8 +21673,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -21702,7 +21705,7 @@
       <c r="U115" s="14"/>
       <c r="V115" s="14"/>
     </row>
-    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="12"/>
       <c r="D116" s="11"/>
       <c r="F116" s="91"/>
@@ -21722,8 +21725,8 @@
       <c r="U116" s="14"/>
       <c r="V116" s="14"/>
     </row>
-    <row r="117" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="116" t="s">
+    <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -21756,8 +21759,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -21788,8 +21791,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -21820,8 +21823,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -21852,8 +21855,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -21884,8 +21887,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -21916,8 +21919,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -21948,8 +21951,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -21980,8 +21983,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22012,8 +22015,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22044,8 +22047,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22076,8 +22079,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22108,8 +22111,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22140,8 +22143,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22172,8 +22175,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22204,8 +22207,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22236,8 +22239,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22268,8 +22271,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22300,8 +22303,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22332,8 +22335,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -22364,8 +22367,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -22396,8 +22399,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -22430,17 +22433,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="41" priority="25" operator="equal">
@@ -22520,78 +22523,78 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:V190"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
-    </row>
-    <row r="3" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="S2" s="109"/>
+    </row>
+    <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-    </row>
-    <row r="4" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+    </row>
+    <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -22624,8 +22627,8 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
     </row>
-    <row r="6" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117"/>
+    <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -22656,8 +22659,8 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
     </row>
-    <row r="7" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
+    <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -22688,8 +22691,8 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
     </row>
-    <row r="8" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="117"/>
+    <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -22720,8 +22723,8 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
     </row>
-    <row r="9" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="117"/>
+    <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -22754,8 +22757,8 @@
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
     </row>
-    <row r="10" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="117"/>
+    <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -22786,8 +22789,8 @@
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
     </row>
-    <row r="11" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="117"/>
+    <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -22818,8 +22821,8 @@
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
     </row>
-    <row r="12" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="117"/>
+    <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -22852,8 +22855,8 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
     </row>
-    <row r="13" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117"/>
+    <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -22884,8 +22887,8 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
     </row>
-    <row r="14" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117"/>
+    <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -22916,8 +22919,8 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
     </row>
-    <row r="15" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117"/>
+    <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -22948,8 +22951,8 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
     </row>
-    <row r="16" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117"/>
+    <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -22982,8 +22985,8 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
     </row>
-    <row r="17" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117"/>
+    <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -23014,8 +23017,8 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
     </row>
-    <row r="18" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117"/>
+    <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -23046,8 +23049,8 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117"/>
+    <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -23080,8 +23083,8 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="118"/>
+    <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -23112,7 +23115,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="11"/>
       <c r="F21" s="91"/>
       <c r="G21" s="92"/>
@@ -23131,8 +23134,8 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
     </row>
-    <row r="22" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+    <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -23165,8 +23168,8 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
     </row>
-    <row r="23" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
+    <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -23197,8 +23200,8 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
     </row>
-    <row r="24" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119"/>
+    <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -23229,8 +23232,8 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
     </row>
-    <row r="25" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119"/>
+    <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -23261,8 +23264,8 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
     </row>
-    <row r="26" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
+    <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -23293,8 +23296,8 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119"/>
+    <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -23329,8 +23332,8 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
     </row>
-    <row r="28" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119"/>
+    <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -23361,8 +23364,8 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
     </row>
-    <row r="29" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119"/>
+    <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -23393,8 +23396,8 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119"/>
+    <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -23425,8 +23428,8 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
     </row>
-    <row r="31" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119"/>
+    <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -23459,8 +23462,8 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
     </row>
-    <row r="32" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
+    <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -23491,8 +23494,8 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
     </row>
-    <row r="33" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119"/>
+    <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -23523,8 +23526,8 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
     </row>
-    <row r="34" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119"/>
+    <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -23557,8 +23560,8 @@
       <c r="U34" s="14"/>
       <c r="V34" s="14"/>
     </row>
-    <row r="35" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119"/>
+    <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -23589,8 +23592,8 @@
       <c r="U35" s="14"/>
       <c r="V35" s="14"/>
     </row>
-    <row r="36" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119"/>
+    <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -23621,8 +23624,8 @@
       <c r="U36" s="14"/>
       <c r="V36" s="14"/>
     </row>
-    <row r="37" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119"/>
+    <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -23657,8 +23660,8 @@
       <c r="U37" s="14"/>
       <c r="V37" s="14"/>
     </row>
-    <row r="38" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119"/>
+    <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -23691,8 +23694,8 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
     </row>
-    <row r="39" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
+    <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -23723,8 +23726,8 @@
       <c r="U39" s="14"/>
       <c r="V39" s="14"/>
     </row>
-    <row r="40" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119"/>
+    <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -23757,8 +23760,8 @@
       <c r="U40" s="14"/>
       <c r="V40" s="14"/>
     </row>
-    <row r="41" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119"/>
+    <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -23791,8 +23794,8 @@
       <c r="U41" s="14"/>
       <c r="V41" s="14"/>
     </row>
-    <row r="42" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119"/>
+    <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -23823,8 +23826,8 @@
       <c r="U42" s="14"/>
       <c r="V42" s="14"/>
     </row>
-    <row r="43" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="119"/>
+    <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -23855,8 +23858,8 @@
       <c r="U43" s="14"/>
       <c r="V43" s="14"/>
     </row>
-    <row r="44" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="119"/>
+    <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -23887,8 +23890,8 @@
       <c r="U44" s="14"/>
       <c r="V44" s="14"/>
     </row>
-    <row r="45" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
+    <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -23923,8 +23926,8 @@
       <c r="U45" s="14"/>
       <c r="V45" s="14"/>
     </row>
-    <row r="46" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="119"/>
+    <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -23955,8 +23958,8 @@
       <c r="U46" s="14"/>
       <c r="V46" s="14"/>
     </row>
-    <row r="47" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
+    <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -23987,8 +23990,8 @@
       <c r="U47" s="14"/>
       <c r="V47" s="14"/>
     </row>
-    <row r="48" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="119"/>
+    <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -24021,8 +24024,8 @@
       <c r="U48" s="14"/>
       <c r="V48" s="14"/>
     </row>
-    <row r="49" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="119"/>
+    <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -24053,8 +24056,8 @@
       <c r="U49" s="14"/>
       <c r="V49" s="14"/>
     </row>
-    <row r="50" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="119"/>
+    <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -24085,8 +24088,8 @@
       <c r="U50" s="14"/>
       <c r="V50" s="14"/>
     </row>
-    <row r="51" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119"/>
+    <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -24117,8 +24120,8 @@
       <c r="U51" s="14"/>
       <c r="V51" s="14"/>
     </row>
-    <row r="52" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="119"/>
+    <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -24149,7 +24152,7 @@
       <c r="U52" s="14"/>
       <c r="V52" s="14"/>
     </row>
-    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="11"/>
       <c r="F53" s="91"/>
       <c r="G53" s="92"/>
@@ -24168,8 +24171,8 @@
       <c r="U53" s="14"/>
       <c r="V53" s="14"/>
     </row>
-    <row r="54" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -24202,8 +24205,8 @@
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
     </row>
-    <row r="55" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="119"/>
+    <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -24234,8 +24237,8 @@
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
     </row>
-    <row r="56" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="119"/>
+    <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -24268,8 +24271,8 @@
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
     </row>
-    <row r="57" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="119"/>
+    <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -24300,8 +24303,8 @@
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
     </row>
-    <row r="58" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="119"/>
+    <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -24332,8 +24335,8 @@
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
     </row>
-    <row r="59" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="119"/>
+    <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -24364,8 +24367,8 @@
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
     </row>
-    <row r="60" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="119"/>
+    <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -24396,8 +24399,8 @@
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
     </row>
-    <row r="61" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="119"/>
+    <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -24428,8 +24431,8 @@
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
     </row>
-    <row r="62" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="119"/>
+    <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -24460,8 +24463,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -24492,8 +24495,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -24526,8 +24529,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -24558,8 +24561,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -24590,8 +24593,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -24622,8 +24625,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -24654,8 +24657,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -24686,8 +24689,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -24720,8 +24723,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -24752,8 +24755,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -24784,8 +24787,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -24816,8 +24819,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -24850,8 +24853,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -24882,8 +24885,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -24914,8 +24917,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -24948,8 +24951,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -24980,8 +24983,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -25012,8 +25015,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -25044,8 +25047,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -25076,8 +25079,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -25108,8 +25111,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -25140,7 +25143,7 @@
       <c r="U83" s="14"/>
       <c r="V83" s="14"/>
     </row>
-    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="12"/>
       <c r="D84" s="11"/>
       <c r="F84" s="91"/>
@@ -25160,8 +25163,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -25194,8 +25197,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -25224,8 +25227,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -25256,8 +25259,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -25288,8 +25291,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -25322,8 +25325,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -25354,8 +25357,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -25386,8 +25389,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -25420,8 +25423,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -25452,8 +25455,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -25484,8 +25487,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -25516,8 +25519,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -25548,8 +25551,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -25580,8 +25583,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -25612,8 +25615,8 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -25644,8 +25647,8 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -25676,8 +25679,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -25708,8 +25711,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -25740,8 +25743,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -25772,8 +25775,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -25804,8 +25807,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -25836,8 +25839,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -25868,8 +25871,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -25900,8 +25903,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -25932,8 +25935,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -25964,8 +25967,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -25996,8 +25999,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -26028,8 +26031,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -26060,8 +26063,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -26092,8 +26095,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -26124,8 +26127,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -26156,7 +26159,7 @@
       <c r="U115" s="14"/>
       <c r="V115" s="14"/>
     </row>
-    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="12"/>
       <c r="D116" s="11"/>
       <c r="F116" s="91"/>
@@ -26176,8 +26179,8 @@
       <c r="U116" s="14"/>
       <c r="V116" s="14"/>
     </row>
-    <row r="117" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="116" t="s">
+    <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -26210,8 +26213,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -26242,8 +26245,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -26274,8 +26277,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -26306,8 +26309,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -26338,8 +26341,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -26370,8 +26373,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -26402,8 +26405,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -26434,8 +26437,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -26466,8 +26469,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -26498,8 +26501,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -26530,8 +26533,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -26562,8 +26565,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -26594,8 +26597,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -26626,8 +26629,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -26658,8 +26661,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -26690,8 +26693,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -26722,8 +26725,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -26754,8 +26757,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -26786,8 +26789,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -26818,8 +26821,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -26850,8 +26853,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -26882,211 +26885,211 @@
       <c r="U138" s="14"/>
       <c r="V138" s="14"/>
     </row>
-    <row r="139" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U139" s="14"/>
       <c r="V139" s="14"/>
     </row>
-    <row r="140" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U140" s="14"/>
       <c r="V140" s="14"/>
     </row>
-    <row r="141" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U141" s="14"/>
       <c r="V141" s="14"/>
     </row>
-    <row r="142" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U142" s="14"/>
       <c r="V142" s="14"/>
     </row>
-    <row r="143" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U143" s="14"/>
       <c r="V143" s="14"/>
     </row>
-    <row r="144" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U144" s="14"/>
       <c r="V144" s="14"/>
     </row>
-    <row r="145" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="145" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U145" s="14"/>
       <c r="V145" s="14"/>
     </row>
-    <row r="146" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="146" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U146" s="14"/>
       <c r="V146" s="14"/>
     </row>
-    <row r="147" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="147" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U147" s="14"/>
       <c r="V147" s="14"/>
     </row>
-    <row r="148" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="148" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U148" s="14"/>
       <c r="V148" s="14"/>
     </row>
-    <row r="149" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="149" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U149" s="14"/>
       <c r="V149" s="14"/>
     </row>
-    <row r="150" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="150" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U150" s="14"/>
       <c r="V150" s="14"/>
     </row>
-    <row r="151" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="151" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U151" s="14"/>
       <c r="V151" s="14"/>
     </row>
-    <row r="152" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="152" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U152" s="14"/>
       <c r="V152" s="14"/>
     </row>
-    <row r="153" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="153" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U153" s="14"/>
       <c r="V153" s="14"/>
     </row>
-    <row r="154" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="154" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U154" s="14"/>
       <c r="V154" s="14"/>
     </row>
-    <row r="155" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="155" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U155" s="14"/>
       <c r="V155" s="14"/>
     </row>
-    <row r="156" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="156" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U156" s="14"/>
       <c r="V156" s="14"/>
     </row>
-    <row r="157" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="157" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U157" s="14"/>
       <c r="V157" s="14"/>
     </row>
-    <row r="158" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="158" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U158" s="14"/>
       <c r="V158" s="14"/>
     </row>
-    <row r="159" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="159" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U159" s="14"/>
       <c r="V159" s="14"/>
     </row>
-    <row r="160" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="160" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U160" s="14"/>
       <c r="V160" s="14"/>
     </row>
-    <row r="161" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="161" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U161" s="14"/>
       <c r="V161" s="14"/>
     </row>
-    <row r="162" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="162" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U162" s="14"/>
       <c r="V162" s="14"/>
     </row>
-    <row r="163" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="163" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U163" s="14"/>
       <c r="V163" s="14"/>
     </row>
-    <row r="164" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="164" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U164" s="14"/>
       <c r="V164" s="14"/>
     </row>
-    <row r="165" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="165" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U165" s="14"/>
       <c r="V165" s="14"/>
     </row>
-    <row r="166" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="166" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U166" s="14"/>
       <c r="V166" s="14"/>
     </row>
-    <row r="167" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="167" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U167" s="14"/>
       <c r="V167" s="14"/>
     </row>
-    <row r="168" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="168" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U168" s="14"/>
       <c r="V168" s="14"/>
     </row>
-    <row r="169" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="169" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U169" s="14"/>
       <c r="V169" s="14"/>
     </row>
-    <row r="170" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="170" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U170" s="14"/>
       <c r="V170" s="14"/>
     </row>
-    <row r="171" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="171" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U171" s="14"/>
       <c r="V171" s="14"/>
     </row>
-    <row r="172" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="172" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U172" s="14"/>
       <c r="V172" s="14"/>
     </row>
-    <row r="173" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="173" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U173" s="14"/>
       <c r="V173" s="14"/>
     </row>
-    <row r="174" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="174" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U174" s="14"/>
       <c r="V174" s="14"/>
     </row>
-    <row r="175" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="175" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U175" s="14"/>
       <c r="V175" s="14"/>
     </row>
-    <row r="176" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="176" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U176" s="14"/>
       <c r="V176" s="14"/>
     </row>
-    <row r="177" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="177" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U177" s="14"/>
       <c r="V177" s="14"/>
     </row>
-    <row r="178" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="178" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U178" s="14"/>
       <c r="V178" s="14"/>
     </row>
-    <row r="179" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="179" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U179" s="14"/>
       <c r="V179" s="14"/>
     </row>
-    <row r="180" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="180" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U180" s="14"/>
       <c r="V180" s="14"/>
     </row>
-    <row r="181" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="181" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U181" s="14"/>
       <c r="V181" s="14"/>
     </row>
-    <row r="182" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="182" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U182" s="14"/>
       <c r="V182" s="14"/>
     </row>
-    <row r="183" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="183" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U183" s="14"/>
       <c r="V183" s="14"/>
     </row>
-    <row r="184" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="184" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U184" s="14"/>
       <c r="V184" s="14"/>
     </row>
-    <row r="185" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="185" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U185" s="14"/>
       <c r="V185" s="14"/>
     </row>
-    <row r="186" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="186" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U186" s="14"/>
       <c r="V186" s="14"/>
     </row>
-    <row r="187" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="187" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U187" s="14"/>
       <c r="V187" s="14"/>
     </row>
-    <row r="188" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="188" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U188" s="14"/>
       <c r="V188" s="14"/>
     </row>
-    <row r="189" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="189" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U189" s="14"/>
       <c r="V189" s="14"/>
     </row>
-    <row r="190" spans="21:22" x14ac:dyDescent="0.35">
+    <row r="190" spans="21:22" x14ac:dyDescent="0.25">
       <c r="U190" s="14"/>
       <c r="V190" s="14"/>
     </row>
@@ -27183,78 +27186,78 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:V138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="2.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.6328125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.6328125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="2.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.6328125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="2.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="35.6328125" style="13" customWidth="1"/>
-    <col min="20" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="2.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="35.5703125" style="13" customWidth="1"/>
+    <col min="20" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+    <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
-    </row>
-    <row r="3" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="S2" s="109"/>
+    </row>
+    <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-    </row>
-    <row r="4" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+    </row>
+    <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -27287,8 +27290,8 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
     </row>
-    <row r="6" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117"/>
+    <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -27319,8 +27322,8 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
     </row>
-    <row r="7" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
+    <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -27351,8 +27354,8 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
     </row>
-    <row r="8" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="117"/>
+    <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -27383,8 +27386,8 @@
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
     </row>
-    <row r="9" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="117"/>
+    <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -27417,8 +27420,8 @@
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
     </row>
-    <row r="10" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="117"/>
+    <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -27449,8 +27452,8 @@
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
     </row>
-    <row r="11" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="117"/>
+    <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -27481,8 +27484,8 @@
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
     </row>
-    <row r="12" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="117"/>
+    <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -27515,8 +27518,8 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
     </row>
-    <row r="13" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117"/>
+    <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -27547,8 +27550,8 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
     </row>
-    <row r="14" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117"/>
+    <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -27579,8 +27582,8 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
     </row>
-    <row r="15" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117"/>
+    <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -27611,8 +27614,8 @@
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
     </row>
-    <row r="16" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117"/>
+    <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -27645,8 +27648,8 @@
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
     </row>
-    <row r="17" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117"/>
+    <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -27677,8 +27680,8 @@
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
     </row>
-    <row r="18" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117"/>
+    <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -27709,8 +27712,8 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117"/>
+    <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -27743,8 +27746,8 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="118"/>
+    <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -27775,7 +27778,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="11"/>
       <c r="F21" s="91"/>
       <c r="G21" s="92"/>
@@ -27794,8 +27797,8 @@
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
     </row>
-    <row r="22" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+    <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -27828,8 +27831,8 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
     </row>
-    <row r="23" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119"/>
+    <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -27860,8 +27863,8 @@
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
     </row>
-    <row r="24" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119"/>
+    <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -27892,8 +27895,8 @@
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
     </row>
-    <row r="25" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119"/>
+    <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -27924,8 +27927,8 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
     </row>
-    <row r="26" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
+    <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -27956,8 +27959,8 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119"/>
+    <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -27992,8 +27995,8 @@
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
     </row>
-    <row r="28" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119"/>
+    <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -28024,8 +28027,8 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
     </row>
-    <row r="29" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119"/>
+    <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -28056,8 +28059,8 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119"/>
+    <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -28088,8 +28091,8 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
     </row>
-    <row r="31" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119"/>
+    <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -28122,8 +28125,8 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
     </row>
-    <row r="32" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119"/>
+    <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -28154,8 +28157,8 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
     </row>
-    <row r="33" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119"/>
+    <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -28186,8 +28189,8 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
     </row>
-    <row r="34" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119"/>
+    <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -28220,8 +28223,8 @@
       <c r="U34" s="14"/>
       <c r="V34" s="14"/>
     </row>
-    <row r="35" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119"/>
+    <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -28252,8 +28255,8 @@
       <c r="U35" s="14"/>
       <c r="V35" s="14"/>
     </row>
-    <row r="36" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119"/>
+    <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -28284,8 +28287,8 @@
       <c r="U36" s="14"/>
       <c r="V36" s="14"/>
     </row>
-    <row r="37" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119"/>
+    <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -28316,8 +28319,8 @@
       <c r="U37" s="14"/>
       <c r="V37" s="14"/>
     </row>
-    <row r="38" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119"/>
+    <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -28350,8 +28353,8 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
     </row>
-    <row r="39" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
+    <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -28384,8 +28387,8 @@
       <c r="U39" s="14"/>
       <c r="V39" s="14"/>
     </row>
-    <row r="40" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119"/>
+    <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -28420,8 +28423,8 @@
       <c r="U40" s="14"/>
       <c r="V40" s="14"/>
     </row>
-    <row r="41" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119"/>
+    <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -28454,8 +28457,8 @@
       <c r="U41" s="14"/>
       <c r="V41" s="14"/>
     </row>
-    <row r="42" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119"/>
+    <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -28486,8 +28489,8 @@
       <c r="U42" s="14"/>
       <c r="V42" s="14"/>
     </row>
-    <row r="43" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="119"/>
+    <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -28518,8 +28521,8 @@
       <c r="U43" s="14"/>
       <c r="V43" s="14"/>
     </row>
-    <row r="44" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="119"/>
+    <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -28550,8 +28553,8 @@
       <c r="U44" s="14"/>
       <c r="V44" s="14"/>
     </row>
-    <row r="45" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
+    <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -28586,8 +28589,8 @@
       <c r="U45" s="14"/>
       <c r="V45" s="14"/>
     </row>
-    <row r="46" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="119"/>
+    <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -28618,8 +28621,8 @@
       <c r="U46" s="14"/>
       <c r="V46" s="14"/>
     </row>
-    <row r="47" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="119"/>
+    <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -28650,8 +28653,8 @@
       <c r="U47" s="14"/>
       <c r="V47" s="14"/>
     </row>
-    <row r="48" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="119"/>
+    <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -28684,8 +28687,8 @@
       <c r="U48" s="14"/>
       <c r="V48" s="14"/>
     </row>
-    <row r="49" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="119"/>
+    <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -28716,8 +28719,8 @@
       <c r="U49" s="14"/>
       <c r="V49" s="14"/>
     </row>
-    <row r="50" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="119"/>
+    <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -28748,8 +28751,8 @@
       <c r="U50" s="14"/>
       <c r="V50" s="14"/>
     </row>
-    <row r="51" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119"/>
+    <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -28780,8 +28783,8 @@
       <c r="U51" s="14"/>
       <c r="V51" s="14"/>
     </row>
-    <row r="52" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="119"/>
+    <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -28812,7 +28815,7 @@
       <c r="U52" s="14"/>
       <c r="V52" s="14"/>
     </row>
-    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:22" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="11"/>
       <c r="F53" s="91"/>
       <c r="G53" s="92"/>
@@ -28831,8 +28834,8 @@
       <c r="U53" s="14"/>
       <c r="V53" s="14"/>
     </row>
-    <row r="54" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -28865,8 +28868,8 @@
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
     </row>
-    <row r="55" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="119"/>
+    <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -28897,8 +28900,8 @@
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
     </row>
-    <row r="56" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="119"/>
+    <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -28931,8 +28934,8 @@
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
     </row>
-    <row r="57" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="119"/>
+    <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -28965,8 +28968,8 @@
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
     </row>
-    <row r="58" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="119"/>
+    <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -28999,8 +29002,8 @@
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
     </row>
-    <row r="59" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="119"/>
+    <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -29031,8 +29034,8 @@
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
     </row>
-    <row r="60" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="119"/>
+    <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -29063,8 +29066,8 @@
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
     </row>
-    <row r="61" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="119"/>
+    <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -29095,8 +29098,8 @@
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
     </row>
-    <row r="62" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="119"/>
+    <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -29127,8 +29130,8 @@
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B63" s="119"/>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -29159,8 +29162,8 @@
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B64" s="119"/>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -29193,8 +29196,8 @@
       <c r="U64" s="14"/>
       <c r="V64" s="14"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B65" s="119"/>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -29225,8 +29228,8 @@
       <c r="U65" s="14"/>
       <c r="V65" s="14"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B66" s="119"/>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -29257,8 +29260,8 @@
       <c r="U66" s="14"/>
       <c r="V66" s="14"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B67" s="119"/>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -29289,8 +29292,8 @@
       <c r="U67" s="14"/>
       <c r="V67" s="14"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B68" s="119"/>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -29321,8 +29324,8 @@
       <c r="U68" s="14"/>
       <c r="V68" s="14"/>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B69" s="119"/>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -29357,8 +29360,8 @@
       <c r="U69" s="14"/>
       <c r="V69" s="14"/>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B70" s="119"/>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -29391,8 +29394,8 @@
       <c r="U70" s="14"/>
       <c r="V70" s="14"/>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B71" s="119"/>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -29423,8 +29426,8 @@
       <c r="U71" s="14"/>
       <c r="V71" s="14"/>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B72" s="119"/>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -29457,8 +29460,8 @@
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B73" s="119"/>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -29489,8 +29492,8 @@
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B74" s="119"/>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -29523,8 +29526,8 @@
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B75" s="119"/>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -29555,8 +29558,8 @@
       <c r="U75" s="14"/>
       <c r="V75" s="14"/>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B76" s="119"/>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -29587,8 +29590,8 @@
       <c r="U76" s="14"/>
       <c r="V76" s="14"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B77" s="119"/>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -29621,8 +29624,8 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B78" s="119"/>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -29653,8 +29656,8 @@
       <c r="U78" s="14"/>
       <c r="V78" s="14"/>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B79" s="119"/>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -29685,8 +29688,8 @@
       <c r="U79" s="14"/>
       <c r="V79" s="14"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B80" s="119"/>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -29717,8 +29720,8 @@
       <c r="U80" s="14"/>
       <c r="V80" s="14"/>
     </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B81" s="119"/>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -29749,8 +29752,8 @@
       <c r="U81" s="14"/>
       <c r="V81" s="14"/>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B82" s="119"/>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -29783,8 +29786,8 @@
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
     </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B83" s="119"/>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -29815,7 +29818,7 @@
       <c r="U83" s="14"/>
       <c r="V83" s="14"/>
     </row>
-    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="12"/>
       <c r="D84" s="11"/>
       <c r="F84" s="91"/>
@@ -29835,8 +29838,8 @@
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
     </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B85" s="119" t="s">
+    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -29871,8 +29874,8 @@
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
     </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B86" s="119"/>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -29907,8 +29910,8 @@
       <c r="U86" s="14"/>
       <c r="V86" s="14"/>
     </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B87" s="119"/>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -29939,8 +29942,8 @@
       <c r="U87" s="14"/>
       <c r="V87" s="14"/>
     </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B88" s="119"/>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -29971,8 +29974,8 @@
       <c r="U88" s="14"/>
       <c r="V88" s="14"/>
     </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B89" s="119"/>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -30005,8 +30008,8 @@
       <c r="U89" s="14"/>
       <c r="V89" s="14"/>
     </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B90" s="119"/>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -30037,8 +30040,8 @@
       <c r="U90" s="14"/>
       <c r="V90" s="14"/>
     </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B91" s="119"/>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -30069,8 +30072,8 @@
       <c r="U91" s="14"/>
       <c r="V91" s="14"/>
     </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B92" s="119"/>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -30109,8 +30112,8 @@
       <c r="U92" s="14"/>
       <c r="V92" s="14"/>
     </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B93" s="119"/>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -30141,8 +30144,8 @@
       <c r="U93" s="14"/>
       <c r="V93" s="14"/>
     </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B94" s="119"/>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -30173,8 +30176,8 @@
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
     </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B95" s="119"/>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -30207,8 +30210,8 @@
       <c r="U95" s="14"/>
       <c r="V95" s="14"/>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B96" s="119"/>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -30239,8 +30242,8 @@
       <c r="U96" s="14"/>
       <c r="V96" s="14"/>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B97" s="119"/>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -30271,8 +30274,8 @@
       <c r="U97" s="14"/>
       <c r="V97" s="14"/>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B98" s="119"/>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -30303,15 +30306,17 @@
       <c r="U98" s="14"/>
       <c r="V98" s="14"/>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B99" s="119"/>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
       <c r="F99" s="76">
-        <v>0</v>
-      </c>
-      <c r="G99" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="H99" s="90"/>
       <c r="I99" s="77">
         <v>0</v>
@@ -30335,15 +30340,14 @@
       <c r="U99" s="14"/>
       <c r="V99" s="14"/>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B100" s="119"/>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
       <c r="F100" s="76">
         <v>0</v>
       </c>
-      <c r="G100" s="4"/>
       <c r="H100" s="90"/>
       <c r="I100" s="77">
         <v>0</v>
@@ -30367,8 +30371,8 @@
       <c r="U100" s="14"/>
       <c r="V100" s="14"/>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B101" s="119"/>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -30399,8 +30403,8 @@
       <c r="U101" s="14"/>
       <c r="V101" s="14"/>
     </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B102" s="119"/>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -30431,8 +30435,8 @@
       <c r="U102" s="14"/>
       <c r="V102" s="14"/>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B103" s="119"/>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -30463,8 +30467,8 @@
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B104" s="119"/>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -30495,8 +30499,8 @@
       <c r="U104" s="14"/>
       <c r="V104" s="14"/>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B105" s="119"/>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -30527,8 +30531,8 @@
       <c r="U105" s="14"/>
       <c r="V105" s="14"/>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B106" s="119"/>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -30559,8 +30563,8 @@
       <c r="U106" s="14"/>
       <c r="V106" s="14"/>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B107" s="119"/>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -30591,8 +30595,8 @@
       <c r="U107" s="14"/>
       <c r="V107" s="14"/>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B108" s="119"/>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -30623,8 +30627,8 @@
       <c r="U108" s="14"/>
       <c r="V108" s="14"/>
     </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B109" s="119"/>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -30655,8 +30659,8 @@
       <c r="U109" s="14"/>
       <c r="V109" s="14"/>
     </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B110" s="119"/>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -30687,8 +30691,8 @@
       <c r="U110" s="14"/>
       <c r="V110" s="14"/>
     </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B111" s="119"/>
+    <row r="111" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -30719,8 +30723,8 @@
       <c r="U111" s="14"/>
       <c r="V111" s="14"/>
     </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B112" s="119"/>
+    <row r="112" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -30751,8 +30755,8 @@
       <c r="U112" s="14"/>
       <c r="V112" s="14"/>
     </row>
-    <row r="113" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B113" s="119"/>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -30783,8 +30787,8 @@
       <c r="U113" s="14"/>
       <c r="V113" s="14"/>
     </row>
-    <row r="114" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B114" s="119"/>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -30815,8 +30819,8 @@
       <c r="U114" s="14"/>
       <c r="V114" s="14"/>
     </row>
-    <row r="115" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B115" s="119"/>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -30847,7 +30851,7 @@
       <c r="U115" s="14"/>
       <c r="V115" s="14"/>
     </row>
-    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="12"/>
       <c r="D116" s="11"/>
       <c r="F116" s="91"/>
@@ -30867,8 +30871,8 @@
       <c r="U116" s="14"/>
       <c r="V116" s="14"/>
     </row>
-    <row r="117" spans="2:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="116" t="s">
+    <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -30901,8 +30905,8 @@
       <c r="U117" s="14"/>
       <c r="V117" s="14"/>
     </row>
-    <row r="118" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B118" s="117"/>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -30933,8 +30937,8 @@
       <c r="U118" s="14"/>
       <c r="V118" s="14"/>
     </row>
-    <row r="119" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B119" s="117"/>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -30965,8 +30969,8 @@
       <c r="U119" s="14"/>
       <c r="V119" s="14"/>
     </row>
-    <row r="120" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B120" s="117"/>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -30997,8 +31001,8 @@
       <c r="U120" s="14"/>
       <c r="V120" s="14"/>
     </row>
-    <row r="121" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B121" s="117"/>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -31029,8 +31033,8 @@
       <c r="U121" s="14"/>
       <c r="V121" s="14"/>
     </row>
-    <row r="122" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B122" s="117"/>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -31061,8 +31065,8 @@
       <c r="U122" s="14"/>
       <c r="V122" s="14"/>
     </row>
-    <row r="123" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B123" s="117"/>
+    <row r="123" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -31093,8 +31097,8 @@
       <c r="U123" s="14"/>
       <c r="V123" s="14"/>
     </row>
-    <row r="124" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B124" s="117"/>
+    <row r="124" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -31125,8 +31129,8 @@
       <c r="U124" s="14"/>
       <c r="V124" s="14"/>
     </row>
-    <row r="125" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B125" s="117"/>
+    <row r="125" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -31157,8 +31161,8 @@
       <c r="U125" s="14"/>
       <c r="V125" s="14"/>
     </row>
-    <row r="126" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B126" s="117"/>
+    <row r="126" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -31189,8 +31193,8 @@
       <c r="U126" s="14"/>
       <c r="V126" s="14"/>
     </row>
-    <row r="127" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B127" s="117"/>
+    <row r="127" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -31221,8 +31225,8 @@
       <c r="U127" s="14"/>
       <c r="V127" s="14"/>
     </row>
-    <row r="128" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B128" s="117"/>
+    <row r="128" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -31253,8 +31257,8 @@
       <c r="U128" s="14"/>
       <c r="V128" s="14"/>
     </row>
-    <row r="129" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B129" s="117"/>
+    <row r="129" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -31285,8 +31289,8 @@
       <c r="U129" s="14"/>
       <c r="V129" s="14"/>
     </row>
-    <row r="130" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B130" s="117"/>
+    <row r="130" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -31317,8 +31321,8 @@
       <c r="U130" s="14"/>
       <c r="V130" s="14"/>
     </row>
-    <row r="131" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B131" s="117"/>
+    <row r="131" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -31349,8 +31353,8 @@
       <c r="U131" s="14"/>
       <c r="V131" s="14"/>
     </row>
-    <row r="132" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B132" s="117"/>
+    <row r="132" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -31381,8 +31385,8 @@
       <c r="U132" s="14"/>
       <c r="V132" s="14"/>
     </row>
-    <row r="133" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B133" s="117"/>
+    <row r="133" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -31413,8 +31417,8 @@
       <c r="U133" s="14"/>
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B134" s="117"/>
+    <row r="134" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -31445,8 +31449,8 @@
       <c r="U134" s="14"/>
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B135" s="117"/>
+    <row r="135" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -31477,8 +31481,8 @@
       <c r="U135" s="14"/>
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B136" s="117"/>
+    <row r="136" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -31509,8 +31513,8 @@
       <c r="U136" s="14"/>
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B137" s="117"/>
+    <row r="137" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -31541,8 +31545,8 @@
       <c r="U137" s="14"/>
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B138" s="118"/>
+    <row r="138" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -31575,17 +31579,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="13" priority="23" operator="equal">
@@ -31665,21 +31669,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:H119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="14" customWidth="1"/>
     <col min="4" max="4" width="13" style="14" customWidth="1"/>
-    <col min="5" max="5" width="150.6328125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="2.6328125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="18.08984375" style="14" customWidth="1"/>
-    <col min="9" max="16384" width="10.90625" style="14"/>
+    <col min="5" max="5" width="150.5703125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="2.5703125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="10.85546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="123" t="s">
         <v>63</v>
       </c>
@@ -31693,13 +31697,13 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
       <c r="E3" s="123"/>
     </row>
-    <row r="4" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="124">
         <v>1</v>
       </c>
@@ -31717,7 +31721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="124"/>
       <c r="C5" s="5"/>
       <c r="D5" s="81" t="s">
@@ -31733,7 +31737,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="124"/>
       <c r="C6" s="5"/>
       <c r="D6" s="81" t="s">
@@ -31749,7 +31753,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="124"/>
       <c r="C7" s="5"/>
       <c r="D7" s="81" t="s">
@@ -31759,7 +31763,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="124"/>
       <c r="C8" s="5"/>
       <c r="D8" s="81" t="s">
@@ -31769,7 +31773,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="124"/>
       <c r="C9" s="5"/>
       <c r="D9" s="81" t="s">
@@ -31779,7 +31783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="124"/>
       <c r="C10" s="5"/>
       <c r="D10" s="81" t="s">
@@ -31789,7 +31793,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="124"/>
       <c r="C11" s="5"/>
       <c r="D11" s="81" t="s">
@@ -31799,7 +31803,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="120">
         <v>2</v>
       </c>
@@ -31819,7 +31823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="121"/>
       <c r="C13" s="88">
         <v>3</v>
@@ -31837,7 +31841,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="121"/>
       <c r="C14" s="88">
         <v>3</v>
@@ -31855,7 +31859,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="122"/>
       <c r="C15" s="88">
         <v>5</v>
@@ -31867,110 +31871,110 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B12:B15"/>

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C0A6F-5972-4142-A727-B64E39E4BCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0708CBB5-AA24-4D5A-83C1-1C324AB316A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -348,6 +348,15 @@
   </si>
   <si>
     <t>Busqueda por indice para usuarios, libros y posts</t>
+  </si>
+  <si>
+    <t>Cloudinary</t>
+  </si>
+  <si>
+    <t>SearchPage</t>
+  </si>
+  <si>
+    <t>Cloudinary documentacion y api</t>
   </si>
 </sst>
 </file>
@@ -1669,18 +1678,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1713,6 +1710,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2549,19 +2558,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>109.5</c:v>
+                  <c:v>111.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>68.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>116</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4603,19 +4612,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>12.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9191,12 +9200,12 @@
       </c>
       <c r="H6" s="63">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="31">
         <f>SUM(D6:H6)</f>
-        <v>109.5</v>
+        <v>111.5</v>
       </c>
       <c r="K6" s="20"/>
     </row>
@@ -9279,12 +9288,12 @@
       </c>
       <c r="H10" s="69">
         <f>SUM(WENJIE!L5:L138)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" s="41"/>
       <c r="J10" s="42">
         <f>SUM(D10:H10)</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" s="20"/>
     </row>
@@ -9367,12 +9376,12 @@
       </c>
       <c r="H14" s="75">
         <f>SUM(WENJIE!R5:R138)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="49"/>
       <c r="J14" s="50">
         <f>SUM(D14:H14)</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="20"/>
     </row>
@@ -9410,12 +9419,12 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>365.5</v>
+        <v>371.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9465,52 +9474,52 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9542,7 +9551,7 @@
       <c r="S5" s="60"/>
     </row>
     <row r="6" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9572,7 +9581,7 @@
       <c r="S6" s="60"/>
     </row>
     <row r="7" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9602,7 +9611,7 @@
       <c r="S7" s="60"/>
     </row>
     <row r="8" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9632,7 +9641,7 @@
       <c r="S8" s="60"/>
     </row>
     <row r="9" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -9664,7 +9673,7 @@
       <c r="S9" s="60"/>
     </row>
     <row r="10" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -9694,7 +9703,7 @@
       <c r="S10" s="60"/>
     </row>
     <row r="11" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -9724,7 +9733,7 @@
       <c r="S11" s="60"/>
     </row>
     <row r="12" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -9756,7 +9765,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -9786,7 +9795,7 @@
       <c r="S13" s="60"/>
     </row>
     <row r="14" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -9816,7 +9825,7 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -9846,7 +9855,7 @@
       <c r="S15" s="60"/>
     </row>
     <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -9878,7 +9887,7 @@
       <c r="S16" s="60"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -9908,7 +9917,7 @@
       <c r="S17" s="60"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -9938,7 +9947,7 @@
       <c r="S18" s="60"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -9970,7 +9979,7 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -10017,7 +10026,7 @@
       <c r="S21" s="101"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10049,7 +10058,7 @@
       <c r="S22" s="60"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10079,7 +10088,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10109,7 +10118,7 @@
       <c r="S24" s="60"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10139,7 +10148,7 @@
       <c r="S25" s="60"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10169,7 +10178,7 @@
       <c r="S26" s="60"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10203,7 +10212,7 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10233,7 +10242,7 @@
       <c r="S28" s="60"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10263,7 +10272,7 @@
       <c r="S29" s="60"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10293,7 +10302,7 @@
       <c r="S30" s="60"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10325,7 +10334,7 @@
       <c r="S31" s="60"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10355,7 +10364,7 @@
       <c r="S32" s="60"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10385,7 +10394,7 @@
       <c r="S33" s="60"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10417,7 +10426,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10447,7 +10456,7 @@
       <c r="S35" s="60"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10477,7 +10486,7 @@
       <c r="S36" s="60"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10507,7 +10516,7 @@
       <c r="S37" s="60"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10539,7 +10548,7 @@
       <c r="S38" s="60"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10571,7 +10580,7 @@
       <c r="S39" s="60"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10601,7 +10610,7 @@
       <c r="S40" s="60"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10633,7 +10642,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -10663,7 +10672,7 @@
       <c r="S42" s="60"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -10693,7 +10702,7 @@
       <c r="S43" s="60"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -10723,7 +10732,7 @@
       <c r="S44" s="60"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -10757,7 +10766,7 @@
       <c r="S45" s="60"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -10787,7 +10796,7 @@
       <c r="S46" s="60"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -10817,7 +10826,7 @@
       <c r="S47" s="60"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -10849,7 +10858,7 @@
       </c>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -10879,7 +10888,7 @@
       <c r="S49" s="60"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -10909,7 +10918,7 @@
       <c r="S50" s="60"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -10939,7 +10948,7 @@
       <c r="S51" s="60"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -10986,7 +10995,7 @@
       <c r="S53" s="101"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11018,7 +11027,7 @@
       <c r="S54" s="60"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11048,7 +11057,7 @@
       <c r="S55" s="60"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11080,7 +11089,7 @@
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11110,7 +11119,7 @@
       <c r="S57" s="60"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11140,7 +11149,7 @@
       <c r="S58" s="60"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11170,7 +11179,7 @@
       <c r="S59" s="60"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11200,7 +11209,7 @@
       <c r="S60" s="60"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11230,7 +11239,7 @@
       <c r="S61" s="60"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11260,7 +11269,7 @@
       <c r="S62" s="60"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11290,7 +11299,7 @@
       <c r="S63" s="60"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11322,7 +11331,7 @@
       </c>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11352,7 +11361,7 @@
       <c r="S65" s="60"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11382,7 +11391,7 @@
       <c r="S66" s="60"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11412,7 +11421,7 @@
       <c r="S67" s="60"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11442,7 +11451,7 @@
       <c r="S68" s="60"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11476,7 +11485,7 @@
       <c r="S69" s="60"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11508,7 +11517,7 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11538,7 +11547,7 @@
       <c r="S71" s="60"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11568,7 +11577,7 @@
       <c r="S72" s="60"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11598,7 +11607,7 @@
       <c r="S73" s="60"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11630,7 +11639,7 @@
       <c r="S74" s="60"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -11660,7 +11669,7 @@
       <c r="S75" s="60"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -11690,7 +11699,7 @@
       <c r="S76" s="60"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -11722,7 +11731,7 @@
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -11752,7 +11761,7 @@
       <c r="S78" s="60"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -11782,7 +11791,7 @@
       <c r="S79" s="60"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -11812,7 +11821,7 @@
       <c r="S80" s="60"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -11842,7 +11851,7 @@
       <c r="S81" s="60"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -11872,7 +11881,7 @@
       <c r="S82" s="60"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -11920,7 +11929,7 @@
       <c r="S84" s="101"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -11954,7 +11963,7 @@
       </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -11984,7 +11993,7 @@
       <c r="S86" s="60"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12014,7 +12023,7 @@
       <c r="S87" s="60"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12044,7 +12053,7 @@
       <c r="S88" s="60"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12076,7 +12085,7 @@
       </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12104,7 +12113,7 @@
       <c r="S90" s="60"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12134,7 +12143,7 @@
       <c r="S91" s="60"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12166,7 +12175,7 @@
       </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12196,7 +12205,7 @@
       <c r="S93" s="60"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12226,7 +12235,7 @@
       <c r="S94" s="60"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12256,7 +12265,7 @@
       <c r="S95" s="60"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12286,7 +12295,7 @@
       <c r="S96" s="60"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12316,7 +12325,7 @@
       <c r="S97" s="60"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12346,7 +12355,7 @@
       <c r="S98" s="60"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12376,7 +12385,7 @@
       <c r="S99" s="60"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12406,7 +12415,7 @@
       <c r="S100" s="60"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12436,7 +12445,7 @@
       <c r="S101" s="60"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12466,7 +12475,7 @@
       <c r="S102" s="60"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12496,7 +12505,7 @@
       <c r="S103" s="60"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12526,7 +12535,7 @@
       <c r="S104" s="60"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12556,7 +12565,7 @@
       <c r="S105" s="60"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12586,7 +12595,7 @@
       <c r="S106" s="60"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12616,7 +12625,7 @@
       <c r="S107" s="60"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -12646,7 +12655,7 @@
       <c r="S108" s="60"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -12676,7 +12685,7 @@
       <c r="S109" s="60"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -12706,7 +12715,7 @@
       <c r="S110" s="60"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -12736,7 +12745,7 @@
       <c r="S111" s="60"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -12766,7 +12775,7 @@
       <c r="S112" s="60"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -12796,7 +12805,7 @@
       <c r="S113" s="60"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -12826,7 +12835,7 @@
       <c r="S114" s="60"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -12874,7 +12883,7 @@
       <c r="S116" s="101"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -12906,7 +12915,7 @@
       <c r="S117" s="60"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -12936,7 +12945,7 @@
       <c r="S118" s="60"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -12966,7 +12975,7 @@
       <c r="S119" s="60"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -12996,7 +13005,7 @@
       <c r="S120" s="60"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13026,7 +13035,7 @@
       <c r="S121" s="60"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13056,7 +13065,7 @@
       <c r="S122" s="60"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13086,7 +13095,7 @@
       <c r="S123" s="60"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13116,7 +13125,7 @@
       <c r="S124" s="60"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13146,7 +13155,7 @@
       <c r="S125" s="60"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13176,7 +13185,7 @@
       <c r="S126" s="60"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13206,7 +13215,7 @@
       <c r="S127" s="60"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13236,7 +13245,7 @@
       <c r="S128" s="60"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13266,7 +13275,7 @@
       <c r="S129" s="60"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13296,7 +13305,7 @@
       <c r="S130" s="60"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13326,7 +13335,7 @@
       <c r="S131" s="60"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13356,7 +13365,7 @@
       <c r="S132" s="60"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13386,7 +13395,7 @@
       <c r="S133" s="60"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13416,7 +13425,7 @@
       <c r="S134" s="60"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13446,7 +13455,7 @@
       <c r="S135" s="60"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13476,7 +13485,7 @@
       <c r="S136" s="60"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13506,7 +13515,7 @@
       <c r="S137" s="60"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13537,17 +13546,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
@@ -13633,52 +13642,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -13712,7 +13721,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -13744,7 +13753,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -13776,7 +13785,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -13808,7 +13817,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -13842,7 +13851,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -13874,7 +13883,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -13906,7 +13915,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -13940,7 +13949,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -13972,7 +13981,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14004,7 +14013,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14036,7 +14045,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14070,7 +14079,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14102,7 +14111,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14134,7 +14143,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14168,7 +14177,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14219,7 +14228,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14253,7 +14262,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14285,7 +14294,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14317,7 +14326,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14349,7 +14358,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14381,7 +14390,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14417,7 +14426,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14449,7 +14458,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14481,7 +14490,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14513,7 +14522,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14547,7 +14556,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14579,7 +14588,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14611,7 +14620,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -14645,7 +14654,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -14677,7 +14686,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -14709,7 +14718,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -14741,7 +14750,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -14775,7 +14784,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -14809,7 +14818,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -14841,7 +14850,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -14875,7 +14884,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -14907,7 +14916,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -14939,7 +14948,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -14971,7 +14980,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15007,7 +15016,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15039,7 +15048,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15071,7 +15080,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15105,7 +15114,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15137,7 +15146,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15169,7 +15178,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15201,7 +15210,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15252,7 +15261,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15286,7 +15295,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15318,7 +15327,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15352,7 +15361,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15384,7 +15393,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15416,7 +15425,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15448,7 +15457,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15480,7 +15489,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15512,7 +15521,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15544,7 +15553,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15576,7 +15585,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15610,7 +15619,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -15642,7 +15651,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -15674,7 +15683,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -15706,7 +15715,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -15738,7 +15747,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -15774,7 +15783,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -15808,7 +15817,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -15840,7 +15849,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -15872,7 +15881,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -15904,7 +15913,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -15938,7 +15947,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -15970,7 +15979,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -16002,7 +16011,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16036,7 +16045,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16068,7 +16077,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16100,7 +16109,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16132,7 +16141,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16164,7 +16173,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16196,7 +16205,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16248,7 +16257,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16284,7 +16293,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16316,7 +16325,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16348,7 +16357,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16380,7 +16389,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16414,7 +16423,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16446,7 +16455,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16478,7 +16487,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16512,7 +16521,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16544,7 +16553,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16576,7 +16585,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16608,7 +16617,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16640,7 +16649,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -16672,7 +16681,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -16704,7 +16713,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -16736,7 +16745,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -16768,7 +16777,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -16800,7 +16809,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -16832,7 +16841,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -16864,7 +16873,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -16896,7 +16905,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -16928,7 +16937,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -16960,7 +16969,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -16992,7 +17001,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17024,7 +17033,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17056,7 +17065,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17088,7 +17097,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17120,7 +17129,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17152,7 +17161,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17184,7 +17193,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17216,7 +17225,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17268,7 +17277,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17302,7 +17311,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17334,7 +17343,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17366,7 +17375,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17398,7 +17407,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17430,7 +17439,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17462,7 +17471,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17494,7 +17503,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17526,7 +17535,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17558,7 +17567,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17590,7 +17599,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17622,7 +17631,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -17654,7 +17663,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -17686,7 +17695,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -17718,7 +17727,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -17750,7 +17759,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -17782,7 +17791,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -17814,7 +17823,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -17846,7 +17855,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -17878,7 +17887,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -17910,7 +17919,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -17942,7 +17951,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -17975,17 +17984,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
@@ -18091,52 +18100,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18170,7 +18179,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18202,7 +18211,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18234,7 +18243,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18266,7 +18275,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18300,7 +18309,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18332,7 +18341,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18364,7 +18373,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18398,7 +18407,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18430,7 +18439,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18462,7 +18471,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18494,7 +18503,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18528,7 +18537,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18560,7 +18569,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -18592,7 +18601,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -18626,7 +18635,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -18677,7 +18686,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -18711,7 +18720,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -18743,7 +18752,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -18775,7 +18784,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -18807,7 +18816,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -18839,7 +18848,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -18875,7 +18884,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -18907,7 +18916,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -18939,7 +18948,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -18971,7 +18980,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19005,7 +19014,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19037,7 +19046,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19069,7 +19078,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19103,7 +19112,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19135,7 +19144,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19167,7 +19176,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19199,7 +19208,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19235,7 +19244,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19267,7 +19276,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19299,7 +19308,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19333,7 +19342,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19365,7 +19374,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19397,7 +19406,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19429,7 +19438,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19465,7 +19474,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19497,7 +19506,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19529,7 +19538,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19563,7 +19572,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -19595,7 +19604,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -19627,7 +19636,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -19659,7 +19668,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -19710,7 +19719,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -19744,7 +19753,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -19776,7 +19785,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -19810,7 +19819,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -19842,7 +19851,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -19874,7 +19883,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -19906,7 +19915,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -19938,7 +19947,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -19970,7 +19979,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -20002,7 +20011,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20034,7 +20043,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20068,7 +20077,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20100,7 +20109,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20132,7 +20141,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20164,7 +20173,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20200,7 +20209,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20232,7 +20241,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20266,7 +20275,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20298,7 +20307,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20330,7 +20339,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20362,7 +20371,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20396,7 +20405,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20428,7 +20437,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20460,7 +20469,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20494,7 +20503,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20526,7 +20535,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20558,7 +20567,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -20590,7 +20599,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -20622,7 +20631,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -20654,7 +20663,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -20706,7 +20715,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -20742,7 +20751,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -20774,7 +20783,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -20806,7 +20815,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -20838,7 +20847,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -20872,7 +20881,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -20904,7 +20913,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -20936,7 +20945,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -20970,7 +20979,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -21002,7 +21011,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21034,7 +21043,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21066,7 +21075,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21098,7 +21107,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21130,7 +21139,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21162,7 +21171,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21194,7 +21203,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21226,7 +21235,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21258,7 +21267,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21290,7 +21299,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21322,7 +21331,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21354,7 +21363,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21386,7 +21395,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21418,7 +21427,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21450,7 +21459,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21482,7 +21491,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21514,7 +21523,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21546,7 +21555,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -21578,7 +21587,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -21610,7 +21619,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -21642,7 +21651,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -21674,7 +21683,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -21726,7 +21735,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -21760,7 +21769,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -21792,7 +21801,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -21824,7 +21833,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -21856,7 +21865,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -21888,7 +21897,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -21920,7 +21929,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -21952,7 +21961,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -21984,7 +21993,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22016,7 +22025,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22048,7 +22057,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22080,7 +22089,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22112,7 +22121,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22144,7 +22153,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22176,7 +22185,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22208,7 +22217,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22240,7 +22249,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22272,7 +22281,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22304,7 +22313,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22336,7 +22345,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -22368,7 +22377,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -22400,7 +22409,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -22433,17 +22442,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="41" priority="25" operator="equal">
@@ -22549,52 +22558,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -22628,7 +22637,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -22660,7 +22669,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -22692,7 +22701,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -22724,7 +22733,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -22758,7 +22767,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -22790,7 +22799,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -22822,7 +22831,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -22856,7 +22865,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -22888,7 +22897,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -22920,7 +22929,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -22952,7 +22961,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -22986,7 +22995,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -23018,7 +23027,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -23050,7 +23059,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -23084,7 +23093,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -23135,7 +23144,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -23169,7 +23178,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -23201,7 +23210,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -23233,7 +23242,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -23265,7 +23274,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -23297,7 +23306,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -23333,7 +23342,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -23365,7 +23374,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -23397,7 +23406,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -23429,7 +23438,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -23463,7 +23472,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -23495,7 +23504,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -23527,7 +23536,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -23561,7 +23570,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -23593,7 +23602,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -23625,7 +23634,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -23661,7 +23670,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -23695,7 +23704,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -23727,7 +23736,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -23761,7 +23770,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -23795,7 +23804,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -23827,7 +23836,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -23859,7 +23868,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -23891,7 +23900,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -23927,7 +23936,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -23959,7 +23968,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -23991,7 +24000,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -24025,7 +24034,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -24057,7 +24066,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -24089,7 +24098,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -24121,7 +24130,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -24172,7 +24181,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -24206,7 +24215,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -24238,7 +24247,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -24272,7 +24281,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -24304,7 +24313,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -24336,7 +24345,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -24368,7 +24377,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -24400,7 +24409,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -24432,7 +24441,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -24464,7 +24473,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -24496,7 +24505,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -24530,7 +24539,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -24562,7 +24571,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -24594,7 +24603,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -24626,7 +24635,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -24658,7 +24667,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -24690,7 +24699,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -24724,7 +24733,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -24756,7 +24765,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -24788,7 +24797,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -24820,7 +24829,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -24854,7 +24863,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -24886,7 +24895,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -24918,7 +24927,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -24952,7 +24961,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -24984,7 +24993,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -25016,7 +25025,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -25048,7 +25057,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -25080,7 +25089,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -25112,7 +25121,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -25164,7 +25173,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -25198,7 +25207,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -25228,7 +25237,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -25260,7 +25269,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -25292,7 +25301,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -25326,7 +25335,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -25358,7 +25367,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -25390,7 +25399,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -25424,7 +25433,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -25456,7 +25465,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -25488,7 +25497,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -25520,7 +25529,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -25552,7 +25561,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -25584,7 +25593,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -25616,7 +25625,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -25648,7 +25657,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -25680,7 +25689,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -25712,7 +25721,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -25744,7 +25753,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -25776,7 +25785,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -25808,7 +25817,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -25840,7 +25849,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -25872,7 +25881,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -25904,7 +25913,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -25936,7 +25945,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -25968,7 +25977,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -26000,7 +26009,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -26032,7 +26041,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -26064,7 +26073,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -26096,7 +26105,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -26128,7 +26137,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -26180,7 +26189,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -26214,7 +26223,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -26246,7 +26255,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -26278,7 +26287,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -26310,7 +26319,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -26342,7 +26351,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -26374,7 +26383,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -26406,7 +26415,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -26438,7 +26447,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -26470,7 +26479,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -26502,7 +26511,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -26534,7 +26543,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -26566,7 +26575,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -26598,7 +26607,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -26630,7 +26639,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -26662,7 +26671,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -26694,7 +26703,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -26726,7 +26735,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -26758,7 +26767,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -26790,7 +26799,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -26822,7 +26831,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -26854,7 +26863,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -27212,52 +27221,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -27291,7 +27300,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -27323,7 +27332,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -27355,7 +27364,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -27387,7 +27396,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -27421,7 +27430,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -27453,7 +27462,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -27485,7 +27494,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -27519,7 +27528,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -27551,7 +27560,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -27583,7 +27592,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -27615,7 +27624,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -27649,7 +27658,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -27681,7 +27690,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -27713,7 +27722,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -27747,7 +27756,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -27798,7 +27807,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -27832,7 +27841,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -27864,7 +27873,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -27896,7 +27905,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -27928,7 +27937,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -27960,7 +27969,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -27996,7 +28005,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -28028,7 +28037,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -28060,7 +28069,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -28092,7 +28101,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -28126,7 +28135,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -28158,7 +28167,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -28190,7 +28199,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -28224,7 +28233,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -28256,7 +28265,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -28288,7 +28297,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -28320,7 +28329,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -28354,7 +28363,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -28388,7 +28397,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -28424,7 +28433,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -28458,7 +28467,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -28490,7 +28499,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -28522,7 +28531,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -28554,7 +28563,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -28590,7 +28599,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -28622,7 +28631,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -28654,7 +28663,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -28688,7 +28697,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -28720,7 +28729,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -28752,7 +28761,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -28784,7 +28793,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -28835,7 +28844,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -28869,7 +28878,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -28901,7 +28910,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -28935,7 +28944,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -28969,7 +28978,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -29003,7 +29012,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -29035,7 +29044,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -29067,7 +29076,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -29099,7 +29108,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -29131,7 +29140,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -29163,7 +29172,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -29197,7 +29206,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -29229,7 +29238,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -29261,7 +29270,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -29293,7 +29302,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -29325,7 +29334,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -29361,7 +29370,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -29395,7 +29404,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -29427,7 +29436,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -29461,7 +29470,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -29493,7 +29502,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -29527,7 +29536,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -29559,7 +29568,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -29591,7 +29600,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -29625,7 +29634,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -29657,7 +29666,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -29689,7 +29698,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -29721,7 +29730,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -29753,7 +29762,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -29787,7 +29796,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -29839,7 +29848,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -29875,7 +29884,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -29911,7 +29920,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -29943,7 +29952,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -29975,7 +29984,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -30009,7 +30018,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -30041,7 +30050,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -30073,7 +30082,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -30113,7 +30122,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -30145,7 +30154,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -30177,7 +30186,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -30211,7 +30220,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -30243,7 +30252,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -30275,7 +30284,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -30307,7 +30316,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -30341,7 +30350,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -30372,7 +30381,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -30404,7 +30413,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -30436,14 +30445,16 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
       <c r="F103" s="76">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="H103" s="90"/>
       <c r="I103" s="77">
         <v>0</v>
@@ -30451,9 +30462,11 @@
       <c r="J103" s="57"/>
       <c r="K103" s="90"/>
       <c r="L103" s="78">
-        <v>0</v>
-      </c>
-      <c r="M103" s="58"/>
+        <v>3</v>
+      </c>
+      <c r="M103" s="58" t="s">
+        <v>103</v>
+      </c>
       <c r="N103" s="90"/>
       <c r="O103" s="79">
         <v>0</v>
@@ -30461,14 +30474,16 @@
       <c r="P103" s="59"/>
       <c r="Q103" s="90"/>
       <c r="R103" s="80">
-        <v>0</v>
-      </c>
-      <c r="S103" s="60"/>
+        <v>1</v>
+      </c>
+      <c r="S103" s="60" t="s">
+        <v>104</v>
+      </c>
       <c r="U103" s="14"/>
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -30500,7 +30515,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -30532,7 +30547,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -30564,7 +30579,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -30596,7 +30611,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -30628,7 +30643,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -30660,7 +30675,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -30692,7 +30707,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -30724,7 +30739,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -30756,7 +30771,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -30788,7 +30803,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -30820,7 +30835,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -30872,7 +30887,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -30906,7 +30921,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -30938,7 +30953,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -30970,7 +30985,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -31002,7 +31017,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -31034,7 +31049,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -31066,7 +31081,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -31098,7 +31113,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -31130,7 +31145,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -31162,7 +31177,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -31194,7 +31209,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -31226,7 +31241,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -31258,7 +31273,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -31290,7 +31305,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -31322,7 +31337,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -31354,7 +31369,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -31386,7 +31401,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -31418,7 +31433,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -31450,7 +31465,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -31482,7 +31497,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -31514,7 +31529,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -31546,7 +31561,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -31579,17 +31594,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="13" priority="23" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0708CBB5-AA24-4D5A-83C1-1C324AB316A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695FF3EA-E9F0-4F9E-9DAF-3A34640A726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="106">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>Cloudinary documentacion y api</t>
+  </si>
+  <si>
+    <t>Cloudinary signature as token</t>
   </si>
 </sst>
 </file>
@@ -1678,6 +1681,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1710,18 +1725,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2558,7 +2561,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>111.5</c:v>
+                  <c:v>113.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39.5</c:v>
@@ -4612,7 +4615,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
@@ -9200,12 +9203,12 @@
       </c>
       <c r="H6" s="63">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="31">
         <f>SUM(D6:H6)</f>
-        <v>111.5</v>
+        <v>113.5</v>
       </c>
       <c r="K6" s="20"/>
     </row>
@@ -9419,12 +9422,12 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>371.5</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9474,52 +9477,52 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9551,7 +9554,7 @@
       <c r="S5" s="60"/>
     </row>
     <row r="6" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9581,7 +9584,7 @@
       <c r="S6" s="60"/>
     </row>
     <row r="7" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9611,7 +9614,7 @@
       <c r="S7" s="60"/>
     </row>
     <row r="8" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9641,7 +9644,7 @@
       <c r="S8" s="60"/>
     </row>
     <row r="9" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -9673,7 +9676,7 @@
       <c r="S9" s="60"/>
     </row>
     <row r="10" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -9703,7 +9706,7 @@
       <c r="S10" s="60"/>
     </row>
     <row r="11" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -9733,7 +9736,7 @@
       <c r="S11" s="60"/>
     </row>
     <row r="12" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -9765,7 +9768,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -9795,7 +9798,7 @@
       <c r="S13" s="60"/>
     </row>
     <row r="14" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -9825,7 +9828,7 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -9855,7 +9858,7 @@
       <c r="S15" s="60"/>
     </row>
     <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -9887,7 +9890,7 @@
       <c r="S16" s="60"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -9917,7 +9920,7 @@
       <c r="S17" s="60"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -9947,7 +9950,7 @@
       <c r="S18" s="60"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -9979,7 +9982,7 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -10026,7 +10029,7 @@
       <c r="S21" s="101"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10058,7 +10061,7 @@
       <c r="S22" s="60"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10088,7 +10091,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10118,7 +10121,7 @@
       <c r="S24" s="60"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10148,7 +10151,7 @@
       <c r="S25" s="60"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10178,7 +10181,7 @@
       <c r="S26" s="60"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10212,7 +10215,7 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10242,7 +10245,7 @@
       <c r="S28" s="60"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10272,7 +10275,7 @@
       <c r="S29" s="60"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10302,7 +10305,7 @@
       <c r="S30" s="60"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10334,7 +10337,7 @@
       <c r="S31" s="60"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10364,7 +10367,7 @@
       <c r="S32" s="60"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10394,7 +10397,7 @@
       <c r="S33" s="60"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10426,7 +10429,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10456,7 +10459,7 @@
       <c r="S35" s="60"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10486,7 +10489,7 @@
       <c r="S36" s="60"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10516,7 +10519,7 @@
       <c r="S37" s="60"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10548,7 +10551,7 @@
       <c r="S38" s="60"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10580,7 +10583,7 @@
       <c r="S39" s="60"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10610,7 +10613,7 @@
       <c r="S40" s="60"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10642,7 +10645,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -10672,7 +10675,7 @@
       <c r="S42" s="60"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -10702,7 +10705,7 @@
       <c r="S43" s="60"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -10732,7 +10735,7 @@
       <c r="S44" s="60"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -10766,7 +10769,7 @@
       <c r="S45" s="60"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -10796,7 +10799,7 @@
       <c r="S46" s="60"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -10826,7 +10829,7 @@
       <c r="S47" s="60"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -10858,7 +10861,7 @@
       </c>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -10888,7 +10891,7 @@
       <c r="S49" s="60"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -10918,7 +10921,7 @@
       <c r="S50" s="60"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -10948,7 +10951,7 @@
       <c r="S51" s="60"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -10995,7 +10998,7 @@
       <c r="S53" s="101"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11027,7 +11030,7 @@
       <c r="S54" s="60"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11057,7 +11060,7 @@
       <c r="S55" s="60"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11089,7 +11092,7 @@
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11119,7 +11122,7 @@
       <c r="S57" s="60"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11149,7 +11152,7 @@
       <c r="S58" s="60"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11179,7 +11182,7 @@
       <c r="S59" s="60"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11209,7 +11212,7 @@
       <c r="S60" s="60"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11239,7 +11242,7 @@
       <c r="S61" s="60"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11269,7 +11272,7 @@
       <c r="S62" s="60"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11299,7 +11302,7 @@
       <c r="S63" s="60"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11331,7 +11334,7 @@
       </c>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11361,7 +11364,7 @@
       <c r="S65" s="60"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11391,7 +11394,7 @@
       <c r="S66" s="60"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11421,7 +11424,7 @@
       <c r="S67" s="60"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11451,7 +11454,7 @@
       <c r="S68" s="60"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11485,7 +11488,7 @@
       <c r="S69" s="60"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11517,7 +11520,7 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11547,7 +11550,7 @@
       <c r="S71" s="60"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11577,7 +11580,7 @@
       <c r="S72" s="60"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11607,7 +11610,7 @@
       <c r="S73" s="60"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11639,7 +11642,7 @@
       <c r="S74" s="60"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -11669,7 +11672,7 @@
       <c r="S75" s="60"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -11699,7 +11702,7 @@
       <c r="S76" s="60"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -11731,7 +11734,7 @@
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -11761,7 +11764,7 @@
       <c r="S78" s="60"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -11791,7 +11794,7 @@
       <c r="S79" s="60"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -11821,7 +11824,7 @@
       <c r="S80" s="60"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -11851,7 +11854,7 @@
       <c r="S81" s="60"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -11881,7 +11884,7 @@
       <c r="S82" s="60"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -11929,7 +11932,7 @@
       <c r="S84" s="101"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -11963,7 +11966,7 @@
       </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -11993,7 +11996,7 @@
       <c r="S86" s="60"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12023,7 +12026,7 @@
       <c r="S87" s="60"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12053,7 +12056,7 @@
       <c r="S88" s="60"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12085,7 +12088,7 @@
       </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12113,7 +12116,7 @@
       <c r="S90" s="60"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12143,7 +12146,7 @@
       <c r="S91" s="60"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12175,7 +12178,7 @@
       </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12205,7 +12208,7 @@
       <c r="S93" s="60"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12235,7 +12238,7 @@
       <c r="S94" s="60"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12265,7 +12268,7 @@
       <c r="S95" s="60"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12295,7 +12298,7 @@
       <c r="S96" s="60"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12325,7 +12328,7 @@
       <c r="S97" s="60"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12355,7 +12358,7 @@
       <c r="S98" s="60"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12385,7 +12388,7 @@
       <c r="S99" s="60"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12415,7 +12418,7 @@
       <c r="S100" s="60"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12445,7 +12448,7 @@
       <c r="S101" s="60"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12475,7 +12478,7 @@
       <c r="S102" s="60"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12505,7 +12508,7 @@
       <c r="S103" s="60"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12535,7 +12538,7 @@
       <c r="S104" s="60"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12565,7 +12568,7 @@
       <c r="S105" s="60"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12595,7 +12598,7 @@
       <c r="S106" s="60"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12625,7 +12628,7 @@
       <c r="S107" s="60"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -12655,7 +12658,7 @@
       <c r="S108" s="60"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -12685,7 +12688,7 @@
       <c r="S109" s="60"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -12715,7 +12718,7 @@
       <c r="S110" s="60"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -12745,7 +12748,7 @@
       <c r="S111" s="60"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -12775,7 +12778,7 @@
       <c r="S112" s="60"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -12805,7 +12808,7 @@
       <c r="S113" s="60"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -12835,7 +12838,7 @@
       <c r="S114" s="60"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -12883,7 +12886,7 @@
       <c r="S116" s="101"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -12915,7 +12918,7 @@
       <c r="S117" s="60"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -12945,7 +12948,7 @@
       <c r="S118" s="60"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -12975,7 +12978,7 @@
       <c r="S119" s="60"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -13005,7 +13008,7 @@
       <c r="S120" s="60"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13035,7 +13038,7 @@
       <c r="S121" s="60"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13065,7 +13068,7 @@
       <c r="S122" s="60"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13095,7 +13098,7 @@
       <c r="S123" s="60"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13125,7 +13128,7 @@
       <c r="S124" s="60"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13155,7 +13158,7 @@
       <c r="S125" s="60"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13185,7 +13188,7 @@
       <c r="S126" s="60"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13215,7 +13218,7 @@
       <c r="S127" s="60"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13245,7 +13248,7 @@
       <c r="S128" s="60"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13275,7 +13278,7 @@
       <c r="S129" s="60"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13305,7 +13308,7 @@
       <c r="S130" s="60"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13335,7 +13338,7 @@
       <c r="S131" s="60"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13365,7 +13368,7 @@
       <c r="S132" s="60"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13395,7 +13398,7 @@
       <c r="S133" s="60"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13425,7 +13428,7 @@
       <c r="S134" s="60"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13455,7 +13458,7 @@
       <c r="S135" s="60"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13485,7 +13488,7 @@
       <c r="S136" s="60"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13515,7 +13518,7 @@
       <c r="S137" s="60"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13546,17 +13549,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
@@ -13642,52 +13645,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -13721,7 +13724,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -13753,7 +13756,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -13785,7 +13788,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -13817,7 +13820,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -13851,7 +13854,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -13883,7 +13886,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -13915,7 +13918,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -13949,7 +13952,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -13981,7 +13984,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14013,7 +14016,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14045,7 +14048,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14079,7 +14082,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14111,7 +14114,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14143,7 +14146,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14177,7 +14180,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14228,7 +14231,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14262,7 +14265,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14294,7 +14297,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14326,7 +14329,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14358,7 +14361,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14390,7 +14393,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14426,7 +14429,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14458,7 +14461,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14490,7 +14493,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14522,7 +14525,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14556,7 +14559,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14588,7 +14591,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14620,7 +14623,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -14654,7 +14657,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -14686,7 +14689,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -14718,7 +14721,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -14750,7 +14753,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -14784,7 +14787,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -14818,7 +14821,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -14850,7 +14853,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -14884,7 +14887,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -14916,7 +14919,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -14948,7 +14951,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -14980,7 +14983,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15016,7 +15019,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15048,7 +15051,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15080,7 +15083,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15114,7 +15117,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15146,7 +15149,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15178,7 +15181,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15210,7 +15213,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15261,7 +15264,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15295,7 +15298,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15327,7 +15330,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15361,7 +15364,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15393,7 +15396,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15425,7 +15428,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15457,7 +15460,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15489,7 +15492,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15521,7 +15524,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15553,7 +15556,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15585,7 +15588,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15619,7 +15622,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -15651,7 +15654,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -15683,7 +15686,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -15715,7 +15718,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -15747,7 +15750,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -15783,7 +15786,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -15817,7 +15820,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -15849,7 +15852,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -15881,7 +15884,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -15913,7 +15916,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -15947,7 +15950,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -15979,7 +15982,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -16011,7 +16014,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16045,7 +16048,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16077,7 +16080,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16109,7 +16112,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16141,7 +16144,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16173,7 +16176,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16205,7 +16208,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16257,7 +16260,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16293,7 +16296,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16325,7 +16328,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16357,7 +16360,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16389,7 +16392,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16423,7 +16426,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16455,7 +16458,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16487,7 +16490,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16521,7 +16524,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16553,7 +16556,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16585,7 +16588,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16617,7 +16620,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16649,7 +16652,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -16681,7 +16684,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -16713,7 +16716,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -16745,7 +16748,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -16777,7 +16780,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -16809,7 +16812,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -16841,7 +16844,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -16873,7 +16876,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -16905,7 +16908,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -16937,7 +16940,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -16969,7 +16972,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -17001,7 +17004,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17033,7 +17036,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17065,7 +17068,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17097,7 +17100,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17129,7 +17132,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17161,7 +17164,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17193,7 +17196,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17225,7 +17228,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17277,7 +17280,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17311,7 +17314,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17343,7 +17346,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17375,7 +17378,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17407,7 +17410,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17439,7 +17442,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17471,7 +17474,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17503,7 +17506,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17535,7 +17538,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17567,7 +17570,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17599,7 +17602,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17631,7 +17634,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -17663,7 +17666,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -17695,7 +17698,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -17727,7 +17730,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -17759,7 +17762,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -17791,7 +17794,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -17823,7 +17826,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -17855,7 +17858,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -17887,7 +17890,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -17919,7 +17922,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -17951,7 +17954,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -17984,17 +17987,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
@@ -18100,52 +18103,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18179,7 +18182,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18211,7 +18214,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18243,7 +18246,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18275,7 +18278,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18309,7 +18312,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18341,7 +18344,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18373,7 +18376,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18407,7 +18410,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18439,7 +18442,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18471,7 +18474,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18503,7 +18506,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18537,7 +18540,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18569,7 +18572,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -18601,7 +18604,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -18635,7 +18638,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -18686,7 +18689,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -18720,7 +18723,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -18752,7 +18755,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -18784,7 +18787,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -18816,7 +18819,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -18848,7 +18851,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -18884,7 +18887,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -18916,7 +18919,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -18948,7 +18951,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -18980,7 +18983,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19014,7 +19017,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19046,7 +19049,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19078,7 +19081,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19112,7 +19115,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19144,7 +19147,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19176,7 +19179,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19208,7 +19211,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19244,7 +19247,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19276,7 +19279,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19308,7 +19311,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19342,7 +19345,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19374,7 +19377,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19406,7 +19409,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19438,7 +19441,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19474,7 +19477,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19506,7 +19509,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19538,7 +19541,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19572,7 +19575,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -19604,7 +19607,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -19636,7 +19639,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -19668,7 +19671,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -19719,7 +19722,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -19753,7 +19756,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -19785,7 +19788,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -19819,7 +19822,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -19851,7 +19854,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -19883,7 +19886,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -19915,7 +19918,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -19947,7 +19950,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -19979,7 +19982,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -20011,7 +20014,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20043,7 +20046,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20077,7 +20080,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20109,7 +20112,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20141,7 +20144,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20173,7 +20176,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20209,7 +20212,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20241,7 +20244,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20275,7 +20278,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20307,7 +20310,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20339,7 +20342,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20371,7 +20374,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20405,7 +20408,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20437,7 +20440,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20469,7 +20472,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20503,7 +20506,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20535,7 +20538,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20567,7 +20570,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -20599,7 +20602,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -20631,7 +20634,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -20663,7 +20666,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -20715,7 +20718,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -20751,7 +20754,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -20783,7 +20786,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -20815,7 +20818,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -20847,7 +20850,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -20881,7 +20884,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -20913,7 +20916,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -20945,7 +20948,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -20979,7 +20982,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -21011,7 +21014,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21043,7 +21046,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21075,7 +21078,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21107,7 +21110,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21139,7 +21142,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21171,7 +21174,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21203,7 +21206,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21235,7 +21238,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21267,7 +21270,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21299,7 +21302,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21331,7 +21334,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21363,7 +21366,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21395,7 +21398,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21427,7 +21430,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21459,7 +21462,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21491,7 +21494,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21523,7 +21526,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21555,7 +21558,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -21587,7 +21590,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -21619,7 +21622,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -21651,7 +21654,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -21683,7 +21686,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -21735,7 +21738,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -21769,7 +21772,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -21801,7 +21804,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -21833,7 +21836,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -21865,7 +21868,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -21897,7 +21900,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -21929,7 +21932,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -21961,7 +21964,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -21993,7 +21996,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22025,7 +22028,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22057,7 +22060,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22089,7 +22092,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22121,7 +22124,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22153,7 +22156,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22185,7 +22188,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22217,7 +22220,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22249,7 +22252,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22281,7 +22284,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22313,7 +22316,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22345,7 +22348,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -22377,7 +22380,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -22409,7 +22412,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -22442,17 +22445,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="41" priority="25" operator="equal">
@@ -22558,52 +22561,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -22637,7 +22640,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -22669,7 +22672,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -22701,7 +22704,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -22733,7 +22736,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -22767,7 +22770,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -22799,7 +22802,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -22831,7 +22834,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -22865,7 +22868,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -22897,7 +22900,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -22929,7 +22932,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -22961,7 +22964,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -22995,7 +22998,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -23027,7 +23030,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -23059,7 +23062,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -23093,7 +23096,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -23144,7 +23147,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -23178,7 +23181,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -23210,7 +23213,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -23242,7 +23245,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -23274,7 +23277,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -23306,7 +23309,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -23342,7 +23345,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -23374,7 +23377,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -23406,7 +23409,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -23438,7 +23441,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -23472,7 +23475,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -23504,7 +23507,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -23536,7 +23539,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -23570,7 +23573,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -23602,7 +23605,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -23634,7 +23637,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -23670,7 +23673,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -23704,7 +23707,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -23736,7 +23739,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -23770,7 +23773,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -23804,7 +23807,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -23836,7 +23839,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -23868,7 +23871,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -23900,7 +23903,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -23936,7 +23939,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -23968,7 +23971,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -24000,7 +24003,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -24034,7 +24037,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -24066,7 +24069,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -24098,7 +24101,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -24130,7 +24133,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -24181,7 +24184,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -24215,7 +24218,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -24247,7 +24250,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -24281,7 +24284,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -24313,7 +24316,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -24345,7 +24348,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -24377,7 +24380,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -24409,7 +24412,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -24441,7 +24444,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -24473,7 +24476,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -24505,7 +24508,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -24539,7 +24542,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -24571,7 +24574,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -24603,7 +24606,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -24635,7 +24638,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -24667,7 +24670,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -24699,7 +24702,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -24733,7 +24736,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -24765,7 +24768,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -24797,7 +24800,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -24829,7 +24832,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -24863,7 +24866,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -24895,7 +24898,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -24927,7 +24930,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -24961,7 +24964,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -24993,7 +24996,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -25025,7 +25028,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -25057,7 +25060,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -25089,7 +25092,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -25121,7 +25124,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -25173,7 +25176,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -25207,7 +25210,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -25237,7 +25240,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -25269,7 +25272,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -25301,7 +25304,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -25335,7 +25338,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -25367,7 +25370,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -25399,7 +25402,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -25433,7 +25436,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -25465,7 +25468,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -25497,7 +25500,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -25529,7 +25532,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -25561,7 +25564,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -25593,7 +25596,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -25625,7 +25628,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -25657,7 +25660,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -25689,7 +25692,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -25721,7 +25724,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -25753,7 +25756,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -25785,7 +25788,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -25817,7 +25820,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -25849,7 +25852,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -25881,7 +25884,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -25913,7 +25916,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -25945,7 +25948,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -25977,7 +25980,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -26009,7 +26012,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -26041,7 +26044,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -26073,7 +26076,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -26105,7 +26108,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -26137,7 +26140,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -26189,7 +26192,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -26223,7 +26226,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -26255,7 +26258,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -26287,7 +26290,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -26319,7 +26322,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -26351,7 +26354,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -26383,7 +26386,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -26415,7 +26418,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -26447,7 +26450,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -26479,7 +26482,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -26511,7 +26514,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -26543,7 +26546,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -26575,7 +26578,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -26607,7 +26610,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -26639,7 +26642,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -26671,7 +26674,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -26703,7 +26706,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -26735,7 +26738,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -26767,7 +26770,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -26799,7 +26802,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -26831,7 +26834,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -26863,7 +26866,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -27221,52 +27224,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -27300,7 +27303,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -27332,7 +27335,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -27364,7 +27367,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -27396,7 +27399,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -27430,7 +27433,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -27462,7 +27465,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -27494,7 +27497,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -27528,7 +27531,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -27560,7 +27563,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -27592,7 +27595,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -27624,7 +27627,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -27658,7 +27661,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -27690,7 +27693,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -27722,7 +27725,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -27756,7 +27759,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -27807,7 +27810,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -27841,7 +27844,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -27873,7 +27876,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -27905,7 +27908,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -27937,7 +27940,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -27969,7 +27972,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -28005,7 +28008,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -28037,7 +28040,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -28069,7 +28072,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -28101,7 +28104,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -28135,7 +28138,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -28167,7 +28170,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -28199,7 +28202,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -28233,7 +28236,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -28265,7 +28268,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -28297,7 +28300,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -28329,7 +28332,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -28363,7 +28366,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -28397,7 +28400,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -28433,7 +28436,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -28467,7 +28470,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -28499,7 +28502,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -28531,7 +28534,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -28563,7 +28566,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -28599,7 +28602,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -28631,7 +28634,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -28663,7 +28666,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -28697,7 +28700,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -28729,7 +28732,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -28761,7 +28764,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -28793,7 +28796,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -28844,7 +28847,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -28878,7 +28881,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -28910,7 +28913,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -28944,7 +28947,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -28978,7 +28981,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -29012,7 +29015,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -29044,7 +29047,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -29076,7 +29079,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -29108,7 +29111,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -29140,7 +29143,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -29172,7 +29175,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -29206,7 +29209,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -29238,7 +29241,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -29270,7 +29273,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -29302,7 +29305,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -29334,7 +29337,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -29370,7 +29373,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -29404,7 +29407,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -29436,7 +29439,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -29470,7 +29473,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -29502,7 +29505,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -29536,7 +29539,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -29568,7 +29571,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -29600,7 +29603,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -29634,7 +29637,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -29666,7 +29669,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -29698,7 +29701,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -29730,7 +29733,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -29762,7 +29765,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -29796,7 +29799,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -29848,7 +29851,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -29884,7 +29887,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -29920,7 +29923,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -29952,7 +29955,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -29984,7 +29987,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -30018,7 +30021,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -30050,7 +30053,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -30082,7 +30085,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -30122,7 +30125,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -30154,7 +30157,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -30186,7 +30189,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -30220,7 +30223,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -30252,7 +30255,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -30284,7 +30287,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -30316,7 +30319,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -30350,7 +30353,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -30381,7 +30384,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -30413,7 +30416,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -30445,7 +30448,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -30483,7 +30486,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -30515,7 +30518,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -30547,14 +30550,16 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
       <c r="F106" s="76">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="H106" s="90"/>
       <c r="I106" s="77">
         <v>0</v>
@@ -30579,7 +30584,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -30611,7 +30616,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -30643,7 +30648,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -30675,7 +30680,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -30707,7 +30712,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -30739,7 +30744,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -30771,7 +30776,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -30803,7 +30808,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -30835,7 +30840,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -30887,7 +30892,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -30921,7 +30926,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -30953,7 +30958,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -30985,7 +30990,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -31017,7 +31022,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -31049,7 +31054,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -31081,7 +31086,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -31113,7 +31118,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -31145,7 +31150,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -31177,7 +31182,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -31209,7 +31214,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -31241,7 +31246,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -31273,7 +31278,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -31305,7 +31310,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -31337,7 +31342,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -31369,7 +31374,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -31401,7 +31406,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -31433,7 +31438,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -31465,7 +31470,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -31497,7 +31502,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -31529,7 +31534,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -31561,7 +31566,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -31594,17 +31599,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="13" priority="23" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695FF3EA-E9F0-4F9E-9DAF-3A34640A726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70ECCAC-E387-4FB6-9E70-DC4FC229EC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="110">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -360,6 +360,18 @@
   </si>
   <si>
     <t>Cloudinary signature as token</t>
+  </si>
+  <si>
+    <t>Emulator branch fixes</t>
+  </si>
+  <si>
+    <t>Some fixes</t>
+  </si>
+  <si>
+    <t>Image Service and some fixes</t>
+  </si>
+  <si>
+    <t>ImageService implemented</t>
   </si>
 </sst>
 </file>
@@ -1681,18 +1693,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,6 +1725,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2561,16 +2573,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>113.5</c:v>
+                  <c:v>115.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>68.5</c:v>
+                  <c:v>74.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>117</c:v>
@@ -4615,16 +4627,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>29</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>24</c:v>
@@ -9203,12 +9215,12 @@
       </c>
       <c r="H6" s="63">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="31">
         <f>SUM(D6:H6)</f>
-        <v>113.5</v>
+        <v>115.5</v>
       </c>
       <c r="K6" s="20"/>
     </row>
@@ -9291,12 +9303,12 @@
       </c>
       <c r="H10" s="69">
         <f>SUM(WENJIE!L5:L138)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I10" s="41"/>
       <c r="J10" s="42">
         <f>SUM(D10:H10)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K10" s="20"/>
     </row>
@@ -9335,12 +9347,12 @@
       </c>
       <c r="H12" s="72">
         <f>SUM(WENJIE!O5:O138)</f>
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="I12" s="45"/>
       <c r="J12" s="46">
         <f>SUM(D12:H12)</f>
-        <v>68.5</v>
+        <v>74.5</v>
       </c>
       <c r="K12" s="20"/>
     </row>
@@ -9422,12 +9434,12 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>373.5</v>
+        <v>383.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9477,52 +9489,52 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9554,7 +9566,7 @@
       <c r="S5" s="60"/>
     </row>
     <row r="6" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9584,7 +9596,7 @@
       <c r="S6" s="60"/>
     </row>
     <row r="7" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9614,7 +9626,7 @@
       <c r="S7" s="60"/>
     </row>
     <row r="8" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9644,7 +9656,7 @@
       <c r="S8" s="60"/>
     </row>
     <row r="9" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -9676,7 +9688,7 @@
       <c r="S9" s="60"/>
     </row>
     <row r="10" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -9706,7 +9718,7 @@
       <c r="S10" s="60"/>
     </row>
     <row r="11" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -9736,7 +9748,7 @@
       <c r="S11" s="60"/>
     </row>
     <row r="12" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -9768,7 +9780,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -9798,7 +9810,7 @@
       <c r="S13" s="60"/>
     </row>
     <row r="14" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -9828,7 +9840,7 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -9858,7 +9870,7 @@
       <c r="S15" s="60"/>
     </row>
     <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -9890,7 +9902,7 @@
       <c r="S16" s="60"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -9920,7 +9932,7 @@
       <c r="S17" s="60"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -9950,7 +9962,7 @@
       <c r="S18" s="60"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -9982,7 +9994,7 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -10029,7 +10041,7 @@
       <c r="S21" s="101"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10061,7 +10073,7 @@
       <c r="S22" s="60"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10091,7 +10103,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10121,7 +10133,7 @@
       <c r="S24" s="60"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10151,7 +10163,7 @@
       <c r="S25" s="60"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10181,7 +10193,7 @@
       <c r="S26" s="60"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10215,7 +10227,7 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10245,7 +10257,7 @@
       <c r="S28" s="60"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10275,7 +10287,7 @@
       <c r="S29" s="60"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10305,7 +10317,7 @@
       <c r="S30" s="60"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10337,7 +10349,7 @@
       <c r="S31" s="60"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10367,7 +10379,7 @@
       <c r="S32" s="60"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10397,7 +10409,7 @@
       <c r="S33" s="60"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10429,7 +10441,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10459,7 +10471,7 @@
       <c r="S35" s="60"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10489,7 +10501,7 @@
       <c r="S36" s="60"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10519,7 +10531,7 @@
       <c r="S37" s="60"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10551,7 +10563,7 @@
       <c r="S38" s="60"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10583,7 +10595,7 @@
       <c r="S39" s="60"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10613,7 +10625,7 @@
       <c r="S40" s="60"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10645,7 +10657,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -10675,7 +10687,7 @@
       <c r="S42" s="60"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -10705,7 +10717,7 @@
       <c r="S43" s="60"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -10735,7 +10747,7 @@
       <c r="S44" s="60"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -10769,7 +10781,7 @@
       <c r="S45" s="60"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -10799,7 +10811,7 @@
       <c r="S46" s="60"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -10829,7 +10841,7 @@
       <c r="S47" s="60"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -10861,7 +10873,7 @@
       </c>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -10891,7 +10903,7 @@
       <c r="S49" s="60"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -10921,7 +10933,7 @@
       <c r="S50" s="60"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -10951,7 +10963,7 @@
       <c r="S51" s="60"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -10998,7 +11010,7 @@
       <c r="S53" s="101"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11030,7 +11042,7 @@
       <c r="S54" s="60"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11060,7 +11072,7 @@
       <c r="S55" s="60"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11092,7 +11104,7 @@
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11122,7 +11134,7 @@
       <c r="S57" s="60"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11152,7 +11164,7 @@
       <c r="S58" s="60"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11182,7 +11194,7 @@
       <c r="S59" s="60"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11212,7 +11224,7 @@
       <c r="S60" s="60"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11242,7 +11254,7 @@
       <c r="S61" s="60"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11272,7 +11284,7 @@
       <c r="S62" s="60"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11302,7 +11314,7 @@
       <c r="S63" s="60"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11334,7 +11346,7 @@
       </c>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11364,7 +11376,7 @@
       <c r="S65" s="60"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11394,7 +11406,7 @@
       <c r="S66" s="60"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11424,7 +11436,7 @@
       <c r="S67" s="60"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11454,7 +11466,7 @@
       <c r="S68" s="60"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11488,7 +11500,7 @@
       <c r="S69" s="60"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11520,7 +11532,7 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11550,7 +11562,7 @@
       <c r="S71" s="60"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11580,7 +11592,7 @@
       <c r="S72" s="60"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11610,7 +11622,7 @@
       <c r="S73" s="60"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11642,7 +11654,7 @@
       <c r="S74" s="60"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -11672,7 +11684,7 @@
       <c r="S75" s="60"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -11702,7 +11714,7 @@
       <c r="S76" s="60"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -11734,7 +11746,7 @@
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -11764,7 +11776,7 @@
       <c r="S78" s="60"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -11794,7 +11806,7 @@
       <c r="S79" s="60"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -11824,7 +11836,7 @@
       <c r="S80" s="60"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -11854,7 +11866,7 @@
       <c r="S81" s="60"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -11884,7 +11896,7 @@
       <c r="S82" s="60"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -11932,7 +11944,7 @@
       <c r="S84" s="101"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -11996,7 +12008,7 @@
       <c r="S86" s="60"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12026,7 +12038,7 @@
       <c r="S87" s="60"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12056,7 +12068,7 @@
       <c r="S88" s="60"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12088,7 +12100,7 @@
       </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12116,7 +12128,7 @@
       <c r="S90" s="60"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12146,7 +12158,7 @@
       <c r="S91" s="60"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12178,7 +12190,7 @@
       </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12208,7 +12220,7 @@
       <c r="S93" s="60"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12238,7 +12250,7 @@
       <c r="S94" s="60"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12268,7 +12280,7 @@
       <c r="S95" s="60"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12298,7 +12310,7 @@
       <c r="S96" s="60"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12328,7 +12340,7 @@
       <c r="S97" s="60"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12358,7 +12370,7 @@
       <c r="S98" s="60"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12388,7 +12400,7 @@
       <c r="S99" s="60"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12418,7 +12430,7 @@
       <c r="S100" s="60"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12448,7 +12460,7 @@
       <c r="S101" s="60"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12478,7 +12490,7 @@
       <c r="S102" s="60"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12508,7 +12520,7 @@
       <c r="S103" s="60"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12538,7 +12550,7 @@
       <c r="S104" s="60"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12568,7 +12580,7 @@
       <c r="S105" s="60"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12598,7 +12610,7 @@
       <c r="S106" s="60"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12628,7 +12640,7 @@
       <c r="S107" s="60"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -12658,7 +12670,7 @@
       <c r="S108" s="60"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -12688,7 +12700,7 @@
       <c r="S109" s="60"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -12718,7 +12730,7 @@
       <c r="S110" s="60"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -12748,7 +12760,7 @@
       <c r="S111" s="60"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -12778,7 +12790,7 @@
       <c r="S112" s="60"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -12808,7 +12820,7 @@
       <c r="S113" s="60"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -12838,7 +12850,7 @@
       <c r="S114" s="60"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -12886,7 +12898,7 @@
       <c r="S116" s="101"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -12918,7 +12930,7 @@
       <c r="S117" s="60"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -12948,7 +12960,7 @@
       <c r="S118" s="60"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -12978,7 +12990,7 @@
       <c r="S119" s="60"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -13008,7 +13020,7 @@
       <c r="S120" s="60"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13038,7 +13050,7 @@
       <c r="S121" s="60"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13068,7 +13080,7 @@
       <c r="S122" s="60"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13098,7 +13110,7 @@
       <c r="S123" s="60"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13128,7 +13140,7 @@
       <c r="S124" s="60"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13158,7 +13170,7 @@
       <c r="S125" s="60"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13188,7 +13200,7 @@
       <c r="S126" s="60"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13218,7 +13230,7 @@
       <c r="S127" s="60"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13248,7 +13260,7 @@
       <c r="S128" s="60"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13278,7 +13290,7 @@
       <c r="S129" s="60"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13308,7 +13320,7 @@
       <c r="S130" s="60"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13338,7 +13350,7 @@
       <c r="S131" s="60"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13368,7 +13380,7 @@
       <c r="S132" s="60"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13398,7 +13410,7 @@
       <c r="S133" s="60"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13428,7 +13440,7 @@
       <c r="S134" s="60"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13458,7 +13470,7 @@
       <c r="S135" s="60"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13488,7 +13500,7 @@
       <c r="S136" s="60"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13518,7 +13530,7 @@
       <c r="S137" s="60"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13549,17 +13561,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
@@ -13645,52 +13657,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -13724,7 +13736,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -13756,7 +13768,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -13788,7 +13800,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -13820,7 +13832,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -13854,7 +13866,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -13886,7 +13898,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -13918,7 +13930,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -13952,7 +13964,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -13984,7 +13996,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14016,7 +14028,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14048,7 +14060,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14082,7 +14094,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14114,7 +14126,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14146,7 +14158,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14180,7 +14192,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14231,7 +14243,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14265,7 +14277,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14297,7 +14309,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14329,7 +14341,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14361,7 +14373,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14393,7 +14405,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14429,7 +14441,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14461,7 +14473,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14493,7 +14505,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14525,7 +14537,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14559,7 +14571,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14591,7 +14603,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14623,7 +14635,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -14657,7 +14669,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -14689,7 +14701,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -14721,7 +14733,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -14753,7 +14765,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -14787,7 +14799,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -14821,7 +14833,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -14853,7 +14865,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -14887,7 +14899,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -14919,7 +14931,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -14951,7 +14963,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -14983,7 +14995,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15019,7 +15031,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15051,7 +15063,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15083,7 +15095,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15117,7 +15129,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15149,7 +15161,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15181,7 +15193,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15213,7 +15225,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15264,7 +15276,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15298,7 +15310,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15330,7 +15342,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15364,7 +15376,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15396,7 +15408,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15428,7 +15440,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15460,7 +15472,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15492,7 +15504,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15524,7 +15536,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15556,7 +15568,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15588,7 +15600,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15622,7 +15634,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -15654,7 +15666,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -15686,7 +15698,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -15718,7 +15730,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -15750,7 +15762,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -15786,7 +15798,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -15820,7 +15832,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -15852,7 +15864,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -15884,7 +15896,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -15916,7 +15928,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -15950,7 +15962,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -15982,7 +15994,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -16014,7 +16026,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16048,7 +16060,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16080,7 +16092,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16112,7 +16124,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16144,7 +16156,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16176,7 +16188,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16208,7 +16220,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16260,7 +16272,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16296,7 +16308,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16328,7 +16340,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16360,7 +16372,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16392,7 +16404,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16426,7 +16438,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16458,7 +16470,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16490,7 +16502,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16524,7 +16536,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16556,7 +16568,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16588,7 +16600,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16620,7 +16632,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16652,7 +16664,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -16684,7 +16696,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -16716,7 +16728,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -16748,7 +16760,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -16780,7 +16792,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -16812,7 +16824,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -16844,7 +16856,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -16876,7 +16888,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -16908,7 +16920,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -16940,7 +16952,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -16972,7 +16984,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -17004,7 +17016,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17036,7 +17048,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17068,7 +17080,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17100,7 +17112,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17132,7 +17144,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17164,7 +17176,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17196,7 +17208,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17228,7 +17240,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17280,7 +17292,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17314,7 +17326,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17346,7 +17358,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17378,7 +17390,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17410,7 +17422,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17442,7 +17454,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17474,7 +17486,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17506,7 +17518,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17538,7 +17550,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17570,7 +17582,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17602,7 +17614,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17634,7 +17646,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -17666,7 +17678,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -17698,7 +17710,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -17730,7 +17742,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -17762,7 +17774,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -17794,7 +17806,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -17826,7 +17838,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -17858,7 +17870,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -17890,7 +17902,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -17922,7 +17934,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -17954,7 +17966,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -17987,17 +17999,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
@@ -18103,52 +18115,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18182,7 +18194,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18214,7 +18226,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18246,7 +18258,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18278,7 +18290,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18312,7 +18324,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18344,7 +18356,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18376,7 +18388,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18410,7 +18422,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18442,7 +18454,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18474,7 +18486,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18506,7 +18518,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18540,7 +18552,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18572,7 +18584,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -18604,7 +18616,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -18638,7 +18650,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -18689,7 +18701,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -18723,7 +18735,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -18755,7 +18767,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -18787,7 +18799,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -18819,7 +18831,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -18851,7 +18863,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -18887,7 +18899,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -18919,7 +18931,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -18951,7 +18963,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -18983,7 +18995,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19017,7 +19029,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19049,7 +19061,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19081,7 +19093,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19115,7 +19127,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19147,7 +19159,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19179,7 +19191,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19211,7 +19223,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19247,7 +19259,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19279,7 +19291,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19311,7 +19323,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19345,7 +19357,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19377,7 +19389,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19409,7 +19421,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19441,7 +19453,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19477,7 +19489,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19509,7 +19521,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19541,7 +19553,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19575,7 +19587,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -19607,7 +19619,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -19639,7 +19651,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -19671,7 +19683,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -19722,7 +19734,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -19756,7 +19768,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -19788,7 +19800,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -19822,7 +19834,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -19854,7 +19866,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -19886,7 +19898,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -19918,7 +19930,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -19950,7 +19962,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -19982,7 +19994,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -20014,7 +20026,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20046,7 +20058,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20080,7 +20092,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20112,7 +20124,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20144,7 +20156,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20176,7 +20188,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20212,7 +20224,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20244,7 +20256,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20278,7 +20290,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20310,7 +20322,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20342,7 +20354,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20374,7 +20386,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20408,7 +20420,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20440,7 +20452,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20472,7 +20484,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20506,7 +20518,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20538,7 +20550,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20570,7 +20582,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -20602,7 +20614,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -20634,7 +20646,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -20666,7 +20678,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -20718,7 +20730,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -20754,7 +20766,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -20786,7 +20798,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -20818,7 +20830,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -20850,7 +20862,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -20884,7 +20896,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -20916,7 +20928,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -20948,7 +20960,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -20982,7 +20994,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -21014,7 +21026,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21046,7 +21058,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21078,7 +21090,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21110,7 +21122,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21142,7 +21154,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21174,7 +21186,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21206,7 +21218,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21238,7 +21250,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21270,7 +21282,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21302,7 +21314,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21334,7 +21346,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21366,7 +21378,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21398,7 +21410,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21430,7 +21442,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21462,7 +21474,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21494,7 +21506,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21526,7 +21538,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21558,7 +21570,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -21590,7 +21602,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -21622,7 +21634,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -21654,7 +21666,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -21686,7 +21698,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -21738,7 +21750,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -21772,7 +21784,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -21804,7 +21816,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -21836,7 +21848,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -21868,7 +21880,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -21900,7 +21912,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -21932,7 +21944,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -21964,7 +21976,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -21996,7 +22008,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22028,7 +22040,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22060,7 +22072,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22092,7 +22104,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22124,7 +22136,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22156,7 +22168,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22188,7 +22200,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22220,7 +22232,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22252,7 +22264,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22284,7 +22296,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22316,7 +22328,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22348,7 +22360,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -22380,7 +22392,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -22412,7 +22424,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -22445,17 +22457,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="41" priority="25" operator="equal">
@@ -22561,52 +22573,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -22640,7 +22652,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -22672,7 +22684,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -22704,7 +22716,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -22736,7 +22748,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -22770,7 +22782,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -22802,7 +22814,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -22834,7 +22846,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -22868,7 +22880,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -22900,7 +22912,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -22932,7 +22944,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -22964,7 +22976,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -22998,7 +23010,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -23030,7 +23042,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -23062,7 +23074,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -23096,7 +23108,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -23147,7 +23159,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -23181,7 +23193,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -23213,7 +23225,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -23245,7 +23257,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -23277,7 +23289,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -23309,7 +23321,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -23345,7 +23357,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -23377,7 +23389,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -23409,7 +23421,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -23441,7 +23453,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -23475,7 +23487,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -23507,7 +23519,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -23539,7 +23551,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -23573,7 +23585,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -23605,7 +23617,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -23637,7 +23649,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -23673,7 +23685,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -23707,7 +23719,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -23739,7 +23751,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -23773,7 +23785,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -23807,7 +23819,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -23839,7 +23851,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -23871,7 +23883,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -23903,7 +23915,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -23939,7 +23951,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -23971,7 +23983,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -24003,7 +24015,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -24037,7 +24049,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -24069,7 +24081,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -24101,7 +24113,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -24133,7 +24145,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -24184,7 +24196,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -24218,7 +24230,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -24250,7 +24262,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -24284,7 +24296,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -24316,7 +24328,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -24348,7 +24360,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -24380,7 +24392,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -24412,7 +24424,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -24444,7 +24456,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -24476,7 +24488,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -24508,7 +24520,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -24542,7 +24554,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -24574,7 +24586,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -24606,7 +24618,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -24638,7 +24650,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -24670,7 +24682,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -24702,7 +24714,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -24736,7 +24748,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -24768,7 +24780,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -24800,7 +24812,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -24832,7 +24844,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -24866,7 +24878,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -24898,7 +24910,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -24930,7 +24942,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -24964,7 +24976,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -24996,7 +25008,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -25028,7 +25040,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -25060,7 +25072,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -25092,7 +25104,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -25124,7 +25136,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -25176,7 +25188,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -25210,7 +25222,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -25240,7 +25252,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -25272,7 +25284,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -25304,7 +25316,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -25338,7 +25350,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -25370,7 +25382,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -25402,7 +25414,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -25436,7 +25448,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -25468,7 +25480,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -25500,7 +25512,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -25532,7 +25544,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -25564,7 +25576,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -25596,7 +25608,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -25628,7 +25640,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -25660,7 +25672,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -25692,7 +25704,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -25724,7 +25736,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -25756,7 +25768,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -25788,7 +25800,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -25820,7 +25832,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -25852,7 +25864,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -25884,7 +25896,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -25916,7 +25928,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -25948,7 +25960,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -25980,7 +25992,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -26012,7 +26024,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -26044,7 +26056,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -26076,7 +26088,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -26108,7 +26120,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -26140,7 +26152,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -26192,7 +26204,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -26226,7 +26238,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -26258,7 +26270,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -26290,7 +26302,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -26322,7 +26334,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -26354,7 +26366,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -26386,7 +26398,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -26418,7 +26430,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -26450,7 +26462,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -26482,7 +26494,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -26514,7 +26526,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -26546,7 +26558,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -26578,7 +26590,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -26610,7 +26622,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -26642,7 +26654,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -26674,7 +26686,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -26706,7 +26718,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -26738,7 +26750,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -26770,7 +26782,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -26802,7 +26814,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -26834,7 +26846,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -26866,7 +26878,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -27224,52 +27236,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="F2" s="116" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="F2" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="113"/>
+      <c r="L2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="118"/>
-      <c r="O2" s="119" t="s">
+      <c r="M2" s="114"/>
+      <c r="O2" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="R2" s="109" t="s">
+      <c r="P2" s="115"/>
+      <c r="R2" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="116" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -27303,7 +27315,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106"/>
+      <c r="B6" s="117"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -27335,7 +27347,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
+      <c r="B7" s="117"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -27367,7 +27379,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
+      <c r="B8" s="117"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -27399,7 +27411,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
+      <c r="B9" s="117"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -27433,7 +27445,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
+      <c r="B10" s="117"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -27465,7 +27477,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="106"/>
+      <c r="B11" s="117"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -27497,7 +27509,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="106"/>
+      <c r="B12" s="117"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -27531,7 +27543,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
+      <c r="B13" s="117"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -27563,7 +27575,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
+      <c r="B14" s="117"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -27595,7 +27607,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
+      <c r="B15" s="117"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -27627,7 +27639,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
+      <c r="B16" s="117"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -27661,7 +27673,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="106"/>
+      <c r="B17" s="117"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -27693,7 +27705,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
+      <c r="B18" s="117"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -27725,7 +27737,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
+      <c r="B19" s="117"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -27759,7 +27771,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="118"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -27810,7 +27822,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="119" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -27844,7 +27856,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="108"/>
+      <c r="B23" s="119"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -27876,7 +27888,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="108"/>
+      <c r="B24" s="119"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -27908,7 +27920,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108"/>
+      <c r="B25" s="119"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -27940,7 +27952,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="108"/>
+      <c r="B26" s="119"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -27972,7 +27984,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
+      <c r="B27" s="119"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -28008,7 +28020,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="108"/>
+      <c r="B28" s="119"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -28040,7 +28052,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="108"/>
+      <c r="B29" s="119"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -28072,7 +28084,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="108"/>
+      <c r="B30" s="119"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -28104,7 +28116,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="108"/>
+      <c r="B31" s="119"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -28138,7 +28150,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="108"/>
+      <c r="B32" s="119"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -28170,7 +28182,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="108"/>
+      <c r="B33" s="119"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -28202,7 +28214,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="108"/>
+      <c r="B34" s="119"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -28236,7 +28248,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108"/>
+      <c r="B35" s="119"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -28268,7 +28280,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
+      <c r="B36" s="119"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -28300,7 +28312,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
+      <c r="B37" s="119"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -28332,7 +28344,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
+      <c r="B38" s="119"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -28366,7 +28378,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
+      <c r="B39" s="119"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -28400,7 +28412,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="108"/>
+      <c r="B40" s="119"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -28436,7 +28448,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="108"/>
+      <c r="B41" s="119"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -28470,7 +28482,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="108"/>
+      <c r="B42" s="119"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -28502,7 +28514,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="108"/>
+      <c r="B43" s="119"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -28534,7 +28546,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
+      <c r="B44" s="119"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -28566,7 +28578,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="108"/>
+      <c r="B45" s="119"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -28602,7 +28614,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="108"/>
+      <c r="B46" s="119"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -28634,7 +28646,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="108"/>
+      <c r="B47" s="119"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -28666,7 +28678,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="108"/>
+      <c r="B48" s="119"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -28700,7 +28712,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="108"/>
+      <c r="B49" s="119"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -28732,7 +28744,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="108"/>
+      <c r="B50" s="119"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -28764,7 +28776,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="108"/>
+      <c r="B51" s="119"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -28796,7 +28808,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="108"/>
+      <c r="B52" s="119"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -28847,7 +28859,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="108" t="s">
+      <c r="B54" s="119" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -28881,7 +28893,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="108"/>
+      <c r="B55" s="119"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -28913,7 +28925,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="108"/>
+      <c r="B56" s="119"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -28947,7 +28959,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
+      <c r="B57" s="119"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -28981,7 +28993,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
+      <c r="B58" s="119"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -29015,7 +29027,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
+      <c r="B59" s="119"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -29047,7 +29059,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
+      <c r="B60" s="119"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -29079,7 +29091,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="108"/>
+      <c r="B61" s="119"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -29111,7 +29123,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="108"/>
+      <c r="B62" s="119"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -29143,7 +29155,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="108"/>
+      <c r="B63" s="119"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -29175,7 +29187,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
+      <c r="B64" s="119"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -29209,7 +29221,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="108"/>
+      <c r="B65" s="119"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -29241,7 +29253,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
+      <c r="B66" s="119"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -29273,7 +29285,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="108"/>
+      <c r="B67" s="119"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -29305,7 +29317,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="108"/>
+      <c r="B68" s="119"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -29337,7 +29349,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="108"/>
+      <c r="B69" s="119"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -29373,7 +29385,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="108"/>
+      <c r="B70" s="119"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -29407,7 +29419,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="108"/>
+      <c r="B71" s="119"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -29439,7 +29451,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="108"/>
+      <c r="B72" s="119"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -29473,7 +29485,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="108"/>
+      <c r="B73" s="119"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -29505,7 +29517,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="108"/>
+      <c r="B74" s="119"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -29539,7 +29551,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="108"/>
+      <c r="B75" s="119"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -29571,7 +29583,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="108"/>
+      <c r="B76" s="119"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -29603,7 +29615,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="108"/>
+      <c r="B77" s="119"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -29637,7 +29649,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="108"/>
+      <c r="B78" s="119"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -29669,7 +29681,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="108"/>
+      <c r="B79" s="119"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -29701,7 +29713,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="108"/>
+      <c r="B80" s="119"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -29733,7 +29745,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="108"/>
+      <c r="B81" s="119"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -29765,7 +29777,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="108"/>
+      <c r="B82" s="119"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -29799,7 +29811,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="108"/>
+      <c r="B83" s="119"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -29851,7 +29863,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="108" t="s">
+      <c r="B85" s="119" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -29887,7 +29899,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="108"/>
+      <c r="B86" s="119"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -29923,7 +29935,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="108"/>
+      <c r="B87" s="119"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -29955,7 +29967,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="108"/>
+      <c r="B88" s="119"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -29987,7 +29999,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="108"/>
+      <c r="B89" s="119"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -30021,7 +30033,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="108"/>
+      <c r="B90" s="119"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -30053,7 +30065,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="108"/>
+      <c r="B91" s="119"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -30085,7 +30097,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="108"/>
+      <c r="B92" s="119"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -30125,7 +30137,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="108"/>
+      <c r="B93" s="119"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -30157,7 +30169,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="108"/>
+      <c r="B94" s="119"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -30189,7 +30201,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="108"/>
+      <c r="B95" s="119"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -30223,7 +30235,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="108"/>
+      <c r="B96" s="119"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -30255,7 +30267,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="108"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -30287,7 +30299,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="108"/>
+      <c r="B98" s="119"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -30319,7 +30331,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="108"/>
+      <c r="B99" s="119"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -30353,7 +30365,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="108"/>
+      <c r="B100" s="119"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -30384,7 +30396,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
+      <c r="B101" s="119"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -30416,7 +30428,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="108"/>
+      <c r="B102" s="119"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -30448,7 +30460,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="108"/>
+      <c r="B103" s="119"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -30486,7 +30498,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="108"/>
+      <c r="B104" s="119"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -30518,7 +30530,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="108"/>
+      <c r="B105" s="119"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -30550,7 +30562,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="108"/>
+      <c r="B106" s="119"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -30584,7 +30596,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="108"/>
+      <c r="B107" s="119"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -30616,7 +30628,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="108"/>
+      <c r="B108" s="119"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -30648,14 +30660,16 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="108"/>
+      <c r="B109" s="119"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
       <c r="F109" s="76">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="H109" s="90"/>
       <c r="I109" s="77">
         <v>0</v>
@@ -30663,14 +30677,18 @@
       <c r="J109" s="57"/>
       <c r="K109" s="90"/>
       <c r="L109" s="78">
-        <v>0</v>
-      </c>
-      <c r="M109" s="58"/>
+        <v>2</v>
+      </c>
+      <c r="M109" s="58" t="s">
+        <v>109</v>
+      </c>
       <c r="N109" s="90"/>
       <c r="O109" s="79">
-        <v>0</v>
-      </c>
-      <c r="P109" s="59"/>
+        <v>2</v>
+      </c>
+      <c r="P109" s="59" t="s">
+        <v>107</v>
+      </c>
       <c r="Q109" s="90"/>
       <c r="R109" s="80">
         <v>0</v>
@@ -30680,7 +30698,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="108"/>
+      <c r="B110" s="119"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -30712,7 +30730,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="108"/>
+      <c r="B111" s="119"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -30744,7 +30762,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="108"/>
+      <c r="B112" s="119"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -30764,9 +30782,11 @@
       <c r="M112" s="58"/>
       <c r="N112" s="90"/>
       <c r="O112" s="79">
-        <v>0</v>
-      </c>
-      <c r="P112" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="P112" s="59" t="s">
+        <v>108</v>
+      </c>
       <c r="Q112" s="90"/>
       <c r="R112" s="80">
         <v>0</v>
@@ -30776,7 +30796,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="108"/>
+      <c r="B113" s="119"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -30808,7 +30828,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="108"/>
+      <c r="B114" s="119"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -30840,7 +30860,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="108"/>
+      <c r="B115" s="119"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -30892,7 +30912,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="105" t="s">
+      <c r="B117" s="116" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -30926,7 +30946,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
+      <c r="B118" s="117"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -30958,7 +30978,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="106"/>
+      <c r="B119" s="117"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -30990,7 +31010,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="106"/>
+      <c r="B120" s="117"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -31022,7 +31042,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="106"/>
+      <c r="B121" s="117"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -31054,7 +31074,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="106"/>
+      <c r="B122" s="117"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -31086,7 +31106,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="106"/>
+      <c r="B123" s="117"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -31118,7 +31138,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="106"/>
+      <c r="B124" s="117"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -31150,7 +31170,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="106"/>
+      <c r="B125" s="117"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -31182,7 +31202,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="106"/>
+      <c r="B126" s="117"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -31214,7 +31234,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="106"/>
+      <c r="B127" s="117"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -31246,7 +31266,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="106"/>
+      <c r="B128" s="117"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -31278,7 +31298,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="106"/>
+      <c r="B129" s="117"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -31310,7 +31330,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="106"/>
+      <c r="B130" s="117"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -31342,7 +31362,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="106"/>
+      <c r="B131" s="117"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -31374,7 +31394,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="106"/>
+      <c r="B132" s="117"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -31406,7 +31426,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="106"/>
+      <c r="B133" s="117"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -31438,7 +31458,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="106"/>
+      <c r="B134" s="117"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -31470,7 +31490,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="106"/>
+      <c r="B135" s="117"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -31502,7 +31522,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="106"/>
+      <c r="B136" s="117"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -31534,7 +31554,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="106"/>
+      <c r="B137" s="117"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -31566,7 +31586,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="107"/>
+      <c r="B138" s="118"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -31599,17 +31619,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="13" priority="23" operator="equal">

--- a/horas.xlsx
+++ b/horas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Desktop\DSA\EA_ViveBook_TeamManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70ECCAC-E387-4FB6-9E70-DC4FC229EC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35728FBD-8698-4811-B7D1-C3BFE238AA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="114">
   <si>
     <t>UPC - EETAC - EA-M QP2526 Grup 3: Còmput de les hores de treball del projecte ViveBook</t>
   </si>
@@ -372,6 +372,18 @@
   </si>
   <si>
     <t>ImageService implemented</t>
+  </si>
+  <si>
+    <t>Image upload</t>
+  </si>
+  <si>
+    <t>Minimo2</t>
+  </si>
+  <si>
+    <t>Matomo</t>
+  </si>
+  <si>
+    <t>Image Cover</t>
   </si>
 </sst>
 </file>
@@ -1693,6 +1705,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,18 +1749,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2573,19 +2585,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>115.5</c:v>
+                  <c:v>116.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.5</c:v>
+                  <c:v>40.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>74.5</c:v>
+                  <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>117</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4627,19 +4639,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>31</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.5</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9215,12 +9227,12 @@
       </c>
       <c r="H6" s="63">
         <f>SUM(WENJIE!F5:F138)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="31">
         <f>SUM(D6:H6)</f>
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="K6" s="20"/>
     </row>
@@ -9259,12 +9271,12 @@
       </c>
       <c r="H8" s="66">
         <f>SUM(WENJIE!I5:I138)</f>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="I8" s="37"/>
       <c r="J8" s="38">
         <f>SUM(D8:H8)</f>
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="K8" s="20"/>
     </row>
@@ -9347,12 +9359,12 @@
       </c>
       <c r="H12" s="72">
         <f>SUM(WENJIE!O5:O138)</f>
-        <v>18.5</v>
+        <v>21.5</v>
       </c>
       <c r="I12" s="45"/>
       <c r="J12" s="46">
         <f>SUM(D12:H12)</f>
-        <v>74.5</v>
+        <v>77.5</v>
       </c>
       <c r="K12" s="20"/>
     </row>
@@ -9391,12 +9403,12 @@
       </c>
       <c r="H14" s="75">
         <f>SUM(WENJIE!R5:R138)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I14" s="49"/>
       <c r="J14" s="50">
         <f>SUM(D14:H14)</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K14" s="20"/>
     </row>
@@ -9434,12 +9446,12 @@
       </c>
       <c r="H16" s="18">
         <f>SUM(H6:H14)</f>
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="18">
         <f>SUM(D16:H16)</f>
-        <v>383.5</v>
+        <v>389.5</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
@@ -9489,52 +9501,52 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -9566,7 +9578,7 @@
       <c r="S5" s="60"/>
     </row>
     <row r="6" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -9596,7 +9608,7 @@
       <c r="S6" s="60"/>
     </row>
     <row r="7" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -9626,7 +9638,7 @@
       <c r="S7" s="60"/>
     </row>
     <row r="8" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -9656,7 +9668,7 @@
       <c r="S8" s="60"/>
     </row>
     <row r="9" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -9688,7 +9700,7 @@
       <c r="S9" s="60"/>
     </row>
     <row r="10" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -9718,7 +9730,7 @@
       <c r="S10" s="60"/>
     </row>
     <row r="11" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -9748,7 +9760,7 @@
       <c r="S11" s="60"/>
     </row>
     <row r="12" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -9780,7 +9792,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -9810,7 +9822,7 @@
       <c r="S13" s="60"/>
     </row>
     <row r="14" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -9840,7 +9852,7 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -9870,7 +9882,7 @@
       <c r="S15" s="60"/>
     </row>
     <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -9902,7 +9914,7 @@
       <c r="S16" s="60"/>
     </row>
     <row r="17" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -9932,7 +9944,7 @@
       <c r="S17" s="60"/>
     </row>
     <row r="18" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -9962,7 +9974,7 @@
       <c r="S18" s="60"/>
     </row>
     <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -9994,7 +10006,7 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -10041,7 +10053,7 @@
       <c r="S21" s="101"/>
     </row>
     <row r="22" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -10073,7 +10085,7 @@
       <c r="S22" s="60"/>
     </row>
     <row r="23" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -10103,7 +10115,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -10133,7 +10145,7 @@
       <c r="S24" s="60"/>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -10163,7 +10175,7 @@
       <c r="S25" s="60"/>
     </row>
     <row r="26" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -10193,7 +10205,7 @@
       <c r="S26" s="60"/>
     </row>
     <row r="27" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -10257,7 +10269,7 @@
       <c r="S28" s="60"/>
     </row>
     <row r="29" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -10287,7 +10299,7 @@
       <c r="S29" s="60"/>
     </row>
     <row r="30" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -10317,7 +10329,7 @@
       <c r="S30" s="60"/>
     </row>
     <row r="31" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -10349,7 +10361,7 @@
       <c r="S31" s="60"/>
     </row>
     <row r="32" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -10379,7 +10391,7 @@
       <c r="S32" s="60"/>
     </row>
     <row r="33" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -10409,7 +10421,7 @@
       <c r="S33" s="60"/>
     </row>
     <row r="34" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -10441,7 +10453,7 @@
       </c>
     </row>
     <row r="35" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -10471,7 +10483,7 @@
       <c r="S35" s="60"/>
     </row>
     <row r="36" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -10501,7 +10513,7 @@
       <c r="S36" s="60"/>
     </row>
     <row r="37" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -10531,7 +10543,7 @@
       <c r="S37" s="60"/>
     </row>
     <row r="38" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -10563,7 +10575,7 @@
       <c r="S38" s="60"/>
     </row>
     <row r="39" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -10595,7 +10607,7 @@
       <c r="S39" s="60"/>
     </row>
     <row r="40" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -10625,7 +10637,7 @@
       <c r="S40" s="60"/>
     </row>
     <row r="41" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -10657,7 +10669,7 @@
       </c>
     </row>
     <row r="42" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -10687,7 +10699,7 @@
       <c r="S42" s="60"/>
     </row>
     <row r="43" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -10717,7 +10729,7 @@
       <c r="S43" s="60"/>
     </row>
     <row r="44" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -10747,7 +10759,7 @@
       <c r="S44" s="60"/>
     </row>
     <row r="45" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -10781,7 +10793,7 @@
       <c r="S45" s="60"/>
     </row>
     <row r="46" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -10811,7 +10823,7 @@
       <c r="S46" s="60"/>
     </row>
     <row r="47" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -10841,7 +10853,7 @@
       <c r="S47" s="60"/>
     </row>
     <row r="48" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -10873,7 +10885,7 @@
       </c>
     </row>
     <row r="49" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -10903,7 +10915,7 @@
       <c r="S49" s="60"/>
     </row>
     <row r="50" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -10933,7 +10945,7 @@
       <c r="S50" s="60"/>
     </row>
     <row r="51" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -10963,7 +10975,7 @@
       <c r="S51" s="60"/>
     </row>
     <row r="52" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -11010,7 +11022,7 @@
       <c r="S53" s="101"/>
     </row>
     <row r="54" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -11042,7 +11054,7 @@
       <c r="S54" s="60"/>
     </row>
     <row r="55" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -11072,7 +11084,7 @@
       <c r="S55" s="60"/>
     </row>
     <row r="56" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -11104,7 +11116,7 @@
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -11134,7 +11146,7 @@
       <c r="S57" s="60"/>
     </row>
     <row r="58" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -11164,7 +11176,7 @@
       <c r="S58" s="60"/>
     </row>
     <row r="59" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -11194,7 +11206,7 @@
       <c r="S59" s="60"/>
     </row>
     <row r="60" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -11224,7 +11236,7 @@
       <c r="S60" s="60"/>
     </row>
     <row r="61" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -11254,7 +11266,7 @@
       <c r="S61" s="60"/>
     </row>
     <row r="62" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -11284,7 +11296,7 @@
       <c r="S62" s="60"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -11314,7 +11326,7 @@
       <c r="S63" s="60"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -11346,7 +11358,7 @@
       </c>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -11376,7 +11388,7 @@
       <c r="S65" s="60"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -11406,7 +11418,7 @@
       <c r="S66" s="60"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -11436,7 +11448,7 @@
       <c r="S67" s="60"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -11466,7 +11478,7 @@
       <c r="S68" s="60"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -11500,7 +11512,7 @@
       <c r="S69" s="60"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -11532,7 +11544,7 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -11562,7 +11574,7 @@
       <c r="S71" s="60"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -11592,7 +11604,7 @@
       <c r="S72" s="60"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -11622,7 +11634,7 @@
       <c r="S73" s="60"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -11654,7 +11666,7 @@
       <c r="S74" s="60"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -11684,7 +11696,7 @@
       <c r="S75" s="60"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -11714,7 +11726,7 @@
       <c r="S76" s="60"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -11746,7 +11758,7 @@
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -11776,7 +11788,7 @@
       <c r="S78" s="60"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -11806,7 +11818,7 @@
       <c r="S79" s="60"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -11836,7 +11848,7 @@
       <c r="S80" s="60"/>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -11866,7 +11878,7 @@
       <c r="S81" s="60"/>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -11896,7 +11908,7 @@
       <c r="S82" s="60"/>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -11944,7 +11956,7 @@
       <c r="S84" s="101"/>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -11978,7 +11990,7 @@
       </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -12008,7 +12020,7 @@
       <c r="S86" s="60"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -12038,7 +12050,7 @@
       <c r="S87" s="60"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -12068,7 +12080,7 @@
       <c r="S88" s="60"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -12100,7 +12112,7 @@
       </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -12128,7 +12140,7 @@
       <c r="S90" s="60"/>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -12158,7 +12170,7 @@
       <c r="S91" s="60"/>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -12190,7 +12202,7 @@
       </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -12220,7 +12232,7 @@
       <c r="S93" s="60"/>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -12250,7 +12262,7 @@
       <c r="S94" s="60"/>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -12280,7 +12292,7 @@
       <c r="S95" s="60"/>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -12310,7 +12322,7 @@
       <c r="S96" s="60"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -12340,7 +12352,7 @@
       <c r="S97" s="60"/>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -12370,7 +12382,7 @@
       <c r="S98" s="60"/>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -12400,7 +12412,7 @@
       <c r="S99" s="60"/>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -12430,7 +12442,7 @@
       <c r="S100" s="60"/>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -12460,7 +12472,7 @@
       <c r="S101" s="60"/>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -12490,7 +12502,7 @@
       <c r="S102" s="60"/>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -12520,7 +12532,7 @@
       <c r="S103" s="60"/>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -12550,7 +12562,7 @@
       <c r="S104" s="60"/>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -12580,7 +12592,7 @@
       <c r="S105" s="60"/>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -12610,7 +12622,7 @@
       <c r="S106" s="60"/>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -12640,7 +12652,7 @@
       <c r="S107" s="60"/>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -12670,7 +12682,7 @@
       <c r="S108" s="60"/>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -12700,7 +12712,7 @@
       <c r="S109" s="60"/>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -12730,7 +12742,7 @@
       <c r="S110" s="60"/>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -12760,7 +12772,7 @@
       <c r="S111" s="60"/>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -12790,7 +12802,7 @@
       <c r="S112" s="60"/>
     </row>
     <row r="113" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -12820,7 +12832,7 @@
       <c r="S113" s="60"/>
     </row>
     <row r="114" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -12850,7 +12862,7 @@
       <c r="S114" s="60"/>
     </row>
     <row r="115" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -12898,7 +12910,7 @@
       <c r="S116" s="101"/>
     </row>
     <row r="117" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -12930,7 +12942,7 @@
       <c r="S117" s="60"/>
     </row>
     <row r="118" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -12960,7 +12972,7 @@
       <c r="S118" s="60"/>
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -12990,7 +13002,7 @@
       <c r="S119" s="60"/>
     </row>
     <row r="120" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -13020,7 +13032,7 @@
       <c r="S120" s="60"/>
     </row>
     <row r="121" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -13050,7 +13062,7 @@
       <c r="S121" s="60"/>
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -13080,7 +13092,7 @@
       <c r="S122" s="60"/>
     </row>
     <row r="123" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -13110,7 +13122,7 @@
       <c r="S123" s="60"/>
     </row>
     <row r="124" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -13140,7 +13152,7 @@
       <c r="S124" s="60"/>
     </row>
     <row r="125" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -13170,7 +13182,7 @@
       <c r="S125" s="60"/>
     </row>
     <row r="126" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -13200,7 +13212,7 @@
       <c r="S126" s="60"/>
     </row>
     <row r="127" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -13230,7 +13242,7 @@
       <c r="S127" s="60"/>
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -13260,7 +13272,7 @@
       <c r="S128" s="60"/>
     </row>
     <row r="129" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -13290,7 +13302,7 @@
       <c r="S129" s="60"/>
     </row>
     <row r="130" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -13320,7 +13332,7 @@
       <c r="S130" s="60"/>
     </row>
     <row r="131" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -13350,7 +13362,7 @@
       <c r="S131" s="60"/>
     </row>
     <row r="132" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -13380,7 +13392,7 @@
       <c r="S132" s="60"/>
     </row>
     <row r="133" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -13410,7 +13422,7 @@
       <c r="S133" s="60"/>
     </row>
     <row r="134" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -13440,7 +13452,7 @@
       <c r="S134" s="60"/>
     </row>
     <row r="135" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -13470,7 +13482,7 @@
       <c r="S135" s="60"/>
     </row>
     <row r="136" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -13500,7 +13512,7 @@
       <c r="S136" s="60"/>
     </row>
     <row r="137" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -13530,7 +13542,7 @@
       <c r="S137" s="60"/>
     </row>
     <row r="138" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -13561,17 +13573,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
@@ -13657,52 +13669,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -13736,7 +13748,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -13768,7 +13780,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -13800,7 +13812,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -13832,7 +13844,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -13866,7 +13878,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -13898,7 +13910,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -13930,7 +13942,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -13964,7 +13976,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -13996,7 +14008,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -14028,7 +14040,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -14060,7 +14072,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -14094,7 +14106,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -14126,7 +14138,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -14158,7 +14170,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -14192,7 +14204,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -14243,7 +14255,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -14277,7 +14289,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -14309,7 +14321,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -14341,7 +14353,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -14373,7 +14385,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -14405,7 +14417,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -14441,7 +14453,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -14473,7 +14485,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -14505,7 +14517,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -14537,7 +14549,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -14571,7 +14583,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -14603,7 +14615,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -14635,7 +14647,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -14669,7 +14681,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -14701,7 +14713,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -14733,7 +14745,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -14765,7 +14777,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -14799,7 +14811,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -14833,7 +14845,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -14865,7 +14877,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -14899,7 +14911,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -14931,7 +14943,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -14963,7 +14975,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -14995,7 +15007,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -15031,7 +15043,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -15063,7 +15075,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -15095,7 +15107,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -15129,7 +15141,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -15161,7 +15173,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -15193,7 +15205,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -15225,7 +15237,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -15276,7 +15288,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -15310,7 +15322,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -15342,7 +15354,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -15376,7 +15388,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -15408,7 +15420,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -15440,7 +15452,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -15472,7 +15484,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -15504,7 +15516,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -15536,7 +15548,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -15568,7 +15580,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -15600,7 +15612,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -15634,7 +15646,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -15666,7 +15678,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -15698,7 +15710,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -15730,7 +15742,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -15762,7 +15774,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -15798,7 +15810,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -15832,7 +15844,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -15864,7 +15876,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -15896,7 +15908,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -15928,7 +15940,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -15962,7 +15974,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -15994,7 +16006,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -16026,7 +16038,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -16060,7 +16072,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -16092,7 +16104,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -16124,7 +16136,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -16156,7 +16168,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -16188,7 +16200,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -16220,7 +16232,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -16272,7 +16284,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -16308,7 +16320,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -16340,7 +16352,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -16372,7 +16384,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -16404,7 +16416,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -16438,7 +16450,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -16470,7 +16482,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -16502,7 +16514,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -16536,7 +16548,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -16568,7 +16580,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -16600,7 +16612,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -16632,7 +16644,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -16664,7 +16676,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -16696,7 +16708,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -16728,7 +16740,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -16760,7 +16772,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -16792,7 +16804,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -16824,7 +16836,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -16856,7 +16868,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -16888,7 +16900,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -16920,7 +16932,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -16952,7 +16964,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -16984,7 +16996,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -17016,7 +17028,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -17048,7 +17060,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -17080,7 +17092,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -17112,7 +17124,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -17144,7 +17156,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -17176,7 +17188,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -17208,7 +17220,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -17240,7 +17252,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -17292,7 +17304,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -17326,7 +17338,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -17358,7 +17370,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -17390,7 +17402,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -17422,7 +17434,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -17454,7 +17466,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -17486,7 +17498,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -17518,7 +17530,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -17550,7 +17562,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -17582,7 +17594,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -17614,7 +17626,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -17646,7 +17658,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -17678,7 +17690,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -17710,7 +17722,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -17742,7 +17754,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -17774,7 +17786,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -17806,7 +17818,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -17838,7 +17850,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -17870,7 +17882,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -17902,7 +17914,7 @@
       <c r="V135" s="14"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="117"/>
+      <c r="B136" s="106"/>
       <c r="D136" s="22">
         <v>20</v>
       </c>
@@ -17934,7 +17946,7 @@
       <c r="V136" s="14"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="117"/>
+      <c r="B137" s="106"/>
       <c r="D137" s="22">
         <v>21</v>
       </c>
@@ -17966,7 +17978,7 @@
       <c r="V137" s="14"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="118"/>
+      <c r="B138" s="107"/>
       <c r="D138" s="56">
         <v>22</v>
       </c>
@@ -17999,17 +18011,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="B22:B52"/>
-    <mergeCell ref="B54:B83"/>
-    <mergeCell ref="B85:B115"/>
-    <mergeCell ref="B117:B138"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="F2:G3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="L2:M3"/>
     <mergeCell ref="O2:P3"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="B22:B52"/>
+    <mergeCell ref="B54:B83"/>
+    <mergeCell ref="B85:B115"/>
+    <mergeCell ref="B117:B138"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F20 F22:F52 F54:F83 F85:F115 F117:F138">
     <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
@@ -18115,52 +18127,52 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="108"/>
-      <c r="F2" s="112" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="F2" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="112"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="L2" s="114" t="s">
+      <c r="J2" s="117"/>
+      <c r="L2" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="118"/>
+      <c r="O2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="R2" s="105" t="s">
+      <c r="P2" s="119"/>
+      <c r="R2" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="105"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="22">
@@ -18194,7 +18206,7 @@
       <c r="V5" s="14"/>
     </row>
     <row r="6" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
+      <c r="B6" s="106"/>
       <c r="D6" s="22">
         <v>14</v>
       </c>
@@ -18226,7 +18238,7 @@
       <c r="V6" s="14"/>
     </row>
     <row r="7" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="117"/>
+      <c r="B7" s="106"/>
       <c r="D7" s="22">
         <v>15</v>
       </c>
@@ -18258,7 +18270,7 @@
       <c r="V7" s="14"/>
     </row>
     <row r="8" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117"/>
+      <c r="B8" s="106"/>
       <c r="D8" s="22">
         <v>16</v>
       </c>
@@ -18290,7 +18302,7 @@
       <c r="V8" s="14"/>
     </row>
     <row r="9" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="22">
         <v>17</v>
       </c>
@@ -18324,7 +18336,7 @@
       <c r="V9" s="14"/>
     </row>
     <row r="10" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="106"/>
       <c r="D10" s="22">
         <v>18</v>
       </c>
@@ -18356,7 +18368,7 @@
       <c r="V10" s="14"/>
     </row>
     <row r="11" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="117"/>
+      <c r="B11" s="106"/>
       <c r="D11" s="22">
         <v>19</v>
       </c>
@@ -18388,7 +18400,7 @@
       <c r="V11" s="14"/>
     </row>
     <row r="12" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="117"/>
+      <c r="B12" s="106"/>
       <c r="D12" s="22">
         <v>20</v>
       </c>
@@ -18422,7 +18434,7 @@
       <c r="V12" s="14"/>
     </row>
     <row r="13" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="106"/>
       <c r="D13" s="22">
         <v>21</v>
       </c>
@@ -18454,7 +18466,7 @@
       <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
+      <c r="B14" s="106"/>
       <c r="D14" s="22">
         <v>22</v>
       </c>
@@ -18486,7 +18498,7 @@
       <c r="V14" s="14"/>
     </row>
     <row r="15" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="117"/>
+      <c r="B15" s="106"/>
       <c r="D15" s="22">
         <v>23</v>
       </c>
@@ -18518,7 +18530,7 @@
       <c r="V15" s="14"/>
     </row>
     <row r="16" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="106"/>
       <c r="D16" s="22">
         <v>24</v>
       </c>
@@ -18552,7 +18564,7 @@
       <c r="V16" s="14"/>
     </row>
     <row r="17" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
+      <c r="B17" s="106"/>
       <c r="D17" s="22">
         <v>25</v>
       </c>
@@ -18584,7 +18596,7 @@
       <c r="V17" s="14"/>
     </row>
     <row r="18" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
+      <c r="B18" s="106"/>
       <c r="D18" s="22">
         <v>26</v>
       </c>
@@ -18616,7 +18628,7 @@
       <c r="V18" s="14"/>
     </row>
     <row r="19" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
+      <c r="B19" s="106"/>
       <c r="D19" s="22">
         <v>27</v>
       </c>
@@ -18650,7 +18662,7 @@
       <c r="V19" s="14"/>
     </row>
     <row r="20" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
+      <c r="B20" s="107"/>
       <c r="D20" s="22">
         <v>28</v>
       </c>
@@ -18701,7 +18713,7 @@
       <c r="V21" s="14"/>
     </row>
     <row r="22" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="22">
@@ -18735,7 +18747,7 @@
       <c r="V22" s="14"/>
     </row>
     <row r="23" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="119"/>
+      <c r="B23" s="108"/>
       <c r="D23" s="22">
         <v>2</v>
       </c>
@@ -18767,7 +18779,7 @@
       <c r="V23" s="14"/>
     </row>
     <row r="24" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119"/>
+      <c r="B24" s="108"/>
       <c r="D24" s="22">
         <v>3</v>
       </c>
@@ -18799,7 +18811,7 @@
       <c r="V24" s="14"/>
     </row>
     <row r="25" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119"/>
+      <c r="B25" s="108"/>
       <c r="D25" s="22">
         <v>4</v>
       </c>
@@ -18831,7 +18843,7 @@
       <c r="V25" s="14"/>
     </row>
     <row r="26" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
+      <c r="B26" s="108"/>
       <c r="D26" s="22">
         <v>5</v>
       </c>
@@ -18863,7 +18875,7 @@
       <c r="V26" s="14"/>
     </row>
     <row r="27" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
+      <c r="B27" s="108"/>
       <c r="D27" s="22">
         <v>6</v>
       </c>
@@ -18899,7 +18911,7 @@
       <c r="V27" s="14"/>
     </row>
     <row r="28" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
+      <c r="B28" s="108"/>
       <c r="D28" s="22">
         <v>7</v>
       </c>
@@ -18931,7 +18943,7 @@
       <c r="V28" s="14"/>
     </row>
     <row r="29" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
+      <c r="B29" s="108"/>
       <c r="D29" s="22">
         <v>8</v>
       </c>
@@ -18963,7 +18975,7 @@
       <c r="V29" s="14"/>
     </row>
     <row r="30" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="119"/>
+      <c r="B30" s="108"/>
       <c r="D30" s="22">
         <v>9</v>
       </c>
@@ -18995,7 +19007,7 @@
       <c r="V30" s="14"/>
     </row>
     <row r="31" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="119"/>
+      <c r="B31" s="108"/>
       <c r="D31" s="22">
         <v>10</v>
       </c>
@@ -19029,7 +19041,7 @@
       <c r="V31" s="14"/>
     </row>
     <row r="32" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="119"/>
+      <c r="B32" s="108"/>
       <c r="D32" s="22">
         <v>11</v>
       </c>
@@ -19061,7 +19073,7 @@
       <c r="V32" s="14"/>
     </row>
     <row r="33" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="119"/>
+      <c r="B33" s="108"/>
       <c r="D33" s="22">
         <v>12</v>
       </c>
@@ -19093,7 +19105,7 @@
       <c r="V33" s="14"/>
     </row>
     <row r="34" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="119"/>
+      <c r="B34" s="108"/>
       <c r="D34" s="22">
         <v>13</v>
       </c>
@@ -19127,7 +19139,7 @@
       <c r="V34" s="14"/>
     </row>
     <row r="35" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="119"/>
+      <c r="B35" s="108"/>
       <c r="D35" s="22">
         <v>14</v>
       </c>
@@ -19159,7 +19171,7 @@
       <c r="V35" s="14"/>
     </row>
     <row r="36" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="119"/>
+      <c r="B36" s="108"/>
       <c r="D36" s="22">
         <v>15</v>
       </c>
@@ -19191,7 +19203,7 @@
       <c r="V36" s="14"/>
     </row>
     <row r="37" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="119"/>
+      <c r="B37" s="108"/>
       <c r="D37" s="22">
         <v>16</v>
       </c>
@@ -19223,7 +19235,7 @@
       <c r="V37" s="14"/>
     </row>
     <row r="38" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="119"/>
+      <c r="B38" s="108"/>
       <c r="D38" s="22">
         <v>17</v>
       </c>
@@ -19259,7 +19271,7 @@
       <c r="V38" s="14"/>
     </row>
     <row r="39" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="119"/>
+      <c r="B39" s="108"/>
       <c r="D39" s="22">
         <v>18</v>
       </c>
@@ -19291,7 +19303,7 @@
       <c r="V39" s="14"/>
     </row>
     <row r="40" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="119"/>
+      <c r="B40" s="108"/>
       <c r="D40" s="22">
         <v>19</v>
       </c>
@@ -19323,7 +19335,7 @@
       <c r="V40" s="14"/>
     </row>
     <row r="41" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="119"/>
+      <c r="B41" s="108"/>
       <c r="D41" s="56">
         <v>20</v>
       </c>
@@ -19357,7 +19369,7 @@
       <c r="V41" s="14"/>
     </row>
     <row r="42" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="119"/>
+      <c r="B42" s="108"/>
       <c r="D42" s="22">
         <v>21</v>
       </c>
@@ -19389,7 +19401,7 @@
       <c r="V42" s="14"/>
     </row>
     <row r="43" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="119"/>
+      <c r="B43" s="108"/>
       <c r="D43" s="22">
         <v>22</v>
       </c>
@@ -19421,7 +19433,7 @@
       <c r="V43" s="14"/>
     </row>
     <row r="44" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="119"/>
+      <c r="B44" s="108"/>
       <c r="D44" s="22">
         <v>23</v>
       </c>
@@ -19453,7 +19465,7 @@
       <c r="V44" s="14"/>
     </row>
     <row r="45" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="119"/>
+      <c r="B45" s="108"/>
       <c r="D45" s="22">
         <v>24</v>
       </c>
@@ -19489,7 +19501,7 @@
       <c r="V45" s="14"/>
     </row>
     <row r="46" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="119"/>
+      <c r="B46" s="108"/>
       <c r="D46" s="22">
         <v>25</v>
       </c>
@@ -19521,7 +19533,7 @@
       <c r="V46" s="14"/>
     </row>
     <row r="47" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="119"/>
+      <c r="B47" s="108"/>
       <c r="D47" s="22">
         <v>26</v>
       </c>
@@ -19553,7 +19565,7 @@
       <c r="V47" s="14"/>
     </row>
     <row r="48" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="119"/>
+      <c r="B48" s="108"/>
       <c r="D48" s="22">
         <v>27</v>
       </c>
@@ -19587,7 +19599,7 @@
       <c r="V48" s="14"/>
     </row>
     <row r="49" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="119"/>
+      <c r="B49" s="108"/>
       <c r="D49" s="22">
         <v>28</v>
       </c>
@@ -19619,7 +19631,7 @@
       <c r="V49" s="14"/>
     </row>
     <row r="50" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="119"/>
+      <c r="B50" s="108"/>
       <c r="D50" s="22">
         <v>29</v>
       </c>
@@ -19651,7 +19663,7 @@
       <c r="V50" s="14"/>
     </row>
     <row r="51" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="119"/>
+      <c r="B51" s="108"/>
       <c r="D51" s="22">
         <v>30</v>
       </c>
@@ -19683,7 +19695,7 @@
       <c r="V51" s="14"/>
     </row>
     <row r="52" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="119"/>
+      <c r="B52" s="108"/>
       <c r="D52" s="22">
         <v>31</v>
       </c>
@@ -19734,7 +19746,7 @@
       <c r="V53" s="14"/>
     </row>
     <row r="54" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="108" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="22">
@@ -19768,7 +19780,7 @@
       <c r="V54" s="14"/>
     </row>
     <row r="55" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="119"/>
+      <c r="B55" s="108"/>
       <c r="D55" s="22">
         <v>2</v>
       </c>
@@ -19800,7 +19812,7 @@
       <c r="V55" s="14"/>
     </row>
     <row r="56" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="119"/>
+      <c r="B56" s="108"/>
       <c r="D56" s="22">
         <v>3</v>
       </c>
@@ -19834,7 +19846,7 @@
       <c r="V56" s="14"/>
     </row>
     <row r="57" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="119"/>
+      <c r="B57" s="108"/>
       <c r="D57" s="22">
         <v>4</v>
       </c>
@@ -19866,7 +19878,7 @@
       <c r="V57" s="14"/>
     </row>
     <row r="58" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="119"/>
+      <c r="B58" s="108"/>
       <c r="D58" s="22">
         <v>5</v>
       </c>
@@ -19898,7 +19910,7 @@
       <c r="V58" s="14"/>
     </row>
     <row r="59" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="119"/>
+      <c r="B59" s="108"/>
       <c r="D59" s="22">
         <v>6</v>
       </c>
@@ -19930,7 +19942,7 @@
       <c r="V59" s="14"/>
     </row>
     <row r="60" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="119"/>
+      <c r="B60" s="108"/>
       <c r="D60" s="22">
         <v>7</v>
       </c>
@@ -19962,7 +19974,7 @@
       <c r="V60" s="14"/>
     </row>
     <row r="61" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="119"/>
+      <c r="B61" s="108"/>
       <c r="D61" s="22">
         <v>8</v>
       </c>
@@ -19994,7 +20006,7 @@
       <c r="V61" s="14"/>
     </row>
     <row r="62" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="119"/>
+      <c r="B62" s="108"/>
       <c r="D62" s="22">
         <v>9</v>
       </c>
@@ -20026,7 +20038,7 @@
       <c r="V62" s="14"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="119"/>
+      <c r="B63" s="108"/>
       <c r="D63" s="22">
         <v>10</v>
       </c>
@@ -20058,7 +20070,7 @@
       <c r="V63" s="14"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="119"/>
+      <c r="B64" s="108"/>
       <c r="D64" s="22">
         <v>11</v>
       </c>
@@ -20092,7 +20104,7 @@
       <c r="V64" s="14"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="119"/>
+      <c r="B65" s="108"/>
       <c r="D65" s="22">
         <v>12</v>
       </c>
@@ -20124,7 +20136,7 @@
       <c r="V65" s="14"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="119"/>
+      <c r="B66" s="108"/>
       <c r="D66" s="22">
         <v>13</v>
       </c>
@@ -20156,7 +20168,7 @@
       <c r="V66" s="14"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B67" s="119"/>
+      <c r="B67" s="108"/>
       <c r="D67" s="22">
         <v>14</v>
       </c>
@@ -20188,7 +20200,7 @@
       <c r="V67" s="14"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B68" s="119"/>
+      <c r="B68" s="108"/>
       <c r="D68" s="22">
         <v>15</v>
       </c>
@@ -20224,7 +20236,7 @@
       <c r="V68" s="14"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="119"/>
+      <c r="B69" s="108"/>
       <c r="D69" s="22">
         <v>16</v>
       </c>
@@ -20256,7 +20268,7 @@
       <c r="V69" s="14"/>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="119"/>
+      <c r="B70" s="108"/>
       <c r="D70" s="56">
         <v>17</v>
       </c>
@@ -20290,7 +20302,7 @@
       <c r="V70" s="14"/>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="119"/>
+      <c r="B71" s="108"/>
       <c r="D71" s="22">
         <v>18</v>
       </c>
@@ -20322,7 +20334,7 @@
       <c r="V71" s="14"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="119"/>
+      <c r="B72" s="108"/>
       <c r="D72" s="22">
         <v>19</v>
       </c>
@@ -20354,7 +20366,7 @@
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="119"/>
+      <c r="B73" s="108"/>
       <c r="D73" s="22">
         <v>20</v>
       </c>
@@ -20386,7 +20398,7 @@
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="119"/>
+      <c r="B74" s="108"/>
       <c r="D74" s="22">
         <v>21</v>
       </c>
@@ -20420,7 +20432,7 @@
       <c r="V74" s="14"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="119"/>
+      <c r="B75" s="108"/>
       <c r="D75" s="22">
         <v>22</v>
       </c>
@@ -20452,7 +20464,7 @@
       <c r="V75" s="14"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="119"/>
+      <c r="B76" s="108"/>
       <c r="D76" s="22">
         <v>23</v>
       </c>
@@ -20484,7 +20496,7 @@
       <c r="V76" s="14"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B77" s="119"/>
+      <c r="B77" s="108"/>
       <c r="D77" s="22">
         <v>24</v>
       </c>
@@ -20518,7 +20530,7 @@
       <c r="V77" s="14"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B78" s="119"/>
+      <c r="B78" s="108"/>
       <c r="D78" s="22">
         <v>25</v>
       </c>
@@ -20550,7 +20562,7 @@
       <c r="V78" s="14"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B79" s="119"/>
+      <c r="B79" s="108"/>
       <c r="D79" s="22">
         <v>26</v>
       </c>
@@ -20582,7 +20594,7 @@
       <c r="V79" s="14"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B80" s="119"/>
+      <c r="B80" s="108"/>
       <c r="D80" s="22">
         <v>27</v>
       </c>
@@ -20614,7 +20626,7 @@
       <c r="V80" s="14"/>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B81" s="119"/>
+      <c r="B81" s="108"/>
       <c r="D81" s="22">
         <v>28</v>
       </c>
@@ -20646,7 +20658,7 @@
       <c r="V81" s="14"/>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B82" s="119"/>
+      <c r="B82" s="108"/>
       <c r="D82" s="22">
         <v>29</v>
       </c>
@@ -20678,7 +20690,7 @@
       <c r="V82" s="14"/>
     </row>
     <row r="83" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B83" s="119"/>
+      <c r="B83" s="108"/>
       <c r="D83" s="22">
         <v>30</v>
       </c>
@@ -20730,7 +20742,7 @@
       <c r="V84" s="14"/>
     </row>
     <row r="85" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B85" s="119" t="s">
+      <c r="B85" s="108" t="s">
         <v>38</v>
       </c>
       <c r="D85" s="22">
@@ -20766,7 +20778,7 @@
       <c r="V85" s="14"/>
     </row>
     <row r="86" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B86" s="119"/>
+      <c r="B86" s="108"/>
       <c r="D86" s="22">
         <v>2</v>
       </c>
@@ -20798,7 +20810,7 @@
       <c r="V86" s="14"/>
     </row>
     <row r="87" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B87" s="119"/>
+      <c r="B87" s="108"/>
       <c r="D87" s="22">
         <v>3</v>
       </c>
@@ -20830,7 +20842,7 @@
       <c r="V87" s="14"/>
     </row>
     <row r="88" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B88" s="119"/>
+      <c r="B88" s="108"/>
       <c r="D88" s="22">
         <v>4</v>
       </c>
@@ -20862,7 +20874,7 @@
       <c r="V88" s="14"/>
     </row>
     <row r="89" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B89" s="119"/>
+      <c r="B89" s="108"/>
       <c r="D89" s="22">
         <v>5</v>
       </c>
@@ -20896,7 +20908,7 @@
       <c r="V89" s="14"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B90" s="119"/>
+      <c r="B90" s="108"/>
       <c r="D90" s="22">
         <v>6</v>
       </c>
@@ -20928,7 +20940,7 @@
       <c r="V90" s="14"/>
     </row>
     <row r="91" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B91" s="119"/>
+      <c r="B91" s="108"/>
       <c r="D91" s="22">
         <v>7</v>
       </c>
@@ -20960,7 +20972,7 @@
       <c r="V91" s="14"/>
     </row>
     <row r="92" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B92" s="119"/>
+      <c r="B92" s="108"/>
       <c r="D92" s="22">
         <v>8</v>
       </c>
@@ -20994,7 +21006,7 @@
       <c r="V92" s="14"/>
     </row>
     <row r="93" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B93" s="119"/>
+      <c r="B93" s="108"/>
       <c r="D93" s="22">
         <v>9</v>
       </c>
@@ -21026,7 +21038,7 @@
       <c r="V93" s="14"/>
     </row>
     <row r="94" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B94" s="119"/>
+      <c r="B94" s="108"/>
       <c r="D94" s="22">
         <v>10</v>
       </c>
@@ -21058,7 +21070,7 @@
       <c r="V94" s="14"/>
     </row>
     <row r="95" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B95" s="119"/>
+      <c r="B95" s="108"/>
       <c r="D95" s="22">
         <v>11</v>
       </c>
@@ -21090,7 +21102,7 @@
       <c r="V95" s="14"/>
     </row>
     <row r="96" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B96" s="119"/>
+      <c r="B96" s="108"/>
       <c r="D96" s="56">
         <v>12</v>
       </c>
@@ -21122,7 +21134,7 @@
       <c r="V96" s="14"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B97" s="119"/>
+      <c r="B97" s="108"/>
       <c r="D97" s="22">
         <v>13</v>
       </c>
@@ -21154,7 +21166,7 @@
       <c r="V97" s="14"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B98" s="119"/>
+      <c r="B98" s="108"/>
       <c r="D98" s="22">
         <v>14</v>
       </c>
@@ -21186,7 +21198,7 @@
       <c r="V98" s="14"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B99" s="119"/>
+      <c r="B99" s="108"/>
       <c r="D99" s="22">
         <v>15</v>
       </c>
@@ -21218,7 +21230,7 @@
       <c r="V99" s="14"/>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B100" s="119"/>
+      <c r="B100" s="108"/>
       <c r="D100" s="22">
         <v>16</v>
       </c>
@@ -21250,7 +21262,7 @@
       <c r="V100" s="14"/>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B101" s="119"/>
+      <c r="B101" s="108"/>
       <c r="D101" s="22">
         <v>17</v>
       </c>
@@ -21282,7 +21294,7 @@
       <c r="V101" s="14"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B102" s="119"/>
+      <c r="B102" s="108"/>
       <c r="D102" s="22">
         <v>18</v>
       </c>
@@ -21314,7 +21326,7 @@
       <c r="V102" s="14"/>
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B103" s="119"/>
+      <c r="B103" s="108"/>
       <c r="D103" s="22">
         <v>19</v>
       </c>
@@ -21346,7 +21358,7 @@
       <c r="V103" s="14"/>
     </row>
     <row r="104" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B104" s="119"/>
+      <c r="B104" s="108"/>
       <c r="D104" s="22">
         <v>20</v>
       </c>
@@ -21378,7 +21390,7 @@
       <c r="V104" s="14"/>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B105" s="119"/>
+      <c r="B105" s="108"/>
       <c r="D105" s="22">
         <v>21</v>
       </c>
@@ -21410,7 +21422,7 @@
       <c r="V105" s="14"/>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B106" s="119"/>
+      <c r="B106" s="108"/>
       <c r="D106" s="22">
         <v>22</v>
       </c>
@@ -21442,7 +21454,7 @@
       <c r="V106" s="14"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B107" s="119"/>
+      <c r="B107" s="108"/>
       <c r="D107" s="22">
         <v>23</v>
       </c>
@@ -21474,7 +21486,7 @@
       <c r="V107" s="14"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B108" s="119"/>
+      <c r="B108" s="108"/>
       <c r="D108" s="22">
         <v>24</v>
       </c>
@@ -21506,7 +21518,7 @@
       <c r="V108" s="14"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B109" s="119"/>
+      <c r="B109" s="108"/>
       <c r="D109" s="22">
         <v>25</v>
       </c>
@@ -21538,7 +21550,7 @@
       <c r="V109" s="14"/>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B110" s="119"/>
+      <c r="B110" s="108"/>
       <c r="D110" s="22">
         <v>26</v>
       </c>
@@ -21570,7 +21582,7 @@
       <c r="V110" s="14"/>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B111" s="119"/>
+      <c r="B111" s="108"/>
       <c r="D111" s="22">
         <v>27</v>
       </c>
@@ -21602,7 +21614,7 @@
       <c r="V111" s="14"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B112" s="119"/>
+      <c r="B112" s="108"/>
       <c r="D112" s="22">
         <v>28</v>
       </c>
@@ -21634,7 +21646,7 @@
       <c r="V112" s="14"/>
     </row>
     <row r="113" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B113" s="119"/>
+      <c r="B113" s="108"/>
       <c r="D113" s="22">
         <v>29</v>
       </c>
@@ -21666,7 +21678,7 @@
       <c r="V113" s="14"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B114" s="119"/>
+      <c r="B114" s="108"/>
       <c r="D114" s="22">
         <v>30</v>
       </c>
@@ -21698,7 +21710,7 @@
       <c r="V114" s="14"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="119"/>
+      <c r="B115" s="108"/>
       <c r="D115" s="22">
         <v>31</v>
       </c>
@@ -21750,7 +21762,7 @@
       <c r="V116" s="14"/>
     </row>
     <row r="117" spans="2:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="105" t="s">
         <v>40</v>
       </c>
       <c r="D117" s="22">
@@ -21784,7 +21796,7 @@
       <c r="V117" s="14"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="117"/>
+      <c r="B118" s="106"/>
       <c r="D118" s="22">
         <v>2</v>
       </c>
@@ -21816,7 +21828,7 @@
       <c r="V118" s="14"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="117"/>
+      <c r="B119" s="106"/>
       <c r="D119" s="22">
         <v>3</v>
       </c>
@@ -21848,7 +21860,7 @@
       <c r="V119" s="14"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="117"/>
+      <c r="B120" s="106"/>
       <c r="D120" s="22">
         <v>4</v>
       </c>
@@ -21880,7 +21892,7 @@
       <c r="V120" s="14"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="117"/>
+      <c r="B121" s="106"/>
       <c r="D121" s="22">
         <v>5</v>
       </c>
@@ -21912,7 +21924,7 @@
       <c r="V121" s="14"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="117"/>
+      <c r="B122" s="106"/>
       <c r="D122" s="22">
         <v>6</v>
       </c>
@@ -21944,7 +21956,7 @@
       <c r="V122" s="14"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="117"/>
+      <c r="B123" s="106"/>
       <c r="D123" s="22">
         <v>7</v>
       </c>
@@ -21976,7 +21988,7 @@
       <c r="V123" s="14"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="117"/>
+      <c r="B124" s="106"/>
       <c r="D124" s="22">
         <v>8</v>
       </c>
@@ -22008,7 +22020,7 @@
       <c r="V124" s="14"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="117"/>
+      <c r="B125" s="106"/>
       <c r="D125" s="22">
         <v>9</v>
       </c>
@@ -22040,7 +22052,7 @@
       <c r="V125" s="14"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="117"/>
+      <c r="B126" s="106"/>
       <c r="D126" s="22">
         <v>10</v>
       </c>
@@ -22072,7 +22084,7 @@
       <c r="V126" s="14"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="117"/>
+      <c r="B127" s="106"/>
       <c r="D127" s="22">
         <v>11</v>
       </c>
@@ -22104,7 +22116,7 @@
       <c r="V127" s="14"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="117"/>
+      <c r="B128" s="106"/>
       <c r="D128" s="22">
         <v>12</v>
       </c>
@@ -22136,7 +22148,7 @@
       <c r="V128" s="14"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="117"/>
+      <c r="B129" s="106"/>
       <c r="D129" s="22">
         <v>13</v>
       </c>
@@ -22168,7 +22180,7 @@
       <c r="V129" s="14"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="117"/>
+      <c r="B130" s="106"/>
       <c r="D130" s="22">
         <v>14</v>
       </c>
@@ -22200,7 +22212,7 @@
       <c r="V130" s="14"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="117"/>
+      <c r="B131" s="106"/>
       <c r="D131" s="22">
         <v>15</v>
       </c>
@@ -22232,7 +22244,7 @@
       <c r="V131" s="14"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="117"/>
+      <c r="B132" s="106"/>
       <c r="D132" s="22">
         <v>16</v>
       </c>
@@ -22264,7 +22276,7 @@
       <c r="V132" s="14"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="117"/>
+      <c r="B133" s="106"/>
       <c r="D133" s="22">
         <v>17</v>
       </c>
@@ -22296,7 +22308,7 @@
       <c r="V133" s="14"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="117"/>
+      <c r="B134" s="106"/>
       <c r="D134" s="22">
         <v>18</v>
       </c>
@@ -22328,7 +22340,7 @@
       <c r="V134" s="14"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="117"/>
+      <c r="B135" s="106"/>
       <c r="D135" s="22">
         <v>19</v>
       </c>
@@ -22360,7 +22372,7 @@
    